--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,35 +499,30 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>模型意见</t>
+          <t>PE分位数得分</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>PE分位数得分</t>
+          <t>换手率分位数得分</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>换手率分位数得分</t>
+          <t>ROE同比得分</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ROE同比得分</t>
+          <t>动量得分</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>动量得分</t>
+          <t>模型总得分</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>模型总得分</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>分析师意见</t>
         </is>
@@ -539,10 +534,8 @@
           <t>农林牧渔</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>801010</t>
-        </is>
+      <c r="B2" t="n">
+        <v>801010</v>
       </c>
       <c r="C2" t="n">
         <v>1.2717</v>
@@ -586,27 +579,22 @@
       <c r="P2" t="n">
         <v>-11.14</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q2" t="n">
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V2" t="n">
         <v>-2</v>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -618,10 +606,8 @@
           <t>基础化工</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>801030</t>
-        </is>
+      <c r="B3" t="n">
+        <v>801030</v>
       </c>
       <c r="C3" t="n">
         <v>4.5216</v>
@@ -665,27 +651,22 @@
       <c r="P3" t="n">
         <v>4.45</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q3" t="n">
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
-      <c r="W3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -697,10 +678,8 @@
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>801040</t>
-        </is>
+      <c r="B4" t="n">
+        <v>801040</v>
       </c>
       <c r="C4" t="n">
         <v>0.5907</v>
@@ -744,10 +723,8 @@
       <c r="P4" t="n">
         <v>-12.89</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q4" t="n">
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -756,15 +733,12 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
         <v>-1</v>
       </c>
-      <c r="V4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -776,10 +750,8 @@
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>801050</t>
-        </is>
+      <c r="B5" t="n">
+        <v>801050</v>
       </c>
       <c r="C5" t="n">
         <v>5.4014</v>
@@ -823,27 +795,22 @@
       <c r="P5" t="n">
         <v>28.83</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q5" t="n">
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -855,10 +822,8 @@
           <t>电子</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>801080</t>
-        </is>
+      <c r="B6" t="n">
+        <v>801080</v>
       </c>
       <c r="C6" t="n">
         <v>19.5875</v>
@@ -902,27 +867,22 @@
       <c r="P6" t="n">
         <v>36.37</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q6" t="n">
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -934,10 +894,8 @@
           <t>汽车</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>801880</t>
-        </is>
+      <c r="B7" t="n">
+        <v>801880</v>
       </c>
       <c r="C7" t="n">
         <v>3.5523</v>
@@ -981,10 +939,8 @@
       <c r="P7" t="n">
         <v>-19.63</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q7" t="n">
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -993,15 +949,12 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
         <v>-1</v>
       </c>
-      <c r="V7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1013,10 +966,8 @@
           <t>家用电器</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>801110</t>
-        </is>
+      <c r="B8" t="n">
+        <v>801110</v>
       </c>
       <c r="C8" t="n">
         <v>2.1358</v>
@@ -1060,10 +1011,8 @@
       <c r="P8" t="n">
         <v>-6.08</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q8" t="n">
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1072,15 +1021,12 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
         <v>-1</v>
       </c>
-      <c r="V8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1092,10 +1038,8 @@
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>801120</t>
-        </is>
+      <c r="B9" t="n">
+        <v>801120</v>
       </c>
       <c r="C9" t="n">
         <v>3.2293</v>
@@ -1139,27 +1083,22 @@
       <c r="P9" t="n">
         <v>-21.6</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q9" t="n">
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1171,10 +1110,8 @@
           <t>纺织服饰</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>801130</t>
-        </is>
+      <c r="B10" t="n">
+        <v>801130</v>
       </c>
       <c r="C10" t="n">
         <v>0.5027</v>
@@ -1218,10 +1155,8 @@
       <c r="P10" t="n">
         <v>-8.52</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1230,15 +1165,12 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
         <v>-1</v>
       </c>
-      <c r="V10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1250,10 +1182,8 @@
           <t>轻工制造</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>801140</t>
-        </is>
+      <c r="B11" t="n">
+        <v>801140</v>
       </c>
       <c r="C11" t="n">
         <v>0.7813</v>
@@ -1297,27 +1227,22 @@
       <c r="P11" t="n">
         <v>-9.81</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q11" t="n">
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V11" t="n">
         <v>-2</v>
       </c>
-      <c r="W11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1329,10 +1254,8 @@
           <t>医药生物</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>801150</t>
-        </is>
+      <c r="B12" t="n">
+        <v>801150</v>
       </c>
       <c r="C12" t="n">
         <v>6.1812</v>
@@ -1376,10 +1299,8 @@
       <c r="P12" t="n">
         <v>-16.55</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q12" t="n">
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -1388,15 +1309,12 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U12" t="n">
         <v>-1</v>
       </c>
-      <c r="V12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1408,10 +1326,8 @@
           <t>公用事业</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>801160</t>
-        </is>
+      <c r="B13" t="n">
+        <v>801160</v>
       </c>
       <c r="C13" t="n">
         <v>2.5204</v>
@@ -1455,10 +1371,8 @@
       <c r="P13" t="n">
         <v>3.32</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q13" t="n">
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1467,15 +1381,12 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
         <v>1</v>
       </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1487,10 +1398,8 @@
           <t>交通运输</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>801170</t>
-        </is>
+      <c r="B14" t="n">
+        <v>801170</v>
       </c>
       <c r="C14" t="n">
         <v>1.9118</v>
@@ -1534,27 +1443,22 @@
       <c r="P14" t="n">
         <v>-8.85</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1566,10 +1470,8 @@
           <t>房地产</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>801180</t>
-        </is>
+      <c r="B15" t="n">
+        <v>801180</v>
       </c>
       <c r="C15" t="n">
         <v>0.8358</v>
@@ -1613,10 +1515,8 @@
       <c r="P15" t="n">
         <v>-18.07</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q15" t="n">
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1625,15 +1525,12 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
         <v>-1</v>
       </c>
-      <c r="V15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1645,10 +1542,8 @@
           <t>商贸零售</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>801200</t>
-        </is>
+      <c r="B16" t="n">
+        <v>801200</v>
       </c>
       <c r="C16" t="n">
         <v>0.8363</v>
@@ -1692,27 +1587,22 @@
       <c r="P16" t="n">
         <v>-23.65</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q16" t="n">
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
-      <c r="W16" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V16" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1724,10 +1614,8 @@
           <t>社会服务</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>801210</t>
-        </is>
+      <c r="B17" t="n">
+        <v>801210</v>
       </c>
       <c r="C17" t="n">
         <v>0.5127</v>
@@ -1771,10 +1659,8 @@
       <c r="P17" t="n">
         <v>-18.42</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q17" t="n">
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1783,15 +1669,12 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
         <v>-1</v>
       </c>
-      <c r="V17" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1803,10 +1686,8 @@
           <t>银行</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>801780</t>
-        </is>
+      <c r="B18" t="n">
+        <v>801780</v>
       </c>
       <c r="C18" t="n">
         <v>5.5027</v>
@@ -1850,10 +1731,8 @@
       <c r="P18" t="n">
         <v>-2.12</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q18" t="n">
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1867,10 +1746,7 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1882,10 +1758,8 @@
           <t>非银金融</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>801790</t>
-        </is>
+      <c r="B19" t="n">
+        <v>801790</v>
       </c>
       <c r="C19" t="n">
         <v>5.0072</v>
@@ -1929,27 +1803,22 @@
       <c r="P19" t="n">
         <v>-17.74</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q19" t="n">
+        <v>1</v>
       </c>
       <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>1</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1961,10 +1830,8 @@
           <t>综合</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>801230</t>
-        </is>
+      <c r="B20" t="n">
+        <v>801230</v>
       </c>
       <c r="C20" t="n">
         <v>0.2053</v>
@@ -2008,27 +1875,22 @@
       <c r="P20" t="n">
         <v>15.83</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q20" t="n">
+        <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U20" t="n">
         <v>-1</v>
       </c>
-      <c r="V20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2040,10 +1902,8 @@
           <t>建筑材料</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>801710</t>
-        </is>
+      <c r="B21" t="n">
+        <v>801710</v>
       </c>
       <c r="C21" t="n">
         <v>0.9036</v>
@@ -2087,27 +1947,22 @@
       <c r="P21" t="n">
         <v>13.84</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q21" t="n">
+        <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V21" t="n">
         <v>-2</v>
       </c>
-      <c r="W21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2119,10 +1974,8 @@
           <t>建筑装饰</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>801720</t>
-        </is>
+      <c r="B22" t="n">
+        <v>801720</v>
       </c>
       <c r="C22" t="n">
         <v>1.3128</v>
@@ -2166,27 +2019,22 @@
       <c r="P22" t="n">
         <v>-6.75</v>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q22" t="n">
+        <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V22" t="n">
         <v>-2</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2198,10 +2046,8 @@
           <t>电力设备</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>801730</t>
-        </is>
+      <c r="B23" t="n">
+        <v>801730</v>
       </c>
       <c r="C23" t="n">
         <v>8.142799999999999</v>
@@ -2245,27 +2091,22 @@
       <c r="P23" t="n">
         <v>4.93</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2277,10 +2118,8 @@
           <t>机械设备</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>801890</t>
-        </is>
+      <c r="B24" t="n">
+        <v>801890</v>
       </c>
       <c r="C24" t="n">
         <v>6.1882</v>
@@ -2324,27 +2163,22 @@
       <c r="P24" t="n">
         <v>9.029999999999999</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q24" t="n">
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V24" t="n">
         <v>-2</v>
       </c>
-      <c r="W24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2356,10 +2190,8 @@
           <t>国防军工</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>801740</t>
-        </is>
+      <c r="B25" t="n">
+        <v>801740</v>
       </c>
       <c r="C25" t="n">
         <v>2.7404</v>
@@ -2403,10 +2235,8 @@
       <c r="P25" t="n">
         <v>-9.08</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q25" t="n">
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2415,15 +2245,12 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2435,10 +2262,8 @@
           <t>计算机</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>801750</t>
-        </is>
+      <c r="B26" t="n">
+        <v>801750</v>
       </c>
       <c r="C26" t="n">
         <v>4.6743</v>
@@ -2482,10 +2307,8 @@
       <c r="P26" t="n">
         <v>-27.11</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q26" t="n">
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2494,15 +2317,12 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
         <v>-1</v>
       </c>
-      <c r="V26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2514,10 +2334,8 @@
           <t>传媒</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>801760</t>
-        </is>
+      <c r="B27" t="n">
+        <v>801760</v>
       </c>
       <c r="C27" t="n">
         <v>1.727</v>
@@ -2561,27 +2379,22 @@
       <c r="P27" t="n">
         <v>-17.31</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q27" t="n">
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2593,10 +2406,8 @@
           <t>通信</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>801770</t>
-        </is>
+      <c r="B28" t="n">
+        <v>801770</v>
       </c>
       <c r="C28" t="n">
         <v>6.1313</v>
@@ -2640,27 +2451,22 @@
       <c r="P28" t="n">
         <v>50.22</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q28" t="n">
+        <v>-1</v>
       </c>
       <c r="R28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U28" t="n">
         <v>-1</v>
       </c>
-      <c r="V28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2672,10 +2478,8 @@
           <t>煤炭</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>801950</t>
-        </is>
+      <c r="B29" t="n">
+        <v>801950</v>
       </c>
       <c r="C29" t="n">
         <v>0.9338</v>
@@ -2719,27 +2523,22 @@
       <c r="P29" t="n">
         <v>27.66</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
         <v>-1</v>
       </c>
-      <c r="V29" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2751,10 +2550,8 @@
           <t>石油石化</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>801960</t>
-        </is>
+      <c r="B30" t="n">
+        <v>801960</v>
       </c>
       <c r="C30" t="n">
         <v>1.1843</v>
@@ -2798,27 +2595,22 @@
       <c r="P30" t="n">
         <v>18.25</v>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q30" t="n">
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2830,10 +2622,8 @@
           <t>环保</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>801970</t>
-        </is>
+      <c r="B31" t="n">
+        <v>801970</v>
       </c>
       <c r="C31" t="n">
         <v>0.7925</v>
@@ -2877,10 +2667,8 @@
       <c r="P31" t="n">
         <v>-3.56</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q31" t="n">
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2889,15 +2677,12 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
         <v>-1</v>
       </c>
-      <c r="V31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2909,10 +2694,8 @@
           <t>美容护理</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>801980</t>
-        </is>
+      <c r="B32" t="n">
+        <v>801980</v>
       </c>
       <c r="C32" t="n">
         <v>0.1811</v>
@@ -2956,27 +2739,22 @@
       <c r="P32" t="n">
         <v>-32.71</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q32" t="n">
+        <v>1</v>
       </c>
       <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
         <v>1</v>
       </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
       <c r="T32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U32" t="n">
         <v>1</v>
       </c>
-      <c r="U32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>平配</t>
         </is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2152</v>
+        <v>1.2774</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>81.75</v>
       </c>
       <c r="E2" t="n">
-        <v>58.43</v>
+        <v>80.26000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74</v>
+        <v>49.08</v>
       </c>
       <c r="G2" t="n">
-        <v>96.41</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -567,28 +567,28 @@
         <v>-9.41</v>
       </c>
       <c r="N2" t="n">
-        <v>6.46</v>
+        <v>1.73</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93</v>
+        <v>-0.21</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.22</v>
+        <v>-16.33</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.657</v>
+        <v>4.6256</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24</v>
+        <v>25.44</v>
       </c>
       <c r="E3" t="n">
-        <v>89.39</v>
+        <v>73.12</v>
       </c>
       <c r="F3" t="n">
-        <v>44.64</v>
+        <v>37.85</v>
       </c>
       <c r="G3" t="n">
-        <v>70.65000000000001</v>
+        <v>51.72</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -635,13 +635,13 @@
         <v>1.25</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>-1.92</v>
       </c>
       <c r="O3" t="n">
-        <v>8.91</v>
+        <v>-4.74</v>
       </c>
       <c r="P3" t="n">
-        <v>17.02</v>
+        <v>1.58</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -653,10 +653,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.591</v>
+        <v>0.6012</v>
       </c>
       <c r="D4" t="n">
-        <v>29.91</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>77.04000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="F4" t="n">
-        <v>20.73</v>
+        <v>19.66</v>
       </c>
       <c r="G4" t="n">
-        <v>41.95</v>
+        <v>39.36</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -703,13 +703,13 @@
         <v>-1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>-3.36</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.91</v>
+        <v>-14.37</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -721,10 +721,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6791</v>
+        <v>5.2633</v>
       </c>
       <c r="D5" t="n">
-        <v>22.51</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="n">
-        <v>64.77</v>
+        <v>28.59</v>
       </c>
       <c r="F5" t="n">
-        <v>48.93</v>
+        <v>27.71</v>
       </c>
       <c r="G5" t="n">
-        <v>77.27</v>
+        <v>35.21</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
@@ -771,13 +771,13 @@
         <v>4.6</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>-1.17</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35</v>
+        <v>-10.07</v>
       </c>
       <c r="P5" t="n">
-        <v>51.35</v>
+        <v>13.67</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -789,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -812,19 +812,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8026</v>
+        <v>18.6971</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47</v>
+        <v>55.24</v>
       </c>
       <c r="E6" t="n">
-        <v>95.95999999999999</v>
+        <v>71.64</v>
       </c>
       <c r="F6" t="n">
-        <v>55.94</v>
+        <v>56.04</v>
       </c>
       <c r="G6" t="n">
-        <v>82.93000000000001</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
@@ -839,16 +839,16 @@
         <v>7.53</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-11.7</v>
       </c>
       <c r="O6" t="n">
-        <v>10.24</v>
+        <v>-9.24</v>
       </c>
       <c r="P6" t="n">
-        <v>69.34</v>
+        <v>21.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -857,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
         <v>-1</v>
@@ -880,19 +880,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5901</v>
+        <v>3.6383</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97</v>
+        <v>24.94</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79</v>
+        <v>19.5</v>
       </c>
       <c r="F7" t="n">
-        <v>27.86</v>
+        <v>38.29</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>45.77</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -907,13 +907,13 @@
         <v>-0.87</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>-2.24</v>
       </c>
       <c r="O7" t="n">
-        <v>0.23</v>
+        <v>-4.83</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.67</v>
+        <v>-25.82</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -925,10 +925,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -948,19 +948,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.0936</v>
+        <v>2.1643</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>14.72</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>58.51</v>
       </c>
       <c r="F8" t="n">
-        <v>28.88</v>
+        <v>26.29</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>37.79</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -975,13 +975,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>-1.12</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5</v>
+        <v>-3.81</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.36</v>
+        <v>-8.19</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.2137</v>
+        <v>3.3669</v>
       </c>
       <c r="D9" t="n">
-        <v>19.98</v>
+        <v>20.73</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61</v>
+        <v>20.12</v>
       </c>
       <c r="F9" t="n">
-        <v>38.84</v>
+        <v>31.16</v>
       </c>
       <c r="G9" t="n">
-        <v>85.65000000000001</v>
+        <v>61.66</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1043,13 +1043,13 @@
         <v>-1.28</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.04</v>
+        <v>-1.1</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.26</v>
+        <v>-22.18</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1084,19 +1084,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.512</v>
+        <v>0.5324</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93</v>
+        <v>24.61</v>
       </c>
       <c r="E10" t="n">
-        <v>67.54000000000001</v>
+        <v>63.17</v>
       </c>
       <c r="F10" t="n">
-        <v>41.31</v>
+        <v>41.89</v>
       </c>
       <c r="G10" t="n">
-        <v>62.76</v>
+        <v>63.85</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1111,13 +1111,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>0.1</v>
       </c>
       <c r="O10" t="n">
-        <v>5.71</v>
+        <v>-2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.95</v>
+        <v>-8.73</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1129,10 +1129,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1152,19 +1152,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7734</v>
+        <v>0.8158</v>
       </c>
       <c r="D11" t="n">
-        <v>32.45</v>
+        <v>33.75</v>
       </c>
       <c r="E11" t="n">
-        <v>88.92</v>
+        <v>91.22</v>
       </c>
       <c r="F11" t="n">
-        <v>33.55</v>
+        <v>41.74</v>
       </c>
       <c r="G11" t="n">
-        <v>46.73</v>
+        <v>61.03</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -1179,16 +1179,16 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>-1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>5.76</v>
+        <v>-2.09</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7</v>
+        <v>-12.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1197,10 +1197,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1220,19 +1220,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3566</v>
+        <v>6.7547</v>
       </c>
       <c r="D12" t="n">
-        <v>33.76</v>
+        <v>33.17</v>
       </c>
       <c r="E12" t="n">
-        <v>69.98999999999999</v>
+        <v>66.81999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>54.75</v>
+        <v>43.48</v>
       </c>
       <c r="G12" t="n">
-        <v>96.48999999999999</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>13.12</v>
@@ -1253,28 +1253,28 @@
         <v>6.43</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.43</v>
+        <v>0.57</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>0.92</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.45</v>
+        <v>-14.1</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1294,19 +1294,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4189</v>
+        <v>2.5989</v>
       </c>
       <c r="D13" t="n">
-        <v>20.98</v>
+        <v>21.98</v>
       </c>
       <c r="E13" t="n">
-        <v>54.24</v>
+        <v>60.3</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8</v>
+        <v>26.2</v>
       </c>
       <c r="G13" t="n">
-        <v>48.72</v>
+        <v>39.59</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1321,13 +1321,13 @@
         <v>-0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>2.26</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.79</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="P13" t="n">
-        <v>4.06</v>
+        <v>1.31</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1339,10 +1339,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1362,19 +1362,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.8702</v>
+        <v>1.9957</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06</v>
+        <v>17.09</v>
       </c>
       <c r="E14" t="n">
-        <v>79.81</v>
+        <v>80.5</v>
       </c>
       <c r="F14" t="n">
-        <v>21.02</v>
+        <v>20.38</v>
       </c>
       <c r="G14" t="n">
-        <v>50.64</v>
+        <v>47.5</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1389,13 +1389,13 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.18</v>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.79</v>
+        <v>-7.77</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1430,19 +1430,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8423</v>
+        <v>0.9339</v>
       </c>
       <c r="D15" t="n">
-        <v>20.13</v>
+        <v>17.32</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>59.21</v>
       </c>
       <c r="F15" t="n">
-        <v>35.1</v>
+        <v>66.31</v>
       </c>
       <c r="G15" t="n">
-        <v>57.89</v>
+        <v>95.15000000000001</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1457,19 +1457,19 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.59</v>
+        <v>2.06</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>5.53</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.88</v>
+        <v>-17.11</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
         <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1498,19 +1498,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8192</v>
+        <v>0.8509</v>
       </c>
       <c r="D16" t="n">
-        <v>34.96</v>
+        <v>33.24</v>
       </c>
       <c r="E16" t="n">
-        <v>58.75</v>
+        <v>48.48</v>
       </c>
       <c r="F16" t="n">
-        <v>34.91</v>
+        <v>36.48</v>
       </c>
       <c r="G16" t="n">
-        <v>58.61</v>
+        <v>60.72</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1525,13 +1525,13 @@
         <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>0.79</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>-3.31</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.46</v>
+        <v>-26.48</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1543,10 +1543,10 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1566,19 +1566,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4965</v>
+        <v>0.518</v>
       </c>
       <c r="D17" t="n">
-        <v>40.41</v>
+        <v>41.84</v>
       </c>
       <c r="E17" t="n">
-        <v>21.69</v>
+        <v>26.34</v>
       </c>
       <c r="F17" t="n">
-        <v>36.99</v>
+        <v>41.44</v>
       </c>
       <c r="G17" t="n">
-        <v>28.87</v>
+        <v>39.36</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1593,13 +1593,13 @@
         <v>-0.58</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>-2.42</v>
       </c>
       <c r="O17" t="n">
-        <v>4.96</v>
+        <v>-2.61</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.84</v>
+        <v>-20.57</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1611,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1634,19 +1634,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1334</v>
+        <v>5.6855</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17</v>
+        <v>6.41</v>
       </c>
       <c r="E18" t="n">
-        <v>72.84</v>
+        <v>83.37</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28</v>
+        <v>11.1</v>
       </c>
       <c r="G18" t="n">
-        <v>73.44</v>
+        <v>61.11</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1661,13 +1661,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>1.49</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.38</v>
+        <v>0.9</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.55</v>
+        <v>2.13</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1679,10 +1679,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1702,19 +1702,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.011</v>
+        <v>5.0418</v>
       </c>
       <c r="D19" t="n">
-        <v>11.58</v>
+        <v>8.99</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0.31</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92</v>
+        <v>13.98</v>
       </c>
       <c r="G19" t="n">
-        <v>38.2</v>
+        <v>13.15</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1729,13 +1729,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>-0.98</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1</v>
+        <v>-6.74</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.25</v>
+        <v>-16.57</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1770,19 +1770,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.2066</v>
       </c>
       <c r="D20" t="n">
-        <v>93.7</v>
+        <v>78.08</v>
       </c>
       <c r="E20" t="n">
-        <v>93.98</v>
+        <v>90.75</v>
       </c>
       <c r="F20" t="n">
-        <v>55.43</v>
+        <v>54.26</v>
       </c>
       <c r="G20" t="n">
-        <v>90.59</v>
+        <v>88.97</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1797,19 +1797,19 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-1.8</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74</v>
+        <v>-2.48</v>
       </c>
       <c r="P20" t="n">
-        <v>34.83</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1818,7 +1818,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1838,19 +1838,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.9002</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>36.68</v>
       </c>
       <c r="E21" t="n">
-        <v>94.14</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>35.75</v>
+        <v>46.74</v>
       </c>
       <c r="G21" t="n">
-        <v>66.34999999999999</v>
+        <v>80.44</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1865,13 +1865,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>-5.24</v>
       </c>
       <c r="O21" t="n">
-        <v>6.86</v>
+        <v>-3.7</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1883,10 +1883,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -1906,19 +1906,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2957</v>
+        <v>1.3379</v>
       </c>
       <c r="D22" t="n">
-        <v>13.42</v>
+        <v>14.53</v>
       </c>
       <c r="E22" t="n">
-        <v>90.42</v>
+        <v>93.86</v>
       </c>
       <c r="F22" t="n">
-        <v>29.6</v>
+        <v>24.5</v>
       </c>
       <c r="G22" t="n">
-        <v>47.77</v>
+        <v>28.95</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1933,13 +1933,13 @@
         <v>0.57</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>-1.42</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>-2.76</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.59</v>
+        <v>-11.01</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -1974,19 +1974,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4611</v>
+        <v>8.1325</v>
       </c>
       <c r="D23" t="n">
-        <v>31.78</v>
+        <v>27.56</v>
       </c>
       <c r="E23" t="n">
-        <v>49.01</v>
+        <v>31.08</v>
       </c>
       <c r="F23" t="n">
-        <v>39.05</v>
+        <v>36.46</v>
       </c>
       <c r="G23" t="n">
-        <v>52.39</v>
+        <v>49.53</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -2001,13 +2001,13 @@
         <v>0.15</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.87</v>
+        <v>-1.3</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>-6.84</v>
       </c>
       <c r="P23" t="n">
-        <v>19.13</v>
+        <v>-13.69</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2042,19 +2042,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1859</v>
+        <v>5.9873</v>
       </c>
       <c r="D24" t="n">
-        <v>43.64</v>
+        <v>39.7</v>
       </c>
       <c r="E24" t="n">
-        <v>93.98</v>
+        <v>86.17</v>
       </c>
       <c r="F24" t="n">
-        <v>39.48</v>
+        <v>36.44</v>
       </c>
       <c r="G24" t="n">
-        <v>54.55</v>
+        <v>50.78</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -2069,16 +2069,16 @@
         <v>0.72</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>-7.73</v>
       </c>
       <c r="O24" t="n">
-        <v>8.4</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>19.08</v>
+        <v>-3.97</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2110,19 +2110,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6109</v>
+        <v>2.639</v>
       </c>
       <c r="D25" t="n">
-        <v>59.69</v>
+        <v>56.67</v>
       </c>
       <c r="E25" t="n">
-        <v>50.75</v>
+        <v>41.96</v>
       </c>
       <c r="F25" t="n">
-        <v>31.28</v>
+        <v>35.31</v>
       </c>
       <c r="G25" t="n">
-        <v>44.1</v>
+        <v>53.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2137,13 +2137,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>-4.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.28</v>
+        <v>-4.18</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.06</v>
+        <v>-7.08</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2155,10 +2155,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2178,19 +2178,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7258</v>
+        <v>4.7818</v>
       </c>
       <c r="D26" t="n">
-        <v>67.65000000000001</v>
+        <v>59.85</v>
       </c>
       <c r="E26" t="n">
-        <v>63.97</v>
+        <v>47.32</v>
       </c>
       <c r="F26" t="n">
-        <v>39.09</v>
+        <v>36.32</v>
       </c>
       <c r="G26" t="n">
-        <v>33.57</v>
+        <v>27.7</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2205,13 +2205,13 @@
         <v>0.71</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>-2.31</v>
       </c>
       <c r="O26" t="n">
-        <v>0.41</v>
+        <v>-6.13</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6</v>
+        <v>-25.58</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2246,19 +2246,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.6308</v>
+        <v>1.7793</v>
       </c>
       <c r="D27" t="n">
-        <v>34.73</v>
+        <v>35.01</v>
       </c>
       <c r="E27" t="n">
-        <v>44.73</v>
+        <v>46.31</v>
       </c>
       <c r="F27" t="n">
-        <v>35.42</v>
+        <v>46.49</v>
       </c>
       <c r="G27" t="n">
-        <v>29.59</v>
+        <v>53.91</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2273,13 +2273,13 @@
         <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>0.22</v>
+        <v>1.39</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.94</v>
+        <v>-0.35</v>
       </c>
       <c r="P27" t="n">
-        <v>-14.27</v>
+        <v>-22.77</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2314,19 +2314,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.8119</v>
+        <v>5.6191</v>
       </c>
       <c r="D28" t="n">
-        <v>57.04</v>
+        <v>46.52</v>
       </c>
       <c r="E28" t="n">
-        <v>93.27</v>
+        <v>82.36</v>
       </c>
       <c r="F28" t="n">
-        <v>49.14</v>
+        <v>43.49</v>
       </c>
       <c r="G28" t="n">
-        <v>70.26000000000001</v>
+        <v>62.21</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2341,16 +2341,16 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.13</v>
+        <v>-12.2</v>
       </c>
       <c r="O28" t="n">
-        <v>10.13</v>
+        <v>-6.62</v>
       </c>
       <c r="P28" t="n">
-        <v>85.06999999999999</v>
+        <v>33.86</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2362,7 +2362,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2382,19 +2382,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9446</v>
+        <v>1.0286</v>
       </c>
       <c r="D29" t="n">
-        <v>22.77</v>
+        <v>18.86</v>
       </c>
       <c r="E29" t="n">
-        <v>98.59</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>45.46</v>
+        <v>35.52</v>
       </c>
       <c r="G29" t="n">
-        <v>82.79000000000001</v>
+        <v>61.95</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2409,16 +2409,16 @@
         <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>2.25</v>
       </c>
       <c r="O29" t="n">
-        <v>9.9</v>
+        <v>0.31</v>
       </c>
       <c r="P29" t="n">
-        <v>31.81</v>
+        <v>25.3</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2427,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2450,19 +2450,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.1858</v>
+        <v>1.2102</v>
       </c>
       <c r="D30" t="n">
-        <v>21.36</v>
+        <v>16.74</v>
       </c>
       <c r="E30" t="n">
-        <v>94.01000000000001</v>
+        <v>74.22</v>
       </c>
       <c r="F30" t="n">
-        <v>28.39</v>
+        <v>22.97</v>
       </c>
       <c r="G30" t="n">
-        <v>72.31999999999999</v>
+        <v>47.78</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2477,16 +2477,16 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>8.75</v>
+        <v>-2.74</v>
       </c>
       <c r="P30" t="n">
-        <v>25.75</v>
+        <v>19.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="n">
         <v>-1</v>
@@ -2518,19 +2518,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8045</v>
+        <v>0.8187</v>
       </c>
       <c r="D31" t="n">
-        <v>26.31</v>
+        <v>25.12</v>
       </c>
       <c r="E31" t="n">
-        <v>80.90000000000001</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>30.74</v>
+        <v>27.43</v>
       </c>
       <c r="G31" t="n">
-        <v>51.11</v>
+        <v>43.79</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2545,13 +2545,13 @@
         <v>1.69</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>-1.2</v>
       </c>
       <c r="O31" t="n">
-        <v>6.79</v>
+        <v>-3.58</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>-4.48</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2563,10 +2563,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2586,19 +2586,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1823</v>
+        <v>0.197</v>
       </c>
       <c r="D32" t="n">
-        <v>30.39</v>
+        <v>29.05</v>
       </c>
       <c r="E32" t="n">
-        <v>16.55</v>
+        <v>11.29</v>
       </c>
       <c r="F32" t="n">
-        <v>38.72</v>
+        <v>41.25</v>
       </c>
       <c r="G32" t="n">
-        <v>61.58</v>
+        <v>67.42</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2613,13 +2613,13 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>1.66</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.54</v>
+        <v>1.66</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.31</v>
+        <v>-29.24</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -2631,10 +2631,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2774</v>
+        <v>1.288</v>
       </c>
       <c r="D2" t="n">
-        <v>81.75</v>
+        <v>81.22</v>
       </c>
       <c r="E2" t="n">
-        <v>80.26000000000001</v>
+        <v>80.12</v>
       </c>
       <c r="F2" t="n">
-        <v>49.08</v>
+        <v>49.35</v>
       </c>
       <c r="G2" t="n">
-        <v>88.65000000000001</v>
+        <v>89.05</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -567,13 +567,13 @@
         <v>-9.41</v>
       </c>
       <c r="N2" t="n">
-        <v>1.73</v>
+        <v>1.04</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.21</v>
+        <v>-4.81</v>
       </c>
       <c r="P2" t="n">
-        <v>-16.33</v>
+        <v>-15.09</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.6256</v>
+        <v>4.56</v>
       </c>
       <c r="D3" t="n">
-        <v>25.44</v>
+        <v>24.71</v>
       </c>
       <c r="E3" t="n">
-        <v>73.12</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>37.85</v>
+        <v>38.92</v>
       </c>
       <c r="G3" t="n">
-        <v>51.72</v>
+        <v>54.96</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -635,13 +635,13 @@
         <v>1.25</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.92</v>
+        <v>-1.83</v>
       </c>
       <c r="O3" t="n">
-        <v>-4.74</v>
+        <v>-6.63</v>
       </c>
       <c r="P3" t="n">
-        <v>1.58</v>
+        <v>-0.06</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -676,19 +676,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6012</v>
+        <v>0.6071</v>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>29.85</v>
       </c>
       <c r="E4" t="n">
-        <v>76.3</v>
+        <v>75.78</v>
       </c>
       <c r="F4" t="n">
-        <v>19.66</v>
+        <v>19.86</v>
       </c>
       <c r="G4" t="n">
-        <v>39.36</v>
+        <v>39.87</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -703,13 +703,13 @@
         <v>-1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>1.89</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.36</v>
+        <v>-3.98</v>
       </c>
       <c r="P4" t="n">
-        <v>-14.37</v>
+        <v>-13.06</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -744,40 +744,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.2633</v>
+        <v>5.1745</v>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>16.17</v>
       </c>
       <c r="E5" t="n">
-        <v>28.59</v>
+        <v>26.55</v>
       </c>
       <c r="F5" t="n">
-        <v>27.71</v>
+        <v>27.89</v>
       </c>
       <c r="G5" t="n">
-        <v>35.21</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>35.5</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-38.58</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-45.02</v>
+      </c>
       <c r="K5" t="n">
-        <v>12.64</v>
+        <v>-38.58</v>
       </c>
       <c r="L5" t="n">
-        <v>78.26000000000001</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>4.6</v>
+        <v>-50.96</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.17</v>
+        <v>-0.52</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.07</v>
+        <v>-11.4</v>
       </c>
       <c r="P5" t="n">
-        <v>13.67</v>
+        <v>14.16</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -812,40 +818,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.6971</v>
+        <v>18.3685</v>
       </c>
       <c r="D6" t="n">
-        <v>55.24</v>
+        <v>53.49</v>
       </c>
       <c r="E6" t="n">
-        <v>71.64</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>56.04</v>
+        <v>53.86</v>
       </c>
       <c r="G6" t="n">
-        <v>83.26000000000001</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>81.16</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="I6" t="n">
+        <v>80</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.21</v>
+      </c>
       <c r="K6" t="n">
-        <v>11.72</v>
+        <v>5.88</v>
       </c>
       <c r="L6" t="n">
-        <v>95.65000000000001</v>
+        <v>58.33</v>
       </c>
       <c r="M6" t="n">
-        <v>7.53</v>
+        <v>-1.94</v>
       </c>
       <c r="N6" t="n">
-        <v>-11.7</v>
+        <v>-10.09</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.24</v>
+        <v>-9.69</v>
       </c>
       <c r="P6" t="n">
-        <v>21.87</v>
+        <v>16.88</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -854,13 +866,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V6" t="inlineStr">
         <is>
@@ -880,19 +892,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6383</v>
+        <v>3.6611</v>
       </c>
       <c r="D7" t="n">
-        <v>24.94</v>
+        <v>24.71</v>
       </c>
       <c r="E7" t="n">
-        <v>19.5</v>
+        <v>17.08</v>
       </c>
       <c r="F7" t="n">
-        <v>38.29</v>
+        <v>37.11</v>
       </c>
       <c r="G7" t="n">
-        <v>45.77</v>
+        <v>43.32</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -907,13 +919,13 @@
         <v>-0.87</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.24</v>
+        <v>-1.93</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.83</v>
+        <v>-5.19</v>
       </c>
       <c r="P7" t="n">
-        <v>-25.82</v>
+        <v>-26.23</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -948,19 +960,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.1643</v>
+        <v>2.205</v>
       </c>
       <c r="D8" t="n">
-        <v>14.72</v>
+        <v>14.78</v>
       </c>
       <c r="E8" t="n">
-        <v>58.51</v>
+        <v>61.18</v>
       </c>
       <c r="F8" t="n">
-        <v>26.29</v>
+        <v>25.83</v>
       </c>
       <c r="G8" t="n">
-        <v>37.79</v>
+        <v>35.18</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -975,13 +987,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.12</v>
+        <v>0.24</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.81</v>
+        <v>-3.42</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.19</v>
+        <v>-7.53</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1016,19 +1028,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.3669</v>
+        <v>3.4389</v>
       </c>
       <c r="D9" t="n">
-        <v>20.73</v>
+        <v>20.86</v>
       </c>
       <c r="E9" t="n">
-        <v>20.12</v>
+        <v>22.52</v>
       </c>
       <c r="F9" t="n">
-        <v>31.16</v>
+        <v>31.42</v>
       </c>
       <c r="G9" t="n">
-        <v>61.66</v>
+        <v>62.31</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1043,13 +1055,13 @@
         <v>-1.28</v>
       </c>
       <c r="N9" t="n">
-        <v>1.83</v>
+        <v>2.66</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.1</v>
+        <v>-2.53</v>
       </c>
       <c r="P9" t="n">
-        <v>-22.18</v>
+        <v>-20.42</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1084,19 +1096,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5324</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>24.61</v>
+        <v>24.22</v>
       </c>
       <c r="E10" t="n">
-        <v>63.17</v>
+        <v>58.39</v>
       </c>
       <c r="F10" t="n">
-        <v>41.89</v>
+        <v>42.6</v>
       </c>
       <c r="G10" t="n">
-        <v>63.85</v>
+        <v>66.54000000000001</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1111,13 +1123,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1</v>
+        <v>0.51</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.05</v>
+        <v>-3.68</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.73</v>
+        <v>-9.09</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1152,19 +1164,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8158</v>
+        <v>0.8179</v>
       </c>
       <c r="D11" t="n">
-        <v>33.75</v>
+        <v>33.34</v>
       </c>
       <c r="E11" t="n">
-        <v>91.22</v>
+        <v>89.36</v>
       </c>
       <c r="F11" t="n">
-        <v>41.74</v>
+        <v>41.32</v>
       </c>
       <c r="G11" t="n">
-        <v>61.03</v>
+        <v>59.89</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -1179,16 +1191,16 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.6</v>
+        <v>-0.76</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.09</v>
+        <v>-3.37</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.14</v>
+        <v>-11.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -1200,7 +1212,7 @@
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1220,19 +1232,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7547</v>
+        <v>6.7636</v>
       </c>
       <c r="D12" t="n">
-        <v>33.17</v>
+        <v>32.73</v>
       </c>
       <c r="E12" t="n">
-        <v>66.81999999999999</v>
+        <v>63.74</v>
       </c>
       <c r="F12" t="n">
-        <v>43.48</v>
+        <v>44.33</v>
       </c>
       <c r="G12" t="n">
-        <v>85.20999999999999</v>
+        <v>86.16</v>
       </c>
       <c r="H12" t="n">
         <v>13.12</v>
@@ -1253,13 +1265,13 @@
         <v>6.43</v>
       </c>
       <c r="N12" t="n">
-        <v>0.57</v>
+        <v>-0.41</v>
       </c>
       <c r="O12" t="n">
-        <v>0.92</v>
+        <v>0.01</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.1</v>
+        <v>-14.85</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1271,10 +1283,10 @@
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1294,19 +1306,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.5989</v>
+        <v>2.6312</v>
       </c>
       <c r="D13" t="n">
-        <v>21.98</v>
+        <v>21.93</v>
       </c>
       <c r="E13" t="n">
-        <v>60.3</v>
+        <v>59.94</v>
       </c>
       <c r="F13" t="n">
-        <v>26.2</v>
+        <v>26.11</v>
       </c>
       <c r="G13" t="n">
-        <v>39.59</v>
+        <v>39.33</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
@@ -1321,13 +1333,13 @@
         <v>-0.3</v>
       </c>
       <c r="N13" t="n">
-        <v>2.26</v>
+        <v>1.86</v>
       </c>
       <c r="O13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="P13" t="n">
-        <v>1.31</v>
+        <v>2.71</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1362,19 +1374,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.9957</v>
+        <v>2.0081</v>
       </c>
       <c r="D14" t="n">
-        <v>17.09</v>
+        <v>16.94</v>
       </c>
       <c r="E14" t="n">
-        <v>80.5</v>
+        <v>78.03</v>
       </c>
       <c r="F14" t="n">
-        <v>20.38</v>
+        <v>20.67</v>
       </c>
       <c r="G14" t="n">
-        <v>47.5</v>
+        <v>48.79</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1389,13 +1401,13 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>2.18</v>
+        <v>1.66</v>
       </c>
       <c r="O14" t="n">
-        <v>0.67</v>
+        <v>-0.6</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.77</v>
+        <v>-7.14</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1407,10 +1419,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1430,19 +1442,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9339</v>
+        <v>0.9208</v>
       </c>
       <c r="D15" t="n">
-        <v>17.32</v>
+        <v>16.83</v>
       </c>
       <c r="E15" t="n">
-        <v>59.21</v>
+        <v>58.39</v>
       </c>
       <c r="F15" t="n">
-        <v>66.31</v>
+        <v>68.23999999999999</v>
       </c>
       <c r="G15" t="n">
-        <v>95.15000000000001</v>
+        <v>96.01000000000001</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1457,13 +1469,13 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.06</v>
+        <v>0.33</v>
       </c>
       <c r="O15" t="n">
-        <v>5.53</v>
+        <v>1.35</v>
       </c>
       <c r="P15" t="n">
-        <v>-17.11</v>
+        <v>-17.67</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1498,19 +1510,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8509</v>
+        <v>0.8507</v>
       </c>
       <c r="D16" t="n">
-        <v>33.24</v>
+        <v>32.74</v>
       </c>
       <c r="E16" t="n">
-        <v>48.48</v>
+        <v>45.19</v>
       </c>
       <c r="F16" t="n">
-        <v>36.48</v>
+        <v>35.96</v>
       </c>
       <c r="G16" t="n">
-        <v>60.72</v>
+        <v>60.05</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1525,13 +1537,13 @@
         <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.79</v>
+        <v>0.61</v>
       </c>
       <c r="O16" t="n">
-        <v>-3.31</v>
+        <v>-5.88</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.48</v>
+        <v>-26.53</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1566,19 +1578,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.518</v>
+        <v>0.5187</v>
       </c>
       <c r="D17" t="n">
-        <v>41.84</v>
+        <v>41.28</v>
       </c>
       <c r="E17" t="n">
-        <v>26.34</v>
+        <v>23.99</v>
       </c>
       <c r="F17" t="n">
-        <v>41.44</v>
+        <v>40</v>
       </c>
       <c r="G17" t="n">
-        <v>39.36</v>
+        <v>35.65</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1593,13 +1605,13 @@
         <v>-0.58</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.42</v>
+        <v>-0.97</v>
       </c>
       <c r="O17" t="n">
-        <v>-2.61</v>
+        <v>-4.7</v>
       </c>
       <c r="P17" t="n">
-        <v>-20.57</v>
+        <v>-21.66</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1634,19 +1646,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.6855</v>
+        <v>5.9042</v>
       </c>
       <c r="D18" t="n">
-        <v>6.41</v>
+        <v>6.56</v>
       </c>
       <c r="E18" t="n">
-        <v>83.37</v>
+        <v>89.91</v>
       </c>
       <c r="F18" t="n">
-        <v>11.1</v>
+        <v>11.34</v>
       </c>
       <c r="G18" t="n">
-        <v>61.11</v>
+        <v>64.11</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1661,13 +1673,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>1.49</v>
+        <v>4.02</v>
       </c>
       <c r="O18" t="n">
-        <v>0.9</v>
+        <v>2.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.13</v>
+        <v>6.53</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1702,19 +1714,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.0418</v>
+        <v>5.1398</v>
       </c>
       <c r="D19" t="n">
-        <v>8.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.31</v>
+        <v>0.39</v>
       </c>
       <c r="F19" t="n">
-        <v>13.98</v>
+        <v>13.69</v>
       </c>
       <c r="G19" t="n">
-        <v>13.15</v>
+        <v>11.49</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1729,13 +1741,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.98</v>
+        <v>1.24</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.74</v>
+        <v>-6.84</v>
       </c>
       <c r="P19" t="n">
-        <v>-16.57</v>
+        <v>-13.77</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1770,19 +1782,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2066</v>
+        <v>0.2046</v>
       </c>
       <c r="D20" t="n">
-        <v>78.08</v>
+        <v>76.14</v>
       </c>
       <c r="E20" t="n">
-        <v>90.75</v>
+        <v>90.14</v>
       </c>
       <c r="F20" t="n">
-        <v>54.26</v>
+        <v>54.83</v>
       </c>
       <c r="G20" t="n">
-        <v>88.97</v>
+        <v>89.37</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1797,13 +1809,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8</v>
+        <v>-1.68</v>
       </c>
       <c r="O20" t="n">
-        <v>-2.48</v>
+        <v>-3.16</v>
       </c>
       <c r="P20" t="n">
-        <v>1.41</v>
+        <v>1.63</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
@@ -1838,19 +1850,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9002</v>
+        <v>0.9004</v>
       </c>
       <c r="D21" t="n">
-        <v>36.68</v>
+        <v>36.15</v>
       </c>
       <c r="E21" t="n">
-        <v>93.40000000000001</v>
+        <v>92.7</v>
       </c>
       <c r="F21" t="n">
-        <v>46.74</v>
+        <v>44.71</v>
       </c>
       <c r="G21" t="n">
-        <v>80.44</v>
+        <v>77.25</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1865,13 +1877,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.24</v>
+        <v>-2.26</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.7</v>
+        <v>-3.01</v>
       </c>
       <c r="P21" t="n">
-        <v>8.460000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1906,19 +1918,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3379</v>
+        <v>1.3533</v>
       </c>
       <c r="D22" t="n">
-        <v>14.53</v>
+        <v>14.48</v>
       </c>
       <c r="E22" t="n">
-        <v>93.86</v>
+        <v>93.31999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>24.5</v>
+        <v>24.31</v>
       </c>
       <c r="G22" t="n">
-        <v>28.95</v>
+        <v>28.23</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1933,13 +1945,13 @@
         <v>0.57</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.42</v>
+        <v>0.52</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.76</v>
+        <v>-3.24</v>
       </c>
       <c r="P22" t="n">
-        <v>-11.01</v>
+        <v>-10.24</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -1974,19 +1986,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.1325</v>
+        <v>8.226900000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>27.56</v>
+        <v>27.29</v>
       </c>
       <c r="E23" t="n">
-        <v>31.08</v>
+        <v>30.36</v>
       </c>
       <c r="F23" t="n">
-        <v>36.46</v>
+        <v>36.75</v>
       </c>
       <c r="G23" t="n">
-        <v>49.53</v>
+        <v>50.2</v>
       </c>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
@@ -2001,13 +2013,13 @@
         <v>0.15</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.3</v>
+        <v>0.57</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.84</v>
+        <v>-6.91</v>
       </c>
       <c r="P23" t="n">
-        <v>-13.69</v>
+        <v>-12.96</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2042,40 +2054,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.9873</v>
+        <v>5.9643</v>
       </c>
       <c r="D24" t="n">
-        <v>39.7</v>
+        <v>38.97</v>
       </c>
       <c r="E24" t="n">
-        <v>86.17</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>36.44</v>
+        <v>36.11</v>
       </c>
       <c r="G24" t="n">
-        <v>50.78</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
+        <v>50.27</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="I24" t="n">
+        <v>25</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-2.36</v>
+      </c>
       <c r="K24" t="n">
-        <v>4.54</v>
+        <v>1.6</v>
       </c>
       <c r="L24" t="n">
-        <v>39.13</v>
+        <v>8.33</v>
       </c>
       <c r="M24" t="n">
-        <v>0.72</v>
+        <v>-3.74</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.73</v>
+        <v>-5.97</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.960000000000001</v>
+        <v>-9.94</v>
       </c>
       <c r="P24" t="n">
-        <v>-3.97</v>
+        <v>-5.17</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2110,19 +2128,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.639</v>
+        <v>2.6177</v>
       </c>
       <c r="D25" t="n">
-        <v>56.67</v>
+        <v>55.38</v>
       </c>
       <c r="E25" t="n">
-        <v>41.96</v>
+        <v>35.25</v>
       </c>
       <c r="F25" t="n">
-        <v>35.31</v>
+        <v>34.78</v>
       </c>
       <c r="G25" t="n">
-        <v>53.6</v>
+        <v>51.76</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2137,13 +2155,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.61</v>
+        <v>-4.25</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.18</v>
+        <v>-7.35</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.08</v>
+        <v>-8.69</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2178,19 +2196,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7818</v>
+        <v>4.8106</v>
       </c>
       <c r="D26" t="n">
-        <v>59.85</v>
+        <v>59.32</v>
       </c>
       <c r="E26" t="n">
-        <v>47.32</v>
+        <v>46.27</v>
       </c>
       <c r="F26" t="n">
-        <v>36.32</v>
+        <v>36.21</v>
       </c>
       <c r="G26" t="n">
-        <v>27.7</v>
+        <v>27.68</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2205,13 +2223,13 @@
         <v>0.71</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.31</v>
+        <v>-0.66</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.13</v>
+        <v>-6.65</v>
       </c>
       <c r="P26" t="n">
-        <v>-25.58</v>
+        <v>-25.31</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2246,19 +2264,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.7793</v>
+        <v>1.8325</v>
       </c>
       <c r="D27" t="n">
-        <v>35.01</v>
+        <v>35.53</v>
       </c>
       <c r="E27" t="n">
-        <v>46.31</v>
+        <v>48.84</v>
       </c>
       <c r="F27" t="n">
-        <v>46.49</v>
+        <v>49.45</v>
       </c>
       <c r="G27" t="n">
-        <v>53.91</v>
+        <v>59.66</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2273,13 +2291,13 @@
         <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>1.39</v>
+        <v>5.57</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.35</v>
+        <v>-2</v>
       </c>
       <c r="P27" t="n">
-        <v>-22.77</v>
+        <v>-19.83</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2314,19 +2332,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.6191</v>
+        <v>5.4467</v>
       </c>
       <c r="D28" t="n">
-        <v>46.52</v>
+        <v>44.43</v>
       </c>
       <c r="E28" t="n">
-        <v>82.36</v>
+        <v>80.98</v>
       </c>
       <c r="F28" t="n">
-        <v>43.49</v>
+        <v>42.54</v>
       </c>
       <c r="G28" t="n">
-        <v>62.21</v>
+        <v>60.05</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2341,13 +2359,13 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-12.2</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>-6.62</v>
+        <v>-9.85</v>
       </c>
       <c r="P28" t="n">
-        <v>33.86</v>
+        <v>27.6</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2382,19 +2400,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0286</v>
+        <v>1.0358</v>
       </c>
       <c r="D29" t="n">
-        <v>18.86</v>
+        <v>18.72</v>
       </c>
       <c r="E29" t="n">
-        <v>86.29000000000001</v>
+        <v>85.44</v>
       </c>
       <c r="F29" t="n">
-        <v>35.52</v>
+        <v>37.38</v>
       </c>
       <c r="G29" t="n">
-        <v>61.95</v>
+        <v>66.84</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2409,13 +2427,13 @@
         <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>2.25</v>
+        <v>1.44</v>
       </c>
       <c r="O29" t="n">
-        <v>0.31</v>
+        <v>-0.24</v>
       </c>
       <c r="P29" t="n">
-        <v>25.3</v>
+        <v>26.52</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2427,10 +2445,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2450,19 +2468,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2102</v>
+        <v>1.2076</v>
       </c>
       <c r="D30" t="n">
-        <v>16.74</v>
+        <v>16.46</v>
       </c>
       <c r="E30" t="n">
-        <v>74.22</v>
+        <v>70.54000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>22.97</v>
+        <v>23.79</v>
       </c>
       <c r="G30" t="n">
-        <v>47.78</v>
+        <v>51.82</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2477,13 +2495,13 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>-0.71</v>
       </c>
       <c r="O30" t="n">
-        <v>-2.74</v>
+        <v>-4.04</v>
       </c>
       <c r="P30" t="n">
-        <v>19.46</v>
+        <v>19.67</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2518,19 +2536,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8187</v>
+        <v>0.8117</v>
       </c>
       <c r="D31" t="n">
-        <v>25.12</v>
+        <v>24.54</v>
       </c>
       <c r="E31" t="n">
-        <v>75.59999999999999</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>27.43</v>
+        <v>28.06</v>
       </c>
       <c r="G31" t="n">
-        <v>43.79</v>
+        <v>45.4</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2545,13 +2563,13 @@
         <v>1.69</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.2</v>
+        <v>-1.01</v>
       </c>
       <c r="O31" t="n">
-        <v>-3.58</v>
+        <v>-5.06</v>
       </c>
       <c r="P31" t="n">
-        <v>-4.48</v>
+        <v>-5.15</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2586,19 +2604,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.197</v>
+        <v>0.1977</v>
       </c>
       <c r="D32" t="n">
-        <v>29.05</v>
+        <v>28.74</v>
       </c>
       <c r="E32" t="n">
-        <v>11.29</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>41.25</v>
+        <v>41.5</v>
       </c>
       <c r="G32" t="n">
-        <v>67.42</v>
+        <v>67.97</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2613,16 +2631,16 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>1.66</v>
+        <v>1.98</v>
       </c>
       <c r="O32" t="n">
-        <v>1.66</v>
+        <v>-0.84</v>
       </c>
       <c r="P32" t="n">
-        <v>-29.24</v>
+        <v>-28.41</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2631,10 +2649,10 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.288</v>
+        <v>1.2834</v>
       </c>
       <c r="D2" t="n">
-        <v>81.22</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>80.12</v>
+        <v>79.91</v>
       </c>
       <c r="F2" t="n">
-        <v>49.35</v>
+        <v>48.87</v>
       </c>
       <c r="G2" t="n">
-        <v>89.05</v>
+        <v>88.28</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
@@ -567,13 +567,13 @@
         <v>-9.41</v>
       </c>
       <c r="N2" t="n">
-        <v>1.04</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>-4.81</v>
+        <v>-6.75</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.09</v>
+        <v>-15.34</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -608,19 +608,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.56</v>
+        <v>4.5542</v>
       </c>
       <c r="D3" t="n">
-        <v>24.71</v>
+        <v>24.68</v>
       </c>
       <c r="E3" t="n">
-        <v>68.70999999999999</v>
+        <v>67.95999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>38.92</v>
+        <v>38.52</v>
       </c>
       <c r="G3" t="n">
-        <v>54.96</v>
+        <v>53.83</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -635,13 +635,13 @@
         <v>1.25</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.83</v>
+        <v>-1.71</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.63</v>
+        <v>-6.93</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.06</v>
+        <v>-0.33</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -676,40 +676,40 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6071</v>
+        <v>0.6076</v>
       </c>
       <c r="D4" t="n">
-        <v>29.85</v>
+        <v>29.87</v>
       </c>
       <c r="E4" t="n">
-        <v>75.78</v>
+        <v>75.8</v>
       </c>
       <c r="F4" t="n">
-        <v>19.86</v>
+        <v>19.62</v>
       </c>
       <c r="G4" t="n">
-        <v>39.87</v>
+        <v>39.14</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>0.86</v>
+        <v>4.66</v>
       </c>
       <c r="L4" t="n">
-        <v>21.74</v>
+        <v>62.5</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.01</v>
+        <v>1.63</v>
       </c>
       <c r="N4" t="n">
-        <v>1.89</v>
+        <v>1.23</v>
       </c>
       <c r="O4" t="n">
-        <v>-3.98</v>
+        <v>-2.73</v>
       </c>
       <c r="P4" t="n">
-        <v>-13.06</v>
+        <v>-12.7</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -744,19 +744,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1745</v>
+        <v>5.2018</v>
       </c>
       <c r="D5" t="n">
-        <v>16.17</v>
+        <v>16.26</v>
       </c>
       <c r="E5" t="n">
-        <v>26.55</v>
+        <v>27.08</v>
       </c>
       <c r="F5" t="n">
-        <v>27.89</v>
+        <v>27.17</v>
       </c>
       <c r="G5" t="n">
-        <v>35.5</v>
+        <v>34.06</v>
       </c>
       <c r="H5" t="n">
         <v>-38.58</v>
@@ -777,13 +777,13 @@
         <v>-50.96</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.52</v>
+        <v>-1.31</v>
       </c>
       <c r="O5" t="n">
-        <v>-11.4</v>
+        <v>-10.59</v>
       </c>
       <c r="P5" t="n">
-        <v>14.16</v>
+        <v>13.42</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -818,19 +818,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.3685</v>
+        <v>18.4798</v>
       </c>
       <c r="D6" t="n">
-        <v>53.49</v>
+        <v>53.81</v>
       </c>
       <c r="E6" t="n">
-        <v>67.93000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="F6" t="n">
-        <v>53.86</v>
+        <v>50.61</v>
       </c>
       <c r="G6" t="n">
-        <v>81.16</v>
+        <v>78.44</v>
       </c>
       <c r="H6" t="n">
         <v>5.54</v>
@@ -851,13 +851,13 @@
         <v>-1.94</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.09</v>
+        <v>-10.38</v>
       </c>
       <c r="O6" t="n">
-        <v>-9.69</v>
+        <v>-12.63</v>
       </c>
       <c r="P6" t="n">
-        <v>16.88</v>
+        <v>18.05</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -892,19 +892,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6611</v>
+        <v>3.625</v>
       </c>
       <c r="D7" t="n">
-        <v>24.71</v>
+        <v>24.46</v>
       </c>
       <c r="E7" t="n">
-        <v>17.08</v>
+        <v>14.97</v>
       </c>
       <c r="F7" t="n">
-        <v>37.11</v>
+        <v>36.79</v>
       </c>
       <c r="G7" t="n">
-        <v>43.32</v>
+        <v>42.42</v>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
@@ -919,13 +919,13 @@
         <v>-0.87</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.93</v>
+        <v>-3.08</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.19</v>
+        <v>-6.74</v>
       </c>
       <c r="P7" t="n">
-        <v>-26.23</v>
+        <v>-25.51</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.205</v>
+        <v>2.1944</v>
       </c>
       <c r="D8" t="n">
-        <v>14.78</v>
+        <v>14.71</v>
       </c>
       <c r="E8" t="n">
-        <v>61.18</v>
+        <v>57.49</v>
       </c>
       <c r="F8" t="n">
-        <v>25.83</v>
+        <v>25.62</v>
       </c>
       <c r="G8" t="n">
-        <v>35.18</v>
+        <v>33.83</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -987,13 +987,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.24</v>
+        <v>-0.01</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.42</v>
+        <v>-3.6</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.53</v>
+        <v>-7.62</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1028,19 +1028,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.4389</v>
+        <v>3.4125</v>
       </c>
       <c r="D9" t="n">
-        <v>20.86</v>
+        <v>20.7</v>
       </c>
       <c r="E9" t="n">
-        <v>22.52</v>
+        <v>19.71</v>
       </c>
       <c r="F9" t="n">
-        <v>31.42</v>
+        <v>31.94</v>
       </c>
       <c r="G9" t="n">
-        <v>62.31</v>
+        <v>64.38</v>
       </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
@@ -1055,13 +1055,13 @@
         <v>-1.28</v>
       </c>
       <c r="N9" t="n">
-        <v>2.66</v>
+        <v>2.2</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.53</v>
+        <v>-2.92</v>
       </c>
       <c r="P9" t="n">
-        <v>-20.42</v>
+        <v>-21.12</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1096,19 +1096,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5318000000000001</v>
+        <v>0.5353</v>
       </c>
       <c r="D10" t="n">
-        <v>24.22</v>
+        <v>24.38</v>
       </c>
       <c r="E10" t="n">
-        <v>58.39</v>
+        <v>60.2</v>
       </c>
       <c r="F10" t="n">
-        <v>42.6</v>
+        <v>41.53</v>
       </c>
       <c r="G10" t="n">
-        <v>66.54000000000001</v>
+        <v>62.97</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1123,13 +1123,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.51</v>
+        <v>0.92</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.68</v>
+        <v>-2.84</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.09</v>
+        <v>-8.9</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1164,19 +1164,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8179</v>
+        <v>0.8192</v>
       </c>
       <c r="D11" t="n">
-        <v>33.34</v>
+        <v>33.38</v>
       </c>
       <c r="E11" t="n">
-        <v>89.36</v>
+        <v>89.53</v>
       </c>
       <c r="F11" t="n">
-        <v>41.32</v>
+        <v>40.6</v>
       </c>
       <c r="G11" t="n">
-        <v>59.89</v>
+        <v>58.59</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -1191,13 +1191,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.76</v>
+        <v>-1.31</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.37</v>
+        <v>-3.7</v>
       </c>
       <c r="P11" t="n">
-        <v>-11.87</v>
+        <v>-11.67</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1232,19 +1232,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7636</v>
+        <v>6.6976</v>
       </c>
       <c r="D12" t="n">
-        <v>32.73</v>
+        <v>32.41</v>
       </c>
       <c r="E12" t="n">
-        <v>63.74</v>
+        <v>62.3</v>
       </c>
       <c r="F12" t="n">
-        <v>44.33</v>
+        <v>43.66</v>
       </c>
       <c r="G12" t="n">
-        <v>86.16</v>
+        <v>85.16</v>
       </c>
       <c r="H12" t="n">
         <v>13.12</v>
@@ -1265,13 +1265,13 @@
         <v>6.43</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.41</v>
+        <v>-1.37</v>
       </c>
       <c r="O12" t="n">
-        <v>0.01</v>
+        <v>-0.95</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.85</v>
+        <v>-14.47</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1306,40 +1306,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6312</v>
+        <v>2.6157</v>
       </c>
       <c r="D13" t="n">
-        <v>21.93</v>
+        <v>21.8</v>
       </c>
       <c r="E13" t="n">
-        <v>59.94</v>
+        <v>59.04</v>
       </c>
       <c r="F13" t="n">
-        <v>26.11</v>
+        <v>26.24</v>
       </c>
       <c r="G13" t="n">
-        <v>39.33</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>39.77</v>
+      </c>
+      <c r="H13" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="I13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.12</v>
+      </c>
       <c r="K13" t="n">
-        <v>4.41</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>39.13</v>
+        <v>95.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3</v>
+        <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>0.38</v>
+        <v>0.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.71</v>
+        <v>2.56</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1348,13 +1354,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1374,19 +1380,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0081</v>
+        <v>2.0249</v>
       </c>
       <c r="D14" t="n">
-        <v>16.94</v>
+        <v>17.09</v>
       </c>
       <c r="E14" t="n">
-        <v>78.03</v>
+        <v>80.45</v>
       </c>
       <c r="F14" t="n">
-        <v>20.67</v>
+        <v>20.72</v>
       </c>
       <c r="G14" t="n">
-        <v>48.79</v>
+        <v>49.06</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1401,13 +1407,13 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>1.66</v>
+        <v>2.94</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.6</v>
+        <v>0.83</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.14</v>
+        <v>-6.92</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1419,10 +1425,10 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1442,19 +1448,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9208</v>
+        <v>0.9145</v>
       </c>
       <c r="D15" t="n">
-        <v>16.83</v>
+        <v>16.71</v>
       </c>
       <c r="E15" t="n">
-        <v>58.39</v>
+        <v>58.03</v>
       </c>
       <c r="F15" t="n">
-        <v>68.23999999999999</v>
+        <v>65.39</v>
       </c>
       <c r="G15" t="n">
-        <v>96.01000000000001</v>
+        <v>94.69</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1469,13 +1475,13 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>0.33</v>
+        <v>-4.23</v>
       </c>
       <c r="O15" t="n">
-        <v>1.35</v>
+        <v>0.49</v>
       </c>
       <c r="P15" t="n">
-        <v>-17.67</v>
+        <v>-18.53</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1487,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1510,19 +1516,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8507</v>
+        <v>0.8603</v>
       </c>
       <c r="D16" t="n">
-        <v>32.74</v>
+        <v>33.11</v>
       </c>
       <c r="E16" t="n">
-        <v>45.19</v>
+        <v>47.94</v>
       </c>
       <c r="F16" t="n">
-        <v>35.96</v>
+        <v>35.24</v>
       </c>
       <c r="G16" t="n">
-        <v>60.05</v>
+        <v>58.28</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1537,13 +1543,13 @@
         <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>0.61</v>
+        <v>1.52</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.88</v>
+        <v>-5.86</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.53</v>
+        <v>-25.71</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1578,19 +1584,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5187</v>
+        <v>0.522</v>
       </c>
       <c r="D17" t="n">
-        <v>41.28</v>
+        <v>41.54</v>
       </c>
       <c r="E17" t="n">
-        <v>23.99</v>
+        <v>24.9</v>
       </c>
       <c r="F17" t="n">
-        <v>40</v>
+        <v>38.34</v>
       </c>
       <c r="G17" t="n">
-        <v>35.65</v>
+        <v>30.94</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1605,13 +1611,13 @@
         <v>-0.58</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.97</v>
+        <v>-0.48</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.7</v>
+        <v>-5.55</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.66</v>
+        <v>-21.95</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1646,19 +1652,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.9042</v>
+        <v>5.8778</v>
       </c>
       <c r="D18" t="n">
-        <v>6.56</v>
+        <v>6.53</v>
       </c>
       <c r="E18" t="n">
-        <v>89.91</v>
+        <v>88.20999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>11.34</v>
+        <v>11.77</v>
       </c>
       <c r="G18" t="n">
-        <v>64.11</v>
+        <v>68.98</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1673,13 +1679,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>4.02</v>
+        <v>3.32</v>
       </c>
       <c r="O18" t="n">
-        <v>2.35</v>
+        <v>3.45</v>
       </c>
       <c r="P18" t="n">
-        <v>6.53</v>
+        <v>5.99</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1714,19 +1720,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1398</v>
+        <v>5.089</v>
       </c>
       <c r="D19" t="n">
-        <v>9.029999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.39</v>
+        <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>13.69</v>
+        <v>13.68</v>
       </c>
       <c r="G19" t="n">
-        <v>11.49</v>
+        <v>11.48</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1741,13 +1747,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.24</v>
+        <v>0.24</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.84</v>
+        <v>-6</v>
       </c>
       <c r="P19" t="n">
-        <v>-13.77</v>
+        <v>-13.87</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1782,19 +1788,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2046</v>
+        <v>0.2075</v>
       </c>
       <c r="D20" t="n">
-        <v>76.14</v>
+        <v>77.25</v>
       </c>
       <c r="E20" t="n">
-        <v>90.14</v>
+        <v>90.3</v>
       </c>
       <c r="F20" t="n">
-        <v>54.83</v>
+        <v>52.82</v>
       </c>
       <c r="G20" t="n">
-        <v>89.37</v>
+        <v>87.66</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1809,13 +1815,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.68</v>
+        <v>-1</v>
       </c>
       <c r="O20" t="n">
-        <v>-3.16</v>
+        <v>-4.34</v>
       </c>
       <c r="P20" t="n">
-        <v>1.63</v>
+        <v>3.72</v>
       </c>
       <c r="Q20" t="n">
         <v>-1</v>
@@ -1850,19 +1856,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9004</v>
+        <v>0.9005</v>
       </c>
       <c r="D21" t="n">
-        <v>36.15</v>
+        <v>36.16</v>
       </c>
       <c r="E21" t="n">
-        <v>92.7</v>
+        <v>92.70999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>44.71</v>
+        <v>42.22</v>
       </c>
       <c r="G21" t="n">
-        <v>77.25</v>
+        <v>74.45</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1877,13 +1883,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.26</v>
+        <v>-3.23</v>
       </c>
       <c r="O21" t="n">
-        <v>-3.01</v>
+        <v>-4.32</v>
       </c>
       <c r="P21" t="n">
-        <v>8.039999999999999</v>
+        <v>6.92</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1918,19 +1924,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3533</v>
+        <v>1.3565</v>
       </c>
       <c r="D22" t="n">
-        <v>14.48</v>
+        <v>14.51</v>
       </c>
       <c r="E22" t="n">
-        <v>93.31999999999999</v>
+        <v>93.72</v>
       </c>
       <c r="F22" t="n">
-        <v>24.31</v>
+        <v>23.77</v>
       </c>
       <c r="G22" t="n">
-        <v>28.23</v>
+        <v>26.02</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
@@ -1945,13 +1951,13 @@
         <v>0.57</v>
       </c>
       <c r="N22" t="n">
-        <v>0.52</v>
+        <v>-0.01</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.24</v>
+        <v>-3.42</v>
       </c>
       <c r="P22" t="n">
-        <v>-10.24</v>
+        <v>-9.84</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -1986,40 +1992,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.226900000000001</v>
+        <v>8.0611</v>
       </c>
       <c r="D23" t="n">
-        <v>27.29</v>
+        <v>26.75</v>
       </c>
       <c r="E23" t="n">
-        <v>30.36</v>
+        <v>29.33</v>
       </c>
       <c r="F23" t="n">
-        <v>36.75</v>
+        <v>37.93</v>
       </c>
       <c r="G23" t="n">
-        <v>50.2</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+        <v>51.72</v>
+      </c>
+      <c r="H23" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="I23" t="n">
+        <v>90</v>
+      </c>
+      <c r="J23" t="n">
+        <v>6.33</v>
+      </c>
       <c r="K23" t="n">
-        <v>5.53</v>
+        <v>10.23</v>
       </c>
       <c r="L23" t="n">
-        <v>39.13</v>
+        <v>75</v>
       </c>
       <c r="M23" t="n">
-        <v>0.15</v>
+        <v>1.81</v>
       </c>
       <c r="N23" t="n">
-        <v>0.57</v>
+        <v>-1.88</v>
       </c>
       <c r="O23" t="n">
-        <v>-6.91</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="P23" t="n">
-        <v>-12.96</v>
+        <v>-14.26</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2028,13 +2040,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2054,19 +2066,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.9643</v>
+        <v>5.9954</v>
       </c>
       <c r="D24" t="n">
-        <v>38.97</v>
+        <v>39.17</v>
       </c>
       <c r="E24" t="n">
-        <v>85.70999999999999</v>
+        <v>85.8</v>
       </c>
       <c r="F24" t="n">
-        <v>36.11</v>
+        <v>35.32</v>
       </c>
       <c r="G24" t="n">
-        <v>50.27</v>
+        <v>47.58</v>
       </c>
       <c r="H24" t="n">
         <v>1.6</v>
@@ -2087,13 +2099,13 @@
         <v>-3.74</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.97</v>
+        <v>-5.6</v>
       </c>
       <c r="O24" t="n">
-        <v>-9.94</v>
+        <v>-11.69</v>
       </c>
       <c r="P24" t="n">
-        <v>-5.17</v>
+        <v>-4.09</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2128,19 +2140,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6177</v>
+        <v>2.6881</v>
       </c>
       <c r="D25" t="n">
-        <v>55.38</v>
+        <v>56.83</v>
       </c>
       <c r="E25" t="n">
-        <v>35.25</v>
+        <v>42.51</v>
       </c>
       <c r="F25" t="n">
-        <v>34.78</v>
+        <v>33.46</v>
       </c>
       <c r="G25" t="n">
-        <v>51.76</v>
+        <v>48.59</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2155,13 +2167,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.25</v>
+        <v>-1.81</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.35</v>
+        <v>-4.72</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.69</v>
+        <v>-7.02</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2196,19 +2208,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.8106</v>
+        <v>4.8237</v>
       </c>
       <c r="D26" t="n">
-        <v>59.32</v>
+        <v>59.49</v>
       </c>
       <c r="E26" t="n">
-        <v>46.27</v>
+        <v>46.47</v>
       </c>
       <c r="F26" t="n">
-        <v>36.21</v>
+        <v>35.71</v>
       </c>
       <c r="G26" t="n">
-        <v>27.68</v>
+        <v>26.48</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2223,13 +2235,13 @@
         <v>0.71</v>
       </c>
       <c r="N26" t="n">
-        <v>-0.66</v>
+        <v>-1.31</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.65</v>
+        <v>-6.17</v>
       </c>
       <c r="P26" t="n">
-        <v>-25.31</v>
+        <v>-24.14</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2264,19 +2276,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8325</v>
+        <v>1.8398</v>
       </c>
       <c r="D27" t="n">
-        <v>35.53</v>
+        <v>35.67</v>
       </c>
       <c r="E27" t="n">
-        <v>48.84</v>
+        <v>49.26</v>
       </c>
       <c r="F27" t="n">
-        <v>49.45</v>
+        <v>52.4</v>
       </c>
       <c r="G27" t="n">
-        <v>59.66</v>
+        <v>63.52</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2291,13 +2303,13 @@
         <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>5.57</v>
+        <v>4.03</v>
       </c>
       <c r="O27" t="n">
-        <v>-2</v>
+        <v>-3.25</v>
       </c>
       <c r="P27" t="n">
-        <v>-19.83</v>
+        <v>-19.93</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2332,19 +2344,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.4467</v>
+        <v>5.5441</v>
       </c>
       <c r="D28" t="n">
-        <v>44.43</v>
+        <v>45.22</v>
       </c>
       <c r="E28" t="n">
-        <v>80.98</v>
+        <v>81.38</v>
       </c>
       <c r="F28" t="n">
-        <v>42.54</v>
+        <v>39.4</v>
       </c>
       <c r="G28" t="n">
-        <v>60.05</v>
+        <v>54.37</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2359,13 +2371,13 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-9.470000000000001</v>
+        <v>-7.95</v>
       </c>
       <c r="O28" t="n">
-        <v>-9.85</v>
+        <v>-13.58</v>
       </c>
       <c r="P28" t="n">
-        <v>27.6</v>
+        <v>29.04</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2400,19 +2412,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0358</v>
+        <v>1.0426</v>
       </c>
       <c r="D29" t="n">
-        <v>18.72</v>
+        <v>18.84</v>
       </c>
       <c r="E29" t="n">
-        <v>85.44</v>
+        <v>86.06</v>
       </c>
       <c r="F29" t="n">
-        <v>37.38</v>
+        <v>37.98</v>
       </c>
       <c r="G29" t="n">
-        <v>66.84</v>
+        <v>68.78</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2427,13 +2439,13 @@
         <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>1.44</v>
+        <v>3.49</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.24</v>
+        <v>3.01</v>
       </c>
       <c r="P29" t="n">
-        <v>26.52</v>
+        <v>24.88</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2445,10 +2457,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2468,19 +2480,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2076</v>
+        <v>1.219</v>
       </c>
       <c r="D30" t="n">
-        <v>16.46</v>
+        <v>16.62</v>
       </c>
       <c r="E30" t="n">
-        <v>70.54000000000001</v>
+        <v>73.15000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>23.79</v>
+        <v>23.46</v>
       </c>
       <c r="G30" t="n">
-        <v>51.82</v>
+        <v>49.78</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2495,13 +2507,13 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.71</v>
+        <v>1.92</v>
       </c>
       <c r="O30" t="n">
-        <v>-4.04</v>
+        <v>-1.63</v>
       </c>
       <c r="P30" t="n">
-        <v>19.67</v>
+        <v>20.5</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2536,19 +2548,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8117</v>
+        <v>0.8096</v>
       </c>
       <c r="D31" t="n">
-        <v>24.54</v>
+        <v>24.44</v>
       </c>
       <c r="E31" t="n">
-        <v>73.81999999999999</v>
+        <v>73.06</v>
       </c>
       <c r="F31" t="n">
-        <v>28.06</v>
+        <v>27.89</v>
       </c>
       <c r="G31" t="n">
-        <v>45.4</v>
+        <v>45.01</v>
       </c>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
@@ -2563,13 +2575,13 @@
         <v>1.69</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.01</v>
+        <v>-2.18</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.06</v>
+        <v>-5.77</v>
       </c>
       <c r="P31" t="n">
-        <v>-5.15</v>
+        <v>-5.5</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2604,19 +2616,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1977</v>
+        <v>0.1972</v>
       </c>
       <c r="D32" t="n">
-        <v>28.74</v>
+        <v>28.66</v>
       </c>
       <c r="E32" t="n">
-        <v>8.609999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="F32" t="n">
-        <v>41.5</v>
+        <v>40.49</v>
       </c>
       <c r="G32" t="n">
-        <v>67.97</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2631,13 +2643,13 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>1.98</v>
+        <v>1.68</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.84</v>
+        <v>-1.31</v>
       </c>
       <c r="P32" t="n">
-        <v>-28.41</v>
+        <v>-28.79</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,40 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2834</v>
+        <v>1.2905</v>
       </c>
       <c r="D2" t="n">
-        <v>80.93000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="E2" t="n">
-        <v>79.91</v>
+        <v>79.53</v>
       </c>
       <c r="F2" t="n">
-        <v>48.87</v>
+        <v>47.74</v>
       </c>
       <c r="G2" t="n">
-        <v>88.28</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+        <v>86.73</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-107.87</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" t="n">
+        <v>-110.5</v>
+      </c>
       <c r="K2" t="n">
-        <v>-3.85</v>
+        <v>-107.87</v>
       </c>
       <c r="L2" t="n">
-        <v>13.04</v>
+        <v>4.17</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.41</v>
+        <v>-114.28</v>
       </c>
       <c r="N2" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.39</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.75</v>
+        <v>-9.050000000000001</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.34</v>
+        <v>-15.45</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -608,40 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5542</v>
+        <v>4.5458</v>
       </c>
       <c r="D3" t="n">
-        <v>24.68</v>
+        <v>24.24</v>
       </c>
       <c r="E3" t="n">
-        <v>67.95999999999999</v>
+        <v>63.41</v>
       </c>
       <c r="F3" t="n">
-        <v>38.52</v>
+        <v>38.28</v>
       </c>
       <c r="G3" t="n">
-        <v>53.83</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+        <v>52.93</v>
+      </c>
+      <c r="H3" t="n">
+        <v>11.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>95</v>
+      </c>
+      <c r="J3" t="n">
+        <v>6.98</v>
+      </c>
       <c r="K3" t="n">
-        <v>5.62</v>
+        <v>11.2</v>
       </c>
       <c r="L3" t="n">
-        <v>34.78</v>
+        <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>1.25</v>
+        <v>4.29</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.71</v>
+        <v>-3.81</v>
       </c>
       <c r="O3" t="n">
-        <v>-6.93</v>
+        <v>-10.1</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.33</v>
+        <v>-1.51</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -650,13 +662,13 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -676,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6076</v>
+        <v>0.6171</v>
       </c>
       <c r="D4" t="n">
-        <v>29.87</v>
+        <v>29.85</v>
       </c>
       <c r="E4" t="n">
-        <v>75.8</v>
+        <v>75.66</v>
       </c>
       <c r="F4" t="n">
-        <v>19.62</v>
+        <v>19.55</v>
       </c>
       <c r="G4" t="n">
-        <v>39.14</v>
+        <v>38.8</v>
       </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
@@ -703,13 +715,13 @@
         <v>1.63</v>
       </c>
       <c r="N4" t="n">
-        <v>1.23</v>
+        <v>-0.09</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.73</v>
+        <v>-4.65</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.7</v>
+        <v>-12.56</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -744,19 +756,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.2018</v>
+        <v>5.1944</v>
       </c>
       <c r="D5" t="n">
-        <v>16.26</v>
+        <v>15.98</v>
       </c>
       <c r="E5" t="n">
-        <v>27.08</v>
+        <v>25.12</v>
       </c>
       <c r="F5" t="n">
-        <v>27.17</v>
+        <v>26.16</v>
       </c>
       <c r="G5" t="n">
-        <v>34.06</v>
+        <v>31.69</v>
       </c>
       <c r="H5" t="n">
         <v>-38.58</v>
@@ -777,13 +789,13 @@
         <v>-50.96</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.31</v>
+        <v>-3.49</v>
       </c>
       <c r="O5" t="n">
-        <v>-10.59</v>
+        <v>-13.5</v>
       </c>
       <c r="P5" t="n">
-        <v>13.42</v>
+        <v>10.08</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -818,46 +830,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.4798</v>
+        <v>18.2463</v>
       </c>
       <c r="D6" t="n">
-        <v>53.81</v>
+        <v>52.28</v>
       </c>
       <c r="E6" t="n">
-        <v>68.58</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>50.61</v>
+        <v>48.09</v>
       </c>
       <c r="G6" t="n">
-        <v>78.44</v>
+        <v>75.41</v>
       </c>
       <c r="H6" t="n">
-        <v>5.54</v>
+        <v>6.04</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>2.21</v>
+        <v>2.71</v>
       </c>
       <c r="K6" t="n">
-        <v>5.88</v>
+        <v>5.99</v>
       </c>
       <c r="L6" t="n">
         <v>58.33</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.94</v>
+        <v>-1.83</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.38</v>
+        <v>-10.82</v>
       </c>
       <c r="O6" t="n">
-        <v>-12.63</v>
+        <v>-14.18</v>
       </c>
       <c r="P6" t="n">
-        <v>18.05</v>
+        <v>10.58</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -892,40 +904,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.625</v>
+        <v>3.6035</v>
       </c>
       <c r="D7" t="n">
-        <v>24.46</v>
+        <v>23.93</v>
       </c>
       <c r="E7" t="n">
-        <v>14.97</v>
+        <v>11.16</v>
       </c>
       <c r="F7" t="n">
-        <v>36.79</v>
+        <v>36.69</v>
       </c>
       <c r="G7" t="n">
-        <v>42.42</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>42.08</v>
+      </c>
+      <c r="H7" t="n">
+        <v>20.96</v>
+      </c>
+      <c r="I7" t="n">
+        <v>100</v>
+      </c>
+      <c r="J7" t="n">
+        <v>15.22</v>
+      </c>
       <c r="K7" t="n">
-        <v>3.91</v>
+        <v>20.96</v>
       </c>
       <c r="L7" t="n">
-        <v>30.43</v>
+        <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.87</v>
+        <v>14.01</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.08</v>
+        <v>-5.85</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.74</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-25.51</v>
+        <v>-27.73</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -934,13 +952,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -960,19 +978,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.1944</v>
+        <v>2.2213</v>
       </c>
       <c r="D8" t="n">
-        <v>14.71</v>
+        <v>14.65</v>
       </c>
       <c r="E8" t="n">
-        <v>57.49</v>
+        <v>54.5</v>
       </c>
       <c r="F8" t="n">
-        <v>25.62</v>
+        <v>25.36</v>
       </c>
       <c r="G8" t="n">
-        <v>33.83</v>
+        <v>32.16</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -987,13 +1005,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.01</v>
+        <v>0.16</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.6</v>
+        <v>-3.19</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.62</v>
+        <v>-7.37</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1028,40 +1046,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.4125</v>
+        <v>3.4842</v>
       </c>
       <c r="D9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="E9" t="n">
-        <v>19.71</v>
+        <v>21.71</v>
       </c>
       <c r="F9" t="n">
-        <v>31.94</v>
+        <v>31.53</v>
       </c>
       <c r="G9" t="n">
-        <v>64.38</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>62.61</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="I9" t="n">
+        <v>25</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-1.68</v>
+      </c>
       <c r="K9" t="n">
-        <v>11.6</v>
+        <v>2.95</v>
       </c>
       <c r="L9" t="n">
-        <v>26.09</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.28</v>
+        <v>-15.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.2</v>
+        <v>0.96</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.92</v>
+        <v>-2.31</v>
       </c>
       <c r="P9" t="n">
-        <v>-21.12</v>
+        <v>-19.8</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1096,19 +1120,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5353</v>
+        <v>0.54</v>
       </c>
       <c r="D10" t="n">
-        <v>24.38</v>
+        <v>24.2</v>
       </c>
       <c r="E10" t="n">
-        <v>60.2</v>
+        <v>58.22</v>
       </c>
       <c r="F10" t="n">
-        <v>41.53</v>
+        <v>40.65</v>
       </c>
       <c r="G10" t="n">
-        <v>62.97</v>
+        <v>60.81</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1123,13 +1147,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.92</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.84</v>
+        <v>-4.25</v>
       </c>
       <c r="P10" t="n">
-        <v>-8.9</v>
+        <v>-9.130000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1164,19 +1188,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8192</v>
+        <v>0.8197</v>
       </c>
       <c r="D11" t="n">
-        <v>33.38</v>
+        <v>32.86</v>
       </c>
       <c r="E11" t="n">
-        <v>89.53</v>
+        <v>87.83</v>
       </c>
       <c r="F11" t="n">
-        <v>40.6</v>
+        <v>39.84</v>
       </c>
       <c r="G11" t="n">
-        <v>58.59</v>
+        <v>57.46</v>
       </c>
       <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
@@ -1191,13 +1215,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.31</v>
+        <v>-3.05</v>
       </c>
       <c r="O11" t="n">
-        <v>-3.7</v>
+        <v>-5.65</v>
       </c>
       <c r="P11" t="n">
-        <v>-11.67</v>
+        <v>-12.28</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1232,19 +1256,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.6976</v>
+        <v>6.7323</v>
       </c>
       <c r="D12" t="n">
-        <v>32.41</v>
+        <v>32.05</v>
       </c>
       <c r="E12" t="n">
-        <v>62.3</v>
+        <v>59.92</v>
       </c>
       <c r="F12" t="n">
-        <v>43.66</v>
+        <v>41.88</v>
       </c>
       <c r="G12" t="n">
-        <v>85.16</v>
+        <v>83.06</v>
       </c>
       <c r="H12" t="n">
         <v>13.12</v>
@@ -1265,13 +1289,13 @@
         <v>6.43</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.37</v>
+        <v>-5.08</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.95</v>
+        <v>-3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.47</v>
+        <v>-15.33</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1306,19 +1330,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6157</v>
+        <v>2.6854</v>
       </c>
       <c r="D13" t="n">
-        <v>21.8</v>
+        <v>22.02</v>
       </c>
       <c r="E13" t="n">
-        <v>59.04</v>
+        <v>60.85</v>
       </c>
       <c r="F13" t="n">
-        <v>26.24</v>
+        <v>26.62</v>
       </c>
       <c r="G13" t="n">
-        <v>39.77</v>
+        <v>41.37</v>
       </c>
       <c r="H13" t="n">
         <v>9.529999999999999</v>
@@ -1339,13 +1363,13 @@
         <v>1.01</v>
       </c>
       <c r="N13" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6</v>
+        <v>0.83</v>
       </c>
       <c r="P13" t="n">
-        <v>2.56</v>
+        <v>3.98</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1380,19 +1404,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0249</v>
+        <v>2.0689</v>
       </c>
       <c r="D14" t="n">
-        <v>17.09</v>
+        <v>17.18</v>
       </c>
       <c r="E14" t="n">
-        <v>80.45</v>
+        <v>82.02</v>
       </c>
       <c r="F14" t="n">
-        <v>20.72</v>
+        <v>20.86</v>
       </c>
       <c r="G14" t="n">
-        <v>49.06</v>
+        <v>49.57</v>
       </c>
       <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
@@ -1407,13 +1431,13 @@
         <v>0.24</v>
       </c>
       <c r="N14" t="n">
-        <v>2.94</v>
+        <v>2.51</v>
       </c>
       <c r="O14" t="n">
-        <v>0.83</v>
+        <v>1.04</v>
       </c>
       <c r="P14" t="n">
-        <v>-6.92</v>
+        <v>-5.55</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1448,19 +1472,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9145</v>
+        <v>0.9199000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>16.71</v>
+        <v>13.4</v>
       </c>
       <c r="E15" t="n">
-        <v>58.03</v>
+        <v>38.91</v>
       </c>
       <c r="F15" t="n">
-        <v>65.39</v>
+        <v>62.15</v>
       </c>
       <c r="G15" t="n">
-        <v>94.69</v>
+        <v>93.13</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1475,13 +1499,13 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.23</v>
+        <v>-6.3</v>
       </c>
       <c r="O15" t="n">
-        <v>0.49</v>
+        <v>-2.98</v>
       </c>
       <c r="P15" t="n">
-        <v>-18.53</v>
+        <v>-19.9</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1516,19 +1540,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8603</v>
+        <v>0.8602</v>
       </c>
       <c r="D16" t="n">
-        <v>33.11</v>
+        <v>32.58</v>
       </c>
       <c r="E16" t="n">
-        <v>47.94</v>
+        <v>43.72</v>
       </c>
       <c r="F16" t="n">
-        <v>35.24</v>
+        <v>35.5</v>
       </c>
       <c r="G16" t="n">
-        <v>58.28</v>
+        <v>59.02</v>
       </c>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
@@ -1543,13 +1567,13 @@
         <v>3.38</v>
       </c>
       <c r="N16" t="n">
-        <v>1.52</v>
+        <v>-0.79</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.86</v>
+        <v>-8.27</v>
       </c>
       <c r="P16" t="n">
-        <v>-25.71</v>
+        <v>-25.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1584,19 +1608,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.522</v>
+        <v>0.5249</v>
       </c>
       <c r="D17" t="n">
-        <v>41.54</v>
+        <v>41.1</v>
       </c>
       <c r="E17" t="n">
-        <v>24.9</v>
+        <v>22.56</v>
       </c>
       <c r="F17" t="n">
-        <v>38.34</v>
+        <v>36.67</v>
       </c>
       <c r="G17" t="n">
-        <v>30.94</v>
+        <v>27.95</v>
       </c>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
@@ -1611,13 +1635,13 @@
         <v>-0.58</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.48</v>
+        <v>-1.27</v>
       </c>
       <c r="O17" t="n">
-        <v>-5.55</v>
+        <v>-7.72</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.95</v>
+        <v>-21.18</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1652,19 +1676,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.8778</v>
+        <v>5.9669</v>
       </c>
       <c r="D18" t="n">
-        <v>6.53</v>
+        <v>6.52</v>
       </c>
       <c r="E18" t="n">
-        <v>88.20999999999999</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>11.77</v>
+        <v>12.11</v>
       </c>
       <c r="G18" t="n">
-        <v>68.98</v>
+        <v>71.66</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1679,13 +1703,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>3.32</v>
+        <v>1.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.45</v>
+        <v>2.96</v>
       </c>
       <c r="P18" t="n">
-        <v>5.99</v>
+        <v>6.98</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1697,10 +1721,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1720,19 +1744,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.089</v>
+        <v>5.1401</v>
       </c>
       <c r="D19" t="n">
-        <v>8.869999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>13.68</v>
+        <v>13.36</v>
       </c>
       <c r="G19" t="n">
-        <v>11.48</v>
+        <v>9.68</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1747,19 +1771,19 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>0.24</v>
+        <v>-1.05</v>
       </c>
       <c r="O19" t="n">
-        <v>-6</v>
+        <v>-6.09</v>
       </c>
       <c r="P19" t="n">
-        <v>-13.87</v>
+        <v>-15.1</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1768,7 +1792,7 @@
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1788,19 +1812,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2075</v>
+        <v>0.2071</v>
       </c>
       <c r="D20" t="n">
-        <v>77.25</v>
+        <v>75.84999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>90.3</v>
+        <v>89.92</v>
       </c>
       <c r="F20" t="n">
-        <v>52.82</v>
+        <v>52.75</v>
       </c>
       <c r="G20" t="n">
-        <v>87.66</v>
+        <v>87.59</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1815,16 +1839,16 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-1</v>
+        <v>-3.32</v>
       </c>
       <c r="O20" t="n">
-        <v>-4.34</v>
+        <v>-7.74</v>
       </c>
       <c r="P20" t="n">
-        <v>3.72</v>
+        <v>1.57</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -1836,7 +1860,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1856,19 +1880,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.9005</v>
+        <v>0.8875999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>36.16</v>
+        <v>35.06</v>
       </c>
       <c r="E21" t="n">
-        <v>92.70999999999999</v>
+        <v>91.16</v>
       </c>
       <c r="F21" t="n">
-        <v>42.22</v>
+        <v>41.37</v>
       </c>
       <c r="G21" t="n">
-        <v>74.45</v>
+        <v>73.22</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1883,13 +1907,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>-3.23</v>
+        <v>-6.11</v>
       </c>
       <c r="O21" t="n">
-        <v>-4.32</v>
+        <v>-7.55</v>
       </c>
       <c r="P21" t="n">
-        <v>6.92</v>
+        <v>4.68</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1924,40 +1948,40 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3565</v>
+        <v>1.369</v>
       </c>
       <c r="D22" t="n">
-        <v>14.51</v>
+        <v>14.41</v>
       </c>
       <c r="E22" t="n">
-        <v>93.72</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>23.77</v>
+        <v>23.74</v>
       </c>
       <c r="G22" t="n">
-        <v>26.02</v>
+        <v>25.92</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="n">
-        <v>1.42</v>
+        <v>3.05</v>
       </c>
       <c r="L22" t="n">
-        <v>30.43</v>
+        <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>0.57</v>
+        <v>0.72</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.01</v>
+        <v>-1.18</v>
       </c>
       <c r="O22" t="n">
-        <v>-3.42</v>
+        <v>-5</v>
       </c>
       <c r="P22" t="n">
-        <v>-9.84</v>
+        <v>-9.51</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -1992,19 +2016,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.0611</v>
+        <v>7.959</v>
       </c>
       <c r="D23" t="n">
-        <v>26.75</v>
+        <v>25.98</v>
       </c>
       <c r="E23" t="n">
-        <v>29.33</v>
+        <v>27.29</v>
       </c>
       <c r="F23" t="n">
-        <v>37.93</v>
+        <v>38.45</v>
       </c>
       <c r="G23" t="n">
-        <v>51.72</v>
+        <v>52.46</v>
       </c>
       <c r="H23" t="n">
         <v>10.23</v>
@@ -2025,13 +2049,13 @@
         <v>1.81</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.88</v>
+        <v>-5.28</v>
       </c>
       <c r="O23" t="n">
-        <v>-9.380000000000001</v>
+        <v>-10.94</v>
       </c>
       <c r="P23" t="n">
-        <v>-14.26</v>
+        <v>-16.93</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2066,19 +2090,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.9954</v>
+        <v>5.9472</v>
       </c>
       <c r="D24" t="n">
-        <v>39.17</v>
+        <v>38.23</v>
       </c>
       <c r="E24" t="n">
-        <v>85.8</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>35.32</v>
+        <v>34.77</v>
       </c>
       <c r="G24" t="n">
-        <v>47.58</v>
+        <v>46.21</v>
       </c>
       <c r="H24" t="n">
         <v>1.6</v>
@@ -2099,13 +2123,13 @@
         <v>-3.74</v>
       </c>
       <c r="N24" t="n">
-        <v>-5.6</v>
+        <v>-7.04</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.69</v>
+        <v>-13.59</v>
       </c>
       <c r="P24" t="n">
-        <v>-4.09</v>
+        <v>-7.2</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2140,19 +2164,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6881</v>
+        <v>2.7005</v>
       </c>
       <c r="D25" t="n">
-        <v>56.83</v>
+        <v>56.15</v>
       </c>
       <c r="E25" t="n">
-        <v>42.51</v>
+        <v>39.53</v>
       </c>
       <c r="F25" t="n">
-        <v>33.46</v>
+        <v>32.97</v>
       </c>
       <c r="G25" t="n">
-        <v>48.59</v>
+        <v>46.92</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2167,13 +2191,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.81</v>
+        <v>-2.92</v>
       </c>
       <c r="O25" t="n">
-        <v>-4.72</v>
+        <v>-7.09</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.02</v>
+        <v>-8.58</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2208,19 +2232,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.8237</v>
+        <v>4.8226</v>
       </c>
       <c r="D26" t="n">
-        <v>59.49</v>
+        <v>58.51</v>
       </c>
       <c r="E26" t="n">
-        <v>46.47</v>
+        <v>44.42</v>
       </c>
       <c r="F26" t="n">
-        <v>35.71</v>
+        <v>34.08</v>
       </c>
       <c r="G26" t="n">
-        <v>26.48</v>
+        <v>22.95</v>
       </c>
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
@@ -2235,13 +2259,13 @@
         <v>0.71</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.31</v>
+        <v>-1.99</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.17</v>
+        <v>-6.85</v>
       </c>
       <c r="P26" t="n">
-        <v>-24.14</v>
+        <v>-26.64</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2276,19 +2300,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8398</v>
+        <v>1.891</v>
       </c>
       <c r="D27" t="n">
-        <v>35.67</v>
+        <v>36.07</v>
       </c>
       <c r="E27" t="n">
-        <v>49.26</v>
+        <v>51.63</v>
       </c>
       <c r="F27" t="n">
-        <v>52.4</v>
+        <v>54.68</v>
       </c>
       <c r="G27" t="n">
-        <v>63.52</v>
+        <v>66.51000000000001</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -2303,13 +2327,13 @@
         <v>2.16</v>
       </c>
       <c r="N27" t="n">
-        <v>4.03</v>
+        <v>5.76</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.25</v>
+        <v>-2.61</v>
       </c>
       <c r="P27" t="n">
-        <v>-19.93</v>
+        <v>-18.48</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2344,19 +2368,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.5441</v>
+        <v>5.4136</v>
       </c>
       <c r="D28" t="n">
-        <v>45.22</v>
+        <v>43.44</v>
       </c>
       <c r="E28" t="n">
-        <v>81.38</v>
+        <v>80.16</v>
       </c>
       <c r="F28" t="n">
-        <v>39.4</v>
+        <v>37.45</v>
       </c>
       <c r="G28" t="n">
-        <v>54.37</v>
+        <v>50.04</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2371,13 +2395,13 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-7.95</v>
+        <v>-11.02</v>
       </c>
       <c r="O28" t="n">
-        <v>-13.58</v>
+        <v>-16.73</v>
       </c>
       <c r="P28" t="n">
-        <v>29.04</v>
+        <v>23.51</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2412,19 +2436,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0426</v>
+        <v>1.0745</v>
       </c>
       <c r="D29" t="n">
-        <v>18.84</v>
+        <v>19.11</v>
       </c>
       <c r="E29" t="n">
-        <v>86.06</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>37.98</v>
+        <v>38.42</v>
       </c>
       <c r="G29" t="n">
-        <v>68.78</v>
+        <v>69.67</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2439,13 +2463,13 @@
         <v>1.2</v>
       </c>
       <c r="N29" t="n">
-        <v>3.49</v>
+        <v>4.05</v>
       </c>
       <c r="O29" t="n">
-        <v>3.01</v>
+        <v>3.07</v>
       </c>
       <c r="P29" t="n">
-        <v>24.88</v>
+        <v>27.8</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2480,19 +2504,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.219</v>
+        <v>1.2602</v>
       </c>
       <c r="D30" t="n">
-        <v>16.62</v>
+        <v>16.9</v>
       </c>
       <c r="E30" t="n">
-        <v>73.15000000000001</v>
+        <v>76.53</v>
       </c>
       <c r="F30" t="n">
-        <v>23.46</v>
+        <v>23.89</v>
       </c>
       <c r="G30" t="n">
-        <v>49.78</v>
+        <v>52.34</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2507,13 +2531,13 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>1.92</v>
+        <v>3.21</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.63</v>
+        <v>-3.5</v>
       </c>
       <c r="P30" t="n">
-        <v>20.5</v>
+        <v>23.87</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2548,40 +2572,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8096</v>
+        <v>0.8086</v>
       </c>
       <c r="D31" t="n">
-        <v>24.44</v>
+        <v>24.02</v>
       </c>
       <c r="E31" t="n">
-        <v>73.06</v>
+        <v>71.28</v>
       </c>
       <c r="F31" t="n">
-        <v>27.89</v>
+        <v>27.69</v>
       </c>
       <c r="G31" t="n">
-        <v>45.01</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
+        <v>44.28</v>
+      </c>
+      <c r="H31" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="I31" t="n">
+        <v>85</v>
+      </c>
+      <c r="J31" t="n">
+        <v>2.27</v>
+      </c>
       <c r="K31" t="n">
-        <v>2.27</v>
+        <v>5.62</v>
       </c>
       <c r="L31" t="n">
-        <v>47.83</v>
+        <v>75</v>
       </c>
       <c r="M31" t="n">
-        <v>1.69</v>
+        <v>3.84</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.18</v>
+        <v>-3.92</v>
       </c>
       <c r="O31" t="n">
-        <v>-5.77</v>
+        <v>-8.300000000000001</v>
       </c>
       <c r="P31" t="n">
-        <v>-5.5</v>
+        <v>-7.1</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2590,13 +2620,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2616,19 +2646,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1972</v>
+        <v>0.1979</v>
       </c>
       <c r="D32" t="n">
-        <v>28.66</v>
+        <v>28.3</v>
       </c>
       <c r="E32" t="n">
-        <v>8.43</v>
+        <v>6.71</v>
       </c>
       <c r="F32" t="n">
-        <v>40.49</v>
+        <v>40.13</v>
       </c>
       <c r="G32" t="n">
-        <v>65.65000000000001</v>
+        <v>64.3</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2643,13 +2673,13 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>1.68</v>
+        <v>-1.25</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.31</v>
+        <v>-3.15</v>
       </c>
       <c r="P32" t="n">
-        <v>-28.79</v>
+        <v>-28.69</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -629,22 +629,22 @@
         <v>52.93</v>
       </c>
       <c r="H3" t="n">
-        <v>11.02</v>
+        <v>10.53</v>
       </c>
       <c r="I3" t="n">
         <v>95</v>
       </c>
       <c r="J3" t="n">
-        <v>6.98</v>
+        <v>6.49</v>
       </c>
       <c r="K3" t="n">
-        <v>11.2</v>
+        <v>10.32</v>
       </c>
       <c r="L3" t="n">
         <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>4.29</v>
+        <v>3.41</v>
       </c>
       <c r="N3" t="n">
         <v>-3.81</v>
@@ -771,22 +771,22 @@
         <v>31.69</v>
       </c>
       <c r="H5" t="n">
-        <v>-38.58</v>
+        <v>-13.95</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-45.02</v>
+        <v>-20.39</v>
       </c>
       <c r="K5" t="n">
-        <v>-38.58</v>
+        <v>7.96</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>45.83</v>
       </c>
       <c r="M5" t="n">
-        <v>-50.96</v>
+        <v>-4.43</v>
       </c>
       <c r="N5" t="n">
         <v>-3.49</v>
@@ -1271,22 +1271,22 @@
         <v>83.06</v>
       </c>
       <c r="H12" t="n">
-        <v>13.12</v>
+        <v>13.29</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>9.23</v>
+        <v>9.4</v>
       </c>
       <c r="K12" t="n">
-        <v>13.12</v>
+        <v>13.32</v>
       </c>
       <c r="L12" t="n">
         <v>100</v>
       </c>
       <c r="M12" t="n">
-        <v>6.43</v>
+        <v>6.63</v>
       </c>
       <c r="N12" t="n">
         <v>-5.08</v>
@@ -1345,22 +1345,22 @@
         <v>41.37</v>
       </c>
       <c r="H13" t="n">
-        <v>9.529999999999999</v>
+        <v>4.2</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>4.12</v>
+        <v>-1.21</v>
       </c>
       <c r="K13" t="n">
-        <v>9.529999999999999</v>
+        <v>7.63</v>
       </c>
       <c r="L13" t="n">
-        <v>95.83</v>
+        <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>1.01</v>
+        <v>-0.88</v>
       </c>
       <c r="N13" t="n">
         <v>1.88</v>
@@ -1378,13 +1378,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1418,17 +1418,23 @@
       <c r="G14" t="n">
         <v>49.57</v>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+      <c r="H14" t="n">
+        <v>16.96</v>
+      </c>
+      <c r="I14" t="n">
+        <v>100</v>
+      </c>
+      <c r="J14" t="n">
+        <v>11.92</v>
+      </c>
       <c r="K14" t="n">
-        <v>3.98</v>
+        <v>16.96</v>
       </c>
       <c r="L14" t="n">
-        <v>43.48</v>
+        <v>95.83</v>
       </c>
       <c r="M14" t="n">
-        <v>0.24</v>
+        <v>7.82</v>
       </c>
       <c r="N14" t="n">
         <v>2.51</v>
@@ -1446,13 +1452,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1554,17 +1560,23 @@
       <c r="G16" t="n">
         <v>59.02</v>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="I16" t="n">
+        <v>30</v>
+      </c>
+      <c r="J16" t="n">
+        <v>-0.17</v>
+      </c>
       <c r="K16" t="n">
-        <v>6.64</v>
+        <v>2.01</v>
       </c>
       <c r="L16" t="n">
-        <v>82.61</v>
+        <v>12.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.38</v>
+        <v>-2.51</v>
       </c>
       <c r="N16" t="n">
         <v>-0.79</v>
@@ -1622,17 +1634,23 @@
       <c r="G17" t="n">
         <v>27.95</v>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>-7.14</v>
+      </c>
       <c r="K17" t="n">
-        <v>2.67</v>
+        <v>-2</v>
       </c>
       <c r="L17" t="n">
-        <v>73.91</v>
+        <v>29.17</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.58</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="N17" t="n">
         <v>-1.27</v>
@@ -1962,17 +1980,23 @@
       <c r="G22" t="n">
         <v>25.92</v>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I22" t="n">
+        <v>30</v>
+      </c>
+      <c r="J22" t="n">
+        <v>-1.36</v>
+      </c>
       <c r="K22" t="n">
-        <v>3.05</v>
+        <v>2.44</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>45.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0.72</v>
+        <v>0.11</v>
       </c>
       <c r="N22" t="n">
         <v>-1.18</v>
@@ -2031,22 +2055,22 @@
         <v>52.46</v>
       </c>
       <c r="H23" t="n">
-        <v>10.23</v>
+        <v>6.2</v>
       </c>
       <c r="I23" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J23" t="n">
-        <v>6.33</v>
+        <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>10.23</v>
+        <v>8.44</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>58.33</v>
       </c>
       <c r="M23" t="n">
-        <v>1.81</v>
+        <v>0.02</v>
       </c>
       <c r="N23" t="n">
         <v>-5.28</v>
@@ -2105,13 +2129,13 @@
         <v>46.21</v>
       </c>
       <c r="H24" t="n">
-        <v>1.6</v>
+        <v>7.93</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.36</v>
+        <v>3.97</v>
       </c>
       <c r="K24" t="n">
         <v>1.6</v>
@@ -2138,13 +2162,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2454,13 +2478,13 @@
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="n">
-        <v>5.03</v>
+        <v>-13.24</v>
       </c>
       <c r="L29" t="n">
-        <v>21.74</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1.2</v>
+        <v>-19.59</v>
       </c>
       <c r="N29" t="n">
         <v>4.05</v>
@@ -2587,22 +2611,22 @@
         <v>44.28</v>
       </c>
       <c r="H31" t="n">
-        <v>5.62</v>
+        <v>8.66</v>
       </c>
       <c r="I31" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="J31" t="n">
-        <v>2.27</v>
+        <v>5.31</v>
       </c>
       <c r="K31" t="n">
-        <v>5.62</v>
+        <v>11.28</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>3.84</v>
+        <v>9.49</v>
       </c>
       <c r="N31" t="n">
         <v>-3.92</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2905</v>
+        <v>1.3053</v>
       </c>
       <c r="D2" t="n">
-        <v>80.06</v>
+        <v>79.2</v>
       </c>
       <c r="E2" t="n">
-        <v>79.53</v>
+        <v>79.47</v>
       </c>
       <c r="F2" t="n">
-        <v>47.74</v>
+        <v>47.97</v>
       </c>
       <c r="G2" t="n">
-        <v>86.73</v>
+        <v>86.97</v>
       </c>
       <c r="H2" t="n">
-        <v>-107.87</v>
+        <v>-50.42</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>-110.5</v>
+        <v>-53.06</v>
       </c>
       <c r="K2" t="n">
-        <v>-107.87</v>
+        <v>-32.02</v>
       </c>
       <c r="L2" t="n">
-        <v>4.17</v>
+        <v>8.33</v>
       </c>
       <c r="M2" t="n">
-        <v>-114.28</v>
+        <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.39</v>
+        <v>-1.34</v>
       </c>
       <c r="O2" t="n">
-        <v>-9.050000000000001</v>
+        <v>-10.63</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.45</v>
+        <v>-15.84</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5458</v>
+        <v>4.538</v>
       </c>
       <c r="D3" t="n">
-        <v>24.24</v>
+        <v>23.66</v>
       </c>
       <c r="E3" t="n">
-        <v>63.41</v>
+        <v>57.94</v>
       </c>
       <c r="F3" t="n">
-        <v>38.28</v>
+        <v>38.45</v>
       </c>
       <c r="G3" t="n">
-        <v>52.93</v>
+        <v>53.67</v>
       </c>
       <c r="H3" t="n">
-        <v>10.53</v>
+        <v>11.02</v>
       </c>
       <c r="I3" t="n">
         <v>95</v>
       </c>
       <c r="J3" t="n">
-        <v>6.49</v>
+        <v>6.98</v>
       </c>
       <c r="K3" t="n">
-        <v>10.32</v>
+        <v>26.58</v>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>3.41</v>
+        <v>19.67</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.81</v>
+        <v>-6.31</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.1</v>
+        <v>-12.58</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.51</v>
+        <v>-2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,40 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6171</v>
+        <v>0.6218</v>
       </c>
       <c r="D4" t="n">
-        <v>29.85</v>
+        <v>29.42</v>
       </c>
       <c r="E4" t="n">
-        <v>75.66</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>19.55</v>
+        <v>19.11</v>
       </c>
       <c r="G4" t="n">
-        <v>38.8</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
+        <v>37.29</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="I4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" t="n">
+        <v>1.07</v>
+      </c>
       <c r="K4" t="n">
-        <v>4.66</v>
+        <v>3.67</v>
       </c>
       <c r="L4" t="n">
-        <v>62.5</v>
+        <v>58.33</v>
       </c>
       <c r="M4" t="n">
-        <v>1.63</v>
+        <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.09</v>
+        <v>-1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.65</v>
+        <v>-6.75</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.56</v>
+        <v>-12.12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -730,13 +736,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -756,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1944</v>
+        <v>5.1574</v>
       </c>
       <c r="D5" t="n">
-        <v>15.98</v>
+        <v>15.51</v>
       </c>
       <c r="E5" t="n">
-        <v>25.12</v>
+        <v>19.83</v>
       </c>
       <c r="F5" t="n">
-        <v>26.16</v>
+        <v>26.9</v>
       </c>
       <c r="G5" t="n">
-        <v>31.69</v>
+        <v>33.62</v>
       </c>
       <c r="H5" t="n">
-        <v>-13.95</v>
+        <v>10.68</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="J5" t="n">
-        <v>-20.39</v>
+        <v>4.24</v>
       </c>
       <c r="K5" t="n">
-        <v>7.96</v>
+        <v>8.67</v>
       </c>
       <c r="L5" t="n">
-        <v>45.83</v>
+        <v>50</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.43</v>
+        <v>-3.71</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.49</v>
+        <v>-5.31</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.5</v>
+        <v>-17.22</v>
       </c>
       <c r="P5" t="n">
-        <v>10.08</v>
+        <v>7.72</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -804,13 +810,13 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
         <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -830,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.2463</v>
+        <v>18.009</v>
       </c>
       <c r="D6" t="n">
-        <v>52.28</v>
+        <v>50.47</v>
       </c>
       <c r="E6" t="n">
-        <v>64.56999999999999</v>
+        <v>61.97</v>
       </c>
       <c r="F6" t="n">
-        <v>48.09</v>
+        <v>47.12</v>
       </c>
       <c r="G6" t="n">
-        <v>75.41</v>
+        <v>73.63</v>
       </c>
       <c r="H6" t="n">
-        <v>6.04</v>
+        <v>6.49</v>
       </c>
       <c r="I6" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J6" t="n">
-        <v>2.71</v>
+        <v>3.16</v>
       </c>
       <c r="K6" t="n">
-        <v>5.99</v>
+        <v>8.26</v>
       </c>
       <c r="L6" t="n">
-        <v>58.33</v>
+        <v>79.17</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.83</v>
+        <v>0.43</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.82</v>
+        <v>-10.09</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.18</v>
+        <v>-17.11</v>
       </c>
       <c r="P6" t="n">
-        <v>10.58</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -904,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6035</v>
+        <v>3.659</v>
       </c>
       <c r="D7" t="n">
-        <v>23.93</v>
+        <v>23.77</v>
       </c>
       <c r="E7" t="n">
-        <v>11.16</v>
+        <v>10.53</v>
       </c>
       <c r="F7" t="n">
-        <v>36.69</v>
+        <v>36.14</v>
       </c>
       <c r="G7" t="n">
-        <v>42.08</v>
+        <v>40.56</v>
       </c>
       <c r="H7" t="n">
-        <v>20.96</v>
+        <v>7.54</v>
       </c>
       <c r="I7" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J7" t="n">
-        <v>15.22</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>20.96</v>
+        <v>19.41</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>14.01</v>
+        <v>12.45</v>
       </c>
       <c r="N7" t="n">
-        <v>-5.85</v>
+        <v>-4.22</v>
       </c>
       <c r="O7" t="n">
-        <v>-8.460000000000001</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.73</v>
+        <v>-27.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -978,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2213</v>
+        <v>2.2628</v>
       </c>
       <c r="D8" t="n">
-        <v>14.65</v>
+        <v>14.59</v>
       </c>
       <c r="E8" t="n">
-        <v>54.5</v>
+        <v>51.59</v>
       </c>
       <c r="F8" t="n">
-        <v>25.36</v>
+        <v>25.63</v>
       </c>
       <c r="G8" t="n">
-        <v>32.16</v>
+        <v>34.01</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1005,13 +1011,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.16</v>
+        <v>-0.24</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.19</v>
+        <v>-3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.37</v>
+        <v>-7.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1046,28 +1052,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.4842</v>
+        <v>3.6178</v>
       </c>
       <c r="D9" t="n">
-        <v>20.8</v>
+        <v>21.12</v>
       </c>
       <c r="E9" t="n">
-        <v>21.71</v>
+        <v>28.81</v>
       </c>
       <c r="F9" t="n">
-        <v>31.53</v>
+        <v>30.46</v>
       </c>
       <c r="G9" t="n">
-        <v>62.61</v>
+        <v>57.96</v>
       </c>
       <c r="H9" t="n">
-        <v>2.95</v>
+        <v>-13.64</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.68</v>
+        <v>-18.28</v>
       </c>
       <c r="K9" t="n">
         <v>2.95</v>
@@ -1079,13 +1085,13 @@
         <v>-15.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.96</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.31</v>
+        <v>0.36</v>
       </c>
       <c r="P9" t="n">
-        <v>-19.8</v>
+        <v>-18.03</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1097,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1120,19 +1126,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.54</v>
+        <v>0.5395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.2</v>
+        <v>24.18</v>
       </c>
       <c r="E10" t="n">
-        <v>58.22</v>
+        <v>58.09</v>
       </c>
       <c r="F10" t="n">
-        <v>40.65</v>
+        <v>41.3</v>
       </c>
       <c r="G10" t="n">
-        <v>60.81</v>
+        <v>62.32</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1147,13 +1153,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4</v>
+        <v>-1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.25</v>
+        <v>-5.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.130000000000001</v>
+        <v>-10.29</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1188,23 +1194,29 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8197</v>
+        <v>0.8213</v>
       </c>
       <c r="D11" t="n">
-        <v>32.86</v>
+        <v>32.17</v>
       </c>
       <c r="E11" t="n">
-        <v>87.83</v>
+        <v>85.75</v>
       </c>
       <c r="F11" t="n">
-        <v>39.84</v>
+        <v>39.44</v>
       </c>
       <c r="G11" t="n">
-        <v>57.46</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>56.86</v>
+      </c>
+      <c r="H11" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="I11" t="n">
+        <v>95</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.33</v>
+      </c>
       <c r="K11" t="n">
         <v>0.85</v>
       </c>
@@ -1215,13 +1227,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.05</v>
+        <v>-4.15</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.65</v>
+        <v>-7.35</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.28</v>
+        <v>-12.67</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1230,13 +1242,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1256,19 +1268,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7323</v>
+        <v>6.7437</v>
       </c>
       <c r="D12" t="n">
-        <v>32.05</v>
+        <v>31.4</v>
       </c>
       <c r="E12" t="n">
-        <v>59.92</v>
+        <v>54.92</v>
       </c>
       <c r="F12" t="n">
-        <v>41.88</v>
+        <v>43.03</v>
       </c>
       <c r="G12" t="n">
-        <v>83.06</v>
+        <v>84.17</v>
       </c>
       <c r="H12" t="n">
         <v>13.29</v>
@@ -1289,13 +1301,13 @@
         <v>6.63</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.08</v>
+        <v>-4.63</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.15</v>
+        <v>-3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.33</v>
+        <v>-15.42</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1330,19 +1342,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6854</v>
+        <v>2.6982</v>
       </c>
       <c r="D13" t="n">
-        <v>22.02</v>
+        <v>21.63</v>
       </c>
       <c r="E13" t="n">
-        <v>60.85</v>
+        <v>57.63</v>
       </c>
       <c r="F13" t="n">
-        <v>26.62</v>
+        <v>27.16</v>
       </c>
       <c r="G13" t="n">
-        <v>41.37</v>
+        <v>43.76</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -1363,13 +1375,13 @@
         <v>-0.88</v>
       </c>
       <c r="N13" t="n">
-        <v>1.88</v>
+        <v>-1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>0.83</v>
+        <v>-1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>3.98</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1381,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1404,19 +1416,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0689</v>
+        <v>2.0532</v>
       </c>
       <c r="D14" t="n">
-        <v>17.18</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="n">
-        <v>82.02</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>20.86</v>
+        <v>22.02</v>
       </c>
       <c r="G14" t="n">
-        <v>49.57</v>
+        <v>54.99</v>
       </c>
       <c r="H14" t="n">
         <v>16.96</v>
@@ -1437,13 +1449,13 @@
         <v>7.82</v>
       </c>
       <c r="N14" t="n">
-        <v>2.51</v>
+        <v>-1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>1.04</v>
+        <v>-3</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.55</v>
+        <v>-7.86</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1455,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1478,19 +1490,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9199000000000001</v>
+        <v>0.9298</v>
       </c>
       <c r="D15" t="n">
-        <v>13.4</v>
+        <v>13.25</v>
       </c>
       <c r="E15" t="n">
-        <v>38.91</v>
+        <v>36.48</v>
       </c>
       <c r="F15" t="n">
-        <v>62.15</v>
+        <v>58.68</v>
       </c>
       <c r="G15" t="n">
-        <v>93.13</v>
+        <v>91.42</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1505,13 +1517,13 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.3</v>
+        <v>-6.27</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.98</v>
+        <v>-2.36</v>
       </c>
       <c r="P15" t="n">
-        <v>-19.9</v>
+        <v>-19.27</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1546,46 +1558,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8602</v>
+        <v>0.8581</v>
       </c>
       <c r="D16" t="n">
-        <v>32.58</v>
+        <v>31.79</v>
       </c>
       <c r="E16" t="n">
-        <v>43.72</v>
+        <v>39.5</v>
       </c>
       <c r="F16" t="n">
-        <v>35.5</v>
+        <v>36.18</v>
       </c>
       <c r="G16" t="n">
-        <v>59.02</v>
+        <v>60.45</v>
       </c>
       <c r="H16" t="n">
-        <v>1.68</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.17</v>
+        <v>0.21</v>
       </c>
       <c r="K16" t="n">
-        <v>2.01</v>
+        <v>-0.71</v>
       </c>
       <c r="L16" t="n">
-        <v>12.5</v>
+        <v>4.17</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.51</v>
+        <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.79</v>
+        <v>-2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>-8.27</v>
+        <v>-10.02</v>
       </c>
       <c r="P16" t="n">
-        <v>-25.94</v>
+        <v>-25.53</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1594,13 +1606,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1620,19 +1632,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5249</v>
+        <v>0.5212</v>
       </c>
       <c r="D17" t="n">
-        <v>41.1</v>
+        <v>39.91</v>
       </c>
       <c r="E17" t="n">
-        <v>22.56</v>
+        <v>20.6</v>
       </c>
       <c r="F17" t="n">
-        <v>36.67</v>
+        <v>35.78</v>
       </c>
       <c r="G17" t="n">
-        <v>27.95</v>
+        <v>26.52</v>
       </c>
       <c r="H17" t="n">
         <v>-2</v>
@@ -1653,13 +1665,13 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.27</v>
+        <v>-3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.72</v>
+        <v>-9.81</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.18</v>
+        <v>-21</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1694,19 +1706,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.9669</v>
+        <v>6.0873</v>
       </c>
       <c r="D18" t="n">
-        <v>6.52</v>
+        <v>6.5</v>
       </c>
       <c r="E18" t="n">
-        <v>87.29000000000001</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.11</v>
+        <v>12.77</v>
       </c>
       <c r="G18" t="n">
-        <v>71.66</v>
+        <v>76.05</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1721,13 +1733,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>1.7</v>
+        <v>0.43</v>
       </c>
       <c r="O18" t="n">
-        <v>2.96</v>
+        <v>2.52</v>
       </c>
       <c r="P18" t="n">
-        <v>6.98</v>
+        <v>5.14</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1762,19 +1774,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1401</v>
+        <v>5.242</v>
       </c>
       <c r="D19" t="n">
-        <v>8.82</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>13.36</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>9.68</v>
+        <v>13.57</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1789,19 +1801,19 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.05</v>
+        <v>0.17</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.09</v>
+        <v>-6.41</v>
       </c>
       <c r="P19" t="n">
-        <v>-15.1</v>
+        <v>-14.18</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -1810,7 +1822,7 @@
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1830,19 +1842,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2071</v>
+        <v>0.2058</v>
       </c>
       <c r="D20" t="n">
-        <v>75.84999999999999</v>
+        <v>73.69</v>
       </c>
       <c r="E20" t="n">
-        <v>89.92</v>
+        <v>89.47</v>
       </c>
       <c r="F20" t="n">
-        <v>52.75</v>
+        <v>52.35</v>
       </c>
       <c r="G20" t="n">
-        <v>87.59</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1857,13 +1869,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.32</v>
+        <v>-5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.74</v>
+        <v>-11.01</v>
       </c>
       <c r="P20" t="n">
-        <v>1.57</v>
+        <v>0.83</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1898,19 +1910,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8875999999999999</v>
+        <v>0.889</v>
       </c>
       <c r="D21" t="n">
-        <v>35.06</v>
+        <v>34.35</v>
       </c>
       <c r="E21" t="n">
-        <v>91.16</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>41.37</v>
+        <v>40.58</v>
       </c>
       <c r="G21" t="n">
-        <v>73.22</v>
+        <v>71.84</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1925,13 +1937,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.11</v>
+        <v>-7.19</v>
       </c>
       <c r="O21" t="n">
-        <v>-7.55</v>
+        <v>-9.91</v>
       </c>
       <c r="P21" t="n">
-        <v>4.68</v>
+        <v>3.58</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1966,19 +1978,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.369</v>
+        <v>1.3789</v>
       </c>
       <c r="D22" t="n">
-        <v>14.41</v>
+        <v>14.2</v>
       </c>
       <c r="E22" t="n">
-        <v>93.09999999999999</v>
+        <v>92.56</v>
       </c>
       <c r="F22" t="n">
-        <v>23.74</v>
+        <v>23.75</v>
       </c>
       <c r="G22" t="n">
-        <v>25.92</v>
+        <v>25.98</v>
       </c>
       <c r="H22" t="n">
         <v>1.52</v>
@@ -1999,13 +2011,13 @@
         <v>0.11</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.18</v>
+        <v>-2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>-5</v>
+        <v>-6.39</v>
       </c>
       <c r="P22" t="n">
-        <v>-9.51</v>
+        <v>-10.61</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2040,19 +2052,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.959</v>
+        <v>7.9605</v>
       </c>
       <c r="D23" t="n">
-        <v>25.98</v>
+        <v>25.43</v>
       </c>
       <c r="E23" t="n">
-        <v>27.29</v>
+        <v>25.41</v>
       </c>
       <c r="F23" t="n">
-        <v>38.45</v>
+        <v>39.25</v>
       </c>
       <c r="G23" t="n">
-        <v>52.46</v>
+        <v>53.82</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
@@ -2073,13 +2085,13 @@
         <v>0.02</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.28</v>
+        <v>-6.86</v>
       </c>
       <c r="O23" t="n">
-        <v>-10.94</v>
+        <v>-13.07</v>
       </c>
       <c r="P23" t="n">
-        <v>-16.93</v>
+        <v>-19.07</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2114,46 +2126,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.9472</v>
+        <v>5.8869</v>
       </c>
       <c r="D24" t="n">
-        <v>38.23</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>84.65000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>34.77</v>
+        <v>35.01</v>
       </c>
       <c r="G24" t="n">
-        <v>46.21</v>
+        <v>46.8</v>
       </c>
       <c r="H24" t="n">
-        <v>7.93</v>
+        <v>1.6</v>
       </c>
       <c r="I24" t="n">
-        <v>90</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>3.97</v>
+        <v>-2.36</v>
       </c>
       <c r="K24" t="n">
-        <v>1.6</v>
+        <v>0.64</v>
       </c>
       <c r="L24" t="n">
-        <v>8.33</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.74</v>
+        <v>-4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.04</v>
+        <v>-7.84</v>
       </c>
       <c r="O24" t="n">
-        <v>-13.59</v>
+        <v>-16.42</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.2</v>
+        <v>-9.57</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2162,13 +2174,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2188,19 +2200,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7005</v>
+        <v>2.7304</v>
       </c>
       <c r="D25" t="n">
-        <v>56.15</v>
+        <v>55.52</v>
       </c>
       <c r="E25" t="n">
-        <v>39.53</v>
+        <v>36.48</v>
       </c>
       <c r="F25" t="n">
-        <v>32.97</v>
+        <v>34.91</v>
       </c>
       <c r="G25" t="n">
-        <v>46.92</v>
+        <v>52.42</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2215,13 +2227,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.92</v>
+        <v>-3.57</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.09</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.58</v>
+        <v>-8.74</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2256,40 +2268,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.8226</v>
+        <v>4.7916</v>
       </c>
       <c r="D26" t="n">
-        <v>58.51</v>
+        <v>56.86</v>
       </c>
       <c r="E26" t="n">
-        <v>44.42</v>
+        <v>40.59</v>
       </c>
       <c r="F26" t="n">
-        <v>34.08</v>
+        <v>34.29</v>
       </c>
       <c r="G26" t="n">
-        <v>22.95</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+        <v>23.71</v>
+      </c>
+      <c r="H26" t="n">
+        <v>12.66</v>
+      </c>
+      <c r="I26" t="n">
+        <v>100</v>
+      </c>
+      <c r="J26" t="n">
+        <v>12.41</v>
+      </c>
       <c r="K26" t="n">
-        <v>1.84</v>
+        <v>14.85</v>
       </c>
       <c r="L26" t="n">
-        <v>60.87</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>0.71</v>
+        <v>12.94</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.99</v>
+        <v>-2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.85</v>
+        <v>-8.5</v>
       </c>
       <c r="P26" t="n">
-        <v>-26.64</v>
+        <v>-26.98</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2298,13 +2316,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2324,40 +2342,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.891</v>
+        <v>1.8515</v>
       </c>
       <c r="D27" t="n">
-        <v>36.07</v>
+        <v>34.55</v>
       </c>
       <c r="E27" t="n">
-        <v>51.63</v>
+        <v>43.61</v>
       </c>
       <c r="F27" t="n">
-        <v>54.68</v>
+        <v>59.16</v>
       </c>
       <c r="G27" t="n">
-        <v>66.51000000000001</v>
-      </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+        <v>72.84999999999999</v>
+      </c>
+      <c r="H27" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="I27" t="n">
+        <v>70</v>
+      </c>
+      <c r="J27" t="n">
+        <v>1.02</v>
+      </c>
       <c r="K27" t="n">
-        <v>5.28</v>
+        <v>3.24</v>
       </c>
       <c r="L27" t="n">
-        <v>69.56999999999999</v>
+        <v>45.83</v>
       </c>
       <c r="M27" t="n">
-        <v>2.16</v>
+        <v>-0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>5.76</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.61</v>
+        <v>-4.06</v>
       </c>
       <c r="P27" t="n">
-        <v>-18.48</v>
+        <v>-21.34</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2366,13 +2390,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2392,19 +2416,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.4136</v>
+        <v>5.2828</v>
       </c>
       <c r="D28" t="n">
-        <v>43.44</v>
+        <v>41.46</v>
       </c>
       <c r="E28" t="n">
-        <v>80.16</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>37.45</v>
+        <v>37.23</v>
       </c>
       <c r="G28" t="n">
-        <v>50.04</v>
+        <v>49.38</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2419,13 +2443,13 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-11.02</v>
+        <v>-11.63</v>
       </c>
       <c r="O28" t="n">
-        <v>-16.73</v>
+        <v>-20.99</v>
       </c>
       <c r="P28" t="n">
-        <v>23.51</v>
+        <v>17.9</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2460,19 +2484,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0745</v>
+        <v>1.0833</v>
       </c>
       <c r="D29" t="n">
-        <v>19.11</v>
+        <v>18.84</v>
       </c>
       <c r="E29" t="n">
-        <v>86.93000000000001</v>
+        <v>85.91</v>
       </c>
       <c r="F29" t="n">
-        <v>38.42</v>
+        <v>39.04</v>
       </c>
       <c r="G29" t="n">
-        <v>69.67</v>
+        <v>71.08</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2487,13 +2511,13 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>4.05</v>
+        <v>1.43</v>
       </c>
       <c r="O29" t="n">
-        <v>3.07</v>
+        <v>-1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>27.8</v>
+        <v>24.62</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2505,10 +2529,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2528,19 +2552,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2602</v>
+        <v>1.2659</v>
       </c>
       <c r="D30" t="n">
-        <v>16.9</v>
+        <v>16.6</v>
       </c>
       <c r="E30" t="n">
-        <v>76.53</v>
+        <v>72.77</v>
       </c>
       <c r="F30" t="n">
-        <v>23.89</v>
+        <v>24.63</v>
       </c>
       <c r="G30" t="n">
-        <v>52.34</v>
+        <v>55.06</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2555,13 +2579,13 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.21</v>
+        <v>-1.02</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.5</v>
+        <v>-5.45</v>
       </c>
       <c r="P30" t="n">
-        <v>23.87</v>
+        <v>22.45</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2596,19 +2620,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8086</v>
+        <v>0.8061</v>
       </c>
       <c r="D31" t="n">
-        <v>24.02</v>
+        <v>23.43</v>
       </c>
       <c r="E31" t="n">
-        <v>71.28</v>
+        <v>67.78</v>
       </c>
       <c r="F31" t="n">
-        <v>27.69</v>
+        <v>27.98</v>
       </c>
       <c r="G31" t="n">
-        <v>44.28</v>
+        <v>45.37</v>
       </c>
       <c r="H31" t="n">
         <v>8.66</v>
@@ -2629,13 +2653,13 @@
         <v>9.49</v>
       </c>
       <c r="N31" t="n">
-        <v>-3.92</v>
+        <v>-6.38</v>
       </c>
       <c r="O31" t="n">
-        <v>-8.300000000000001</v>
+        <v>-10.39</v>
       </c>
       <c r="P31" t="n">
-        <v>-7.1</v>
+        <v>-9.34</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2670,19 +2694,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1979</v>
+        <v>0.2019</v>
       </c>
       <c r="D32" t="n">
-        <v>28.3</v>
+        <v>28.24</v>
       </c>
       <c r="E32" t="n">
-        <v>6.71</v>
+        <v>6.36</v>
       </c>
       <c r="F32" t="n">
-        <v>40.13</v>
+        <v>40.3</v>
       </c>
       <c r="G32" t="n">
-        <v>64.3</v>
+        <v>65.02</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2697,13 +2721,13 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.25</v>
+        <v>-1.12</v>
       </c>
       <c r="O32" t="n">
-        <v>-3.15</v>
+        <v>-2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>-28.69</v>
+        <v>-27.67</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3053</v>
+        <v>1.2152</v>
       </c>
       <c r="D2" t="n">
-        <v>79.2</v>
+        <v>42.69</v>
       </c>
       <c r="E2" t="n">
-        <v>79.47</v>
+        <v>58.43</v>
       </c>
       <c r="F2" t="n">
-        <v>47.97</v>
+        <v>57.74</v>
       </c>
       <c r="G2" t="n">
-        <v>86.97</v>
+        <v>96.41</v>
       </c>
       <c r="H2" t="n">
         <v>-50.42</v>
@@ -573,28 +573,28 @@
         <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.34</v>
+        <v>6.46</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.63</v>
+        <v>7.93</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.84</v>
+        <v>-7.22</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.538</v>
+        <v>4.657</v>
       </c>
       <c r="D3" t="n">
-        <v>23.66</v>
+        <v>30.24</v>
       </c>
       <c r="E3" t="n">
-        <v>57.94</v>
+        <v>89.39</v>
       </c>
       <c r="F3" t="n">
-        <v>38.45</v>
+        <v>44.64</v>
       </c>
       <c r="G3" t="n">
-        <v>53.67</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="H3" t="n">
         <v>11.02</v>
@@ -647,13 +647,13 @@
         <v>19.67</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.31</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.58</v>
+        <v>8.91</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.43</v>
+        <v>17.02</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6218</v>
+        <v>0.591</v>
       </c>
       <c r="D4" t="n">
-        <v>29.42</v>
+        <v>29.91</v>
       </c>
       <c r="E4" t="n">
-        <v>73.81999999999999</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>19.11</v>
+        <v>20.73</v>
       </c>
       <c r="G4" t="n">
-        <v>37.29</v>
+        <v>41.95</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.66</v>
+        <v>3.23</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.75</v>
+        <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.12</v>
+        <v>-7.91</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1574</v>
+        <v>5.6791</v>
       </c>
       <c r="D5" t="n">
-        <v>15.51</v>
+        <v>22.51</v>
       </c>
       <c r="E5" t="n">
-        <v>19.83</v>
+        <v>64.77</v>
       </c>
       <c r="F5" t="n">
-        <v>26.9</v>
+        <v>48.93</v>
       </c>
       <c r="G5" t="n">
-        <v>33.62</v>
+        <v>77.27</v>
       </c>
       <c r="H5" t="n">
         <v>10.68</v>
@@ -795,13 +795,13 @@
         <v>-3.71</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.31</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.22</v>
+        <v>11.35</v>
       </c>
       <c r="P5" t="n">
-        <v>7.72</v>
+        <v>51.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.009</v>
+        <v>19.8026</v>
       </c>
       <c r="D6" t="n">
-        <v>50.47</v>
+        <v>80.47</v>
       </c>
       <c r="E6" t="n">
-        <v>61.97</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>47.12</v>
+        <v>55.94</v>
       </c>
       <c r="G6" t="n">
-        <v>73.63</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>6.49</v>
@@ -869,16 +869,16 @@
         <v>0.43</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.09</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.11</v>
+        <v>10.24</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>69.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.659</v>
+        <v>3.5901</v>
       </c>
       <c r="D7" t="n">
-        <v>23.77</v>
+        <v>24.97</v>
       </c>
       <c r="E7" t="n">
-        <v>10.53</v>
+        <v>19.79</v>
       </c>
       <c r="F7" t="n">
-        <v>36.14</v>
+        <v>27.86</v>
       </c>
       <c r="G7" t="n">
-        <v>40.56</v>
+        <v>17.3</v>
       </c>
       <c r="H7" t="n">
         <v>7.54</v>
@@ -943,13 +943,13 @@
         <v>12.45</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.22</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.029999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.92</v>
+        <v>-11.67</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2628</v>
+        <v>2.0936</v>
       </c>
       <c r="D8" t="n">
-        <v>14.59</v>
+        <v>14.85</v>
       </c>
       <c r="E8" t="n">
-        <v>51.59</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>25.63</v>
+        <v>28.88</v>
       </c>
       <c r="G8" t="n">
-        <v>34.01</v>
+        <v>48.8</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.24</v>
+        <v>0.65</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.94</v>
+        <v>-1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.78</v>
+        <v>-1.36</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6178</v>
+        <v>3.2137</v>
       </c>
       <c r="D9" t="n">
-        <v>21.12</v>
+        <v>19.98</v>
       </c>
       <c r="E9" t="n">
-        <v>28.81</v>
+        <v>10.61</v>
       </c>
       <c r="F9" t="n">
-        <v>30.46</v>
+        <v>38.84</v>
       </c>
       <c r="G9" t="n">
-        <v>57.96</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="H9" t="n">
         <v>-13.64</v>
@@ -1085,13 +1085,13 @@
         <v>-15.08</v>
       </c>
       <c r="N9" t="n">
-        <v>2.57</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>0.36</v>
+        <v>-4.04</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.03</v>
+        <v>-17.26</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1126,19 +1126,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5395</v>
+        <v>0.512</v>
       </c>
       <c r="D10" t="n">
-        <v>24.18</v>
+        <v>24.93</v>
       </c>
       <c r="E10" t="n">
-        <v>58.09</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>41.3</v>
+        <v>41.31</v>
       </c>
       <c r="G10" t="n">
-        <v>62.32</v>
+        <v>62.76</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.95</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.69</v>
+        <v>5.71</v>
       </c>
       <c r="P10" t="n">
-        <v>-10.29</v>
+        <v>-3.95</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1171,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8213</v>
+        <v>0.7734</v>
       </c>
       <c r="D11" t="n">
-        <v>32.17</v>
+        <v>32.45</v>
       </c>
       <c r="E11" t="n">
-        <v>85.75</v>
+        <v>88.92</v>
       </c>
       <c r="F11" t="n">
-        <v>39.44</v>
+        <v>33.55</v>
       </c>
       <c r="G11" t="n">
-        <v>56.86</v>
+        <v>46.73</v>
       </c>
       <c r="H11" t="n">
         <v>9.199999999999999</v>
@@ -1227,13 +1227,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.15</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.35</v>
+        <v>5.76</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.67</v>
+        <v>-5.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1268,19 +1268,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7437</v>
+        <v>6.3566</v>
       </c>
       <c r="D12" t="n">
-        <v>31.4</v>
+        <v>33.76</v>
       </c>
       <c r="E12" t="n">
-        <v>54.92</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>43.03</v>
+        <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>84.17</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="H12" t="n">
         <v>13.29</v>
@@ -1301,19 +1301,19 @@
         <v>6.63</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.63</v>
+        <v>-1.43</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.85</v>
+        <v>4.22</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.42</v>
+        <v>-11.45</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6982</v>
+        <v>2.4189</v>
       </c>
       <c r="D13" t="n">
-        <v>21.63</v>
+        <v>20.98</v>
       </c>
       <c r="E13" t="n">
-        <v>57.63</v>
+        <v>54.24</v>
       </c>
       <c r="F13" t="n">
-        <v>27.16</v>
+        <v>28.8</v>
       </c>
       <c r="G13" t="n">
-        <v>43.76</v>
+        <v>48.72</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -1375,13 +1375,13 @@
         <v>-0.88</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.53</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.73</v>
+        <v>-1.79</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>4.06</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0532</v>
+        <v>1.8702</v>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>17.06</v>
       </c>
       <c r="E14" t="n">
-        <v>73.51000000000001</v>
+        <v>79.81</v>
       </c>
       <c r="F14" t="n">
-        <v>22.02</v>
+        <v>21.02</v>
       </c>
       <c r="G14" t="n">
-        <v>54.99</v>
+        <v>50.64</v>
       </c>
       <c r="H14" t="n">
         <v>16.96</v>
@@ -1449,13 +1449,13 @@
         <v>7.82</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.65</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>-3</v>
+        <v>0.42</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.86</v>
+        <v>-5.79</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1490,19 +1490,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9298</v>
+        <v>0.8423</v>
       </c>
       <c r="D15" t="n">
-        <v>13.25</v>
+        <v>20.13</v>
       </c>
       <c r="E15" t="n">
-        <v>36.48</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>58.68</v>
+        <v>35.1</v>
       </c>
       <c r="G15" t="n">
-        <v>91.42</v>
+        <v>57.89</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1517,28 +1517,28 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.27</v>
+        <v>2.59</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.36</v>
+        <v>4.7</v>
       </c>
       <c r="P15" t="n">
-        <v>-19.27</v>
+        <v>-11.88</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8581</v>
+        <v>0.8192</v>
       </c>
       <c r="D16" t="n">
-        <v>31.79</v>
+        <v>34.96</v>
       </c>
       <c r="E16" t="n">
-        <v>39.5</v>
+        <v>58.75</v>
       </c>
       <c r="F16" t="n">
-        <v>36.18</v>
+        <v>34.91</v>
       </c>
       <c r="G16" t="n">
-        <v>60.45</v>
+        <v>58.61</v>
       </c>
       <c r="H16" t="n">
         <v>2.06</v>
@@ -1591,13 +1591,13 @@
         <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.12</v>
+        <v>3.41</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.02</v>
+        <v>1.06</v>
       </c>
       <c r="P16" t="n">
-        <v>-25.53</v>
+        <v>-17.46</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1632,19 +1632,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5212</v>
+        <v>0.4965</v>
       </c>
       <c r="D17" t="n">
-        <v>39.91</v>
+        <v>40.41</v>
       </c>
       <c r="E17" t="n">
-        <v>20.6</v>
+        <v>21.69</v>
       </c>
       <c r="F17" t="n">
-        <v>35.78</v>
+        <v>36.99</v>
       </c>
       <c r="G17" t="n">
-        <v>26.52</v>
+        <v>28.87</v>
       </c>
       <c r="H17" t="n">
         <v>-2</v>
@@ -1665,13 +1665,13 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.5</v>
+        <v>3.32</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.81</v>
+        <v>4.96</v>
       </c>
       <c r="P17" t="n">
-        <v>-21</v>
+        <v>-13.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.0873</v>
+        <v>5.1334</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>6.17</v>
       </c>
       <c r="E18" t="n">
-        <v>86.68000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="F18" t="n">
-        <v>12.77</v>
+        <v>12.28</v>
       </c>
       <c r="G18" t="n">
-        <v>76.05</v>
+        <v>73.44</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1733,13 +1733,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>2.52</v>
+        <v>-1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>5.14</v>
+        <v>-7.55</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1774,19 +1774,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.242</v>
+        <v>5.011</v>
       </c>
       <c r="D19" t="n">
-        <v>8.800000000000001</v>
+        <v>11.58</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>17.92</v>
       </c>
       <c r="G19" t="n">
-        <v>13.57</v>
+        <v>38.2</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.41</v>
+        <v>-0.1</v>
       </c>
       <c r="P19" t="n">
-        <v>-14.18</v>
+        <v>-11.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1842,19 +1842,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2058</v>
+        <v>0.2021</v>
       </c>
       <c r="D20" t="n">
-        <v>73.69</v>
+        <v>93.7</v>
       </c>
       <c r="E20" t="n">
-        <v>89.47</v>
+        <v>93.98</v>
       </c>
       <c r="F20" t="n">
-        <v>52.35</v>
+        <v>55.43</v>
       </c>
       <c r="G20" t="n">
-        <v>87.29000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1869,19 +1869,19 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.7</v>
+        <v>-0.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.01</v>
+        <v>10.74</v>
       </c>
       <c r="P20" t="n">
-        <v>0.83</v>
+        <v>34.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.889</v>
+        <v>0.883</v>
       </c>
       <c r="D21" t="n">
-        <v>34.35</v>
+        <v>36.03</v>
       </c>
       <c r="E21" t="n">
-        <v>90.31999999999999</v>
+        <v>94.14</v>
       </c>
       <c r="F21" t="n">
-        <v>40.58</v>
+        <v>35.75</v>
       </c>
       <c r="G21" t="n">
-        <v>71.84</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.19</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.91</v>
+        <v>6.86</v>
       </c>
       <c r="P21" t="n">
-        <v>3.58</v>
+        <v>21.4</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1955,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3789</v>
+        <v>1.2957</v>
       </c>
       <c r="D22" t="n">
-        <v>14.2</v>
+        <v>13.42</v>
       </c>
       <c r="E22" t="n">
-        <v>92.56</v>
+        <v>90.42</v>
       </c>
       <c r="F22" t="n">
-        <v>23.75</v>
+        <v>29.6</v>
       </c>
       <c r="G22" t="n">
-        <v>25.98</v>
+        <v>47.77</v>
       </c>
       <c r="H22" t="n">
         <v>1.52</v>
@@ -2011,13 +2011,13 @@
         <v>0.11</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.15</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.39</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>-10.61</v>
+        <v>-3.59</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2052,19 +2052,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.9605</v>
+        <v>8.4611</v>
       </c>
       <c r="D23" t="n">
-        <v>25.43</v>
+        <v>31.78</v>
       </c>
       <c r="E23" t="n">
-        <v>25.41</v>
+        <v>49.01</v>
       </c>
       <c r="F23" t="n">
-        <v>39.25</v>
+        <v>39.05</v>
       </c>
       <c r="G23" t="n">
-        <v>53.82</v>
+        <v>52.39</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
@@ -2085,13 +2085,13 @@
         <v>0.02</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.86</v>
+        <v>-2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>-13.07</v>
+        <v>0.67</v>
       </c>
       <c r="P23" t="n">
-        <v>-19.07</v>
+        <v>19.13</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2126,19 +2126,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.8869</v>
+        <v>6.1859</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>43.64</v>
       </c>
       <c r="E24" t="n">
-        <v>80.70999999999999</v>
+        <v>93.98</v>
       </c>
       <c r="F24" t="n">
-        <v>35.01</v>
+        <v>39.48</v>
       </c>
       <c r="G24" t="n">
-        <v>46.8</v>
+        <v>54.55</v>
       </c>
       <c r="H24" t="n">
         <v>1.6</v>
@@ -2159,16 +2159,16 @@
         <v>-4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>-7.84</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.42</v>
+        <v>8.4</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.57</v>
+        <v>19.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2200,19 +2200,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7304</v>
+        <v>2.6109</v>
       </c>
       <c r="D25" t="n">
-        <v>55.52</v>
+        <v>59.69</v>
       </c>
       <c r="E25" t="n">
-        <v>36.48</v>
+        <v>50.75</v>
       </c>
       <c r="F25" t="n">
-        <v>34.91</v>
+        <v>31.28</v>
       </c>
       <c r="G25" t="n">
-        <v>52.42</v>
+        <v>44.1</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2227,13 +2227,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.57</v>
+        <v>1.72</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.279999999999999</v>
+        <v>3.28</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.74</v>
+        <v>-8.06</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7916</v>
+        <v>4.7258</v>
       </c>
       <c r="D26" t="n">
-        <v>56.86</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>40.59</v>
+        <v>63.97</v>
       </c>
       <c r="F26" t="n">
-        <v>34.29</v>
+        <v>39.09</v>
       </c>
       <c r="G26" t="n">
-        <v>23.71</v>
+        <v>33.57</v>
       </c>
       <c r="H26" t="n">
         <v>12.66</v>
@@ -2301,13 +2301,13 @@
         <v>12.94</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.8</v>
+        <v>1.38</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.5</v>
+        <v>0.41</v>
       </c>
       <c r="P26" t="n">
-        <v>-26.98</v>
+        <v>-13.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8515</v>
+        <v>1.6308</v>
       </c>
       <c r="D27" t="n">
-        <v>34.55</v>
+        <v>34.73</v>
       </c>
       <c r="E27" t="n">
-        <v>43.61</v>
+        <v>44.73</v>
       </c>
       <c r="F27" t="n">
-        <v>59.16</v>
+        <v>35.42</v>
       </c>
       <c r="G27" t="n">
-        <v>72.84999999999999</v>
+        <v>29.59</v>
       </c>
       <c r="H27" t="n">
         <v>3.24</v>
@@ -2375,13 +2375,13 @@
         <v>-0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>3.83</v>
+        <v>0.22</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.06</v>
+        <v>-2.94</v>
       </c>
       <c r="P27" t="n">
-        <v>-21.34</v>
+        <v>-14.27</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2828</v>
+        <v>5.8119</v>
       </c>
       <c r="D28" t="n">
-        <v>41.46</v>
+        <v>57.04</v>
       </c>
       <c r="E28" t="n">
-        <v>78.54000000000001</v>
+        <v>93.27</v>
       </c>
       <c r="F28" t="n">
-        <v>37.23</v>
+        <v>49.14</v>
       </c>
       <c r="G28" t="n">
-        <v>49.38</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2443,16 +2443,16 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-11.63</v>
+        <v>-3.13</v>
       </c>
       <c r="O28" t="n">
-        <v>-20.99</v>
+        <v>10.13</v>
       </c>
       <c r="P28" t="n">
-        <v>17.9</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2484,19 +2484,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0833</v>
+        <v>0.9446</v>
       </c>
       <c r="D29" t="n">
-        <v>18.84</v>
+        <v>22.77</v>
       </c>
       <c r="E29" t="n">
-        <v>85.91</v>
+        <v>98.59</v>
       </c>
       <c r="F29" t="n">
-        <v>39.04</v>
+        <v>45.46</v>
       </c>
       <c r="G29" t="n">
-        <v>71.08</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2511,16 +2511,16 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1.43</v>
+        <v>5.13</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.32</v>
+        <v>9.9</v>
       </c>
       <c r="P29" t="n">
-        <v>24.62</v>
+        <v>31.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>-1</v>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2659</v>
+        <v>1.1858</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6</v>
+        <v>21.36</v>
       </c>
       <c r="E30" t="n">
-        <v>72.77</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>24.63</v>
+        <v>28.39</v>
       </c>
       <c r="G30" t="n">
-        <v>55.06</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2579,16 +2579,16 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.02</v>
+        <v>3.23</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.45</v>
+        <v>8.75</v>
       </c>
       <c r="P30" t="n">
-        <v>22.45</v>
+        <v>25.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>-1</v>
@@ -2620,19 +2620,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8061</v>
+        <v>0.8045</v>
       </c>
       <c r="D31" t="n">
-        <v>23.43</v>
+        <v>26.31</v>
       </c>
       <c r="E31" t="n">
-        <v>67.78</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>27.98</v>
+        <v>30.74</v>
       </c>
       <c r="G31" t="n">
-        <v>45.37</v>
+        <v>51.11</v>
       </c>
       <c r="H31" t="n">
         <v>8.66</v>
@@ -2653,13 +2653,13 @@
         <v>9.49</v>
       </c>
       <c r="N31" t="n">
-        <v>-6.38</v>
+        <v>1.98</v>
       </c>
       <c r="O31" t="n">
-        <v>-10.39</v>
+        <v>6.79</v>
       </c>
       <c r="P31" t="n">
-        <v>-9.34</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2019</v>
+        <v>0.1823</v>
       </c>
       <c r="D32" t="n">
-        <v>28.24</v>
+        <v>30.39</v>
       </c>
       <c r="E32" t="n">
-        <v>6.36</v>
+        <v>16.55</v>
       </c>
       <c r="F32" t="n">
-        <v>40.3</v>
+        <v>38.72</v>
       </c>
       <c r="G32" t="n">
-        <v>65.02</v>
+        <v>61.58</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2721,16 +2721,16 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.12</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.01</v>
+        <v>-2.54</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.67</v>
+        <v>-27.31</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2152</v>
+        <v>1.3053</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>79.2</v>
       </c>
       <c r="E2" t="n">
-        <v>58.43</v>
+        <v>79.47</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74</v>
+        <v>47.97</v>
       </c>
       <c r="G2" t="n">
-        <v>96.41</v>
+        <v>86.97</v>
       </c>
       <c r="H2" t="n">
         <v>-50.42</v>
@@ -573,28 +573,28 @@
         <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>6.46</v>
+        <v>-1.34</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93</v>
+        <v>-10.63</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.22</v>
+        <v>-15.84</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.657</v>
+        <v>4.538</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24</v>
+        <v>23.66</v>
       </c>
       <c r="E3" t="n">
-        <v>89.39</v>
+        <v>57.94</v>
       </c>
       <c r="F3" t="n">
-        <v>44.64</v>
+        <v>38.45</v>
       </c>
       <c r="G3" t="n">
-        <v>70.65000000000001</v>
+        <v>53.67</v>
       </c>
       <c r="H3" t="n">
         <v>11.02</v>
@@ -647,13 +647,13 @@
         <v>19.67</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>-6.31</v>
       </c>
       <c r="O3" t="n">
-        <v>8.91</v>
+        <v>-12.58</v>
       </c>
       <c r="P3" t="n">
-        <v>17.02</v>
+        <v>-2.43</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.591</v>
+        <v>0.6218</v>
       </c>
       <c r="D4" t="n">
-        <v>29.91</v>
+        <v>29.42</v>
       </c>
       <c r="E4" t="n">
-        <v>77.04000000000001</v>
+        <v>73.81999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>20.73</v>
+        <v>19.11</v>
       </c>
       <c r="G4" t="n">
-        <v>41.95</v>
+        <v>37.29</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>-1.66</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>-6.75</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.91</v>
+        <v>-12.12</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -762,19 +762,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6791</v>
+        <v>5.1574</v>
       </c>
       <c r="D5" t="n">
-        <v>22.51</v>
+        <v>15.51</v>
       </c>
       <c r="E5" t="n">
-        <v>64.77</v>
+        <v>19.83</v>
       </c>
       <c r="F5" t="n">
-        <v>48.93</v>
+        <v>26.9</v>
       </c>
       <c r="G5" t="n">
-        <v>77.27</v>
+        <v>33.62</v>
       </c>
       <c r="H5" t="n">
         <v>10.68</v>
@@ -795,13 +795,13 @@
         <v>-3.71</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>-5.31</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35</v>
+        <v>-17.22</v>
       </c>
       <c r="P5" t="n">
-        <v>51.35</v>
+        <v>7.72</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -836,19 +836,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8026</v>
+        <v>18.009</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47</v>
+        <v>50.47</v>
       </c>
       <c r="E6" t="n">
-        <v>95.95999999999999</v>
+        <v>61.97</v>
       </c>
       <c r="F6" t="n">
-        <v>55.94</v>
+        <v>47.12</v>
       </c>
       <c r="G6" t="n">
-        <v>82.93000000000001</v>
+        <v>73.63</v>
       </c>
       <c r="H6" t="n">
         <v>6.49</v>
@@ -869,16 +869,16 @@
         <v>0.43</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-10.09</v>
       </c>
       <c r="O6" t="n">
-        <v>10.24</v>
+        <v>-17.11</v>
       </c>
       <c r="P6" t="n">
-        <v>69.34</v>
+        <v>6.8</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5901</v>
+        <v>3.659</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97</v>
+        <v>23.77</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79</v>
+        <v>10.53</v>
       </c>
       <c r="F7" t="n">
-        <v>27.86</v>
+        <v>36.14</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>40.56</v>
       </c>
       <c r="H7" t="n">
         <v>7.54</v>
@@ -943,13 +943,13 @@
         <v>12.45</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>-4.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0.23</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.67</v>
+        <v>-27.92</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.0936</v>
+        <v>2.2628</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>14.59</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>51.59</v>
       </c>
       <c r="F8" t="n">
-        <v>28.88</v>
+        <v>25.63</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>34.01</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
@@ -1011,13 +1011,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>-0.24</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5</v>
+        <v>-3.94</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.36</v>
+        <v>-7.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1052,19 +1052,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.2137</v>
+        <v>3.6178</v>
       </c>
       <c r="D9" t="n">
-        <v>19.98</v>
+        <v>21.12</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61</v>
+        <v>28.81</v>
       </c>
       <c r="F9" t="n">
-        <v>38.84</v>
+        <v>30.46</v>
       </c>
       <c r="G9" t="n">
-        <v>85.65000000000001</v>
+        <v>57.96</v>
       </c>
       <c r="H9" t="n">
         <v>-13.64</v>
@@ -1085,13 +1085,13 @@
         <v>-15.08</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>2.57</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.04</v>
+        <v>0.36</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.26</v>
+        <v>-18.03</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1103,10 +1103,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1126,19 +1126,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.512</v>
+        <v>0.5395</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93</v>
+        <v>24.18</v>
       </c>
       <c r="E10" t="n">
-        <v>67.54000000000001</v>
+        <v>58.09</v>
       </c>
       <c r="F10" t="n">
-        <v>41.31</v>
+        <v>41.3</v>
       </c>
       <c r="G10" t="n">
-        <v>62.76</v>
+        <v>62.32</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1153,13 +1153,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>-1.95</v>
       </c>
       <c r="O10" t="n">
-        <v>5.71</v>
+        <v>-5.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.95</v>
+        <v>-10.29</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1171,10 +1171,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1194,19 +1194,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7734</v>
+        <v>0.8213</v>
       </c>
       <c r="D11" t="n">
-        <v>32.45</v>
+        <v>32.17</v>
       </c>
       <c r="E11" t="n">
-        <v>88.92</v>
+        <v>85.75</v>
       </c>
       <c r="F11" t="n">
-        <v>33.55</v>
+        <v>39.44</v>
       </c>
       <c r="G11" t="n">
-        <v>46.73</v>
+        <v>56.86</v>
       </c>
       <c r="H11" t="n">
         <v>9.199999999999999</v>
@@ -1227,13 +1227,13 @@
         <v>-1.8</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>-4.15</v>
       </c>
       <c r="O11" t="n">
-        <v>5.76</v>
+        <v>-7.35</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7</v>
+        <v>-12.67</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1245,10 +1245,10 @@
         <v>1</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1268,52 +1268,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3566</v>
+        <v>6.7437</v>
       </c>
       <c r="D12" t="n">
-        <v>33.76</v>
+        <v>31.4</v>
       </c>
       <c r="E12" t="n">
-        <v>69.98999999999999</v>
+        <v>54.92</v>
       </c>
       <c r="F12" t="n">
-        <v>54.75</v>
+        <v>43.03</v>
       </c>
       <c r="G12" t="n">
-        <v>96.48999999999999</v>
+        <v>84.17</v>
       </c>
       <c r="H12" t="n">
-        <v>13.29</v>
+        <v>13.12</v>
       </c>
       <c r="I12" t="n">
         <v>100</v>
       </c>
       <c r="J12" t="n">
-        <v>9.4</v>
+        <v>9.23</v>
       </c>
       <c r="K12" t="n">
-        <v>13.32</v>
+        <v>11.57</v>
       </c>
       <c r="L12" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M12" t="n">
-        <v>6.63</v>
+        <v>4.88</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.43</v>
+        <v>-4.63</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>-3.85</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.45</v>
+        <v>-15.42</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1322,7 +1322,7 @@
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1342,19 +1342,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4189</v>
+        <v>2.6982</v>
       </c>
       <c r="D13" t="n">
-        <v>20.98</v>
+        <v>21.63</v>
       </c>
       <c r="E13" t="n">
-        <v>54.24</v>
+        <v>57.63</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8</v>
+        <v>27.16</v>
       </c>
       <c r="G13" t="n">
-        <v>48.72</v>
+        <v>43.76</v>
       </c>
       <c r="H13" t="n">
         <v>4.2</v>
@@ -1375,13 +1375,13 @@
         <v>-0.88</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>-1.53</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.79</v>
+        <v>-1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>4.06</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1416,19 +1416,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.8702</v>
+        <v>2.0532</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="n">
-        <v>79.81</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>21.02</v>
+        <v>22.02</v>
       </c>
       <c r="G14" t="n">
-        <v>50.64</v>
+        <v>54.99</v>
       </c>
       <c r="H14" t="n">
         <v>16.96</v>
@@ -1449,13 +1449,13 @@
         <v>7.82</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>-1.65</v>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>-3</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.79</v>
+        <v>-7.86</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1467,10 +1467,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1490,19 +1490,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8423</v>
+        <v>0.9298</v>
       </c>
       <c r="D15" t="n">
-        <v>20.13</v>
+        <v>13.25</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>36.48</v>
       </c>
       <c r="F15" t="n">
-        <v>35.1</v>
+        <v>58.68</v>
       </c>
       <c r="G15" t="n">
-        <v>57.89</v>
+        <v>91.42</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1517,28 +1517,28 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>2.59</v>
+        <v>-6.27</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>-2.36</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.88</v>
+        <v>-19.27</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1558,19 +1558,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8192</v>
+        <v>0.8581</v>
       </c>
       <c r="D16" t="n">
-        <v>34.96</v>
+        <v>31.79</v>
       </c>
       <c r="E16" t="n">
-        <v>58.75</v>
+        <v>39.5</v>
       </c>
       <c r="F16" t="n">
-        <v>34.91</v>
+        <v>36.18</v>
       </c>
       <c r="G16" t="n">
-        <v>58.61</v>
+        <v>60.45</v>
       </c>
       <c r="H16" t="n">
         <v>2.06</v>
@@ -1591,13 +1591,13 @@
         <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>-2.12</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>-10.02</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.46</v>
+        <v>-25.53</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1609,10 +1609,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1632,19 +1632,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4965</v>
+        <v>0.5212</v>
       </c>
       <c r="D17" t="n">
-        <v>40.41</v>
+        <v>39.91</v>
       </c>
       <c r="E17" t="n">
-        <v>21.69</v>
+        <v>20.6</v>
       </c>
       <c r="F17" t="n">
-        <v>36.99</v>
+        <v>35.78</v>
       </c>
       <c r="G17" t="n">
-        <v>28.87</v>
+        <v>26.52</v>
       </c>
       <c r="H17" t="n">
         <v>-2</v>
@@ -1665,13 +1665,13 @@
         <v>-8.140000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>-3.5</v>
       </c>
       <c r="O17" t="n">
-        <v>4.96</v>
+        <v>-9.81</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.84</v>
+        <v>-21</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1683,10 +1683,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1706,19 +1706,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1334</v>
+        <v>6.0873</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17</v>
+        <v>6.5</v>
       </c>
       <c r="E18" t="n">
-        <v>72.84</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28</v>
+        <v>12.77</v>
       </c>
       <c r="G18" t="n">
-        <v>73.44</v>
+        <v>76.05</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1733,13 +1733,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.38</v>
+        <v>2.52</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.55</v>
+        <v>5.14</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1751,10 +1751,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1774,19 +1774,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.011</v>
+        <v>5.242</v>
       </c>
       <c r="D19" t="n">
-        <v>11.58</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92</v>
+        <v>14</v>
       </c>
       <c r="G19" t="n">
-        <v>38.2</v>
+        <v>13.57</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
@@ -1801,13 +1801,13 @@
         <v>2.03</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>0.17</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1</v>
+        <v>-6.41</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.25</v>
+        <v>-14.18</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1842,19 +1842,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.2058</v>
       </c>
       <c r="D20" t="n">
-        <v>93.7</v>
+        <v>73.69</v>
       </c>
       <c r="E20" t="n">
-        <v>93.98</v>
+        <v>89.47</v>
       </c>
       <c r="F20" t="n">
-        <v>55.43</v>
+        <v>52.35</v>
       </c>
       <c r="G20" t="n">
-        <v>90.59</v>
+        <v>87.29000000000001</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1869,19 +1869,19 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-5.7</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74</v>
+        <v>-11.01</v>
       </c>
       <c r="P20" t="n">
-        <v>34.83</v>
+        <v>0.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1910,19 +1910,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.889</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>34.35</v>
       </c>
       <c r="E21" t="n">
-        <v>94.14</v>
+        <v>90.31999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>35.75</v>
+        <v>40.58</v>
       </c>
       <c r="G21" t="n">
-        <v>66.34999999999999</v>
+        <v>71.84</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1937,13 +1937,13 @@
         <v>1.23</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>-7.19</v>
       </c>
       <c r="O21" t="n">
-        <v>6.86</v>
+        <v>-9.91</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>3.58</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1955,10 +1955,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -1978,19 +1978,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2957</v>
+        <v>1.3789</v>
       </c>
       <c r="D22" t="n">
-        <v>13.42</v>
+        <v>14.2</v>
       </c>
       <c r="E22" t="n">
-        <v>90.42</v>
+        <v>92.56</v>
       </c>
       <c r="F22" t="n">
-        <v>29.6</v>
+        <v>23.75</v>
       </c>
       <c r="G22" t="n">
-        <v>47.77</v>
+        <v>25.98</v>
       </c>
       <c r="H22" t="n">
         <v>1.52</v>
@@ -2011,13 +2011,13 @@
         <v>0.11</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>-2.15</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>-6.39</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.59</v>
+        <v>-10.61</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2029,10 +2029,10 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2052,19 +2052,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4611</v>
+        <v>7.9605</v>
       </c>
       <c r="D23" t="n">
-        <v>31.78</v>
+        <v>25.43</v>
       </c>
       <c r="E23" t="n">
-        <v>49.01</v>
+        <v>25.41</v>
       </c>
       <c r="F23" t="n">
-        <v>39.05</v>
+        <v>39.25</v>
       </c>
       <c r="G23" t="n">
-        <v>52.39</v>
+        <v>53.82</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
@@ -2085,13 +2085,13 @@
         <v>0.02</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.87</v>
+        <v>-6.86</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>-13.07</v>
       </c>
       <c r="P23" t="n">
-        <v>19.13</v>
+        <v>-19.07</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2126,19 +2126,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1859</v>
+        <v>5.8869</v>
       </c>
       <c r="D24" t="n">
-        <v>43.64</v>
+        <v>37</v>
       </c>
       <c r="E24" t="n">
-        <v>93.98</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>39.48</v>
+        <v>35.01</v>
       </c>
       <c r="G24" t="n">
-        <v>54.55</v>
+        <v>46.8</v>
       </c>
       <c r="H24" t="n">
         <v>1.6</v>
@@ -2159,16 +2159,16 @@
         <v>-4.7</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>-7.84</v>
       </c>
       <c r="O24" t="n">
-        <v>8.4</v>
+        <v>-16.42</v>
       </c>
       <c r="P24" t="n">
-        <v>19.08</v>
+        <v>-9.57</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2177,7 +2177,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2200,19 +2200,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6109</v>
+        <v>2.7304</v>
       </c>
       <c r="D25" t="n">
-        <v>59.69</v>
+        <v>55.52</v>
       </c>
       <c r="E25" t="n">
-        <v>50.75</v>
+        <v>36.48</v>
       </c>
       <c r="F25" t="n">
-        <v>31.28</v>
+        <v>34.91</v>
       </c>
       <c r="G25" t="n">
-        <v>44.1</v>
+        <v>52.42</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2227,13 +2227,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>-3.57</v>
       </c>
       <c r="O25" t="n">
-        <v>3.28</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.06</v>
+        <v>-8.74</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2268,19 +2268,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7258</v>
+        <v>4.7916</v>
       </c>
       <c r="D26" t="n">
-        <v>67.65000000000001</v>
+        <v>56.86</v>
       </c>
       <c r="E26" t="n">
-        <v>63.97</v>
+        <v>40.59</v>
       </c>
       <c r="F26" t="n">
-        <v>39.09</v>
+        <v>34.29</v>
       </c>
       <c r="G26" t="n">
-        <v>33.57</v>
+        <v>23.71</v>
       </c>
       <c r="H26" t="n">
         <v>12.66</v>
@@ -2301,13 +2301,13 @@
         <v>12.94</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>-2.8</v>
       </c>
       <c r="O26" t="n">
-        <v>0.41</v>
+        <v>-8.5</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6</v>
+        <v>-26.98</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2319,10 +2319,10 @@
         <v>1</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2342,19 +2342,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.6308</v>
+        <v>1.8515</v>
       </c>
       <c r="D27" t="n">
-        <v>34.73</v>
+        <v>34.55</v>
       </c>
       <c r="E27" t="n">
-        <v>44.73</v>
+        <v>43.61</v>
       </c>
       <c r="F27" t="n">
-        <v>35.42</v>
+        <v>59.16</v>
       </c>
       <c r="G27" t="n">
-        <v>29.59</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="H27" t="n">
         <v>3.24</v>
@@ -2375,13 +2375,13 @@
         <v>-0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>0.22</v>
+        <v>3.83</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.94</v>
+        <v>-4.06</v>
       </c>
       <c r="P27" t="n">
-        <v>-14.27</v>
+        <v>-21.34</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2416,19 +2416,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.8119</v>
+        <v>5.2828</v>
       </c>
       <c r="D28" t="n">
-        <v>57.04</v>
+        <v>41.46</v>
       </c>
       <c r="E28" t="n">
-        <v>93.27</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>49.14</v>
+        <v>37.23</v>
       </c>
       <c r="G28" t="n">
-        <v>70.26000000000001</v>
+        <v>49.38</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
@@ -2443,16 +2443,16 @@
         <v>4.72</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.13</v>
+        <v>-11.63</v>
       </c>
       <c r="O28" t="n">
-        <v>10.13</v>
+        <v>-20.99</v>
       </c>
       <c r="P28" t="n">
-        <v>85.06999999999999</v>
+        <v>17.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2464,7 +2464,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2484,19 +2484,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9446</v>
+        <v>1.0833</v>
       </c>
       <c r="D29" t="n">
-        <v>22.77</v>
+        <v>18.84</v>
       </c>
       <c r="E29" t="n">
-        <v>98.59</v>
+        <v>85.91</v>
       </c>
       <c r="F29" t="n">
-        <v>45.46</v>
+        <v>39.04</v>
       </c>
       <c r="G29" t="n">
-        <v>82.79000000000001</v>
+        <v>71.08</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2511,16 +2511,16 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>1.43</v>
       </c>
       <c r="O29" t="n">
-        <v>9.9</v>
+        <v>-1.32</v>
       </c>
       <c r="P29" t="n">
-        <v>31.81</v>
+        <v>24.62</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
         <v>-1</v>
@@ -2552,19 +2552,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.1858</v>
+        <v>1.2659</v>
       </c>
       <c r="D30" t="n">
-        <v>21.36</v>
+        <v>16.6</v>
       </c>
       <c r="E30" t="n">
-        <v>94.01000000000001</v>
+        <v>72.77</v>
       </c>
       <c r="F30" t="n">
-        <v>28.39</v>
+        <v>24.63</v>
       </c>
       <c r="G30" t="n">
-        <v>72.31999999999999</v>
+        <v>55.06</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -2579,16 +2579,16 @@
         <v>3.12</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>-1.02</v>
       </c>
       <c r="O30" t="n">
-        <v>8.75</v>
+        <v>-5.45</v>
       </c>
       <c r="P30" t="n">
-        <v>25.75</v>
+        <v>22.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2597,7 +2597,7 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U30" t="n">
         <v>-1</v>
@@ -2620,19 +2620,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8045</v>
+        <v>0.8061</v>
       </c>
       <c r="D31" t="n">
-        <v>26.31</v>
+        <v>23.43</v>
       </c>
       <c r="E31" t="n">
-        <v>80.90000000000001</v>
+        <v>67.78</v>
       </c>
       <c r="F31" t="n">
-        <v>30.74</v>
+        <v>27.98</v>
       </c>
       <c r="G31" t="n">
-        <v>51.11</v>
+        <v>45.37</v>
       </c>
       <c r="H31" t="n">
         <v>8.66</v>
@@ -2653,13 +2653,13 @@
         <v>9.49</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>-6.38</v>
       </c>
       <c r="O31" t="n">
-        <v>6.79</v>
+        <v>-10.39</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>-9.34</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2671,10 +2671,10 @@
         <v>1</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2694,19 +2694,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1823</v>
+        <v>0.2019</v>
       </c>
       <c r="D32" t="n">
-        <v>30.39</v>
+        <v>28.24</v>
       </c>
       <c r="E32" t="n">
-        <v>16.55</v>
+        <v>6.36</v>
       </c>
       <c r="F32" t="n">
-        <v>38.72</v>
+        <v>40.3</v>
       </c>
       <c r="G32" t="n">
-        <v>61.58</v>
+        <v>65.02</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -2721,16 +2721,16 @@
         <v>0.09</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>-1.12</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.54</v>
+        <v>-2.01</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.31</v>
+        <v>-27.67</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2742,7 +2742,7 @@
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3053</v>
+        <v>1.2965</v>
       </c>
       <c r="D2" t="n">
-        <v>79.2</v>
+        <v>78.62</v>
       </c>
       <c r="E2" t="n">
-        <v>79.47</v>
+        <v>79.41</v>
       </c>
       <c r="F2" t="n">
-        <v>47.97</v>
+        <v>47.94</v>
       </c>
       <c r="G2" t="n">
-        <v>86.97</v>
+        <v>86.91</v>
       </c>
       <c r="H2" t="n">
         <v>-50.42</v>
@@ -573,13 +573,13 @@
         <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.34</v>
+        <v>-3.84</v>
       </c>
       <c r="O2" t="n">
-        <v>-10.63</v>
+        <v>-8.44</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.84</v>
+        <v>-16.9</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.538</v>
+        <v>4.5457</v>
       </c>
       <c r="D3" t="n">
-        <v>23.66</v>
+        <v>23.69</v>
       </c>
       <c r="E3" t="n">
-        <v>57.94</v>
+        <v>58.36</v>
       </c>
       <c r="F3" t="n">
-        <v>38.45</v>
+        <v>37.98</v>
       </c>
       <c r="G3" t="n">
-        <v>53.67</v>
+        <v>51.99</v>
       </c>
       <c r="H3" t="n">
-        <v>11.02</v>
+        <v>7.52</v>
       </c>
       <c r="I3" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
-        <v>6.98</v>
+        <v>3.48</v>
       </c>
       <c r="K3" t="n">
-        <v>26.58</v>
+        <v>23.65</v>
       </c>
       <c r="L3" t="n">
         <v>100</v>
       </c>
       <c r="M3" t="n">
-        <v>19.67</v>
+        <v>16.74</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.31</v>
+        <v>-6.88</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.58</v>
+        <v>-10.87</v>
       </c>
       <c r="P3" t="n">
-        <v>-2.43</v>
+        <v>-3.94</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6218</v>
+        <v>0.6235000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>29.42</v>
+        <v>29.48</v>
       </c>
       <c r="E4" t="n">
-        <v>73.81999999999999</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>19.11</v>
+        <v>18.41</v>
       </c>
       <c r="G4" t="n">
-        <v>37.29</v>
+        <v>34.92</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.66</v>
+        <v>-1.73</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.75</v>
+        <v>-5.61</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.12</v>
+        <v>-12.76</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1574</v>
+        <v>5.1535</v>
       </c>
       <c r="D5" t="n">
-        <v>15.51</v>
+        <v>15.49</v>
       </c>
       <c r="E5" t="n">
-        <v>19.83</v>
+        <v>19.58</v>
       </c>
       <c r="F5" t="n">
-        <v>26.9</v>
+        <v>26.05</v>
       </c>
       <c r="G5" t="n">
-        <v>33.62</v>
+        <v>31.18</v>
       </c>
       <c r="H5" t="n">
-        <v>10.68</v>
+        <v>14.57</v>
       </c>
       <c r="I5" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>4.24</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>8.67</v>
+        <v>15.09</v>
       </c>
       <c r="L5" t="n">
-        <v>50</v>
+        <v>83.33</v>
       </c>
       <c r="M5" t="n">
-        <v>-3.71</v>
+        <v>2.71</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.31</v>
+        <v>-7.44</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.22</v>
+        <v>-16.28</v>
       </c>
       <c r="P5" t="n">
-        <v>7.72</v>
+        <v>6.12</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.009</v>
+        <v>17.7956</v>
       </c>
       <c r="D6" t="n">
-        <v>50.47</v>
+        <v>49.84</v>
       </c>
       <c r="E6" t="n">
-        <v>61.97</v>
+        <v>60.91</v>
       </c>
       <c r="F6" t="n">
-        <v>47.12</v>
+        <v>45.55</v>
       </c>
       <c r="G6" t="n">
-        <v>73.63</v>
+        <v>71.94</v>
       </c>
       <c r="H6" t="n">
-        <v>6.49</v>
+        <v>5.42</v>
       </c>
       <c r="I6" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>3.16</v>
+        <v>2.09</v>
       </c>
       <c r="K6" t="n">
-        <v>8.26</v>
+        <v>7.98</v>
       </c>
       <c r="L6" t="n">
-        <v>79.17</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>0.43</v>
+        <v>0.16</v>
       </c>
       <c r="N6" t="n">
-        <v>-10.09</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.11</v>
+        <v>-17.69</v>
       </c>
       <c r="P6" t="n">
-        <v>6.8</v>
+        <v>2.63</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.659</v>
+        <v>3.7027</v>
       </c>
       <c r="D7" t="n">
-        <v>23.77</v>
+        <v>24.04</v>
       </c>
       <c r="E7" t="n">
-        <v>10.53</v>
+        <v>11.76</v>
       </c>
       <c r="F7" t="n">
-        <v>36.14</v>
+        <v>35.33</v>
       </c>
       <c r="G7" t="n">
-        <v>40.56</v>
+        <v>39.28</v>
       </c>
       <c r="H7" t="n">
-        <v>7.54</v>
+        <v>4.65</v>
       </c>
       <c r="I7" t="n">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>-1.09</v>
       </c>
       <c r="K7" t="n">
-        <v>19.41</v>
+        <v>17.44</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>12.45</v>
+        <v>10.48</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.22</v>
+        <v>-3.62</v>
       </c>
       <c r="O7" t="n">
-        <v>-9.029999999999999</v>
+        <v>-6.01</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.92</v>
+        <v>-27.36</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,23 +984,29 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2628</v>
+        <v>2.3046</v>
       </c>
       <c r="D8" t="n">
-        <v>14.59</v>
+        <v>14.85</v>
       </c>
       <c r="E8" t="n">
-        <v>51.59</v>
+        <v>64.31999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>25.63</v>
+        <v>25.4</v>
       </c>
       <c r="G8" t="n">
-        <v>34.01</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>32.42</v>
+      </c>
+      <c r="H8" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="I8" t="n">
+        <v>70</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.16</v>
+      </c>
       <c r="K8" t="n">
         <v>8.279999999999999</v>
       </c>
@@ -1011,13 +1017,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.24</v>
+        <v>0.88</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.94</v>
+        <v>-1.82</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.78</v>
+        <v>-6.96</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1026,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1052,19 +1058,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6178</v>
+        <v>3.6107</v>
       </c>
       <c r="D9" t="n">
-        <v>21.12</v>
+        <v>21.07</v>
       </c>
       <c r="E9" t="n">
-        <v>28.81</v>
+        <v>27.55</v>
       </c>
       <c r="F9" t="n">
-        <v>30.46</v>
+        <v>30.79</v>
       </c>
       <c r="G9" t="n">
-        <v>57.96</v>
+        <v>59.94</v>
       </c>
       <c r="H9" t="n">
         <v>-13.64</v>
@@ -1076,22 +1082,22 @@
         <v>-18.28</v>
       </c>
       <c r="K9" t="n">
-        <v>2.95</v>
+        <v>5.23</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-15.08</v>
+        <v>-12.81</v>
       </c>
       <c r="N9" t="n">
-        <v>2.57</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>0.36</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.03</v>
+        <v>-18.34</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1126,19 +1132,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5395</v>
+        <v>0.54</v>
       </c>
       <c r="D10" t="n">
-        <v>24.18</v>
+        <v>24.19</v>
       </c>
       <c r="E10" t="n">
-        <v>58.09</v>
+        <v>58.2</v>
       </c>
       <c r="F10" t="n">
-        <v>41.3</v>
+        <v>40.64</v>
       </c>
       <c r="G10" t="n">
-        <v>62.32</v>
+        <v>60.72</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
@@ -1153,13 +1159,13 @@
         <v>-0.06</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.95</v>
+        <v>-3.77</v>
       </c>
       <c r="O10" t="n">
-        <v>-5.69</v>
+        <v>-4.16</v>
       </c>
       <c r="P10" t="n">
-        <v>-10.29</v>
+        <v>-10.79</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1194,19 +1200,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8213</v>
+        <v>0.822</v>
       </c>
       <c r="D11" t="n">
-        <v>32.17</v>
+        <v>32.18</v>
       </c>
       <c r="E11" t="n">
-        <v>85.75</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>39.44</v>
+        <v>38.58</v>
       </c>
       <c r="G11" t="n">
-        <v>56.86</v>
+        <v>55.57</v>
       </c>
       <c r="H11" t="n">
         <v>9.199999999999999</v>
@@ -1218,22 +1224,22 @@
         <v>5.33</v>
       </c>
       <c r="K11" t="n">
-        <v>0.85</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>4.35</v>
+        <v>87.5</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.8</v>
+        <v>4.58</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.15</v>
+        <v>-4.75</v>
       </c>
       <c r="O11" t="n">
-        <v>-7.35</v>
+        <v>-6.22</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.67</v>
+        <v>-13.4</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1268,46 +1274,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7437</v>
+        <v>6.7735</v>
       </c>
       <c r="D12" t="n">
-        <v>31.4</v>
+        <v>31.52</v>
       </c>
       <c r="E12" t="n">
-        <v>54.92</v>
+        <v>56.27</v>
       </c>
       <c r="F12" t="n">
-        <v>43.03</v>
+        <v>42.81</v>
       </c>
       <c r="G12" t="n">
-        <v>84.17</v>
+        <v>83.87</v>
       </c>
       <c r="H12" t="n">
-        <v>13.12</v>
+        <v>6.25</v>
       </c>
       <c r="I12" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J12" t="n">
-        <v>9.23</v>
+        <v>2.36</v>
       </c>
       <c r="K12" t="n">
-        <v>11.57</v>
+        <v>7.77</v>
       </c>
       <c r="L12" t="n">
-        <v>95.83</v>
+        <v>66.67</v>
       </c>
       <c r="M12" t="n">
-        <v>4.88</v>
+        <v>1.08</v>
       </c>
       <c r="N12" t="n">
-        <v>-4.63</v>
+        <v>-5.03</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.85</v>
+        <v>-1.95</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.42</v>
+        <v>-16.45</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1342,46 +1348,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6982</v>
+        <v>2.7118</v>
       </c>
       <c r="D13" t="n">
-        <v>21.63</v>
+        <v>21.73</v>
       </c>
       <c r="E13" t="n">
-        <v>57.63</v>
+        <v>58.28</v>
       </c>
       <c r="F13" t="n">
-        <v>27.16</v>
+        <v>27.22</v>
       </c>
       <c r="G13" t="n">
-        <v>43.76</v>
+        <v>44.04</v>
       </c>
       <c r="H13" t="n">
-        <v>4.2</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="I13" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.21</v>
+        <v>4.12</v>
       </c>
       <c r="K13" t="n">
-        <v>7.63</v>
+        <v>7.67</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.88</v>
+        <v>-0.85</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.53</v>
+        <v>-1.16</v>
       </c>
       <c r="O13" t="n">
         <v>-1.73</v>
       </c>
       <c r="P13" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1390,13 +1396,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1416,46 +1422,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0532</v>
+        <v>2.0561</v>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16.71</v>
       </c>
       <c r="E14" t="n">
-        <v>73.51000000000001</v>
+        <v>73.53</v>
       </c>
       <c r="F14" t="n">
-        <v>22.02</v>
+        <v>21.97</v>
       </c>
       <c r="G14" t="n">
-        <v>54.99</v>
+        <v>54.72</v>
       </c>
       <c r="H14" t="n">
-        <v>16.96</v>
+        <v>1.8</v>
       </c>
       <c r="I14" t="n">
-        <v>100</v>
+        <v>15</v>
       </c>
       <c r="J14" t="n">
-        <v>11.92</v>
+        <v>-3.24</v>
       </c>
       <c r="K14" t="n">
-        <v>16.96</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>95.83</v>
+        <v>79.17</v>
       </c>
       <c r="M14" t="n">
-        <v>7.82</v>
+        <v>-0.68</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.65</v>
+        <v>-2.2</v>
       </c>
       <c r="O14" t="n">
-        <v>-3</v>
+        <v>-2.66</v>
       </c>
       <c r="P14" t="n">
-        <v>-7.86</v>
+        <v>-8.17</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1464,13 +1470,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1490,19 +1496,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9298</v>
+        <v>0.9157999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>13.25</v>
+        <v>13.04</v>
       </c>
       <c r="E15" t="n">
-        <v>36.48</v>
+        <v>34.21</v>
       </c>
       <c r="F15" t="n">
-        <v>58.68</v>
+        <v>56.28</v>
       </c>
       <c r="G15" t="n">
-        <v>91.42</v>
+        <v>89.79000000000001</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
@@ -1517,19 +1523,19 @@
         <v>-0.33</v>
       </c>
       <c r="N15" t="n">
-        <v>-6.27</v>
+        <v>-7.52</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.36</v>
+        <v>-3.22</v>
       </c>
       <c r="P15" t="n">
-        <v>-19.27</v>
+        <v>-22.29</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
@@ -1538,7 +1544,7 @@
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1558,28 +1564,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8581</v>
+        <v>0.8505</v>
       </c>
       <c r="D16" t="n">
-        <v>31.79</v>
+        <v>31.49</v>
       </c>
       <c r="E16" t="n">
-        <v>39.5</v>
+        <v>38.7</v>
       </c>
       <c r="F16" t="n">
-        <v>36.18</v>
+        <v>36.16</v>
       </c>
       <c r="G16" t="n">
-        <v>60.45</v>
+        <v>60.41</v>
       </c>
       <c r="H16" t="n">
-        <v>2.06</v>
+        <v>2.45</v>
       </c>
       <c r="I16" t="n">
-        <v>45</v>
+        <v>65</v>
       </c>
       <c r="J16" t="n">
-        <v>0.21</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
         <v>-0.71</v>
@@ -1591,13 +1597,13 @@
         <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>-2.12</v>
+        <v>-5.21</v>
       </c>
       <c r="O16" t="n">
-        <v>-10.02</v>
+        <v>-9.49</v>
       </c>
       <c r="P16" t="n">
-        <v>-25.53</v>
+        <v>-26.94</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1632,46 +1638,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5212</v>
+        <v>0.5174</v>
       </c>
       <c r="D17" t="n">
-        <v>39.91</v>
+        <v>39.58</v>
       </c>
       <c r="E17" t="n">
-        <v>20.6</v>
+        <v>19.89</v>
       </c>
       <c r="F17" t="n">
-        <v>35.78</v>
+        <v>34.98</v>
       </c>
       <c r="G17" t="n">
-        <v>26.52</v>
+        <v>24.86</v>
       </c>
       <c r="H17" t="n">
-        <v>-2</v>
+        <v>8.76</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>-7.14</v>
+        <v>3.62</v>
       </c>
       <c r="K17" t="n">
-        <v>-2</v>
+        <v>9.41</v>
       </c>
       <c r="L17" t="n">
-        <v>29.17</v>
+        <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.140000000000001</v>
+        <v>3.27</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.5</v>
+        <v>-5.39</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.81</v>
+        <v>-10.11</v>
       </c>
       <c r="P17" t="n">
-        <v>-21</v>
+        <v>-22.04</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1680,13 +1686,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1706,19 +1712,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.0873</v>
+        <v>6.1878</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>6.61</v>
       </c>
       <c r="E18" t="n">
-        <v>86.68000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="F18" t="n">
-        <v>12.77</v>
+        <v>12.88</v>
       </c>
       <c r="G18" t="n">
-        <v>76.05</v>
+        <v>76.77</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1733,16 +1739,16 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>0.43</v>
+        <v>3.13</v>
       </c>
       <c r="O18" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="P18" t="n">
-        <v>5.14</v>
+        <v>7.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1751,7 +1757,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1774,7 +1780,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.242</v>
+        <v>5.1833</v>
       </c>
       <c r="D19" t="n">
         <v>8.800000000000001</v>
@@ -1783,31 +1789,37 @@
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14</v>
+        <v>14.15</v>
       </c>
       <c r="G19" t="n">
-        <v>13.57</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+        <v>14.26</v>
+      </c>
+      <c r="H19" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="I19" t="n">
+        <v>35</v>
+      </c>
+      <c r="J19" t="n">
+        <v>-2.37</v>
+      </c>
       <c r="K19" t="n">
-        <v>7.49</v>
+        <v>3.04</v>
       </c>
       <c r="L19" t="n">
-        <v>65.22</v>
+        <v>20.83</v>
       </c>
       <c r="M19" t="n">
-        <v>2.03</v>
+        <v>-6.76</v>
       </c>
       <c r="N19" t="n">
-        <v>0.17</v>
+        <v>-1.35</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.41</v>
+        <v>-6.6</v>
       </c>
       <c r="P19" t="n">
-        <v>-14.18</v>
+        <v>-14.8</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1842,19 +1854,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2058</v>
+        <v>0.2019</v>
       </c>
       <c r="D20" t="n">
-        <v>73.69</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>89.47</v>
+        <v>87.93000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>52.35</v>
+        <v>52.32</v>
       </c>
       <c r="G20" t="n">
-        <v>87.29000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1869,13 +1881,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-5.7</v>
+        <v>-7.59</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.01</v>
+        <v>-11.95</v>
       </c>
       <c r="P20" t="n">
-        <v>0.83</v>
+        <v>-1.4</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1910,40 +1922,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.889</v>
+        <v>0.883</v>
       </c>
       <c r="D21" t="n">
-        <v>34.35</v>
+        <v>34.08</v>
       </c>
       <c r="E21" t="n">
-        <v>90.31999999999999</v>
+        <v>90.09</v>
       </c>
       <c r="F21" t="n">
-        <v>40.58</v>
+        <v>38.32</v>
       </c>
       <c r="G21" t="n">
-        <v>71.84</v>
-      </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>68.43000000000001</v>
+      </c>
+      <c r="H21" t="n">
+        <v>8.42</v>
+      </c>
+      <c r="I21" t="n">
+        <v>95</v>
+      </c>
+      <c r="J21" t="n">
+        <v>6.17</v>
+      </c>
       <c r="K21" t="n">
-        <v>4.17</v>
+        <v>15.7</v>
       </c>
       <c r="L21" t="n">
-        <v>43.48</v>
+        <v>95.83</v>
       </c>
       <c r="M21" t="n">
-        <v>1.23</v>
+        <v>11.09</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.19</v>
+        <v>-7.05</v>
       </c>
       <c r="O21" t="n">
-        <v>-9.91</v>
+        <v>-11.13</v>
       </c>
       <c r="P21" t="n">
-        <v>3.58</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1952,13 +1970,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -1978,19 +1996,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3789</v>
+        <v>1.371</v>
       </c>
       <c r="D22" t="n">
-        <v>14.2</v>
+        <v>14.11</v>
       </c>
       <c r="E22" t="n">
-        <v>92.56</v>
+        <v>92.34</v>
       </c>
       <c r="F22" t="n">
-        <v>23.75</v>
+        <v>23.52</v>
       </c>
       <c r="G22" t="n">
-        <v>25.98</v>
+        <v>24.79</v>
       </c>
       <c r="H22" t="n">
         <v>1.52</v>
@@ -2002,22 +2020,22 @@
         <v>-1.36</v>
       </c>
       <c r="K22" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="L22" t="n">
-        <v>45.83</v>
+        <v>41.67</v>
       </c>
       <c r="M22" t="n">
-        <v>0.11</v>
+        <v>-0.03</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.15</v>
+        <v>-2.92</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.39</v>
+        <v>-6.84</v>
       </c>
       <c r="P22" t="n">
-        <v>-10.61</v>
+        <v>-11.55</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2052,19 +2070,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.9605</v>
+        <v>7.9098</v>
       </c>
       <c r="D23" t="n">
-        <v>25.43</v>
+        <v>25.25</v>
       </c>
       <c r="E23" t="n">
-        <v>25.41</v>
+        <v>25.15</v>
       </c>
       <c r="F23" t="n">
-        <v>39.25</v>
+        <v>39.3</v>
       </c>
       <c r="G23" t="n">
-        <v>53.82</v>
+        <v>53.94</v>
       </c>
       <c r="H23" t="n">
         <v>6.2</v>
@@ -2076,22 +2094,22 @@
         <v>2.3</v>
       </c>
       <c r="K23" t="n">
-        <v>8.44</v>
+        <v>8.85</v>
       </c>
       <c r="L23" t="n">
-        <v>58.33</v>
+        <v>70.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.02</v>
+        <v>0.43</v>
       </c>
       <c r="N23" t="n">
-        <v>-6.86</v>
+        <v>-8.06</v>
       </c>
       <c r="O23" t="n">
-        <v>-13.07</v>
+        <v>-13.04</v>
       </c>
       <c r="P23" t="n">
-        <v>-19.07</v>
+        <v>-21.88</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2126,46 +2144,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.8869</v>
+        <v>5.9159</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>37.14</v>
       </c>
       <c r="E24" t="n">
-        <v>80.70999999999999</v>
+        <v>81.11</v>
       </c>
       <c r="F24" t="n">
-        <v>35.01</v>
+        <v>34.07</v>
       </c>
       <c r="G24" t="n">
-        <v>46.8</v>
+        <v>45.13</v>
       </c>
       <c r="H24" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="I24" t="n">
+        <v>60</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K24" t="n">
+        <v>6.94</v>
+      </c>
+      <c r="L24" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="M24" t="n">
         <v>1.6</v>
       </c>
-      <c r="I24" t="n">
-        <v>25</v>
-      </c>
-      <c r="J24" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" t="n">
-        <v>-4.7</v>
-      </c>
       <c r="N24" t="n">
-        <v>-7.84</v>
+        <v>-6.58</v>
       </c>
       <c r="O24" t="n">
-        <v>-16.42</v>
+        <v>-14.73</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.57</v>
+        <v>-10.85</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2174,13 +2192,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2200,19 +2218,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7304</v>
+        <v>2.7731</v>
       </c>
       <c r="D25" t="n">
-        <v>55.52</v>
+        <v>56.34</v>
       </c>
       <c r="E25" t="n">
-        <v>36.48</v>
+        <v>40.48</v>
       </c>
       <c r="F25" t="n">
-        <v>34.91</v>
+        <v>35.05</v>
       </c>
       <c r="G25" t="n">
-        <v>52.42</v>
+        <v>52.92</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -2227,13 +2245,13 @@
         <v>1.16</v>
       </c>
       <c r="N25" t="n">
-        <v>-3.57</v>
+        <v>-0.41</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.279999999999999</v>
+        <v>-7.85</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.74</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2268,46 +2286,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7916</v>
+        <v>4.8363</v>
       </c>
       <c r="D26" t="n">
-        <v>56.86</v>
+        <v>57.35</v>
       </c>
       <c r="E26" t="n">
-        <v>40.59</v>
+        <v>41.56</v>
       </c>
       <c r="F26" t="n">
-        <v>34.29</v>
+        <v>34.1</v>
       </c>
       <c r="G26" t="n">
-        <v>23.71</v>
+        <v>23.07</v>
       </c>
       <c r="H26" t="n">
-        <v>12.66</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>12.41</v>
+        <v>-0.15</v>
       </c>
       <c r="K26" t="n">
-        <v>14.85</v>
+        <v>9.25</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M26" t="n">
-        <v>12.94</v>
+        <v>7.34</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.8</v>
+        <v>-4.18</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.5</v>
+        <v>-6.86</v>
       </c>
       <c r="P26" t="n">
-        <v>-26.98</v>
+        <v>-28.15</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2316,13 +2334,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2342,19 +2360,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8515</v>
+        <v>1.8546</v>
       </c>
       <c r="D27" t="n">
-        <v>34.55</v>
+        <v>34.58</v>
       </c>
       <c r="E27" t="n">
-        <v>43.61</v>
+        <v>43.81</v>
       </c>
       <c r="F27" t="n">
-        <v>59.16</v>
+        <v>61.16</v>
       </c>
       <c r="G27" t="n">
-        <v>72.84999999999999</v>
+        <v>75.84</v>
       </c>
       <c r="H27" t="n">
         <v>3.24</v>
@@ -2375,13 +2393,13 @@
         <v>-0.92</v>
       </c>
       <c r="N27" t="n">
-        <v>3.83</v>
+        <v>-1.28</v>
       </c>
       <c r="O27" t="n">
-        <v>-4.06</v>
+        <v>-2.74</v>
       </c>
       <c r="P27" t="n">
-        <v>-21.34</v>
+        <v>-23.24</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2416,40 +2434,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2828</v>
+        <v>5.2945</v>
       </c>
       <c r="D28" t="n">
-        <v>41.46</v>
+        <v>41.53</v>
       </c>
       <c r="E28" t="n">
-        <v>78.54000000000001</v>
+        <v>78.64</v>
       </c>
       <c r="F28" t="n">
-        <v>37.23</v>
+        <v>35.93</v>
       </c>
       <c r="G28" t="n">
-        <v>49.38</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+        <v>44.89</v>
+      </c>
+      <c r="H28" t="n">
+        <v>16.39</v>
+      </c>
+      <c r="I28" t="n">
+        <v>100</v>
+      </c>
+      <c r="J28" t="n">
+        <v>13.68</v>
+      </c>
       <c r="K28" t="n">
-        <v>19.16</v>
+        <v>14.58</v>
       </c>
       <c r="L28" t="n">
-        <v>91.3</v>
+        <v>83.33</v>
       </c>
       <c r="M28" t="n">
-        <v>4.72</v>
+        <v>-7.84</v>
       </c>
       <c r="N28" t="n">
-        <v>-11.63</v>
+        <v>-10.72</v>
       </c>
       <c r="O28" t="n">
-        <v>-20.99</v>
+        <v>-20.04</v>
       </c>
       <c r="P28" t="n">
-        <v>17.9</v>
+        <v>18.11</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2458,13 +2482,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2484,19 +2508,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0833</v>
+        <v>1.0928</v>
       </c>
       <c r="D29" t="n">
-        <v>18.84</v>
+        <v>18.99</v>
       </c>
       <c r="E29" t="n">
-        <v>85.91</v>
+        <v>86.61</v>
       </c>
       <c r="F29" t="n">
-        <v>39.04</v>
+        <v>38.56</v>
       </c>
       <c r="G29" t="n">
-        <v>71.08</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2511,13 +2535,13 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>1.43</v>
+        <v>0.68</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.32</v>
+        <v>0.73</v>
       </c>
       <c r="P29" t="n">
-        <v>24.62</v>
+        <v>26.01</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2529,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2552,40 +2576,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2659</v>
+        <v>1.2694</v>
       </c>
       <c r="D30" t="n">
-        <v>16.6</v>
+        <v>16.64</v>
       </c>
       <c r="E30" t="n">
-        <v>72.77</v>
+        <v>73.39</v>
       </c>
       <c r="F30" t="n">
-        <v>24.63</v>
+        <v>24.62</v>
       </c>
       <c r="G30" t="n">
-        <v>55.06</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+        <v>54.84</v>
+      </c>
+      <c r="H30" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="I30" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" t="n">
+        <v>4.38</v>
+      </c>
       <c r="K30" t="n">
-        <v>6.53</v>
+        <v>6.41</v>
       </c>
       <c r="L30" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.12</v>
+        <v>1.53</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.02</v>
+        <v>-0.62</v>
       </c>
       <c r="O30" t="n">
-        <v>-5.45</v>
+        <v>-3.78</v>
       </c>
       <c r="P30" t="n">
-        <v>22.45</v>
+        <v>22.01</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2594,13 +2624,13 @@
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
         <v>-1</v>
       </c>
       <c r="U30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2620,46 +2650,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8061</v>
+        <v>0.8046</v>
       </c>
       <c r="D31" t="n">
-        <v>23.43</v>
+        <v>23.39</v>
       </c>
       <c r="E31" t="n">
-        <v>67.78</v>
+        <v>67.47</v>
       </c>
       <c r="F31" t="n">
-        <v>27.98</v>
+        <v>27.8</v>
       </c>
       <c r="G31" t="n">
-        <v>45.37</v>
+        <v>44.38</v>
       </c>
       <c r="H31" t="n">
-        <v>8.66</v>
+        <v>10.9</v>
       </c>
       <c r="I31" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="J31" t="n">
-        <v>5.31</v>
+        <v>7.55</v>
       </c>
       <c r="K31" t="n">
-        <v>11.28</v>
+        <v>11.21</v>
       </c>
       <c r="L31" t="n">
         <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>9.49</v>
+        <v>9.43</v>
       </c>
       <c r="N31" t="n">
-        <v>-6.38</v>
+        <v>-7.08</v>
       </c>
       <c r="O31" t="n">
-        <v>-10.39</v>
+        <v>-9.5</v>
       </c>
       <c r="P31" t="n">
-        <v>-9.34</v>
+        <v>-10.88</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2694,40 +2724,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2019</v>
+        <v>0.202</v>
       </c>
       <c r="D32" t="n">
-        <v>28.24</v>
+        <v>28.23</v>
       </c>
       <c r="E32" t="n">
-        <v>6.36</v>
+        <v>6.27</v>
       </c>
       <c r="F32" t="n">
-        <v>40.3</v>
+        <v>40.51</v>
       </c>
       <c r="G32" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+        <v>65.73999999999999</v>
+      </c>
+      <c r="H32" t="n">
+        <v>12.91</v>
+      </c>
+      <c r="I32" t="n">
+        <v>100</v>
+      </c>
+      <c r="J32" t="n">
+        <v>6.91</v>
+      </c>
       <c r="K32" t="n">
-        <v>6.21</v>
+        <v>12.91</v>
       </c>
       <c r="L32" t="n">
-        <v>34.78</v>
+        <v>87.5</v>
       </c>
       <c r="M32" t="n">
-        <v>0.09</v>
+        <v>4.46</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.12</v>
+        <v>-2.82</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.01</v>
+        <v>-0.1</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.67</v>
+        <v>-28.41</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2736,13 +2772,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,19 +540,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2965</v>
+        <v>1.2925</v>
       </c>
       <c r="D2" t="n">
-        <v>78.62</v>
+        <v>78.64</v>
       </c>
       <c r="E2" t="n">
-        <v>79.41</v>
+        <v>79.43000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>47.94</v>
+        <v>46.62</v>
       </c>
       <c r="G2" t="n">
-        <v>86.91</v>
+        <v>84.97</v>
       </c>
       <c r="H2" t="n">
         <v>-50.42</v>
@@ -573,13 +573,13 @@
         <v>-38.42</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.84</v>
+        <v>-3.19</v>
       </c>
       <c r="O2" t="n">
-        <v>-8.44</v>
+        <v>-6.36</v>
       </c>
       <c r="P2" t="n">
-        <v>-16.9</v>
+        <v>-15.85</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5457</v>
+        <v>4.5551</v>
       </c>
       <c r="D3" t="n">
-        <v>23.69</v>
+        <v>23.8</v>
       </c>
       <c r="E3" t="n">
-        <v>58.36</v>
+        <v>59.01</v>
       </c>
       <c r="F3" t="n">
-        <v>37.98</v>
+        <v>37.03</v>
       </c>
       <c r="G3" t="n">
-        <v>51.99</v>
+        <v>49.07</v>
       </c>
       <c r="H3" t="n">
-        <v>7.52</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="K3" t="n">
-        <v>23.65</v>
+        <v>21.76</v>
       </c>
       <c r="L3" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M3" t="n">
-        <v>16.74</v>
+        <v>14.85</v>
       </c>
       <c r="N3" t="n">
-        <v>-6.88</v>
+        <v>-3.73</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.87</v>
+        <v>-7.74</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.94</v>
+        <v>-3.12</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6235000000000001</v>
+        <v>0.6172</v>
       </c>
       <c r="D4" t="n">
-        <v>29.48</v>
+        <v>29.28</v>
       </c>
       <c r="E4" t="n">
-        <v>73.98999999999999</v>
+        <v>72.78</v>
       </c>
       <c r="F4" t="n">
-        <v>18.41</v>
+        <v>18.17</v>
       </c>
       <c r="G4" t="n">
-        <v>34.92</v>
+        <v>34.11</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.73</v>
+        <v>-1.9</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.61</v>
+        <v>-4.07</v>
       </c>
       <c r="P4" t="n">
-        <v>-12.76</v>
+        <v>-13.32</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.1535</v>
+        <v>5.0908</v>
       </c>
       <c r="D5" t="n">
-        <v>15.49</v>
+        <v>15.36</v>
       </c>
       <c r="E5" t="n">
-        <v>19.58</v>
+        <v>18.72</v>
       </c>
       <c r="F5" t="n">
-        <v>26.05</v>
+        <v>25.81</v>
       </c>
       <c r="G5" t="n">
-        <v>31.18</v>
+        <v>30.76</v>
       </c>
       <c r="H5" t="n">
-        <v>14.57</v>
+        <v>13.71</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>8.130000000000001</v>
+        <v>7.27</v>
       </c>
       <c r="K5" t="n">
-        <v>15.09</v>
+        <v>14.24</v>
       </c>
       <c r="L5" t="n">
         <v>83.33</v>
       </c>
       <c r="M5" t="n">
-        <v>2.71</v>
+        <v>1.86</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.44</v>
+        <v>-5.28</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.28</v>
+        <v>-13.58</v>
       </c>
       <c r="P5" t="n">
-        <v>6.12</v>
+        <v>3.26</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.7956</v>
+        <v>18.0106</v>
       </c>
       <c r="D6" t="n">
-        <v>49.84</v>
+        <v>50.63</v>
       </c>
       <c r="E6" t="n">
-        <v>60.91</v>
+        <v>62.18</v>
       </c>
       <c r="F6" t="n">
-        <v>45.55</v>
+        <v>42.78</v>
       </c>
       <c r="G6" t="n">
-        <v>71.94</v>
+        <v>67.98999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>5.42</v>
+        <v>5.08</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>2.09</v>
+        <v>1.75</v>
       </c>
       <c r="K6" t="n">
-        <v>7.98</v>
+        <v>7.5</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="M6" t="n">
-        <v>0.16</v>
+        <v>-0.33</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.890000000000001</v>
+        <v>-5.61</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.69</v>
+        <v>-15.86</v>
       </c>
       <c r="P6" t="n">
-        <v>2.63</v>
+        <v>4.13</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.7027</v>
+        <v>3.7154</v>
       </c>
       <c r="D7" t="n">
-        <v>24.04</v>
+        <v>24.2</v>
       </c>
       <c r="E7" t="n">
-        <v>11.76</v>
+        <v>13.3</v>
       </c>
       <c r="F7" t="n">
-        <v>35.33</v>
+        <v>34.35</v>
       </c>
       <c r="G7" t="n">
-        <v>39.28</v>
+        <v>37.23</v>
       </c>
       <c r="H7" t="n">
-        <v>4.65</v>
+        <v>7.54</v>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>85</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.09</v>
+        <v>1.8</v>
       </c>
       <c r="K7" t="n">
-        <v>17.44</v>
+        <v>17.72</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>10.48</v>
+        <v>10.76</v>
       </c>
       <c r="N7" t="n">
-        <v>-3.62</v>
+        <v>-2.05</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.01</v>
+        <v>-4.03</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.36</v>
+        <v>-26.73</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.3046</v>
+        <v>2.2767</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>14.72</v>
       </c>
       <c r="E8" t="n">
-        <v>64.31999999999999</v>
+        <v>58.47</v>
       </c>
       <c r="F8" t="n">
-        <v>25.4</v>
+        <v>25.72</v>
       </c>
       <c r="G8" t="n">
-        <v>32.42</v>
+        <v>34.66</v>
       </c>
       <c r="H8" t="n">
         <v>8.26</v>
@@ -1017,13 +1017,13 @@
         <v>-0.55</v>
       </c>
       <c r="N8" t="n">
-        <v>0.88</v>
+        <v>-0.39</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.82</v>
+        <v>-2.13</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.96</v>
+        <v>-6.78</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,19 +1058,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6107</v>
+        <v>3.6032</v>
       </c>
       <c r="D9" t="n">
-        <v>21.07</v>
+        <v>21.09</v>
       </c>
       <c r="E9" t="n">
-        <v>27.55</v>
+        <v>27.84</v>
       </c>
       <c r="F9" t="n">
-        <v>30.79</v>
+        <v>30.51</v>
       </c>
       <c r="G9" t="n">
-        <v>59.94</v>
+        <v>58.57</v>
       </c>
       <c r="H9" t="n">
         <v>-13.64</v>
@@ -1091,13 +1091,13 @@
         <v>-12.81</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.06</v>
       </c>
       <c r="O9" t="n">
-        <v>1.15</v>
+        <v>2.37</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.34</v>
+        <v>-17.74</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1132,40 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.54</v>
+        <v>0.5387999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>24.19</v>
+        <v>24.22</v>
       </c>
       <c r="E10" t="n">
-        <v>58.2</v>
+        <v>58.39</v>
       </c>
       <c r="F10" t="n">
-        <v>40.64</v>
+        <v>38.89</v>
       </c>
       <c r="G10" t="n">
-        <v>60.72</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>56.78</v>
+      </c>
+      <c r="H10" t="n">
+        <v>12.36</v>
+      </c>
+      <c r="I10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J10" t="n">
+        <v>8.59</v>
+      </c>
       <c r="K10" t="n">
-        <v>3.03</v>
+        <v>12.61</v>
       </c>
       <c r="L10" t="n">
-        <v>34.78</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.06</v>
+        <v>8.31</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.77</v>
+        <v>-2.1</v>
       </c>
       <c r="O10" t="n">
-        <v>-4.16</v>
+        <v>-1.69</v>
       </c>
       <c r="P10" t="n">
-        <v>-10.79</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1174,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1200,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.822</v>
+        <v>0.8211000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>32.18</v>
+        <v>32.25</v>
       </c>
       <c r="E11" t="n">
-        <v>85.76000000000001</v>
+        <v>86.16</v>
       </c>
       <c r="F11" t="n">
-        <v>38.58</v>
+        <v>37.29</v>
       </c>
       <c r="G11" t="n">
-        <v>55.57</v>
+        <v>53.04</v>
       </c>
       <c r="H11" t="n">
-        <v>9.199999999999999</v>
+        <v>5.19</v>
       </c>
       <c r="I11" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J11" t="n">
-        <v>5.33</v>
+        <v>1.32</v>
       </c>
       <c r="K11" t="n">
-        <v>8.609999999999999</v>
+        <v>7.97</v>
       </c>
       <c r="L11" t="n">
         <v>87.5</v>
       </c>
       <c r="M11" t="n">
-        <v>4.58</v>
+        <v>3.94</v>
       </c>
       <c r="N11" t="n">
-        <v>-4.75</v>
+        <v>-3.34</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.22</v>
+        <v>-4.13</v>
       </c>
       <c r="P11" t="n">
-        <v>-13.4</v>
+        <v>-12.63</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1274,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.7735</v>
+        <v>6.8339</v>
       </c>
       <c r="D12" t="n">
-        <v>31.52</v>
+        <v>31.91</v>
       </c>
       <c r="E12" t="n">
-        <v>56.27</v>
+        <v>58.7</v>
       </c>
       <c r="F12" t="n">
-        <v>42.81</v>
+        <v>42.09</v>
       </c>
       <c r="G12" t="n">
-        <v>83.87</v>
+        <v>83.02</v>
       </c>
       <c r="H12" t="n">
-        <v>6.25</v>
+        <v>6.27</v>
       </c>
       <c r="I12" t="n">
         <v>75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="K12" t="n">
-        <v>7.77</v>
+        <v>7.51</v>
       </c>
       <c r="L12" t="n">
         <v>66.67</v>
       </c>
       <c r="M12" t="n">
-        <v>1.08</v>
+        <v>0.82</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.03</v>
+        <v>-2.57</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.95</v>
+        <v>1.19</v>
       </c>
       <c r="P12" t="n">
-        <v>-16.45</v>
+        <v>-15.62</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1348,19 +1354,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.7118</v>
+        <v>2.6913</v>
       </c>
       <c r="D13" t="n">
-        <v>21.73</v>
+        <v>21.64</v>
       </c>
       <c r="E13" t="n">
-        <v>58.28</v>
+        <v>57.77</v>
       </c>
       <c r="F13" t="n">
-        <v>27.22</v>
+        <v>27.03</v>
       </c>
       <c r="G13" t="n">
-        <v>44.04</v>
+        <v>43.15</v>
       </c>
       <c r="H13" t="n">
         <v>9.529999999999999</v>
@@ -1381,13 +1387,13 @@
         <v>-0.85</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.16</v>
+        <v>-1.33</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.73</v>
+        <v>-1.89</v>
       </c>
       <c r="P13" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1422,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0561</v>
+        <v>2.0309</v>
       </c>
       <c r="D14" t="n">
-        <v>16.71</v>
+        <v>16.56</v>
       </c>
       <c r="E14" t="n">
-        <v>73.53</v>
+        <v>70.3</v>
       </c>
       <c r="F14" t="n">
-        <v>21.97</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>54.72</v>
+        <v>54.91</v>
       </c>
       <c r="H14" t="n">
-        <v>1.8</v>
+        <v>2.23</v>
       </c>
       <c r="I14" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>-3.24</v>
+        <v>-2.81</v>
       </c>
       <c r="K14" t="n">
-        <v>8.460000000000001</v>
+        <v>11.36</v>
       </c>
       <c r="L14" t="n">
-        <v>79.17</v>
+        <v>91.67</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.68</v>
+        <v>2.22</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2</v>
+        <v>-2.21</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.66</v>
+        <v>-2.06</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.17</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1496,40 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9157999999999999</v>
+        <v>0.9074</v>
       </c>
       <c r="D15" t="n">
-        <v>13.04</v>
+        <v>12.97</v>
       </c>
       <c r="E15" t="n">
-        <v>34.21</v>
+        <v>33.57</v>
       </c>
       <c r="F15" t="n">
-        <v>56.28</v>
+        <v>54.18</v>
       </c>
       <c r="G15" t="n">
-        <v>89.79000000000001</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
+        <v>88.31999999999999</v>
+      </c>
+      <c r="H15" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="I15" t="n">
+        <v>80</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.96</v>
+      </c>
       <c r="K15" t="n">
-        <v>-2.87</v>
+        <v>1.45</v>
       </c>
       <c r="L15" t="n">
-        <v>21.74</v>
+        <v>79.17</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.33</v>
+        <v>5.89</v>
       </c>
       <c r="N15" t="n">
-        <v>-7.52</v>
+        <v>-5.36</v>
       </c>
       <c r="O15" t="n">
-        <v>-3.22</v>
+        <v>-0.88</v>
       </c>
       <c r="P15" t="n">
-        <v>-22.29</v>
+        <v>-22.09</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1538,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1564,28 +1576,28 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8505</v>
+        <v>0.8512</v>
       </c>
       <c r="D16" t="n">
-        <v>31.49</v>
+        <v>31.62</v>
       </c>
       <c r="E16" t="n">
-        <v>38.7</v>
+        <v>38.9</v>
       </c>
       <c r="F16" t="n">
-        <v>36.16</v>
+        <v>35.67</v>
       </c>
       <c r="G16" t="n">
-        <v>60.41</v>
+        <v>59.27</v>
       </c>
       <c r="H16" t="n">
-        <v>2.45</v>
+        <v>4.43</v>
       </c>
       <c r="I16" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6</v>
+        <v>2.58</v>
       </c>
       <c r="K16" t="n">
         <v>-0.71</v>
@@ -1597,13 +1609,13 @@
         <v>-5.24</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.21</v>
+        <v>-3.38</v>
       </c>
       <c r="O16" t="n">
-        <v>-9.49</v>
+        <v>-6.52</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.94</v>
+        <v>-26.17</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1638,46 +1650,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5174</v>
+        <v>0.5197000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>39.58</v>
+        <v>39.89</v>
       </c>
       <c r="E17" t="n">
-        <v>19.89</v>
+        <v>20.57</v>
       </c>
       <c r="F17" t="n">
-        <v>34.98</v>
+        <v>33.68</v>
       </c>
       <c r="G17" t="n">
-        <v>24.86</v>
+        <v>21.88</v>
       </c>
       <c r="H17" t="n">
-        <v>8.76</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>3.62</v>
+        <v>3.07</v>
       </c>
       <c r="K17" t="n">
-        <v>9.41</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>3.27</v>
+        <v>2.82</v>
       </c>
       <c r="N17" t="n">
-        <v>-5.39</v>
+        <v>-3.35</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.11</v>
+        <v>-7.18</v>
       </c>
       <c r="P17" t="n">
-        <v>-22.04</v>
+        <v>-21.57</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1712,19 +1724,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.1878</v>
+        <v>6.1116</v>
       </c>
       <c r="D18" t="n">
-        <v>6.61</v>
+        <v>6.55</v>
       </c>
       <c r="E18" t="n">
-        <v>91.25</v>
+        <v>89.40000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.88</v>
+        <v>13.24</v>
       </c>
       <c r="G18" t="n">
-        <v>76.77</v>
+        <v>79.13</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1739,16 +1751,16 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>3.13</v>
+        <v>-0.11</v>
       </c>
       <c r="O18" t="n">
-        <v>2.58</v>
+        <v>2.1</v>
       </c>
       <c r="P18" t="n">
-        <v>7.2</v>
+        <v>6.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1757,10 +1769,10 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1780,46 +1792,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1833</v>
+        <v>5.0898</v>
       </c>
       <c r="D19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.15</v>
+        <v>14.49</v>
       </c>
       <c r="G19" t="n">
-        <v>14.26</v>
+        <v>16.2</v>
       </c>
       <c r="H19" t="n">
-        <v>3.04</v>
+        <v>0.72</v>
       </c>
       <c r="I19" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>-2.37</v>
+        <v>-4.7</v>
       </c>
       <c r="K19" t="n">
-        <v>3.04</v>
+        <v>-0.42</v>
       </c>
       <c r="L19" t="n">
-        <v>20.83</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-6.76</v>
+        <v>-10.22</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.35</v>
+        <v>-3.24</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.6</v>
+        <v>-5.49</v>
       </c>
       <c r="P19" t="n">
-        <v>-14.8</v>
+        <v>-15.92</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1854,19 +1866,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2019</v>
+        <v>0.2047</v>
       </c>
       <c r="D20" t="n">
-        <v>72.26000000000001</v>
+        <v>73.5</v>
       </c>
       <c r="E20" t="n">
-        <v>87.93000000000001</v>
+        <v>89.17</v>
       </c>
       <c r="F20" t="n">
-        <v>52.32</v>
+        <v>49.47</v>
       </c>
       <c r="G20" t="n">
-        <v>87.22</v>
+        <v>84.58</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1881,13 +1893,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-7.59</v>
+        <v>-3.46</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.95</v>
+        <v>-8.43</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4</v>
+        <v>1.61</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1922,19 +1934,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.8845</v>
       </c>
       <c r="D21" t="n">
-        <v>34.08</v>
+        <v>34.26</v>
       </c>
       <c r="E21" t="n">
-        <v>90.09</v>
+        <v>90.18000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>38.32</v>
+        <v>36.52</v>
       </c>
       <c r="G21" t="n">
-        <v>68.43000000000001</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="H21" t="n">
         <v>8.42</v>
@@ -1955,13 +1967,13 @@
         <v>11.09</v>
       </c>
       <c r="N21" t="n">
-        <v>-7.05</v>
+        <v>-5.21</v>
       </c>
       <c r="O21" t="n">
-        <v>-11.13</v>
+        <v>-10.79</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.66</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1996,46 +2008,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.371</v>
+        <v>1.3656</v>
       </c>
       <c r="D22" t="n">
-        <v>14.11</v>
+        <v>14.1</v>
       </c>
       <c r="E22" t="n">
-        <v>92.34</v>
+        <v>92.27</v>
       </c>
       <c r="F22" t="n">
-        <v>23.52</v>
+        <v>23.33</v>
       </c>
       <c r="G22" t="n">
-        <v>24.79</v>
+        <v>24.07</v>
       </c>
       <c r="H22" t="n">
-        <v>1.52</v>
+        <v>7.11</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.36</v>
+        <v>4.23</v>
       </c>
       <c r="K22" t="n">
-        <v>2.3</v>
+        <v>4.91</v>
       </c>
       <c r="L22" t="n">
-        <v>41.67</v>
+        <v>75</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.03</v>
+        <v>2.58</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.92</v>
+        <v>-2.62</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.84</v>
+        <v>-5.18</v>
       </c>
       <c r="P22" t="n">
-        <v>-11.55</v>
+        <v>-11.14</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2044,13 +2056,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2070,46 +2082,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.9098</v>
+        <v>7.8249</v>
       </c>
       <c r="D23" t="n">
-        <v>25.25</v>
+        <v>25.06</v>
       </c>
       <c r="E23" t="n">
-        <v>25.15</v>
+        <v>24.98</v>
       </c>
       <c r="F23" t="n">
-        <v>39.3</v>
+        <v>38.84</v>
       </c>
       <c r="G23" t="n">
-        <v>53.94</v>
+        <v>52.8</v>
       </c>
       <c r="H23" t="n">
-        <v>6.2</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3</v>
+        <v>4.48</v>
       </c>
       <c r="K23" t="n">
-        <v>8.85</v>
+        <v>17</v>
       </c>
       <c r="L23" t="n">
-        <v>70.83</v>
+        <v>95.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.43</v>
+        <v>8.58</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.06</v>
+        <v>-8.19</v>
       </c>
       <c r="O23" t="n">
-        <v>-13.04</v>
+        <v>-12.14</v>
       </c>
       <c r="P23" t="n">
-        <v>-21.88</v>
+        <v>-23.68</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2144,46 +2156,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5.9159</v>
+        <v>6.0042</v>
       </c>
       <c r="D24" t="n">
-        <v>37.14</v>
+        <v>37.82</v>
       </c>
       <c r="E24" t="n">
-        <v>81.11</v>
+        <v>83.37</v>
       </c>
       <c r="F24" t="n">
-        <v>34.07</v>
+        <v>32.74</v>
       </c>
       <c r="G24" t="n">
-        <v>45.13</v>
+        <v>42.13</v>
       </c>
       <c r="H24" t="n">
-        <v>4.15</v>
+        <v>7.14</v>
       </c>
       <c r="I24" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J24" t="n">
-        <v>0.19</v>
+        <v>3.18</v>
       </c>
       <c r="K24" t="n">
-        <v>6.94</v>
+        <v>10.38</v>
       </c>
       <c r="L24" t="n">
-        <v>70.83</v>
+        <v>91.67</v>
       </c>
       <c r="M24" t="n">
-        <v>1.6</v>
+        <v>5.04</v>
       </c>
       <c r="N24" t="n">
-        <v>-6.58</v>
+        <v>-3.1</v>
       </c>
       <c r="O24" t="n">
-        <v>-14.73</v>
+        <v>-11.46</v>
       </c>
       <c r="P24" t="n">
-        <v>-10.85</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2218,40 +2230,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7731</v>
+        <v>2.7546</v>
       </c>
       <c r="D25" t="n">
-        <v>56.34</v>
+        <v>56.15</v>
       </c>
       <c r="E25" t="n">
-        <v>40.48</v>
+        <v>39.52</v>
       </c>
       <c r="F25" t="n">
-        <v>35.05</v>
+        <v>34.8</v>
       </c>
       <c r="G25" t="n">
-        <v>52.92</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
+        <v>51.87</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-5.45</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-7.3</v>
+      </c>
       <c r="K25" t="n">
-        <v>3.7</v>
+        <v>-5.45</v>
       </c>
       <c r="L25" t="n">
-        <v>47.83</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>1.16</v>
+        <v>-10.2</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.41</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.85</v>
+        <v>-7.75</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.220000000000001</v>
+        <v>-7.91</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2286,46 +2304,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.8363</v>
+        <v>4.9144</v>
       </c>
       <c r="D26" t="n">
-        <v>57.35</v>
+        <v>58.48</v>
       </c>
       <c r="E26" t="n">
-        <v>41.56</v>
+        <v>44.24</v>
       </c>
       <c r="F26" t="n">
-        <v>34.1</v>
+        <v>33.56</v>
       </c>
       <c r="G26" t="n">
-        <v>23.07</v>
+        <v>21.18</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.62</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.15</v>
+        <v>0.38</v>
       </c>
       <c r="K26" t="n">
-        <v>9.25</v>
+        <v>8.99</v>
       </c>
       <c r="L26" t="n">
         <v>95.83</v>
       </c>
       <c r="M26" t="n">
-        <v>7.34</v>
+        <v>7.08</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.18</v>
+        <v>-1.45</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.86</v>
+        <v>-3.56</v>
       </c>
       <c r="P26" t="n">
-        <v>-28.15</v>
+        <v>-27.86</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2334,13 +2352,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2360,46 +2378,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8546</v>
+        <v>1.8593</v>
       </c>
       <c r="D27" t="n">
-        <v>34.58</v>
+        <v>34.79</v>
       </c>
       <c r="E27" t="n">
-        <v>43.81</v>
+        <v>45.01</v>
       </c>
       <c r="F27" t="n">
-        <v>61.16</v>
+        <v>62.6</v>
       </c>
       <c r="G27" t="n">
-        <v>75.84</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>3.24</v>
+        <v>3.62</v>
       </c>
       <c r="I27" t="n">
         <v>70</v>
       </c>
       <c r="J27" t="n">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="K27" t="n">
-        <v>3.24</v>
+        <v>3.35</v>
       </c>
       <c r="L27" t="n">
         <v>45.83</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.92</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-1.28</v>
+        <v>-2.13</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.74</v>
+        <v>-1.17</v>
       </c>
       <c r="P27" t="n">
-        <v>-23.24</v>
+        <v>-24.47</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2434,46 +2452,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2945</v>
+        <v>5.2819</v>
       </c>
       <c r="D28" t="n">
-        <v>41.53</v>
+        <v>41.57</v>
       </c>
       <c r="E28" t="n">
-        <v>78.64</v>
+        <v>78.65000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>35.93</v>
+        <v>34.46</v>
       </c>
       <c r="G28" t="n">
-        <v>44.89</v>
+        <v>39.72</v>
       </c>
       <c r="H28" t="n">
-        <v>16.39</v>
+        <v>12.59</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>13.68</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>14.58</v>
+        <v>10.59</v>
       </c>
       <c r="L28" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="M28" t="n">
-        <v>-7.84</v>
+        <v>-11.83</v>
       </c>
       <c r="N28" t="n">
-        <v>-10.72</v>
+        <v>-6.44</v>
       </c>
       <c r="O28" t="n">
-        <v>-20.04</v>
+        <v>-21.08</v>
       </c>
       <c r="P28" t="n">
-        <v>18.11</v>
+        <v>15.91</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2508,19 +2526,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0928</v>
+        <v>1.0743</v>
       </c>
       <c r="D29" t="n">
-        <v>18.99</v>
+        <v>18.73</v>
       </c>
       <c r="E29" t="n">
-        <v>86.61</v>
+        <v>85.25</v>
       </c>
       <c r="F29" t="n">
-        <v>38.56</v>
+        <v>38.82</v>
       </c>
       <c r="G29" t="n">
-        <v>70.06999999999999</v>
+        <v>70.53</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2535,13 +2553,13 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>0.68</v>
+        <v>0.08</v>
       </c>
       <c r="O29" t="n">
-        <v>0.73</v>
+        <v>0.86</v>
       </c>
       <c r="P29" t="n">
-        <v>26.01</v>
+        <v>25.33</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2553,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2576,46 +2594,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2694</v>
+        <v>1.2681</v>
       </c>
       <c r="D30" t="n">
-        <v>16.64</v>
+        <v>16.68</v>
       </c>
       <c r="E30" t="n">
-        <v>73.39</v>
+        <v>73.76000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>24.62</v>
+        <v>24.11</v>
       </c>
       <c r="G30" t="n">
-        <v>54.84</v>
+        <v>52.81</v>
       </c>
       <c r="H30" t="n">
-        <v>6.41</v>
+        <v>7.06</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>4.38</v>
+        <v>5.03</v>
       </c>
       <c r="K30" t="n">
-        <v>6.41</v>
+        <v>6.95</v>
       </c>
       <c r="L30" t="n">
-        <v>58.33</v>
+        <v>62.5</v>
       </c>
       <c r="M30" t="n">
-        <v>1.53</v>
+        <v>2.08</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.62</v>
+        <v>1.32</v>
       </c>
       <c r="O30" t="n">
-        <v>-3.78</v>
+        <v>-1.2</v>
       </c>
       <c r="P30" t="n">
-        <v>22.01</v>
+        <v>22.51</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2650,46 +2668,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8046</v>
+        <v>0.8042</v>
       </c>
       <c r="D31" t="n">
-        <v>23.39</v>
+        <v>23.45</v>
       </c>
       <c r="E31" t="n">
-        <v>67.47</v>
+        <v>67.92</v>
       </c>
       <c r="F31" t="n">
-        <v>27.8</v>
+        <v>27.13</v>
       </c>
       <c r="G31" t="n">
-        <v>44.38</v>
+        <v>42.61</v>
       </c>
       <c r="H31" t="n">
-        <v>10.9</v>
+        <v>8.31</v>
       </c>
       <c r="I31" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J31" t="n">
-        <v>7.55</v>
+        <v>4.96</v>
       </c>
       <c r="K31" t="n">
-        <v>11.21</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L31" t="n">
         <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>9.43</v>
+        <v>7.93</v>
       </c>
       <c r="N31" t="n">
-        <v>-7.08</v>
+        <v>-4.64</v>
       </c>
       <c r="O31" t="n">
-        <v>-9.5</v>
+        <v>-7.33</v>
       </c>
       <c r="P31" t="n">
-        <v>-10.88</v>
+        <v>-10.03</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2724,19 +2742,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.202</v>
+        <v>0.2024</v>
       </c>
       <c r="D32" t="n">
-        <v>28.23</v>
+        <v>28.38</v>
       </c>
       <c r="E32" t="n">
-        <v>6.27</v>
+        <v>7.03</v>
       </c>
       <c r="F32" t="n">
-        <v>40.51</v>
+        <v>40.16</v>
       </c>
       <c r="G32" t="n">
-        <v>65.73999999999999</v>
+        <v>64.22</v>
       </c>
       <c r="H32" t="n">
         <v>12.91</v>
@@ -2757,13 +2775,13 @@
         <v>4.46</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.82</v>
+        <v>-1.24</v>
       </c>
       <c r="O32" t="n">
-        <v>-0.1</v>
+        <v>2.66</v>
       </c>
       <c r="P32" t="n">
-        <v>-28.41</v>
+        <v>-27.77</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2925</v>
+        <v>1.3233</v>
       </c>
       <c r="D2" t="n">
-        <v>78.64</v>
+        <v>80.17</v>
       </c>
       <c r="E2" t="n">
-        <v>79.43000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>46.62</v>
+        <v>46.51</v>
       </c>
       <c r="G2" t="n">
-        <v>84.97</v>
+        <v>84.75</v>
       </c>
       <c r="H2" t="n">
-        <v>-50.42</v>
+        <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-53.06</v>
+        <v>-1.16</v>
       </c>
       <c r="K2" t="n">
-        <v>-32.02</v>
+        <v>-14.36</v>
       </c>
       <c r="L2" t="n">
-        <v>8.33</v>
+        <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-38.42</v>
+        <v>-20.77</v>
       </c>
       <c r="N2" t="n">
-        <v>-3.19</v>
+        <v>-0.95</v>
       </c>
       <c r="O2" t="n">
-        <v>-6.36</v>
+        <v>-3.08</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.85</v>
+        <v>-14.46</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5551</v>
+        <v>4.5474</v>
       </c>
       <c r="D3" t="n">
-        <v>23.8</v>
+        <v>23.66</v>
       </c>
       <c r="E3" t="n">
-        <v>59.01</v>
+        <v>57.81</v>
       </c>
       <c r="F3" t="n">
-        <v>37.03</v>
+        <v>37.06</v>
       </c>
       <c r="G3" t="n">
-        <v>49.07</v>
+        <v>49.18</v>
       </c>
       <c r="H3" t="n">
-        <v>8.039999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="I3" t="n">
         <v>85</v>
       </c>
       <c r="J3" t="n">
-        <v>4</v>
+        <v>4.09</v>
       </c>
       <c r="K3" t="n">
-        <v>21.76</v>
+        <v>19.94</v>
       </c>
       <c r="L3" t="n">
         <v>95.83</v>
       </c>
       <c r="M3" t="n">
-        <v>14.85</v>
+        <v>13.03</v>
       </c>
       <c r="N3" t="n">
-        <v>-3.73</v>
+        <v>-4.19</v>
       </c>
       <c r="O3" t="n">
-        <v>-7.74</v>
+        <v>-8.65</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.12</v>
+        <v>-3.59</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6172</v>
+        <v>0.6169</v>
       </c>
       <c r="D4" t="n">
-        <v>29.28</v>
+        <v>29.14</v>
       </c>
       <c r="E4" t="n">
-        <v>72.78</v>
+        <v>72.26000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>18.17</v>
+        <v>17.79</v>
       </c>
       <c r="G4" t="n">
-        <v>34.11</v>
+        <v>32.37</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -721,13 +721,13 @@
         <v>0.65</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9</v>
+        <v>-2.46</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.07</v>
+        <v>-4.24</v>
       </c>
       <c r="P4" t="n">
-        <v>-13.32</v>
+        <v>-13.88</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.0908</v>
+        <v>5.097</v>
       </c>
       <c r="D5" t="n">
-        <v>15.36</v>
+        <v>15.31</v>
       </c>
       <c r="E5" t="n">
-        <v>18.72</v>
+        <v>18.01</v>
       </c>
       <c r="F5" t="n">
-        <v>25.81</v>
+        <v>25.53</v>
       </c>
       <c r="G5" t="n">
-        <v>30.76</v>
+        <v>30.35</v>
       </c>
       <c r="H5" t="n">
-        <v>13.71</v>
+        <v>11.38</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>7.27</v>
+        <v>4.94</v>
       </c>
       <c r="K5" t="n">
-        <v>14.24</v>
+        <v>18.14</v>
       </c>
       <c r="L5" t="n">
-        <v>83.33</v>
+        <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>1.86</v>
+        <v>5.76</v>
       </c>
       <c r="N5" t="n">
-        <v>-5.28</v>
+        <v>-6.07</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.58</v>
+        <v>-13.55</v>
       </c>
       <c r="P5" t="n">
-        <v>3.26</v>
+        <v>2.91</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.0106</v>
+        <v>18.2302</v>
       </c>
       <c r="D6" t="n">
-        <v>50.63</v>
+        <v>51.05</v>
       </c>
       <c r="E6" t="n">
-        <v>62.18</v>
+        <v>62.6</v>
       </c>
       <c r="F6" t="n">
-        <v>42.78</v>
+        <v>41.6</v>
       </c>
       <c r="G6" t="n">
-        <v>67.98999999999999</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>5.08</v>
+        <v>5.14</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="K6" t="n">
-        <v>7.5</v>
+        <v>7.91</v>
       </c>
       <c r="L6" t="n">
-        <v>62.5</v>
+        <v>75</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.33</v>
+        <v>0.09</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.61</v>
+        <v>-5.37</v>
       </c>
       <c r="O6" t="n">
-        <v>-15.86</v>
+        <v>-14.53</v>
       </c>
       <c r="P6" t="n">
-        <v>4.13</v>
+        <v>7.92</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.7154</v>
+        <v>3.6858</v>
       </c>
       <c r="D7" t="n">
-        <v>24.2</v>
+        <v>23.91</v>
       </c>
       <c r="E7" t="n">
-        <v>13.3</v>
+        <v>11.21</v>
       </c>
       <c r="F7" t="n">
-        <v>34.35</v>
+        <v>34.01</v>
       </c>
       <c r="G7" t="n">
-        <v>37.23</v>
+        <v>36.5</v>
       </c>
       <c r="H7" t="n">
-        <v>7.54</v>
+        <v>5.65</v>
       </c>
       <c r="I7" t="n">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8</v>
+        <v>-0.09</v>
       </c>
       <c r="K7" t="n">
-        <v>17.72</v>
+        <v>16.69</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>10.76</v>
+        <v>9.74</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.05</v>
+        <v>-2.28</v>
       </c>
       <c r="O7" t="n">
-        <v>-4.03</v>
+        <v>-6.1</v>
       </c>
       <c r="P7" t="n">
-        <v>-26.73</v>
+        <v>-27.21</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -958,13 +958,13 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2767</v>
+        <v>2.2488</v>
       </c>
       <c r="D8" t="n">
-        <v>14.72</v>
+        <v>14.48</v>
       </c>
       <c r="E8" t="n">
-        <v>58.47</v>
+        <v>45.75</v>
       </c>
       <c r="F8" t="n">
-        <v>25.72</v>
+        <v>26.66</v>
       </c>
       <c r="G8" t="n">
-        <v>34.66</v>
+        <v>40.08</v>
       </c>
       <c r="H8" t="n">
         <v>8.26</v>
@@ -1008,22 +1008,22 @@
         <v>3.16</v>
       </c>
       <c r="K8" t="n">
-        <v>8.279999999999999</v>
+        <v>0.96</v>
       </c>
       <c r="L8" t="n">
-        <v>26.09</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.55</v>
+        <v>-12.08</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.39</v>
+        <v>-1.56</v>
       </c>
       <c r="O8" t="n">
-        <v>-2.13</v>
+        <v>-4.02</v>
       </c>
       <c r="P8" t="n">
-        <v>-6.78</v>
+        <v>-8.460000000000001</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,28 +1058,28 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6032</v>
+        <v>3.559</v>
       </c>
       <c r="D9" t="n">
-        <v>21.09</v>
+        <v>20.75</v>
       </c>
       <c r="E9" t="n">
-        <v>27.84</v>
+        <v>20.63</v>
       </c>
       <c r="F9" t="n">
-        <v>30.51</v>
+        <v>31.54</v>
       </c>
       <c r="G9" t="n">
-        <v>58.57</v>
+        <v>62.72</v>
       </c>
       <c r="H9" t="n">
-        <v>-13.64</v>
+        <v>2.95</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>-18.28</v>
+        <v>-1.68</v>
       </c>
       <c r="K9" t="n">
         <v>5.23</v>
@@ -1091,13 +1091,13 @@
         <v>-12.81</v>
       </c>
       <c r="N9" t="n">
-        <v>1.06</v>
+        <v>0.15</v>
       </c>
       <c r="O9" t="n">
-        <v>2.37</v>
+        <v>0.41</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.74</v>
+        <v>-18.98</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1132,19 +1132,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5387999999999999</v>
+        <v>0.5373</v>
       </c>
       <c r="D10" t="n">
-        <v>24.22</v>
+        <v>24.04</v>
       </c>
       <c r="E10" t="n">
-        <v>58.39</v>
+        <v>56.26</v>
       </c>
       <c r="F10" t="n">
-        <v>38.89</v>
+        <v>38.64</v>
       </c>
       <c r="G10" t="n">
-        <v>56.78</v>
+        <v>56.19</v>
       </c>
       <c r="H10" t="n">
         <v>12.36</v>
@@ -1165,13 +1165,13 @@
         <v>8.31</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.1</v>
+        <v>-3.44</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.69</v>
+        <v>-2.81</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.380000000000001</v>
+        <v>-9.69</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8211000000000001</v>
+        <v>0.8194</v>
       </c>
       <c r="D11" t="n">
-        <v>32.25</v>
+        <v>32.05</v>
       </c>
       <c r="E11" t="n">
-        <v>86.16</v>
+        <v>84.93000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>37.29</v>
+        <v>36.81</v>
       </c>
       <c r="G11" t="n">
-        <v>53.04</v>
+        <v>52.45</v>
       </c>
       <c r="H11" t="n">
         <v>5.19</v>
@@ -1239,13 +1239,13 @@
         <v>3.94</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.34</v>
+        <v>-3.96</v>
       </c>
       <c r="O11" t="n">
-        <v>-4.13</v>
+        <v>-5.07</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.63</v>
+        <v>-12.8</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1280,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8339</v>
+        <v>6.8554</v>
       </c>
       <c r="D12" t="n">
-        <v>31.91</v>
+        <v>31.87</v>
       </c>
       <c r="E12" t="n">
-        <v>58.7</v>
+        <v>58.58</v>
       </c>
       <c r="F12" t="n">
-        <v>42.09</v>
+        <v>42.12</v>
       </c>
       <c r="G12" t="n">
-        <v>83.02</v>
+        <v>83.11</v>
       </c>
       <c r="H12" t="n">
-        <v>6.27</v>
+        <v>6.6</v>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J12" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="K12" t="n">
-        <v>7.51</v>
+        <v>5.99</v>
       </c>
       <c r="L12" t="n">
-        <v>66.67</v>
+        <v>37.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0.82</v>
+        <v>-0.7</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.57</v>
+        <v>-1.72</v>
       </c>
       <c r="O12" t="n">
-        <v>1.19</v>
+        <v>-1.12</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.62</v>
+        <v>-14.05</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1354,19 +1354,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6913</v>
+        <v>2.6935</v>
       </c>
       <c r="D13" t="n">
-        <v>21.64</v>
+        <v>21.56</v>
       </c>
       <c r="E13" t="n">
-        <v>57.77</v>
+        <v>57.03</v>
       </c>
       <c r="F13" t="n">
-        <v>27.03</v>
+        <v>27.15</v>
       </c>
       <c r="G13" t="n">
-        <v>43.15</v>
+        <v>43.74</v>
       </c>
       <c r="H13" t="n">
         <v>9.529999999999999</v>
@@ -1387,13 +1387,13 @@
         <v>-0.85</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.33</v>
+        <v>-1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.89</v>
+        <v>-2.52</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.15</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0309</v>
+        <v>2.0255</v>
       </c>
       <c r="D14" t="n">
-        <v>16.56</v>
+        <v>16.45</v>
       </c>
       <c r="E14" t="n">
-        <v>70.3</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>22.23</v>
       </c>
       <c r="G14" t="n">
-        <v>54.91</v>
+        <v>56.11</v>
       </c>
       <c r="H14" t="n">
-        <v>2.23</v>
+        <v>5.57</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.81</v>
+        <v>0.53</v>
       </c>
       <c r="K14" t="n">
-        <v>11.36</v>
+        <v>11.19</v>
       </c>
       <c r="L14" t="n">
         <v>91.67</v>
       </c>
       <c r="M14" t="n">
-        <v>2.22</v>
+        <v>2.06</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.21</v>
+        <v>-3.75</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.06</v>
+        <v>-2.5</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.109999999999999</v>
+        <v>-8.550000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1502,19 +1502,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9074</v>
+        <v>0.9143</v>
       </c>
       <c r="D15" t="n">
-        <v>12.97</v>
+        <v>13.01</v>
       </c>
       <c r="E15" t="n">
-        <v>33.57</v>
+        <v>33.93</v>
       </c>
       <c r="F15" t="n">
-        <v>54.18</v>
+        <v>48.6</v>
       </c>
       <c r="G15" t="n">
-        <v>88.31999999999999</v>
+        <v>81.63</v>
       </c>
       <c r="H15" t="n">
         <v>1.45</v>
@@ -1535,13 +1535,13 @@
         <v>5.89</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.36</v>
+        <v>-4.4</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.88</v>
+        <v>-0.61</v>
       </c>
       <c r="P15" t="n">
-        <v>-22.09</v>
+        <v>-21.99</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1579,43 +1579,43 @@
         <v>0.8512</v>
       </c>
       <c r="D16" t="n">
-        <v>31.62</v>
+        <v>31.49</v>
       </c>
       <c r="E16" t="n">
-        <v>38.9</v>
+        <v>38.64</v>
       </c>
       <c r="F16" t="n">
-        <v>35.67</v>
+        <v>35.34</v>
       </c>
       <c r="G16" t="n">
-        <v>59.27</v>
+        <v>58.29</v>
       </c>
       <c r="H16" t="n">
-        <v>4.43</v>
+        <v>6.41</v>
       </c>
       <c r="I16" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J16" t="n">
-        <v>2.58</v>
+        <v>4.56</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.71</v>
+        <v>9.77</v>
       </c>
       <c r="L16" t="n">
-        <v>4.17</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>-5.24</v>
+        <v>5.25</v>
       </c>
       <c r="N16" t="n">
-        <v>-3.38</v>
+        <v>-4.85</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.52</v>
+        <v>-6.82</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.17</v>
+        <v>-26.12</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1650,46 +1650,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5197000000000001</v>
+        <v>0.5194</v>
       </c>
       <c r="D17" t="n">
-        <v>39.89</v>
+        <v>39.69</v>
       </c>
       <c r="E17" t="n">
-        <v>20.57</v>
+        <v>20.25</v>
       </c>
       <c r="F17" t="n">
-        <v>33.68</v>
+        <v>33.54</v>
       </c>
       <c r="G17" t="n">
-        <v>21.88</v>
+        <v>21.4</v>
       </c>
       <c r="H17" t="n">
-        <v>8.210000000000001</v>
+        <v>7.52</v>
       </c>
       <c r="I17" t="n">
         <v>100</v>
       </c>
       <c r="J17" t="n">
-        <v>3.07</v>
+        <v>2.38</v>
       </c>
       <c r="K17" t="n">
-        <v>8.949999999999999</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>2.82</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.35</v>
+        <v>-4.43</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.18</v>
+        <v>-6.63</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.57</v>
+        <v>-20.71</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.1116</v>
+        <v>6.0961</v>
       </c>
       <c r="D18" t="n">
-        <v>6.55</v>
+        <v>6.5</v>
       </c>
       <c r="E18" t="n">
-        <v>89.40000000000001</v>
+        <v>86.48</v>
       </c>
       <c r="F18" t="n">
-        <v>13.24</v>
+        <v>13.36</v>
       </c>
       <c r="G18" t="n">
-        <v>79.13</v>
+        <v>79.92</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1751,13 +1751,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.11</v>
+        <v>-0.36</v>
       </c>
       <c r="O18" t="n">
-        <v>2.1</v>
+        <v>0.57</v>
       </c>
       <c r="P18" t="n">
-        <v>6.94</v>
+        <v>6.13</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1792,19 +1792,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.0898</v>
+        <v>5.0758</v>
       </c>
       <c r="D19" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.49</v>
+        <v>14.8</v>
       </c>
       <c r="G19" t="n">
-        <v>16.2</v>
+        <v>17.51</v>
       </c>
       <c r="H19" t="n">
         <v>0.72</v>
@@ -1825,13 +1825,13 @@
         <v>-10.22</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.24</v>
+        <v>-2.96</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.49</v>
+        <v>-5.84</v>
       </c>
       <c r="P19" t="n">
-        <v>-15.92</v>
+        <v>-16.34</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1866,19 +1866,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2047</v>
+        <v>0.2058</v>
       </c>
       <c r="D20" t="n">
-        <v>73.5</v>
+        <v>73.61</v>
       </c>
       <c r="E20" t="n">
-        <v>89.17</v>
+        <v>89.34</v>
       </c>
       <c r="F20" t="n">
-        <v>49.47</v>
+        <v>48.72</v>
       </c>
       <c r="G20" t="n">
-        <v>84.58</v>
+        <v>84.05</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1893,13 +1893,13 @@
         <v>-3.88</v>
       </c>
       <c r="N20" t="n">
-        <v>-3.46</v>
+        <v>-4.71</v>
       </c>
       <c r="O20" t="n">
-        <v>-8.43</v>
+        <v>-7.5</v>
       </c>
       <c r="P20" t="n">
-        <v>1.61</v>
+        <v>3.61</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1934,46 +1934,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8845</v>
+        <v>0.8943</v>
       </c>
       <c r="D21" t="n">
-        <v>34.26</v>
+        <v>34.59</v>
       </c>
       <c r="E21" t="n">
-        <v>90.18000000000001</v>
+        <v>90.73</v>
       </c>
       <c r="F21" t="n">
-        <v>36.52</v>
+        <v>35.73</v>
       </c>
       <c r="G21" t="n">
-        <v>66.43000000000001</v>
+        <v>64.75</v>
       </c>
       <c r="H21" t="n">
-        <v>8.42</v>
+        <v>1.54</v>
       </c>
       <c r="I21" t="n">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>6.17</v>
+        <v>-0.71</v>
       </c>
       <c r="K21" t="n">
-        <v>15.7</v>
+        <v>14.24</v>
       </c>
       <c r="L21" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M21" t="n">
-        <v>11.09</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.21</v>
+        <v>-4.65</v>
       </c>
       <c r="O21" t="n">
-        <v>-10.79</v>
+        <v>-10.86</v>
       </c>
       <c r="P21" t="n">
-        <v>2.66</v>
+        <v>4.15</v>
       </c>
       <c r="Q21" t="n">
         <v>-1</v>
@@ -1982,13 +1982,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2008,46 +2008,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3656</v>
+        <v>1.3716</v>
       </c>
       <c r="D22" t="n">
         <v>14.1</v>
       </c>
       <c r="E22" t="n">
-        <v>92.27</v>
+        <v>92.19</v>
       </c>
       <c r="F22" t="n">
-        <v>23.33</v>
+        <v>23.25</v>
       </c>
       <c r="G22" t="n">
-        <v>24.07</v>
+        <v>23.66</v>
       </c>
       <c r="H22" t="n">
-        <v>7.11</v>
+        <v>6.56</v>
       </c>
       <c r="I22" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J22" t="n">
-        <v>4.23</v>
+        <v>3.69</v>
       </c>
       <c r="K22" t="n">
-        <v>4.91</v>
+        <v>5.26</v>
       </c>
       <c r="L22" t="n">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="M22" t="n">
-        <v>2.58</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.62</v>
+        <v>-2.85</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.18</v>
+        <v>-4.74</v>
       </c>
       <c r="P22" t="n">
-        <v>-11.14</v>
+        <v>-11.07</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2082,46 +2082,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.8249</v>
+        <v>7.5705</v>
       </c>
       <c r="D23" t="n">
-        <v>25.06</v>
+        <v>24.14</v>
       </c>
       <c r="E23" t="n">
-        <v>24.98</v>
+        <v>24.11</v>
       </c>
       <c r="F23" t="n">
-        <v>38.84</v>
+        <v>39.89</v>
       </c>
       <c r="G23" t="n">
-        <v>52.8</v>
+        <v>54.47</v>
       </c>
       <c r="H23" t="n">
-        <v>8.380000000000001</v>
+        <v>6.07</v>
       </c>
       <c r="I23" t="n">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="J23" t="n">
-        <v>4.48</v>
+        <v>2.17</v>
       </c>
       <c r="K23" t="n">
-        <v>17</v>
+        <v>15.67</v>
       </c>
       <c r="L23" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M23" t="n">
-        <v>8.58</v>
+        <v>7.25</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.19</v>
+        <v>-9.74</v>
       </c>
       <c r="O23" t="n">
-        <v>-12.14</v>
+        <v>-16.04</v>
       </c>
       <c r="P23" t="n">
-        <v>-23.68</v>
+        <v>-25.48</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2156,46 +2156,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.0042</v>
+        <v>6.0182</v>
       </c>
       <c r="D24" t="n">
-        <v>37.82</v>
+        <v>37.75</v>
       </c>
       <c r="E24" t="n">
-        <v>83.37</v>
+        <v>83.08</v>
       </c>
       <c r="F24" t="n">
-        <v>32.74</v>
+        <v>32.6</v>
       </c>
       <c r="G24" t="n">
-        <v>42.13</v>
+        <v>42.1</v>
       </c>
       <c r="H24" t="n">
-        <v>7.14</v>
+        <v>6.22</v>
       </c>
       <c r="I24" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J24" t="n">
-        <v>3.18</v>
+        <v>2.26</v>
       </c>
       <c r="K24" t="n">
-        <v>10.38</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>91.67</v>
+        <v>79.17</v>
       </c>
       <c r="M24" t="n">
-        <v>5.04</v>
+        <v>3.11</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.1</v>
+        <v>-3.81</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.46</v>
+        <v>-12.07</v>
       </c>
       <c r="P24" t="n">
-        <v>-8.949999999999999</v>
+        <v>-6.99</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2230,46 +2230,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7546</v>
+        <v>2.7529</v>
       </c>
       <c r="D25" t="n">
-        <v>56.15</v>
+        <v>55.86</v>
       </c>
       <c r="E25" t="n">
-        <v>39.52</v>
+        <v>38.49</v>
       </c>
       <c r="F25" t="n">
-        <v>34.8</v>
+        <v>35.58</v>
       </c>
       <c r="G25" t="n">
-        <v>51.87</v>
+        <v>54.32</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.45</v>
+        <v>-0.21</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>-7.3</v>
+        <v>-2.06</v>
       </c>
       <c r="K25" t="n">
-        <v>-5.45</v>
+        <v>-1.05</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-10.2</v>
+        <v>-5.8</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>-1.58</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.75</v>
+        <v>-6.62</v>
       </c>
       <c r="P25" t="n">
-        <v>-7.91</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2304,46 +2304,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.9144</v>
+        <v>4.963</v>
       </c>
       <c r="D26" t="n">
-        <v>58.48</v>
+        <v>58.8</v>
       </c>
       <c r="E26" t="n">
-        <v>44.24</v>
+        <v>45.21</v>
       </c>
       <c r="F26" t="n">
-        <v>33.56</v>
+        <v>34.18</v>
       </c>
       <c r="G26" t="n">
-        <v>21.18</v>
+        <v>23.35</v>
       </c>
       <c r="H26" t="n">
-        <v>0.62</v>
+        <v>1.14</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J26" t="n">
-        <v>0.38</v>
+        <v>0.89</v>
       </c>
       <c r="K26" t="n">
-        <v>8.99</v>
+        <v>7.95</v>
       </c>
       <c r="L26" t="n">
         <v>95.83</v>
       </c>
       <c r="M26" t="n">
-        <v>7.08</v>
+        <v>6.04</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.45</v>
+        <v>-1.18</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.56</v>
+        <v>-3.42</v>
       </c>
       <c r="P26" t="n">
-        <v>-27.86</v>
+        <v>-25.03</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2378,19 +2378,19 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8593</v>
+        <v>1.8665</v>
       </c>
       <c r="D27" t="n">
-        <v>34.79</v>
+        <v>34.77</v>
       </c>
       <c r="E27" t="n">
-        <v>45.01</v>
+        <v>44.9</v>
       </c>
       <c r="F27" t="n">
-        <v>62.6</v>
+        <v>64.25</v>
       </c>
       <c r="G27" t="n">
-        <v>77.95999999999999</v>
+        <v>80.86</v>
       </c>
       <c r="H27" t="n">
         <v>3.62</v>
@@ -2411,13 +2411,13 @@
         <v>-0.8100000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.13</v>
+        <v>-2.53</v>
       </c>
       <c r="O27" t="n">
-        <v>-1.17</v>
+        <v>-0.1</v>
       </c>
       <c r="P27" t="n">
-        <v>-24.47</v>
+        <v>-22.45</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2452,46 +2452,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.2819</v>
+        <v>5.3363</v>
       </c>
       <c r="D28" t="n">
-        <v>41.57</v>
+        <v>41.82</v>
       </c>
       <c r="E28" t="n">
-        <v>78.65000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="F28" t="n">
-        <v>34.46</v>
+        <v>33.65</v>
       </c>
       <c r="G28" t="n">
-        <v>39.72</v>
+        <v>37.04</v>
       </c>
       <c r="H28" t="n">
-        <v>12.59</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>9.880000000000001</v>
+        <v>6.08</v>
       </c>
       <c r="K28" t="n">
-        <v>10.59</v>
+        <v>15.4</v>
       </c>
       <c r="L28" t="n">
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="M28" t="n">
-        <v>-11.83</v>
+        <v>-7.02</v>
       </c>
       <c r="N28" t="n">
-        <v>-6.44</v>
+        <v>-7.54</v>
       </c>
       <c r="O28" t="n">
-        <v>-21.08</v>
+        <v>-18.24</v>
       </c>
       <c r="P28" t="n">
-        <v>15.91</v>
+        <v>19.65</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2526,19 +2526,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0743</v>
+        <v>1.0585</v>
       </c>
       <c r="D29" t="n">
-        <v>18.73</v>
+        <v>18.38</v>
       </c>
       <c r="E29" t="n">
-        <v>85.25</v>
+        <v>83.29000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>38.82</v>
+        <v>38.84</v>
       </c>
       <c r="G29" t="n">
-        <v>70.53</v>
+        <v>70.55</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -2553,13 +2553,13 @@
         <v>-19.59</v>
       </c>
       <c r="N29" t="n">
-        <v>0.08</v>
+        <v>-2.45</v>
       </c>
       <c r="O29" t="n">
-        <v>0.86</v>
+        <v>-0</v>
       </c>
       <c r="P29" t="n">
-        <v>25.33</v>
+        <v>23.51</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2571,10 +2571,10 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2594,19 +2594,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2681</v>
+        <v>1.2639</v>
       </c>
       <c r="D30" t="n">
-        <v>16.68</v>
+        <v>16.55</v>
       </c>
       <c r="E30" t="n">
-        <v>73.76000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="F30" t="n">
-        <v>24.11</v>
+        <v>23.98</v>
       </c>
       <c r="G30" t="n">
-        <v>52.81</v>
+        <v>52.25</v>
       </c>
       <c r="H30" t="n">
         <v>7.06</v>
@@ -2627,13 +2627,13 @@
         <v>2.08</v>
       </c>
       <c r="N30" t="n">
-        <v>1.32</v>
+        <v>-0.4</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.2</v>
+        <v>-0.58</v>
       </c>
       <c r="P30" t="n">
-        <v>22.51</v>
+        <v>20.17</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2668,46 +2668,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8042</v>
+        <v>0.8026</v>
       </c>
       <c r="D31" t="n">
-        <v>23.45</v>
+        <v>23.31</v>
       </c>
       <c r="E31" t="n">
-        <v>67.92</v>
+        <v>67.01000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>27.13</v>
+        <v>26.91</v>
       </c>
       <c r="G31" t="n">
-        <v>42.61</v>
+        <v>41.88</v>
       </c>
       <c r="H31" t="n">
-        <v>8.31</v>
+        <v>6.96</v>
       </c>
       <c r="I31" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J31" t="n">
-        <v>4.96</v>
+        <v>3.61</v>
       </c>
       <c r="K31" t="n">
-        <v>9.710000000000001</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M31" t="n">
-        <v>7.93</v>
+        <v>7.35</v>
       </c>
       <c r="N31" t="n">
-        <v>-4.64</v>
+        <v>-4.74</v>
       </c>
       <c r="O31" t="n">
-        <v>-7.33</v>
+        <v>-8.17</v>
       </c>
       <c r="P31" t="n">
-        <v>-10.03</v>
+        <v>-10.93</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2742,46 +2742,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2024</v>
+        <v>0.1994</v>
       </c>
       <c r="D32" t="n">
-        <v>28.38</v>
+        <v>27.83</v>
       </c>
       <c r="E32" t="n">
-        <v>7.03</v>
+        <v>4.54</v>
       </c>
       <c r="F32" t="n">
-        <v>40.16</v>
+        <v>40.69</v>
       </c>
       <c r="G32" t="n">
-        <v>64.22</v>
+        <v>66.06</v>
       </c>
       <c r="H32" t="n">
-        <v>12.91</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="I32" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J32" t="n">
-        <v>6.91</v>
+        <v>3.54</v>
       </c>
       <c r="K32" t="n">
-        <v>12.91</v>
+        <v>9.91</v>
       </c>
       <c r="L32" t="n">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="M32" t="n">
-        <v>4.46</v>
+        <v>1.46</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.24</v>
+        <v>-2.89</v>
       </c>
       <c r="O32" t="n">
-        <v>2.66</v>
+        <v>0.44</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.77</v>
+        <v>-29.25</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3233</v>
+        <v>1.3358</v>
       </c>
       <c r="D2" t="n">
-        <v>80.17</v>
+        <v>78.91</v>
       </c>
       <c r="E2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.38</v>
       </c>
       <c r="F2" t="n">
-        <v>46.51</v>
+        <v>47.87</v>
       </c>
       <c r="G2" t="n">
-        <v>84.75</v>
+        <v>86.78</v>
       </c>
       <c r="H2" t="n">
-        <v>1.47</v>
+        <v>2.55</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.16</v>
+        <v>-0.08</v>
       </c>
       <c r="K2" t="n">
-        <v>-14.36</v>
+        <v>-12.53</v>
       </c>
       <c r="L2" t="n">
         <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-20.77</v>
+        <v>-18.94</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.95</v>
+        <v>-1.46</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.08</v>
+        <v>-3.16</v>
       </c>
       <c r="P2" t="n">
-        <v>-14.46</v>
+        <v>-15.97</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5474</v>
+        <v>4.5161</v>
       </c>
       <c r="D3" t="n">
-        <v>23.66</v>
+        <v>22.91</v>
       </c>
       <c r="E3" t="n">
-        <v>57.81</v>
+        <v>54.67</v>
       </c>
       <c r="F3" t="n">
-        <v>37.06</v>
+        <v>38.47</v>
       </c>
       <c r="G3" t="n">
-        <v>49.18</v>
+        <v>53.89</v>
       </c>
       <c r="H3" t="n">
-        <v>8.140000000000001</v>
+        <v>6.39</v>
       </c>
       <c r="I3" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J3" t="n">
-        <v>4.09</v>
+        <v>2.35</v>
       </c>
       <c r="K3" t="n">
-        <v>19.94</v>
+        <v>17.19</v>
       </c>
       <c r="L3" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M3" t="n">
-        <v>13.03</v>
+        <v>10.28</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.19</v>
+        <v>-5.52</v>
       </c>
       <c r="O3" t="n">
-        <v>-8.65</v>
+        <v>-11.03</v>
       </c>
       <c r="P3" t="n">
-        <v>-3.59</v>
+        <v>-8.15</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,46 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6169</v>
+        <v>0.623</v>
       </c>
       <c r="D4" t="n">
-        <v>29.14</v>
+        <v>28.7</v>
       </c>
       <c r="E4" t="n">
-        <v>72.26000000000001</v>
+        <v>70.97</v>
       </c>
       <c r="F4" t="n">
         <v>17.79</v>
       </c>
       <c r="G4" t="n">
-        <v>32.37</v>
+        <v>32.27</v>
       </c>
       <c r="H4" t="n">
-        <v>3.23</v>
+        <v>7.51</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J4" t="n">
-        <v>1.07</v>
+        <v>5.35</v>
       </c>
       <c r="K4" t="n">
-        <v>3.67</v>
+        <v>7.26</v>
       </c>
       <c r="L4" t="n">
-        <v>58.33</v>
+        <v>79.17</v>
       </c>
       <c r="M4" t="n">
-        <v>0.65</v>
+        <v>4.23</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.46</v>
+        <v>-3.79</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.24</v>
+        <v>-4.94</v>
       </c>
       <c r="P4" t="n">
-        <v>-13.88</v>
+        <v>-17.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.097</v>
+        <v>5.0721</v>
       </c>
       <c r="D5" t="n">
-        <v>15.31</v>
+        <v>14.85</v>
       </c>
       <c r="E5" t="n">
-        <v>18.01</v>
+        <v>12.2</v>
       </c>
       <c r="F5" t="n">
-        <v>25.53</v>
+        <v>26.79</v>
       </c>
       <c r="G5" t="n">
-        <v>30.35</v>
+        <v>33.28</v>
       </c>
       <c r="H5" t="n">
-        <v>11.38</v>
+        <v>12.9</v>
       </c>
       <c r="I5" t="n">
         <v>100</v>
       </c>
       <c r="J5" t="n">
-        <v>4.94</v>
+        <v>6.47</v>
       </c>
       <c r="K5" t="n">
-        <v>18.14</v>
+        <v>19.76</v>
       </c>
       <c r="L5" t="n">
         <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>5.76</v>
+        <v>7.38</v>
       </c>
       <c r="N5" t="n">
-        <v>-6.07</v>
+        <v>-7.01</v>
       </c>
       <c r="O5" t="n">
-        <v>-13.55</v>
+        <v>-15.46</v>
       </c>
       <c r="P5" t="n">
-        <v>2.91</v>
+        <v>-3.79</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.2302</v>
+        <v>18.0252</v>
       </c>
       <c r="D6" t="n">
-        <v>51.05</v>
+        <v>49.21</v>
       </c>
       <c r="E6" t="n">
-        <v>62.6</v>
+        <v>59.77</v>
       </c>
       <c r="F6" t="n">
-        <v>41.6</v>
+        <v>43.04</v>
       </c>
       <c r="G6" t="n">
-        <v>65.76000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="H6" t="n">
-        <v>5.14</v>
+        <v>5.24</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.81</v>
+        <v>1.91</v>
       </c>
       <c r="K6" t="n">
-        <v>7.91</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="M6" t="n">
-        <v>0.09</v>
+        <v>0.88</v>
       </c>
       <c r="N6" t="n">
-        <v>-5.37</v>
+        <v>-6.09</v>
       </c>
       <c r="O6" t="n">
-        <v>-14.53</v>
+        <v>-18.21</v>
       </c>
       <c r="P6" t="n">
-        <v>7.92</v>
+        <v>2.42</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,49 +910,49 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.6858</v>
+        <v>3.7148</v>
       </c>
       <c r="D7" t="n">
-        <v>23.91</v>
+        <v>23.5</v>
       </c>
       <c r="E7" t="n">
-        <v>11.21</v>
+        <v>9.19</v>
       </c>
       <c r="F7" t="n">
-        <v>34.01</v>
+        <v>33.72</v>
       </c>
       <c r="G7" t="n">
-        <v>36.5</v>
+        <v>36</v>
       </c>
       <c r="H7" t="n">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="I7" t="n">
         <v>65</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.09</v>
+        <v>-0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>16.69</v>
+        <v>14.31</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>9.74</v>
+        <v>7.35</v>
       </c>
       <c r="N7" t="n">
-        <v>-2.28</v>
+        <v>-1.79</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.1</v>
+        <v>-6.49</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.21</v>
+        <v>-29.32</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2488</v>
+        <v>2.3082</v>
       </c>
       <c r="D8" t="n">
-        <v>14.48</v>
+        <v>14.49</v>
       </c>
       <c r="E8" t="n">
-        <v>45.75</v>
+        <v>46.18</v>
       </c>
       <c r="F8" t="n">
-        <v>26.66</v>
+        <v>28.11</v>
       </c>
       <c r="G8" t="n">
-        <v>40.08</v>
+        <v>45.72</v>
       </c>
       <c r="H8" t="n">
-        <v>8.26</v>
+        <v>2.15</v>
       </c>
       <c r="I8" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.16</v>
+        <v>-2.95</v>
       </c>
       <c r="K8" t="n">
-        <v>0.96</v>
+        <v>3.61</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-12.08</v>
+        <v>-9.43</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.56</v>
+        <v>-1.08</v>
       </c>
       <c r="O8" t="n">
-        <v>-4.02</v>
+        <v>-3.64</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.460000000000001</v>
+        <v>-8.82</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1032,13 +1032,13 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>-1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V8" t="inlineStr">
         <is>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.559</v>
+        <v>3.6345</v>
       </c>
       <c r="D9" t="n">
-        <v>20.75</v>
+        <v>20.66</v>
       </c>
       <c r="E9" t="n">
-        <v>20.63</v>
+        <v>18.69</v>
       </c>
       <c r="F9" t="n">
-        <v>31.54</v>
+        <v>31.64</v>
       </c>
       <c r="G9" t="n">
-        <v>62.72</v>
+        <v>63.3</v>
       </c>
       <c r="H9" t="n">
-        <v>2.95</v>
+        <v>7.23</v>
       </c>
       <c r="I9" t="n">
+        <v>75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="K9" t="n">
+        <v>10.39</v>
+      </c>
+      <c r="L9" t="n">
         <v>25</v>
       </c>
-      <c r="J9" t="n">
-        <v>-1.68</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.23</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
       <c r="M9" t="n">
-        <v>-12.81</v>
+        <v>-7.65</v>
       </c>
       <c r="N9" t="n">
-        <v>0.15</v>
+        <v>-0.72</v>
       </c>
       <c r="O9" t="n">
-        <v>0.41</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.98</v>
+        <v>-20.32</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1106,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5373</v>
+        <v>0.5375</v>
       </c>
       <c r="D10" t="n">
-        <v>24.04</v>
+        <v>23.45</v>
       </c>
       <c r="E10" t="n">
-        <v>56.26</v>
+        <v>50.58</v>
       </c>
       <c r="F10" t="n">
-        <v>38.64</v>
+        <v>39.43</v>
       </c>
       <c r="G10" t="n">
-        <v>56.19</v>
+        <v>57.93</v>
       </c>
       <c r="H10" t="n">
-        <v>12.36</v>
+        <v>12.24</v>
       </c>
       <c r="I10" t="n">
         <v>100</v>
       </c>
       <c r="J10" t="n">
-        <v>8.59</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>12.61</v>
+        <v>11.86</v>
       </c>
       <c r="L10" t="n">
         <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>8.31</v>
+        <v>7.56</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.44</v>
+        <v>-5.11</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.81</v>
+        <v>-3.64</v>
       </c>
       <c r="P10" t="n">
-        <v>-9.69</v>
+        <v>-12.03</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8194</v>
+        <v>0.8171</v>
       </c>
       <c r="D11" t="n">
-        <v>32.05</v>
+        <v>30.88</v>
       </c>
       <c r="E11" t="n">
-        <v>84.93000000000001</v>
+        <v>75.29000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>36.81</v>
+        <v>37.3</v>
       </c>
       <c r="G11" t="n">
-        <v>52.45</v>
+        <v>53.11</v>
       </c>
       <c r="H11" t="n">
-        <v>5.19</v>
+        <v>5.4</v>
       </c>
       <c r="I11" t="n">
         <v>75</v>
       </c>
       <c r="J11" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="K11" t="n">
-        <v>7.97</v>
+        <v>7.62</v>
       </c>
       <c r="L11" t="n">
         <v>87.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.94</v>
+        <v>3.59</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.96</v>
+        <v>-5.54</v>
       </c>
       <c r="O11" t="n">
-        <v>-5.07</v>
+        <v>-6.61</v>
       </c>
       <c r="P11" t="n">
-        <v>-12.8</v>
+        <v>-16</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1280,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8554</v>
+        <v>6.8474</v>
       </c>
       <c r="D12" t="n">
-        <v>31.87</v>
+        <v>31.04</v>
       </c>
       <c r="E12" t="n">
-        <v>58.58</v>
+        <v>52.43</v>
       </c>
       <c r="F12" t="n">
-        <v>42.12</v>
+        <v>41.99</v>
       </c>
       <c r="G12" t="n">
-        <v>83.11</v>
+        <v>82.89</v>
       </c>
       <c r="H12" t="n">
-        <v>6.6</v>
+        <v>6.16</v>
       </c>
       <c r="I12" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7</v>
+        <v>2.27</v>
       </c>
       <c r="K12" t="n">
-        <v>5.99</v>
+        <v>6.28</v>
       </c>
       <c r="L12" t="n">
         <v>37.5</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.7</v>
+        <v>-0.41</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.72</v>
+        <v>-3.27</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.12</v>
+        <v>-2.73</v>
       </c>
       <c r="P12" t="n">
-        <v>-14.05</v>
+        <v>-16.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6935</v>
+        <v>2.7325</v>
       </c>
       <c r="D13" t="n">
-        <v>21.56</v>
+        <v>21.33</v>
       </c>
       <c r="E13" t="n">
-        <v>57.03</v>
+        <v>55.37</v>
       </c>
       <c r="F13" t="n">
-        <v>27.15</v>
+        <v>27.86</v>
       </c>
       <c r="G13" t="n">
-        <v>43.74</v>
+        <v>46.19</v>
       </c>
       <c r="H13" t="n">
-        <v>9.529999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>4.12</v>
+        <v>3.03</v>
       </c>
       <c r="K13" t="n">
-        <v>7.67</v>
+        <v>7.57</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.85</v>
+        <v>-0.95</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.1</v>
+        <v>-3.14</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.52</v>
+        <v>-2.86</v>
       </c>
       <c r="P13" t="n">
-        <v>1.15</v>
+        <v>-0.25</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0255</v>
+        <v>2.0369</v>
       </c>
       <c r="D14" t="n">
-        <v>16.45</v>
+        <v>16.13</v>
       </c>
       <c r="E14" t="n">
-        <v>67.54000000000001</v>
+        <v>59.54</v>
       </c>
       <c r="F14" t="n">
-        <v>22.23</v>
+        <v>22.79</v>
       </c>
       <c r="G14" t="n">
-        <v>56.11</v>
+        <v>59.8</v>
       </c>
       <c r="H14" t="n">
-        <v>5.57</v>
+        <v>3.2</v>
       </c>
       <c r="I14" t="n">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.53</v>
+        <v>-1.84</v>
       </c>
       <c r="K14" t="n">
-        <v>11.19</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="M14" t="n">
-        <v>2.06</v>
+        <v>-0</v>
       </c>
       <c r="N14" t="n">
-        <v>-3.75</v>
+        <v>-6.11</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.5</v>
+        <v>-3.95</v>
       </c>
       <c r="P14" t="n">
-        <v>-8.550000000000001</v>
+        <v>-10.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9143</v>
+        <v>0.9084</v>
       </c>
       <c r="D15" t="n">
-        <v>13.01</v>
+        <v>12.6</v>
       </c>
       <c r="E15" t="n">
-        <v>33.93</v>
+        <v>30.04</v>
       </c>
       <c r="F15" t="n">
-        <v>48.6</v>
+        <v>42.22</v>
       </c>
       <c r="G15" t="n">
-        <v>81.63</v>
+        <v>72.08</v>
       </c>
       <c r="H15" t="n">
-        <v>1.45</v>
+        <v>3.68</v>
       </c>
       <c r="I15" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J15" t="n">
-        <v>0.96</v>
+        <v>3.2</v>
       </c>
       <c r="K15" t="n">
-        <v>1.45</v>
+        <v>3.99</v>
       </c>
       <c r="L15" t="n">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="M15" t="n">
-        <v>5.89</v>
+        <v>8.42</v>
       </c>
       <c r="N15" t="n">
-        <v>-4.4</v>
+        <v>-5.98</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.61</v>
+        <v>-2.35</v>
       </c>
       <c r="P15" t="n">
-        <v>-21.99</v>
+        <v>-25.08</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8512</v>
+        <v>0.854</v>
       </c>
       <c r="D16" t="n">
-        <v>31.49</v>
+        <v>30.81</v>
       </c>
       <c r="E16" t="n">
-        <v>38.64</v>
+        <v>37.07</v>
       </c>
       <c r="F16" t="n">
-        <v>35.34</v>
+        <v>35.75</v>
       </c>
       <c r="G16" t="n">
-        <v>58.29</v>
+        <v>59.33</v>
       </c>
       <c r="H16" t="n">
-        <v>6.41</v>
+        <v>2.26</v>
       </c>
       <c r="I16" t="n">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="J16" t="n">
-        <v>4.56</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>9.77</v>
+        <v>7.88</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>87.5</v>
       </c>
       <c r="M16" t="n">
-        <v>5.25</v>
+        <v>3.36</v>
       </c>
       <c r="N16" t="n">
-        <v>-4.85</v>
+        <v>-5.38</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.82</v>
+        <v>-6.05</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.12</v>
+        <v>-28.04</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5194</v>
+        <v>0.5157</v>
       </c>
       <c r="D17" t="n">
-        <v>39.69</v>
+        <v>38.43</v>
       </c>
       <c r="E17" t="n">
-        <v>20.25</v>
+        <v>18.46</v>
       </c>
       <c r="F17" t="n">
-        <v>33.54</v>
+        <v>34.48</v>
       </c>
       <c r="G17" t="n">
-        <v>21.4</v>
+        <v>23.87</v>
       </c>
       <c r="H17" t="n">
         <v>7.52</v>
@@ -1674,22 +1674,22 @@
         <v>2.38</v>
       </c>
       <c r="K17" t="n">
-        <v>9.890000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="L17" t="n">
         <v>100</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>2.84</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.43</v>
+        <v>-6.47</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.63</v>
+        <v>-7.44</v>
       </c>
       <c r="P17" t="n">
-        <v>-20.71</v>
+        <v>-23.05</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.0961</v>
+        <v>6.235</v>
       </c>
       <c r="D18" t="n">
-        <v>6.5</v>
+        <v>6.49</v>
       </c>
       <c r="E18" t="n">
-        <v>86.48</v>
+        <v>86.25</v>
       </c>
       <c r="F18" t="n">
-        <v>13.36</v>
+        <v>13.71</v>
       </c>
       <c r="G18" t="n">
-        <v>79.92</v>
+        <v>81.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
@@ -1751,13 +1751,13 @@
         <v>-0.21</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.36</v>
+        <v>-0.5</v>
       </c>
       <c r="O18" t="n">
-        <v>0.57</v>
+        <v>1.64</v>
       </c>
       <c r="P18" t="n">
-        <v>6.13</v>
+        <v>6.33</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1792,46 +1792,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.0758</v>
+        <v>5.1689</v>
       </c>
       <c r="D19" t="n">
-        <v>8.609999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>14.8</v>
+        <v>15.43</v>
       </c>
       <c r="G19" t="n">
-        <v>17.51</v>
+        <v>22.63</v>
       </c>
       <c r="H19" t="n">
-        <v>0.72</v>
+        <v>4.32</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J19" t="n">
-        <v>-4.7</v>
+        <v>-1.09</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.42</v>
+        <v>3.25</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>20.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.22</v>
+        <v>-6.55</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.96</v>
+        <v>-3.04</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.84</v>
+        <v>-5.7</v>
       </c>
       <c r="P19" t="n">
-        <v>-16.34</v>
+        <v>-20</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1866,40 +1866,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2058</v>
+        <v>0.2013</v>
       </c>
       <c r="D20" t="n">
-        <v>73.61</v>
+        <v>70.18000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>89.34</v>
+        <v>87.18000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>48.72</v>
+        <v>49.38</v>
       </c>
       <c r="G20" t="n">
-        <v>84.05</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+        <v>84.53</v>
+      </c>
+      <c r="H20" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="I20" t="n">
+        <v>100</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.04</v>
+      </c>
       <c r="K20" t="n">
-        <v>-2.69</v>
+        <v>6.3</v>
       </c>
       <c r="L20" t="n">
-        <v>13.04</v>
+        <v>91.67</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.88</v>
+        <v>7.75</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.71</v>
+        <v>-7.48</v>
       </c>
       <c r="O20" t="n">
-        <v>-7.5</v>
+        <v>-10.29</v>
       </c>
       <c r="P20" t="n">
-        <v>3.61</v>
+        <v>-2.99</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1908,13 +1914,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1934,49 +1940,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8943</v>
+        <v>0.8917</v>
       </c>
       <c r="D21" t="n">
-        <v>34.59</v>
+        <v>33.62</v>
       </c>
       <c r="E21" t="n">
-        <v>90.73</v>
+        <v>88.88</v>
       </c>
       <c r="F21" t="n">
-        <v>35.73</v>
+        <v>36.21</v>
       </c>
       <c r="G21" t="n">
-        <v>64.75</v>
+        <v>65.86</v>
       </c>
       <c r="H21" t="n">
-        <v>1.54</v>
+        <v>2.22</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.71</v>
+        <v>-0.04</v>
       </c>
       <c r="K21" t="n">
-        <v>14.24</v>
+        <v>14.44</v>
       </c>
       <c r="L21" t="n">
         <v>91.67</v>
       </c>
       <c r="M21" t="n">
-        <v>9.630000000000001</v>
+        <v>9.83</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.65</v>
+        <v>-4.41</v>
       </c>
       <c r="O21" t="n">
-        <v>-10.86</v>
+        <v>-13.68</v>
       </c>
       <c r="P21" t="n">
-        <v>4.15</v>
+        <v>-0.02</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1988,7 +1994,7 @@
         <v>-1</v>
       </c>
       <c r="U21" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V21" t="inlineStr">
         <is>
@@ -2008,46 +2014,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3716</v>
+        <v>1.3791</v>
       </c>
       <c r="D22" t="n">
-        <v>14.1</v>
+        <v>13.82</v>
       </c>
       <c r="E22" t="n">
-        <v>92.19</v>
+        <v>91.12</v>
       </c>
       <c r="F22" t="n">
-        <v>23.25</v>
+        <v>24.04</v>
       </c>
       <c r="G22" t="n">
-        <v>23.66</v>
+        <v>27.45</v>
       </c>
       <c r="H22" t="n">
-        <v>6.56</v>
+        <v>1.64</v>
       </c>
       <c r="I22" t="n">
-        <v>90</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>3.69</v>
+        <v>-1.24</v>
       </c>
       <c r="K22" t="n">
-        <v>5.26</v>
+        <v>2.83</v>
       </c>
       <c r="L22" t="n">
-        <v>79.17</v>
+        <v>45.83</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>0.5</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.85</v>
+        <v>-4.13</v>
       </c>
       <c r="O22" t="n">
-        <v>-4.74</v>
+        <v>-5.38</v>
       </c>
       <c r="P22" t="n">
-        <v>-11.07</v>
+        <v>-13.42</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2056,13 +2062,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2082,46 +2088,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.5705</v>
+        <v>7.6085</v>
       </c>
       <c r="D23" t="n">
-        <v>24.14</v>
+        <v>23.66</v>
       </c>
       <c r="E23" t="n">
-        <v>24.11</v>
+        <v>23.86</v>
       </c>
       <c r="F23" t="n">
-        <v>39.89</v>
+        <v>40.25</v>
       </c>
       <c r="G23" t="n">
-        <v>54.47</v>
+        <v>54.98</v>
       </c>
       <c r="H23" t="n">
-        <v>6.07</v>
+        <v>5.78</v>
       </c>
       <c r="I23" t="n">
         <v>75</v>
       </c>
       <c r="J23" t="n">
-        <v>2.17</v>
+        <v>1.88</v>
       </c>
       <c r="K23" t="n">
-        <v>15.67</v>
+        <v>15.14</v>
       </c>
       <c r="L23" t="n">
         <v>91.67</v>
       </c>
       <c r="M23" t="n">
-        <v>7.25</v>
+        <v>6.72</v>
       </c>
       <c r="N23" t="n">
-        <v>-9.74</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.04</v>
+        <v>-16.26</v>
       </c>
       <c r="P23" t="n">
-        <v>-25.48</v>
+        <v>-29.16</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2156,46 +2162,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.0182</v>
+        <v>6.0211</v>
       </c>
       <c r="D24" t="n">
-        <v>37.75</v>
+        <v>36.81</v>
       </c>
       <c r="E24" t="n">
-        <v>83.08</v>
+        <v>80.31</v>
       </c>
       <c r="F24" t="n">
-        <v>32.6</v>
+        <v>34.13</v>
       </c>
       <c r="G24" t="n">
-        <v>42.1</v>
+        <v>45.26</v>
       </c>
       <c r="H24" t="n">
-        <v>6.22</v>
+        <v>3.66</v>
       </c>
       <c r="I24" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="J24" t="n">
+        <v>-0.3</v>
+      </c>
+      <c r="K24" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="L24" t="n">
+        <v>75</v>
+      </c>
+      <c r="M24" t="n">
         <v>2.26</v>
       </c>
-      <c r="K24" t="n">
-        <v>8.449999999999999</v>
-      </c>
-      <c r="L24" t="n">
-        <v>79.17</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.11</v>
-      </c>
       <c r="N24" t="n">
-        <v>-3.81</v>
+        <v>-3.84</v>
       </c>
       <c r="O24" t="n">
-        <v>-12.07</v>
+        <v>-13.53</v>
       </c>
       <c r="P24" t="n">
-        <v>-6.99</v>
+        <v>-10.8</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2204,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2230,46 +2236,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7529</v>
+        <v>2.7616</v>
       </c>
       <c r="D25" t="n">
-        <v>55.86</v>
+        <v>54.43</v>
       </c>
       <c r="E25" t="n">
-        <v>38.49</v>
+        <v>28.73</v>
       </c>
       <c r="F25" t="n">
-        <v>35.58</v>
+        <v>37.39</v>
       </c>
       <c r="G25" t="n">
-        <v>54.32</v>
+        <v>58.48</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.21</v>
+        <v>2.36</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.06</v>
+        <v>0.5</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.05</v>
+        <v>0.98</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="M25" t="n">
-        <v>-5.8</v>
+        <v>-3.77</v>
       </c>
       <c r="N25" t="n">
-        <v>-1.58</v>
+        <v>-2.6</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.62</v>
+        <v>-7.67</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.109999999999999</v>
+        <v>-10.42</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2278,13 +2284,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2304,46 +2310,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.963</v>
+        <v>4.9472</v>
       </c>
       <c r="D26" t="n">
-        <v>58.8</v>
+        <v>57.16</v>
       </c>
       <c r="E26" t="n">
-        <v>45.21</v>
+        <v>41.16</v>
       </c>
       <c r="F26" t="n">
-        <v>34.18</v>
+        <v>36.15</v>
       </c>
       <c r="G26" t="n">
-        <v>23.35</v>
+        <v>27.84</v>
       </c>
       <c r="H26" t="n">
-        <v>1.14</v>
+        <v>0.82</v>
       </c>
       <c r="I26" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>0.89</v>
+        <v>0.57</v>
       </c>
       <c r="K26" t="n">
-        <v>7.95</v>
+        <v>9.94</v>
       </c>
       <c r="L26" t="n">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="M26" t="n">
-        <v>6.04</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.18</v>
+        <v>-2.33</v>
       </c>
       <c r="O26" t="n">
-        <v>-3.42</v>
+        <v>-5.22</v>
       </c>
       <c r="P26" t="n">
-        <v>-25.03</v>
+        <v>-28.06</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2378,46 +2384,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8665</v>
+        <v>1.8227</v>
       </c>
       <c r="D27" t="n">
-        <v>34.77</v>
+        <v>33.11</v>
       </c>
       <c r="E27" t="n">
-        <v>44.9</v>
+        <v>39.85</v>
       </c>
       <c r="F27" t="n">
-        <v>64.25</v>
+        <v>70.06</v>
       </c>
       <c r="G27" t="n">
-        <v>80.86</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="I27" t="n">
         <v>70</v>
       </c>
       <c r="J27" t="n">
-        <v>1.4</v>
+        <v>0.91</v>
       </c>
       <c r="K27" t="n">
-        <v>3.35</v>
+        <v>13.86</v>
       </c>
       <c r="L27" t="n">
-        <v>45.83</v>
+        <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.8100000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.53</v>
+        <v>-8.220000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.1</v>
+        <v>-3.72</v>
       </c>
       <c r="P27" t="n">
-        <v>-22.45</v>
+        <v>-26.19</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2452,46 +2458,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.3363</v>
+        <v>5.1351</v>
       </c>
       <c r="D28" t="n">
-        <v>41.82</v>
+        <v>39.24</v>
       </c>
       <c r="E28" t="n">
-        <v>78.75</v>
+        <v>77.37</v>
       </c>
       <c r="F28" t="n">
-        <v>33.65</v>
+        <v>35.85</v>
       </c>
       <c r="G28" t="n">
-        <v>37.04</v>
+        <v>44.63</v>
       </c>
       <c r="H28" t="n">
-        <v>8.789999999999999</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="I28" t="n">
         <v>100</v>
       </c>
       <c r="J28" t="n">
-        <v>6.08</v>
+        <v>5.58</v>
       </c>
       <c r="K28" t="n">
-        <v>15.4</v>
+        <v>11.64</v>
       </c>
       <c r="L28" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="M28" t="n">
-        <v>-7.02</v>
+        <v>-10.78</v>
       </c>
       <c r="N28" t="n">
-        <v>-7.54</v>
+        <v>-9.69</v>
       </c>
       <c r="O28" t="n">
-        <v>-18.24</v>
+        <v>-22.78</v>
       </c>
       <c r="P28" t="n">
-        <v>19.65</v>
+        <v>10.9</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2526,40 +2532,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0585</v>
+        <v>1.0666</v>
       </c>
       <c r="D29" t="n">
-        <v>18.38</v>
+        <v>18.06</v>
       </c>
       <c r="E29" t="n">
-        <v>83.29000000000001</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>38.84</v>
+        <v>39.74</v>
       </c>
       <c r="G29" t="n">
-        <v>70.55</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
+        <v>72.39</v>
+      </c>
+      <c r="H29" t="n">
+        <v>15.33</v>
+      </c>
+      <c r="I29" t="n">
+        <v>80</v>
+      </c>
+      <c r="J29" t="n">
+        <v>12.02</v>
+      </c>
       <c r="K29" t="n">
-        <v>-13.24</v>
+        <v>12.23</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>70.83</v>
       </c>
       <c r="M29" t="n">
-        <v>-19.59</v>
+        <v>5.88</v>
       </c>
       <c r="N29" t="n">
-        <v>-2.45</v>
+        <v>-5.49</v>
       </c>
       <c r="O29" t="n">
-        <v>-0</v>
+        <v>-1.64</v>
       </c>
       <c r="P29" t="n">
-        <v>23.51</v>
+        <v>22.38</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2568,13 +2580,13 @@
         <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
         <v>-1</v>
       </c>
       <c r="U29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2594,46 +2606,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2639</v>
+        <v>1.2745</v>
       </c>
       <c r="D30" t="n">
-        <v>16.55</v>
+        <v>16.27</v>
       </c>
       <c r="E30" t="n">
-        <v>71.89</v>
+        <v>67.20999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>23.98</v>
+        <v>25.05</v>
       </c>
       <c r="G30" t="n">
-        <v>52.25</v>
+        <v>57.2</v>
       </c>
       <c r="H30" t="n">
-        <v>7.06</v>
+        <v>6.41</v>
       </c>
       <c r="I30" t="n">
         <v>100</v>
       </c>
       <c r="J30" t="n">
-        <v>5.03</v>
+        <v>4.38</v>
       </c>
       <c r="K30" t="n">
-        <v>6.95</v>
+        <v>5.4</v>
       </c>
       <c r="L30" t="n">
-        <v>62.5</v>
+        <v>41.67</v>
       </c>
       <c r="M30" t="n">
-        <v>2.08</v>
+        <v>0.53</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.4</v>
+        <v>-3.71</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.58</v>
+        <v>-1.47</v>
       </c>
       <c r="P30" t="n">
-        <v>20.17</v>
+        <v>18.42</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2668,46 +2680,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8026</v>
+        <v>0.8052</v>
       </c>
       <c r="D31" t="n">
-        <v>23.31</v>
+        <v>22.8</v>
       </c>
       <c r="E31" t="n">
-        <v>67.01000000000001</v>
+        <v>62.84</v>
       </c>
       <c r="F31" t="n">
-        <v>26.91</v>
+        <v>27.33</v>
       </c>
       <c r="G31" t="n">
-        <v>41.88</v>
+        <v>43.14</v>
       </c>
       <c r="H31" t="n">
-        <v>6.96</v>
+        <v>6.04</v>
       </c>
       <c r="I31" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J31" t="n">
-        <v>3.61</v>
+        <v>2.69</v>
       </c>
       <c r="K31" t="n">
-        <v>9.130000000000001</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="M31" t="n">
-        <v>7.35</v>
+        <v>8.19</v>
       </c>
       <c r="N31" t="n">
-        <v>-4.74</v>
+        <v>-5.18</v>
       </c>
       <c r="O31" t="n">
-        <v>-8.17</v>
+        <v>-9.029999999999999</v>
       </c>
       <c r="P31" t="n">
-        <v>-10.93</v>
+        <v>-13.92</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2742,46 +2754,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1994</v>
+        <v>0.2027</v>
       </c>
       <c r="D32" t="n">
-        <v>27.83</v>
+        <v>27.58</v>
       </c>
       <c r="E32" t="n">
-        <v>4.54</v>
+        <v>3.68</v>
       </c>
       <c r="F32" t="n">
-        <v>40.69</v>
+        <v>40.52</v>
       </c>
       <c r="G32" t="n">
-        <v>66.06</v>
+        <v>65.75</v>
       </c>
       <c r="H32" t="n">
-        <v>9.539999999999999</v>
+        <v>8.31</v>
       </c>
       <c r="I32" t="n">
         <v>95</v>
       </c>
       <c r="J32" t="n">
-        <v>3.54</v>
+        <v>2.31</v>
       </c>
       <c r="K32" t="n">
-        <v>9.91</v>
+        <v>3.02</v>
       </c>
       <c r="L32" t="n">
-        <v>62.5</v>
+        <v>12.5</v>
       </c>
       <c r="M32" t="n">
-        <v>1.46</v>
+        <v>-5.42</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.89</v>
+        <v>-2.55</v>
       </c>
       <c r="O32" t="n">
-        <v>0.44</v>
+        <v>1.1</v>
       </c>
       <c r="P32" t="n">
-        <v>-29.25</v>
+        <v>-29.83</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3358</v>
+        <v>1.3085</v>
       </c>
       <c r="D2" t="n">
-        <v>78.91</v>
+        <v>78.88</v>
       </c>
       <c r="E2" t="n">
-        <v>79.38</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>47.87</v>
+        <v>48.01</v>
       </c>
       <c r="G2" t="n">
-        <v>86.78</v>
+        <v>87.02</v>
       </c>
       <c r="H2" t="n">
-        <v>2.55</v>
+        <v>1.47</v>
       </c>
       <c r="I2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.08</v>
+        <v>-1.16</v>
       </c>
       <c r="K2" t="n">
-        <v>-12.53</v>
+        <v>-10.21</v>
       </c>
       <c r="L2" t="n">
         <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-18.94</v>
+        <v>-16.62</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.46</v>
+        <v>-0.4</v>
       </c>
       <c r="O2" t="n">
-        <v>-3.16</v>
+        <v>-2.24</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.97</v>
+        <v>-15.96</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5161</v>
+        <v>4.493</v>
       </c>
       <c r="D3" t="n">
-        <v>22.91</v>
+        <v>23.24</v>
       </c>
       <c r="E3" t="n">
-        <v>54.67</v>
+        <v>56.33</v>
       </c>
       <c r="F3" t="n">
-        <v>38.47</v>
+        <v>37.77</v>
       </c>
       <c r="G3" t="n">
-        <v>53.89</v>
+        <v>51.2</v>
       </c>
       <c r="H3" t="n">
-        <v>6.39</v>
+        <v>6.41</v>
       </c>
       <c r="I3" t="n">
         <v>80</v>
       </c>
       <c r="J3" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="K3" t="n">
-        <v>17.19</v>
+        <v>14.76</v>
       </c>
       <c r="L3" t="n">
-        <v>91.67</v>
+        <v>83.33</v>
       </c>
       <c r="M3" t="n">
-        <v>10.28</v>
+        <v>7.85</v>
       </c>
       <c r="N3" t="n">
-        <v>-5.52</v>
+        <v>-1.74</v>
       </c>
       <c r="O3" t="n">
-        <v>-11.03</v>
+        <v>-10.71</v>
       </c>
       <c r="P3" t="n">
-        <v>-8.15</v>
+        <v>-7.59</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,46 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.623</v>
+        <v>0.6093</v>
       </c>
       <c r="D4" t="n">
-        <v>28.7</v>
+        <v>28.65</v>
       </c>
       <c r="E4" t="n">
-        <v>70.97</v>
+        <v>70.83</v>
       </c>
       <c r="F4" t="n">
-        <v>17.79</v>
+        <v>18.15</v>
       </c>
       <c r="G4" t="n">
-        <v>32.27</v>
+        <v>33.8</v>
       </c>
       <c r="H4" t="n">
-        <v>7.51</v>
+        <v>2.86</v>
       </c>
       <c r="I4" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>5.35</v>
+        <v>0.71</v>
       </c>
       <c r="K4" t="n">
-        <v>7.26</v>
+        <v>5.21</v>
       </c>
       <c r="L4" t="n">
-        <v>79.17</v>
+        <v>66.67</v>
       </c>
       <c r="M4" t="n">
-        <v>4.23</v>
+        <v>2.19</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.79</v>
+        <v>-2.56</v>
       </c>
       <c r="O4" t="n">
-        <v>-4.94</v>
+        <v>-5.11</v>
       </c>
       <c r="P4" t="n">
-        <v>-17.2</v>
+        <v>-18.2</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.0721</v>
+        <v>5.0739</v>
       </c>
       <c r="D5" t="n">
-        <v>14.85</v>
+        <v>15.16</v>
       </c>
       <c r="E5" t="n">
-        <v>12.2</v>
+        <v>16.82</v>
       </c>
       <c r="F5" t="n">
-        <v>26.79</v>
+        <v>27.04</v>
       </c>
       <c r="G5" t="n">
-        <v>33.28</v>
+        <v>34.19</v>
       </c>
       <c r="H5" t="n">
-        <v>12.9</v>
+        <v>11.22</v>
       </c>
       <c r="I5" t="n">
+        <v>95</v>
+      </c>
+      <c r="J5" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="K5" t="n">
+        <v>22.08</v>
+      </c>
+      <c r="L5" t="n">
         <v>100</v>
       </c>
-      <c r="J5" t="n">
-        <v>6.47</v>
-      </c>
-      <c r="K5" t="n">
-        <v>19.76</v>
-      </c>
-      <c r="L5" t="n">
-        <v>95.83</v>
-      </c>
       <c r="M5" t="n">
-        <v>7.38</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.01</v>
+        <v>-2.25</v>
       </c>
       <c r="O5" t="n">
-        <v>-15.46</v>
+        <v>-15.17</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.79</v>
+        <v>-4.85</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.0252</v>
+        <v>18.1951</v>
       </c>
       <c r="D6" t="n">
-        <v>49.21</v>
+        <v>50.68</v>
       </c>
       <c r="E6" t="n">
-        <v>59.77</v>
+        <v>62.19</v>
       </c>
       <c r="F6" t="n">
-        <v>43.04</v>
+        <v>42.75</v>
       </c>
       <c r="G6" t="n">
-        <v>68.58</v>
+        <v>67.91</v>
       </c>
       <c r="H6" t="n">
-        <v>5.24</v>
+        <v>5.05</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="K6" t="n">
-        <v>8.699999999999999</v>
+        <v>12.45</v>
       </c>
       <c r="L6" t="n">
-        <v>79.17</v>
+        <v>95.83</v>
       </c>
       <c r="M6" t="n">
-        <v>0.88</v>
+        <v>4.63</v>
       </c>
       <c r="N6" t="n">
-        <v>-6.09</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>-18.21</v>
+        <v>-18.84</v>
       </c>
       <c r="P6" t="n">
-        <v>2.42</v>
+        <v>4.2</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,19 +910,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.7148</v>
+        <v>3.7378</v>
       </c>
       <c r="D7" t="n">
-        <v>23.5</v>
+        <v>24.13</v>
       </c>
       <c r="E7" t="n">
-        <v>9.19</v>
+        <v>12.65</v>
       </c>
       <c r="F7" t="n">
-        <v>33.72</v>
+        <v>33.39</v>
       </c>
       <c r="G7" t="n">
-        <v>36</v>
+        <v>35.51</v>
       </c>
       <c r="H7" t="n">
         <v>5.54</v>
@@ -934,25 +934,25 @@
         <v>-0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>14.31</v>
+        <v>13.15</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>7.35</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.79</v>
+        <v>1.51</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.49</v>
+        <v>-3.7</v>
       </c>
       <c r="P7" t="n">
-        <v>-29.32</v>
+        <v>-27.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -964,7 +964,7 @@
         <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.3082</v>
+        <v>2.2815</v>
       </c>
       <c r="D8" t="n">
-        <v>14.49</v>
+        <v>14.62</v>
       </c>
       <c r="E8" t="n">
-        <v>46.18</v>
+        <v>52.7</v>
       </c>
       <c r="F8" t="n">
-        <v>28.11</v>
+        <v>30.43</v>
       </c>
       <c r="G8" t="n">
-        <v>45.72</v>
+        <v>54.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.15</v>
+        <v>2.92</v>
       </c>
       <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="n">
+        <v>-2.18</v>
+      </c>
+      <c r="K8" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="L8" t="n">
         <v>25</v>
       </c>
-      <c r="J8" t="n">
-        <v>-2.95</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0</v>
-      </c>
       <c r="M8" t="n">
-        <v>-9.43</v>
+        <v>-7.94</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.08</v>
+        <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.64</v>
+        <v>-1.54</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.82</v>
+        <v>-7.49</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6345</v>
+        <v>3.6228</v>
       </c>
       <c r="D9" t="n">
-        <v>20.66</v>
+        <v>21.01</v>
       </c>
       <c r="E9" t="n">
-        <v>18.69</v>
+        <v>26.62</v>
       </c>
       <c r="F9" t="n">
-        <v>31.64</v>
+        <v>31.55</v>
       </c>
       <c r="G9" t="n">
-        <v>63.3</v>
+        <v>62.78</v>
       </c>
       <c r="H9" t="n">
-        <v>7.23</v>
+        <v>7.18</v>
       </c>
       <c r="I9" t="n">
         <v>75</v>
       </c>
       <c r="J9" t="n">
-        <v>2.59</v>
+        <v>2.55</v>
       </c>
       <c r="K9" t="n">
-        <v>10.39</v>
+        <v>8.5</v>
       </c>
       <c r="L9" t="n">
-        <v>25</v>
+        <v>20.83</v>
       </c>
       <c r="M9" t="n">
-        <v>-7.65</v>
+        <v>-9.539999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.72</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8100000000000001</v>
+        <v>2.96</v>
       </c>
       <c r="P9" t="n">
-        <v>-20.32</v>
+        <v>-18.56</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5375</v>
+        <v>0.5336</v>
       </c>
       <c r="D10" t="n">
-        <v>23.45</v>
+        <v>23.78</v>
       </c>
       <c r="E10" t="n">
-        <v>50.58</v>
+        <v>53.55</v>
       </c>
       <c r="F10" t="n">
-        <v>39.43</v>
+        <v>39.55</v>
       </c>
       <c r="G10" t="n">
-        <v>57.93</v>
+        <v>58.2</v>
       </c>
       <c r="H10" t="n">
-        <v>12.24</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="I10" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J10" t="n">
-        <v>8.470000000000001</v>
+        <v>4.79</v>
       </c>
       <c r="K10" t="n">
-        <v>11.86</v>
+        <v>7.7</v>
       </c>
       <c r="L10" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M10" t="n">
-        <v>7.56</v>
+        <v>3.4</v>
       </c>
       <c r="N10" t="n">
-        <v>-5.11</v>
+        <v>-1.66</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.64</v>
+        <v>-3.56</v>
       </c>
       <c r="P10" t="n">
-        <v>-12.03</v>
+        <v>-10.61</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8171</v>
+        <v>0.8101</v>
       </c>
       <c r="D11" t="n">
-        <v>30.88</v>
+        <v>31.24</v>
       </c>
       <c r="E11" t="n">
-        <v>75.29000000000001</v>
+        <v>78.94</v>
       </c>
       <c r="F11" t="n">
-        <v>37.3</v>
+        <v>37.24</v>
       </c>
       <c r="G11" t="n">
-        <v>53.11</v>
+        <v>52.91</v>
       </c>
       <c r="H11" t="n">
-        <v>5.4</v>
+        <v>2.13</v>
       </c>
       <c r="I11" t="n">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>1.53</v>
+        <v>-1.74</v>
       </c>
       <c r="K11" t="n">
-        <v>7.62</v>
+        <v>5</v>
       </c>
       <c r="L11" t="n">
-        <v>87.5</v>
+        <v>62.5</v>
       </c>
       <c r="M11" t="n">
-        <v>3.59</v>
+        <v>0.96</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.54</v>
+        <v>-2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.61</v>
+        <v>-6.81</v>
       </c>
       <c r="P11" t="n">
-        <v>-16</v>
+        <v>-15.1</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1254,13 +1254,13 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1280,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8474</v>
+        <v>6.847</v>
       </c>
       <c r="D12" t="n">
-        <v>31.04</v>
+        <v>31.67</v>
       </c>
       <c r="E12" t="n">
-        <v>52.43</v>
+        <v>57.1</v>
       </c>
       <c r="F12" t="n">
-        <v>41.99</v>
+        <v>40.34</v>
       </c>
       <c r="G12" t="n">
-        <v>82.89</v>
+        <v>80.5</v>
       </c>
       <c r="H12" t="n">
-        <v>6.16</v>
+        <v>5.64</v>
       </c>
       <c r="I12" t="n">
         <v>75</v>
       </c>
       <c r="J12" t="n">
-        <v>2.27</v>
+        <v>1.75</v>
       </c>
       <c r="K12" t="n">
-        <v>6.28</v>
+        <v>6.53</v>
       </c>
       <c r="L12" t="n">
         <v>37.5</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.41</v>
+        <v>-0.16</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.27</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.73</v>
+        <v>-1.27</v>
       </c>
       <c r="P12" t="n">
-        <v>-16.5</v>
+        <v>-15.98</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.7325</v>
+        <v>2.6615</v>
       </c>
       <c r="D13" t="n">
-        <v>21.33</v>
+        <v>21.2</v>
       </c>
       <c r="E13" t="n">
-        <v>55.37</v>
+        <v>54.86</v>
       </c>
       <c r="F13" t="n">
-        <v>27.86</v>
+        <v>27.84</v>
       </c>
       <c r="G13" t="n">
-        <v>46.19</v>
+        <v>46.15</v>
       </c>
       <c r="H13" t="n">
-        <v>8.44</v>
+        <v>7.56</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>3.03</v>
+        <v>2.15</v>
       </c>
       <c r="K13" t="n">
-        <v>7.57</v>
+        <v>7.45</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.95</v>
+        <v>-1.07</v>
       </c>
       <c r="N13" t="n">
-        <v>-3.14</v>
+        <v>-1.99</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.86</v>
+        <v>-3.7</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.25</v>
+        <v>-0.87</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0369</v>
+        <v>2.0066</v>
       </c>
       <c r="D14" t="n">
-        <v>16.13</v>
+        <v>16.21</v>
       </c>
       <c r="E14" t="n">
-        <v>59.54</v>
+        <v>61.19</v>
       </c>
       <c r="F14" t="n">
-        <v>22.79</v>
+        <v>22.5</v>
       </c>
       <c r="G14" t="n">
-        <v>59.8</v>
+        <v>57.89</v>
       </c>
       <c r="H14" t="n">
-        <v>3.2</v>
+        <v>3.44</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.84</v>
+        <v>-1.6</v>
       </c>
       <c r="K14" t="n">
-        <v>9.140000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="L14" t="n">
         <v>83.33</v>
       </c>
       <c r="M14" t="n">
-        <v>-0</v>
+        <v>-0.09</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.11</v>
+        <v>-2.9</v>
       </c>
       <c r="O14" t="n">
-        <v>-3.95</v>
+        <v>-2.86</v>
       </c>
       <c r="P14" t="n">
-        <v>-10.4</v>
+        <v>-9.960000000000001</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9084</v>
+        <v>0.9016</v>
       </c>
       <c r="D15" t="n">
-        <v>12.6</v>
+        <v>12.77</v>
       </c>
       <c r="E15" t="n">
-        <v>30.04</v>
+        <v>31.71</v>
       </c>
       <c r="F15" t="n">
-        <v>42.22</v>
+        <v>37.92</v>
       </c>
       <c r="G15" t="n">
-        <v>72.08</v>
+        <v>62.63</v>
       </c>
       <c r="H15" t="n">
-        <v>3.68</v>
+        <v>-0.28</v>
       </c>
       <c r="I15" t="n">
-        <v>90</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>3.2</v>
+        <v>-0.77</v>
       </c>
       <c r="K15" t="n">
-        <v>3.99</v>
+        <v>0.54</v>
       </c>
       <c r="L15" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="M15" t="n">
-        <v>8.42</v>
+        <v>4.97</v>
       </c>
       <c r="N15" t="n">
-        <v>-5.98</v>
+        <v>-3.61</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.35</v>
+        <v>-2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>-25.08</v>
+        <v>-25.65</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1550,13 +1550,13 @@
         <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
         <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.854</v>
+        <v>0.8554</v>
       </c>
       <c r="D16" t="n">
-        <v>30.81</v>
+        <v>31.49</v>
       </c>
       <c r="E16" t="n">
-        <v>37.07</v>
+        <v>38.66</v>
       </c>
       <c r="F16" t="n">
-        <v>35.75</v>
+        <v>36.05</v>
       </c>
       <c r="G16" t="n">
-        <v>59.33</v>
+        <v>60.37</v>
       </c>
       <c r="H16" t="n">
-        <v>2.26</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.73</v>
       </c>
       <c r="K16" t="n">
-        <v>7.88</v>
+        <v>7.53</v>
       </c>
       <c r="L16" t="n">
         <v>87.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.36</v>
+        <v>3.01</v>
       </c>
       <c r="N16" t="n">
-        <v>-5.38</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.05</v>
+        <v>-4.36</v>
       </c>
       <c r="P16" t="n">
-        <v>-28.04</v>
+        <v>-26.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1650,46 +1650,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5157</v>
+        <v>0.5149</v>
       </c>
       <c r="D17" t="n">
-        <v>38.43</v>
+        <v>39.16</v>
       </c>
       <c r="E17" t="n">
-        <v>18.46</v>
+        <v>19.21</v>
       </c>
       <c r="F17" t="n">
-        <v>34.48</v>
+        <v>34.61</v>
       </c>
       <c r="G17" t="n">
-        <v>23.87</v>
+        <v>24.32</v>
       </c>
       <c r="H17" t="n">
-        <v>7.52</v>
+        <v>6.01</v>
       </c>
       <c r="I17" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>2.38</v>
+        <v>0.87</v>
       </c>
       <c r="K17" t="n">
-        <v>8.98</v>
+        <v>6.32</v>
       </c>
       <c r="L17" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M17" t="n">
-        <v>2.84</v>
+        <v>0.18</v>
       </c>
       <c r="N17" t="n">
-        <v>-6.47</v>
+        <v>-1.87</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.44</v>
+        <v>-6.28</v>
       </c>
       <c r="P17" t="n">
-        <v>-23.05</v>
+        <v>-21.64</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1724,40 +1724,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.235</v>
+        <v>6.0302</v>
       </c>
       <c r="D18" t="n">
-        <v>6.49</v>
+        <v>6.4</v>
       </c>
       <c r="E18" t="n">
-        <v>86.25</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>13.71</v>
+        <v>14.43</v>
       </c>
       <c r="G18" t="n">
-        <v>81.8</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+        <v>86.79000000000001</v>
+      </c>
+      <c r="H18" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="I18" t="n">
+        <v>55</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.15</v>
+      </c>
       <c r="K18" t="n">
-        <v>5.41</v>
+        <v>8.07</v>
       </c>
       <c r="L18" t="n">
-        <v>26.09</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5</v>
+        <v>-1.58</v>
       </c>
       <c r="O18" t="n">
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="P18" t="n">
-        <v>6.33</v>
+        <v>5.73</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1766,13 +1772,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T18" t="n">
         <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1792,46 +1798,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1689</v>
+        <v>5.1419</v>
       </c>
       <c r="D19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.68</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="F19" t="n">
-        <v>15.43</v>
+        <v>16.07</v>
       </c>
       <c r="G19" t="n">
-        <v>22.63</v>
+        <v>26.34</v>
       </c>
       <c r="H19" t="n">
-        <v>4.32</v>
+        <v>4.54</v>
       </c>
       <c r="I19" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.09</v>
+        <v>-0.87</v>
       </c>
       <c r="K19" t="n">
-        <v>3.25</v>
+        <v>11.26</v>
       </c>
       <c r="L19" t="n">
-        <v>20.83</v>
+        <v>95.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-6.55</v>
+        <v>1.46</v>
       </c>
       <c r="N19" t="n">
-        <v>-3.04</v>
+        <v>-1.32</v>
       </c>
       <c r="O19" t="n">
-        <v>-5.7</v>
+        <v>-4.43</v>
       </c>
       <c r="P19" t="n">
-        <v>-20</v>
+        <v>-17.86</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1866,19 +1872,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2013</v>
+        <v>0.1985</v>
       </c>
       <c r="D20" t="n">
-        <v>70.18000000000001</v>
+        <v>70.68000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>87.18000000000001</v>
+        <v>87.27</v>
       </c>
       <c r="F20" t="n">
-        <v>49.38</v>
+        <v>45.96</v>
       </c>
       <c r="G20" t="n">
-        <v>84.53</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="H20" t="n">
         <v>6.3</v>
@@ -1890,22 +1896,22 @@
         <v>3.04</v>
       </c>
       <c r="K20" t="n">
-        <v>6.3</v>
+        <v>6.11</v>
       </c>
       <c r="L20" t="n">
         <v>91.67</v>
       </c>
       <c r="M20" t="n">
-        <v>7.75</v>
+        <v>7.56</v>
       </c>
       <c r="N20" t="n">
-        <v>-7.48</v>
+        <v>-4.12</v>
       </c>
       <c r="O20" t="n">
-        <v>-10.29</v>
+        <v>-11.13</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.99</v>
+        <v>-1.28</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1940,46 +1946,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8917</v>
+        <v>0.8756</v>
       </c>
       <c r="D21" t="n">
-        <v>33.62</v>
+        <v>33.7</v>
       </c>
       <c r="E21" t="n">
-        <v>88.88</v>
+        <v>88.97</v>
       </c>
       <c r="F21" t="n">
-        <v>36.21</v>
+        <v>37.57</v>
       </c>
       <c r="G21" t="n">
-        <v>65.86</v>
+        <v>67.83</v>
       </c>
       <c r="H21" t="n">
-        <v>2.22</v>
+        <v>1.67</v>
       </c>
       <c r="I21" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.04</v>
+        <v>-0.58</v>
       </c>
       <c r="K21" t="n">
-        <v>14.44</v>
+        <v>12.29</v>
       </c>
       <c r="L21" t="n">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="M21" t="n">
-        <v>9.83</v>
+        <v>7.68</v>
       </c>
       <c r="N21" t="n">
-        <v>-4.41</v>
+        <v>-2.21</v>
       </c>
       <c r="O21" t="n">
-        <v>-13.68</v>
+        <v>-14.26</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2014,46 +2020,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3791</v>
+        <v>1.3539</v>
       </c>
       <c r="D22" t="n">
-        <v>13.82</v>
+        <v>13.85</v>
       </c>
       <c r="E22" t="n">
-        <v>91.12</v>
+        <v>91.2</v>
       </c>
       <c r="F22" t="n">
-        <v>24.04</v>
+        <v>24.74</v>
       </c>
       <c r="G22" t="n">
-        <v>27.45</v>
+        <v>30.61</v>
       </c>
       <c r="H22" t="n">
-        <v>1.64</v>
+        <v>2.53</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.24</v>
+        <v>-0.35</v>
       </c>
       <c r="K22" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="L22" t="n">
-        <v>45.83</v>
+        <v>50</v>
       </c>
       <c r="M22" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="N22" t="n">
-        <v>-4.13</v>
+        <v>-2.5</v>
       </c>
       <c r="O22" t="n">
-        <v>-5.38</v>
+        <v>-6.07</v>
       </c>
       <c r="P22" t="n">
-        <v>-13.42</v>
+        <v>-13.92</v>
       </c>
       <c r="Q22" t="n">
         <v>-1</v>
@@ -2088,46 +2094,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.6085</v>
+        <v>7.729</v>
       </c>
       <c r="D23" t="n">
-        <v>23.66</v>
+        <v>24.53</v>
       </c>
       <c r="E23" t="n">
-        <v>23.86</v>
+        <v>24.38</v>
       </c>
       <c r="F23" t="n">
-        <v>40.25</v>
+        <v>38.93</v>
       </c>
       <c r="G23" t="n">
-        <v>54.98</v>
+        <v>52.91</v>
       </c>
       <c r="H23" t="n">
-        <v>5.78</v>
+        <v>4.34</v>
       </c>
       <c r="I23" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="J23" t="n">
-        <v>1.88</v>
+        <v>0.44</v>
       </c>
       <c r="K23" t="n">
-        <v>15.14</v>
+        <v>13.77</v>
       </c>
       <c r="L23" t="n">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="M23" t="n">
-        <v>6.72</v>
+        <v>5.35</v>
       </c>
       <c r="N23" t="n">
-        <v>-8.949999999999999</v>
+        <v>-3.54</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.26</v>
+        <v>-13.08</v>
       </c>
       <c r="P23" t="n">
-        <v>-29.16</v>
+        <v>-27.8</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2162,46 +2168,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.0211</v>
+        <v>6.1087</v>
       </c>
       <c r="D24" t="n">
-        <v>36.81</v>
+        <v>38.11</v>
       </c>
       <c r="E24" t="n">
-        <v>80.31</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>34.13</v>
+        <v>35.09</v>
       </c>
       <c r="G24" t="n">
-        <v>45.26</v>
+        <v>47.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.66</v>
+        <v>3.46</v>
       </c>
       <c r="I24" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
       <c r="K24" t="n">
-        <v>7.6</v>
+        <v>8.07</v>
       </c>
       <c r="L24" t="n">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="M24" t="n">
-        <v>2.26</v>
+        <v>2.73</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.84</v>
+        <v>3.01</v>
       </c>
       <c r="O24" t="n">
-        <v>-13.53</v>
+        <v>-11.77</v>
       </c>
       <c r="P24" t="n">
-        <v>-10.8</v>
+        <v>-7.62</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2236,46 +2242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7616</v>
+        <v>2.7562</v>
       </c>
       <c r="D25" t="n">
-        <v>54.43</v>
+        <v>55.43</v>
       </c>
       <c r="E25" t="n">
-        <v>28.73</v>
+        <v>35.65</v>
       </c>
       <c r="F25" t="n">
-        <v>37.39</v>
+        <v>37.79</v>
       </c>
       <c r="G25" t="n">
-        <v>58.48</v>
+        <v>59.36</v>
       </c>
       <c r="H25" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="I25" t="n">
         <v>55</v>
       </c>
       <c r="J25" t="n">
-        <v>0.5</v>
+        <v>0.42</v>
       </c>
       <c r="K25" t="n">
-        <v>0.98</v>
+        <v>1.22</v>
       </c>
       <c r="L25" t="n">
-        <v>8.33</v>
+        <v>12.5</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.77</v>
+        <v>-3.53</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.6</v>
+        <v>0.32</v>
       </c>
       <c r="O25" t="n">
-        <v>-7.67</v>
+        <v>-6.81</v>
       </c>
       <c r="P25" t="n">
-        <v>-10.42</v>
+        <v>-11.07</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2310,46 +2316,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.9472</v>
+        <v>5.0744</v>
       </c>
       <c r="D26" t="n">
-        <v>57.16</v>
+        <v>59.83</v>
       </c>
       <c r="E26" t="n">
-        <v>41.16</v>
+        <v>47.61</v>
       </c>
       <c r="F26" t="n">
-        <v>36.15</v>
+        <v>37.65</v>
       </c>
       <c r="G26" t="n">
-        <v>27.84</v>
+        <v>31.55</v>
       </c>
       <c r="H26" t="n">
-        <v>0.82</v>
+        <v>1.02</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J26" t="n">
-        <v>0.57</v>
+        <v>0.77</v>
       </c>
       <c r="K26" t="n">
-        <v>9.94</v>
+        <v>7.74</v>
       </c>
       <c r="L26" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M26" t="n">
-        <v>8.029999999999999</v>
+        <v>5.83</v>
       </c>
       <c r="N26" t="n">
-        <v>-2.33</v>
+        <v>5.21</v>
       </c>
       <c r="O26" t="n">
-        <v>-5.22</v>
+        <v>-1.6</v>
       </c>
       <c r="P26" t="n">
-        <v>-28.06</v>
+        <v>-25.55</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2384,46 +2390,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8227</v>
+        <v>1.8537</v>
       </c>
       <c r="D27" t="n">
-        <v>33.11</v>
+        <v>34.36</v>
       </c>
       <c r="E27" t="n">
-        <v>39.85</v>
+        <v>42.82</v>
       </c>
       <c r="F27" t="n">
-        <v>70.06</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>85.06999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="H27" t="n">
-        <v>3.13</v>
+        <v>2.72</v>
       </c>
       <c r="I27" t="n">
         <v>70</v>
       </c>
       <c r="J27" t="n">
-        <v>0.91</v>
+        <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>13.86</v>
+        <v>10.09</v>
       </c>
       <c r="L27" t="n">
         <v>100</v>
       </c>
       <c r="M27" t="n">
-        <v>9.699999999999999</v>
+        <v>5.93</v>
       </c>
       <c r="N27" t="n">
-        <v>-8.220000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="O27" t="n">
-        <v>-3.72</v>
+        <v>-0.31</v>
       </c>
       <c r="P27" t="n">
-        <v>-26.19</v>
+        <v>-23.46</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2458,19 +2464,19 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.1351</v>
+        <v>5.126</v>
       </c>
       <c r="D28" t="n">
-        <v>39.24</v>
+        <v>39.97</v>
       </c>
       <c r="E28" t="n">
-        <v>77.37</v>
+        <v>77.78</v>
       </c>
       <c r="F28" t="n">
-        <v>35.85</v>
+        <v>35.53</v>
       </c>
       <c r="G28" t="n">
-        <v>44.63</v>
+        <v>43.82</v>
       </c>
       <c r="H28" t="n">
         <v>8.289999999999999</v>
@@ -2482,22 +2488,22 @@
         <v>5.58</v>
       </c>
       <c r="K28" t="n">
-        <v>11.64</v>
+        <v>12.43</v>
       </c>
       <c r="L28" t="n">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="M28" t="n">
-        <v>-10.78</v>
+        <v>-9.99</v>
       </c>
       <c r="N28" t="n">
-        <v>-9.69</v>
+        <v>-3.6</v>
       </c>
       <c r="O28" t="n">
-        <v>-22.78</v>
+        <v>-24.77</v>
       </c>
       <c r="P28" t="n">
-        <v>10.9</v>
+        <v>15.08</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2532,46 +2538,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0666</v>
+        <v>1.0454</v>
       </c>
       <c r="D29" t="n">
         <v>18.06</v>
       </c>
       <c r="E29" t="n">
-        <v>81.51000000000001</v>
+        <v>81.44</v>
       </c>
       <c r="F29" t="n">
-        <v>39.74</v>
+        <v>38.55</v>
       </c>
       <c r="G29" t="n">
-        <v>72.39</v>
+        <v>69.83</v>
       </c>
       <c r="H29" t="n">
-        <v>15.33</v>
+        <v>8.81</v>
       </c>
       <c r="I29" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="J29" t="n">
-        <v>12.02</v>
+        <v>5.5</v>
       </c>
       <c r="K29" t="n">
-        <v>12.23</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>70.83</v>
+        <v>45.83</v>
       </c>
       <c r="M29" t="n">
-        <v>5.88</v>
+        <v>2.52</v>
       </c>
       <c r="N29" t="n">
-        <v>-5.49</v>
+        <v>-4.12</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.64</v>
+        <v>-1.41</v>
       </c>
       <c r="P29" t="n">
-        <v>22.38</v>
+        <v>22.41</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2606,46 +2612,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2745</v>
+        <v>1.2546</v>
       </c>
       <c r="D30" t="n">
-        <v>16.27</v>
+        <v>16.35</v>
       </c>
       <c r="E30" t="n">
-        <v>67.20999999999999</v>
+        <v>68.52</v>
       </c>
       <c r="F30" t="n">
-        <v>25.05</v>
+        <v>24.66</v>
       </c>
       <c r="G30" t="n">
-        <v>57.2</v>
+        <v>55.43</v>
       </c>
       <c r="H30" t="n">
-        <v>6.41</v>
+        <v>3.85</v>
       </c>
       <c r="I30" t="n">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>4.38</v>
+        <v>1.82</v>
       </c>
       <c r="K30" t="n">
-        <v>5.4</v>
+        <v>3.7</v>
       </c>
       <c r="L30" t="n">
-        <v>41.67</v>
+        <v>29.17</v>
       </c>
       <c r="M30" t="n">
-        <v>0.53</v>
+        <v>-1.17</v>
       </c>
       <c r="N30" t="n">
-        <v>-3.71</v>
+        <v>-1.54</v>
       </c>
       <c r="O30" t="n">
-        <v>-1.47</v>
+        <v>-0.67</v>
       </c>
       <c r="P30" t="n">
-        <v>18.42</v>
+        <v>19.16</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2680,46 +2686,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8052</v>
+        <v>0.7969000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>22.8</v>
+        <v>23.03</v>
       </c>
       <c r="E31" t="n">
-        <v>62.84</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>27.33</v>
+        <v>27.26</v>
       </c>
       <c r="G31" t="n">
-        <v>43.14</v>
+        <v>42.84</v>
       </c>
       <c r="H31" t="n">
-        <v>6.04</v>
+        <v>4.18</v>
       </c>
       <c r="I31" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="J31" t="n">
-        <v>2.69</v>
+        <v>0.83</v>
       </c>
       <c r="K31" t="n">
-        <v>9.970000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="L31" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M31" t="n">
-        <v>8.19</v>
+        <v>6.77</v>
       </c>
       <c r="N31" t="n">
-        <v>-5.18</v>
+        <v>-1.76</v>
       </c>
       <c r="O31" t="n">
-        <v>-9.029999999999999</v>
+        <v>-9.26</v>
       </c>
       <c r="P31" t="n">
-        <v>-13.92</v>
+        <v>-12.37</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2754,46 +2760,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2027</v>
+        <v>0.2023</v>
       </c>
       <c r="D32" t="n">
-        <v>27.58</v>
+        <v>28.1</v>
       </c>
       <c r="E32" t="n">
-        <v>3.68</v>
+        <v>5.73</v>
       </c>
       <c r="F32" t="n">
-        <v>40.52</v>
+        <v>39.65</v>
       </c>
       <c r="G32" t="n">
-        <v>65.75</v>
+        <v>62.41</v>
       </c>
       <c r="H32" t="n">
-        <v>8.31</v>
+        <v>9.67</v>
       </c>
       <c r="I32" t="n">
         <v>95</v>
       </c>
       <c r="J32" t="n">
-        <v>2.31</v>
+        <v>3.67</v>
       </c>
       <c r="K32" t="n">
-        <v>3.02</v>
+        <v>4.67</v>
       </c>
       <c r="L32" t="n">
-        <v>12.5</v>
+        <v>25</v>
       </c>
       <c r="M32" t="n">
-        <v>-5.42</v>
+        <v>-3.78</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.55</v>
+        <v>-0.47</v>
       </c>
       <c r="O32" t="n">
-        <v>1.1</v>
+        <v>1.95</v>
       </c>
       <c r="P32" t="n">
-        <v>-29.83</v>
+        <v>-28.76</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -555,22 +555,22 @@
         <v>87.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="I2" t="n">
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.16</v>
+        <v>-1.13</v>
       </c>
       <c r="K2" t="n">
-        <v>-10.21</v>
+        <v>-9.210000000000001</v>
       </c>
       <c r="L2" t="n">
         <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-16.62</v>
+        <v>-15.62</v>
       </c>
       <c r="N2" t="n">
         <v>-0.4</v>
@@ -629,22 +629,22 @@
         <v>51.2</v>
       </c>
       <c r="H3" t="n">
-        <v>6.41</v>
+        <v>5.58</v>
       </c>
       <c r="I3" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J3" t="n">
-        <v>2.37</v>
+        <v>1.54</v>
       </c>
       <c r="K3" t="n">
-        <v>14.76</v>
+        <v>14.14</v>
       </c>
       <c r="L3" t="n">
         <v>83.33</v>
       </c>
       <c r="M3" t="n">
-        <v>7.85</v>
+        <v>7.23</v>
       </c>
       <c r="N3" t="n">
         <v>-1.74</v>
@@ -786,13 +786,13 @@
         <v>4.78</v>
       </c>
       <c r="K5" t="n">
-        <v>22.08</v>
+        <v>21.34</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>9.699999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="N5" t="n">
         <v>-2.25</v>
@@ -851,22 +851,22 @@
         <v>67.91</v>
       </c>
       <c r="H6" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>12.45</v>
+        <v>15.43</v>
       </c>
       <c r="L6" t="n">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>4.63</v>
+        <v>7.61</v>
       </c>
       <c r="N6" t="n">
         <v>0.15</v>
@@ -934,13 +934,13 @@
         <v>-0.2</v>
       </c>
       <c r="K7" t="n">
-        <v>13.15</v>
+        <v>11.67</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>4.72</v>
       </c>
       <c r="N7" t="n">
         <v>1.51</v>
@@ -999,22 +999,22 @@
         <v>54.86</v>
       </c>
       <c r="H8" t="n">
-        <v>2.92</v>
+        <v>2.36</v>
       </c>
       <c r="I8" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.18</v>
+        <v>-2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>5.09</v>
+        <v>5.38</v>
       </c>
       <c r="L8" t="n">
         <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.94</v>
+        <v>-7.66</v>
       </c>
       <c r="N8" t="n">
         <v>0.44</v>
@@ -1073,22 +1073,22 @@
         <v>62.78</v>
       </c>
       <c r="H9" t="n">
-        <v>7.18</v>
+        <v>7.44</v>
       </c>
       <c r="I9" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J9" t="n">
-        <v>2.55</v>
+        <v>2.8</v>
       </c>
       <c r="K9" t="n">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="L9" t="n">
         <v>20.83</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.539999999999999</v>
+        <v>-9.380000000000001</v>
       </c>
       <c r="N9" t="n">
         <v>-0.5600000000000001</v>
@@ -1147,22 +1147,22 @@
         <v>58.2</v>
       </c>
       <c r="H10" t="n">
-        <v>8.550000000000001</v>
+        <v>5.96</v>
       </c>
       <c r="I10" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J10" t="n">
-        <v>4.79</v>
+        <v>2.2</v>
       </c>
       <c r="K10" t="n">
-        <v>7.7</v>
+        <v>6.9</v>
       </c>
       <c r="L10" t="n">
         <v>95.83</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>2.59</v>
       </c>
       <c r="N10" t="n">
         <v>-1.66</v>
@@ -1230,13 +1230,13 @@
         <v>-1.74</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="L11" t="n">
-        <v>62.5</v>
+        <v>58.33</v>
       </c>
       <c r="M11" t="n">
-        <v>0.96</v>
+        <v>0.52</v>
       </c>
       <c r="N11" t="n">
         <v>-2.43</v>
@@ -1295,22 +1295,22 @@
         <v>80.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.64</v>
+        <v>5.09</v>
       </c>
       <c r="I12" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="J12" t="n">
-        <v>1.75</v>
+        <v>1.2</v>
       </c>
       <c r="K12" t="n">
-        <v>6.53</v>
+        <v>6.18</v>
       </c>
       <c r="L12" t="n">
         <v>37.5</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.16</v>
+        <v>-0.51</v>
       </c>
       <c r="N12" t="n">
         <v>0.75</v>
@@ -1369,22 +1369,22 @@
         <v>46.15</v>
       </c>
       <c r="H13" t="n">
-        <v>7.56</v>
+        <v>7.16</v>
       </c>
       <c r="I13" t="n">
         <v>100</v>
       </c>
       <c r="J13" t="n">
-        <v>2.15</v>
+        <v>1.75</v>
       </c>
       <c r="K13" t="n">
-        <v>7.45</v>
+        <v>7.43</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.07</v>
+        <v>-1.09</v>
       </c>
       <c r="N13" t="n">
         <v>-1.99</v>
@@ -1443,22 +1443,22 @@
         <v>57.89</v>
       </c>
       <c r="H14" t="n">
-        <v>3.44</v>
+        <v>4.16</v>
       </c>
       <c r="I14" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.6</v>
+        <v>-0.88</v>
       </c>
       <c r="K14" t="n">
-        <v>9.039999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>83.33</v>
+        <v>79.17</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.09</v>
+        <v>-0.28</v>
       </c>
       <c r="N14" t="n">
         <v>-2.9</v>
@@ -1517,22 +1517,22 @@
         <v>62.63</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.28</v>
+        <v>-0.22</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.77</v>
+        <v>-0.7</v>
       </c>
       <c r="K15" t="n">
-        <v>0.54</v>
+        <v>0.15</v>
       </c>
       <c r="L15" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="M15" t="n">
-        <v>4.97</v>
+        <v>4.58</v>
       </c>
       <c r="N15" t="n">
         <v>-3.61</v>
@@ -1591,22 +1591,22 @@
         <v>60.37</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.92</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="J16" t="n">
-        <v>0.73</v>
+        <v>1.06</v>
       </c>
       <c r="K16" t="n">
-        <v>7.53</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>87.5</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>3.01</v>
+        <v>5.19</v>
       </c>
       <c r="N16" t="n">
         <v>-0.9399999999999999</v>
@@ -1665,22 +1665,22 @@
         <v>24.32</v>
       </c>
       <c r="H17" t="n">
-        <v>6.01</v>
+        <v>5.4</v>
       </c>
       <c r="I17" t="n">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="J17" t="n">
-        <v>0.87</v>
+        <v>0.25</v>
       </c>
       <c r="K17" t="n">
-        <v>6.32</v>
+        <v>4.76</v>
       </c>
       <c r="L17" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M17" t="n">
-        <v>0.18</v>
+        <v>-1.38</v>
       </c>
       <c r="N17" t="n">
         <v>-1.87</v>
@@ -1813,22 +1813,22 @@
         <v>26.34</v>
       </c>
       <c r="H19" t="n">
-        <v>4.54</v>
+        <v>4.76</v>
       </c>
       <c r="I19" t="n">
         <v>65</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.87</v>
+        <v>-0.65</v>
       </c>
       <c r="K19" t="n">
-        <v>11.26</v>
+        <v>10.97</v>
       </c>
       <c r="L19" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M19" t="n">
-        <v>1.46</v>
+        <v>1.17</v>
       </c>
       <c r="N19" t="n">
         <v>-1.32</v>
@@ -1961,22 +1961,22 @@
         <v>67.83</v>
       </c>
       <c r="H21" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.58</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>12.29</v>
+        <v>10.92</v>
       </c>
       <c r="L21" t="n">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="M21" t="n">
-        <v>7.68</v>
+        <v>6.31</v>
       </c>
       <c r="N21" t="n">
         <v>-2.21</v>
@@ -2035,22 +2035,22 @@
         <v>30.61</v>
       </c>
       <c r="H22" t="n">
-        <v>2.53</v>
+        <v>2.17</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.35</v>
+        <v>-0.71</v>
       </c>
       <c r="K22" t="n">
-        <v>3.1</v>
+        <v>0.96</v>
       </c>
       <c r="L22" t="n">
-        <v>50</v>
+        <v>20.83</v>
       </c>
       <c r="M22" t="n">
-        <v>0.77</v>
+        <v>-1.37</v>
       </c>
       <c r="N22" t="n">
         <v>-2.5</v>
@@ -2109,22 +2109,22 @@
         <v>52.91</v>
       </c>
       <c r="H23" t="n">
-        <v>4.34</v>
+        <v>4.28</v>
       </c>
       <c r="I23" t="n">
         <v>55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.44</v>
+        <v>0.38</v>
       </c>
       <c r="K23" t="n">
-        <v>13.77</v>
+        <v>13.51</v>
       </c>
       <c r="L23" t="n">
         <v>87.5</v>
       </c>
       <c r="M23" t="n">
-        <v>5.35</v>
+        <v>5.09</v>
       </c>
       <c r="N23" t="n">
         <v>-3.54</v>
@@ -2183,22 +2183,22 @@
         <v>47.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.46</v>
+        <v>3.34</v>
       </c>
       <c r="I24" t="n">
         <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.5</v>
+        <v>-0.62</v>
       </c>
       <c r="K24" t="n">
-        <v>8.07</v>
+        <v>7.39</v>
       </c>
       <c r="L24" t="n">
-        <v>79.17</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.73</v>
+        <v>2.05</v>
       </c>
       <c r="N24" t="n">
         <v>3.01</v>
@@ -2257,22 +2257,22 @@
         <v>59.36</v>
       </c>
       <c r="H25" t="n">
-        <v>2.27</v>
+        <v>0.55</v>
       </c>
       <c r="I25" t="n">
-        <v>55</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>0.42</v>
+        <v>-1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>1.22</v>
+        <v>0.46</v>
       </c>
       <c r="L25" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.53</v>
+        <v>-4.29</v>
       </c>
       <c r="N25" t="n">
         <v>0.32</v>
@@ -2290,13 +2290,13 @@
         <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2331,22 +2331,22 @@
         <v>31.55</v>
       </c>
       <c r="H26" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="I26" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="J26" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="K26" t="n">
-        <v>7.74</v>
+        <v>7.06</v>
       </c>
       <c r="L26" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M26" t="n">
-        <v>5.83</v>
+        <v>5.15</v>
       </c>
       <c r="N26" t="n">
         <v>5.21</v>
@@ -2414,13 +2414,13 @@
         <v>0.5</v>
       </c>
       <c r="K27" t="n">
-        <v>10.09</v>
+        <v>-1.6</v>
       </c>
       <c r="L27" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>5.93</v>
+        <v>-5.76</v>
       </c>
       <c r="N27" t="n">
         <v>-0.53</v>
@@ -2479,22 +2479,22 @@
         <v>43.82</v>
       </c>
       <c r="H28" t="n">
-        <v>8.289999999999999</v>
+        <v>5.12</v>
       </c>
       <c r="I28" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="J28" t="n">
-        <v>5.58</v>
+        <v>2.42</v>
       </c>
       <c r="K28" t="n">
-        <v>12.43</v>
+        <v>11.74</v>
       </c>
       <c r="L28" t="n">
         <v>70.83</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.99</v>
+        <v>-10.69</v>
       </c>
       <c r="N28" t="n">
         <v>-3.6</v>
@@ -2627,22 +2627,22 @@
         <v>55.43</v>
       </c>
       <c r="H30" t="n">
-        <v>3.85</v>
+        <v>2.58</v>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>45</v>
       </c>
       <c r="J30" t="n">
-        <v>1.82</v>
+        <v>0.55</v>
       </c>
       <c r="K30" t="n">
-        <v>3.7</v>
+        <v>11.58</v>
       </c>
       <c r="L30" t="n">
-        <v>29.17</v>
+        <v>95.83</v>
       </c>
       <c r="M30" t="n">
-        <v>-1.17</v>
+        <v>6.71</v>
       </c>
       <c r="N30" t="n">
         <v>-1.54</v>
@@ -2701,22 +2701,22 @@
         <v>42.84</v>
       </c>
       <c r="H31" t="n">
-        <v>4.18</v>
+        <v>2.53</v>
       </c>
       <c r="I31" t="n">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="J31" t="n">
-        <v>0.83</v>
+        <v>-0.82</v>
       </c>
       <c r="K31" t="n">
-        <v>8.56</v>
+        <v>7.76</v>
       </c>
       <c r="L31" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M31" t="n">
-        <v>6.77</v>
+        <v>5.98</v>
       </c>
       <c r="N31" t="n">
         <v>-1.76</v>
@@ -2734,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -555,22 +555,22 @@
         <v>87.02</v>
       </c>
       <c r="H2" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="I2" t="n">
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.13</v>
+        <v>-0.92</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.210000000000001</v>
+        <v>-2.73</v>
       </c>
       <c r="L2" t="n">
-        <v>12.5</v>
+        <v>16.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-15.62</v>
+        <v>-9.140000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>-0.4</v>
@@ -629,22 +629,22 @@
         <v>51.2</v>
       </c>
       <c r="H3" t="n">
-        <v>5.58</v>
+        <v>4.72</v>
       </c>
       <c r="I3" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J3" t="n">
-        <v>1.54</v>
+        <v>0.67</v>
       </c>
       <c r="K3" t="n">
-        <v>14.14</v>
+        <v>11.51</v>
       </c>
       <c r="L3" t="n">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>7.23</v>
+        <v>4.6</v>
       </c>
       <c r="N3" t="n">
         <v>-1.74</v>
@@ -703,22 +703,22 @@
         <v>33.8</v>
       </c>
       <c r="H4" t="n">
-        <v>2.86</v>
+        <v>3.23</v>
       </c>
       <c r="I4" t="n">
         <v>80</v>
       </c>
       <c r="J4" t="n">
-        <v>0.71</v>
+        <v>1.07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.21</v>
+        <v>4.83</v>
       </c>
       <c r="L4" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="M4" t="n">
-        <v>2.19</v>
+        <v>1.8</v>
       </c>
       <c r="N4" t="n">
         <v>-2.56</v>
@@ -777,22 +777,22 @@
         <v>34.19</v>
       </c>
       <c r="H5" t="n">
-        <v>11.22</v>
+        <v>11.02</v>
       </c>
       <c r="I5" t="n">
         <v>95</v>
       </c>
       <c r="J5" t="n">
-        <v>4.78</v>
+        <v>4.58</v>
       </c>
       <c r="K5" t="n">
-        <v>21.34</v>
+        <v>20.06</v>
       </c>
       <c r="L5" t="n">
         <v>100</v>
       </c>
       <c r="M5" t="n">
-        <v>8.949999999999999</v>
+        <v>7.68</v>
       </c>
       <c r="N5" t="n">
         <v>-2.25</v>
@@ -860,13 +860,13 @@
         <v>1.71</v>
       </c>
       <c r="K6" t="n">
-        <v>15.43</v>
+        <v>17.48</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>7.61</v>
+        <v>9.66</v>
       </c>
       <c r="N6" t="n">
         <v>0.15</v>
@@ -925,22 +925,22 @@
         <v>35.51</v>
       </c>
       <c r="H7" t="n">
-        <v>5.54</v>
+        <v>5.46</v>
       </c>
       <c r="I7" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.2</v>
+        <v>-0.28</v>
       </c>
       <c r="K7" t="n">
-        <v>11.67</v>
+        <v>10.12</v>
       </c>
       <c r="L7" t="n">
         <v>100</v>
       </c>
       <c r="M7" t="n">
-        <v>4.72</v>
+        <v>3.17</v>
       </c>
       <c r="N7" t="n">
         <v>1.51</v>
@@ -1008,13 +1008,13 @@
         <v>-2.74</v>
       </c>
       <c r="K8" t="n">
-        <v>5.38</v>
+        <v>8.57</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>29.17</v>
       </c>
       <c r="M8" t="n">
-        <v>-7.66</v>
+        <v>-4.46</v>
       </c>
       <c r="N8" t="n">
         <v>0.44</v>
@@ -1073,22 +1073,22 @@
         <v>62.78</v>
       </c>
       <c r="H9" t="n">
-        <v>7.44</v>
+        <v>6.36</v>
       </c>
       <c r="I9" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="J9" t="n">
-        <v>2.8</v>
+        <v>1.72</v>
       </c>
       <c r="K9" t="n">
-        <v>8.65</v>
+        <v>6.99</v>
       </c>
       <c r="L9" t="n">
-        <v>20.83</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.380000000000001</v>
+        <v>-11.04</v>
       </c>
       <c r="N9" t="n">
         <v>-0.5600000000000001</v>
@@ -1147,22 +1147,22 @@
         <v>58.2</v>
       </c>
       <c r="H10" t="n">
-        <v>5.96</v>
+        <v>4.83</v>
       </c>
       <c r="I10" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="J10" t="n">
-        <v>2.2</v>
+        <v>1.06</v>
       </c>
       <c r="K10" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="L10" t="n">
-        <v>95.83</v>
+        <v>83.33</v>
       </c>
       <c r="M10" t="n">
-        <v>2.59</v>
+        <v>1.67</v>
       </c>
       <c r="N10" t="n">
         <v>-1.66</v>
@@ -1221,22 +1221,22 @@
         <v>52.91</v>
       </c>
       <c r="H11" t="n">
-        <v>2.13</v>
+        <v>1.89</v>
       </c>
       <c r="I11" t="n">
         <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.74</v>
+        <v>-1.98</v>
       </c>
       <c r="K11" t="n">
-        <v>4.55</v>
+        <v>3.49</v>
       </c>
       <c r="L11" t="n">
-        <v>58.33</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>0.52</v>
+        <v>-0.54</v>
       </c>
       <c r="N11" t="n">
         <v>-2.43</v>
@@ -1295,22 +1295,22 @@
         <v>80.5</v>
       </c>
       <c r="H12" t="n">
-        <v>5.09</v>
+        <v>4.82</v>
       </c>
       <c r="I12" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2</v>
+        <v>0.93</v>
       </c>
       <c r="K12" t="n">
-        <v>6.18</v>
+        <v>11.11</v>
       </c>
       <c r="L12" t="n">
-        <v>37.5</v>
+        <v>95.83</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.51</v>
+        <v>4.42</v>
       </c>
       <c r="N12" t="n">
         <v>0.75</v>
@@ -1369,22 +1369,22 @@
         <v>46.15</v>
       </c>
       <c r="H13" t="n">
-        <v>7.16</v>
+        <v>5.84</v>
       </c>
       <c r="I13" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J13" t="n">
-        <v>1.75</v>
+        <v>0.43</v>
       </c>
       <c r="K13" t="n">
-        <v>7.43</v>
+        <v>6.6</v>
       </c>
       <c r="L13" t="n">
         <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.09</v>
+        <v>-1.92</v>
       </c>
       <c r="N13" t="n">
         <v>-1.99</v>
@@ -1443,22 +1443,22 @@
         <v>57.89</v>
       </c>
       <c r="H14" t="n">
-        <v>4.16</v>
+        <v>5.18</v>
       </c>
       <c r="I14" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.88</v>
+        <v>0.15</v>
       </c>
       <c r="K14" t="n">
-        <v>8.859999999999999</v>
+        <v>8.02</v>
       </c>
       <c r="L14" t="n">
-        <v>79.17</v>
+        <v>75</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.28</v>
+        <v>-1.11</v>
       </c>
       <c r="N14" t="n">
         <v>-2.9</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
         <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1517,22 +1517,22 @@
         <v>62.63</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="I15" t="n">
         <v>15</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.7</v>
+        <v>-0.64</v>
       </c>
       <c r="K15" t="n">
-        <v>0.15</v>
+        <v>1.1</v>
       </c>
       <c r="L15" t="n">
-        <v>62.5</v>
+        <v>70.83</v>
       </c>
       <c r="M15" t="n">
-        <v>4.58</v>
+        <v>5.54</v>
       </c>
       <c r="N15" t="n">
         <v>-3.61</v>
@@ -1591,22 +1591,22 @@
         <v>60.37</v>
       </c>
       <c r="H16" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="I16" t="n">
         <v>75</v>
       </c>
       <c r="J16" t="n">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="K16" t="n">
-        <v>9.710000000000001</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M16" t="n">
-        <v>5.19</v>
+        <v>4.44</v>
       </c>
       <c r="N16" t="n">
         <v>-0.9399999999999999</v>
@@ -1665,22 +1665,22 @@
         <v>24.32</v>
       </c>
       <c r="H17" t="n">
-        <v>5.4</v>
+        <v>6.14</v>
       </c>
       <c r="I17" t="n">
-        <v>80</v>
+        <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>0.25</v>
+        <v>0.99</v>
       </c>
       <c r="K17" t="n">
-        <v>4.76</v>
+        <v>5.55</v>
       </c>
       <c r="L17" t="n">
         <v>91.67</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.38</v>
+        <v>-0.58</v>
       </c>
       <c r="N17" t="n">
         <v>-1.87</v>
@@ -1813,22 +1813,22 @@
         <v>26.34</v>
       </c>
       <c r="H19" t="n">
-        <v>4.76</v>
+        <v>5.44</v>
       </c>
       <c r="I19" t="n">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.65</v>
+        <v>0.04</v>
       </c>
       <c r="K19" t="n">
-        <v>10.97</v>
+        <v>10.47</v>
       </c>
       <c r="L19" t="n">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="M19" t="n">
-        <v>1.17</v>
+        <v>0.68</v>
       </c>
       <c r="N19" t="n">
         <v>-1.32</v>
@@ -1846,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1887,22 +1887,22 @@
         <v>81.51000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>6.3</v>
+        <v>3.29</v>
       </c>
       <c r="I20" t="n">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="J20" t="n">
-        <v>3.04</v>
+        <v>0.03</v>
       </c>
       <c r="K20" t="n">
-        <v>6.11</v>
+        <v>5.99</v>
       </c>
       <c r="L20" t="n">
         <v>91.67</v>
       </c>
       <c r="M20" t="n">
-        <v>7.56</v>
+        <v>7.44</v>
       </c>
       <c r="N20" t="n">
         <v>-4.12</v>
@@ -1961,22 +1961,22 @@
         <v>67.83</v>
       </c>
       <c r="H21" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.46</v>
       </c>
       <c r="K21" t="n">
-        <v>10.92</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>6.31</v>
+        <v>5.35</v>
       </c>
       <c r="N21" t="n">
         <v>-2.21</v>
@@ -2035,22 +2035,22 @@
         <v>30.61</v>
       </c>
       <c r="H22" t="n">
-        <v>2.17</v>
+        <v>3.03</v>
       </c>
       <c r="I22" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.71</v>
+        <v>0.15</v>
       </c>
       <c r="K22" t="n">
-        <v>0.96</v>
+        <v>1.9</v>
       </c>
       <c r="L22" t="n">
-        <v>20.83</v>
+        <v>37.5</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.37</v>
+        <v>-0.43</v>
       </c>
       <c r="N22" t="n">
         <v>-2.5</v>
@@ -2068,13 +2068,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V22" t="inlineStr">
         <is>
@@ -2109,22 +2109,22 @@
         <v>52.91</v>
       </c>
       <c r="H23" t="n">
-        <v>4.28</v>
+        <v>4.38</v>
       </c>
       <c r="I23" t="n">
         <v>55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.38</v>
+        <v>0.48</v>
       </c>
       <c r="K23" t="n">
-        <v>13.51</v>
+        <v>12.15</v>
       </c>
       <c r="L23" t="n">
-        <v>87.5</v>
+        <v>83.33</v>
       </c>
       <c r="M23" t="n">
-        <v>5.09</v>
+        <v>3.73</v>
       </c>
       <c r="N23" t="n">
         <v>-3.54</v>
@@ -2183,22 +2183,22 @@
         <v>47.16</v>
       </c>
       <c r="H24" t="n">
-        <v>3.34</v>
+        <v>3.97</v>
       </c>
       <c r="I24" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.62</v>
+        <v>0.01</v>
       </c>
       <c r="K24" t="n">
-        <v>7.39</v>
+        <v>7.98</v>
       </c>
       <c r="L24" t="n">
-        <v>75</v>
+        <v>79.17</v>
       </c>
       <c r="M24" t="n">
-        <v>2.05</v>
+        <v>2.64</v>
       </c>
       <c r="N24" t="n">
         <v>3.01</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2257,22 +2257,22 @@
         <v>59.36</v>
       </c>
       <c r="H25" t="n">
-        <v>0.55</v>
+        <v>0.3</v>
       </c>
       <c r="I25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3</v>
+        <v>-1.56</v>
       </c>
       <c r="K25" t="n">
-        <v>0.46</v>
+        <v>5.41</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>-4.29</v>
+        <v>0.66</v>
       </c>
       <c r="N25" t="n">
         <v>0.32</v>
@@ -2331,22 +2331,22 @@
         <v>31.55</v>
       </c>
       <c r="H26" t="n">
-        <v>1.07</v>
+        <v>0.51</v>
       </c>
       <c r="I26" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="J26" t="n">
-        <v>0.82</v>
+        <v>0.26</v>
       </c>
       <c r="K26" t="n">
-        <v>7.06</v>
+        <v>5.67</v>
       </c>
       <c r="L26" t="n">
         <v>91.67</v>
       </c>
       <c r="M26" t="n">
-        <v>5.15</v>
+        <v>3.76</v>
       </c>
       <c r="N26" t="n">
         <v>5.21</v>
@@ -2405,22 +2405,22 @@
         <v>85.94</v>
       </c>
       <c r="H27" t="n">
-        <v>2.72</v>
+        <v>1.29</v>
       </c>
       <c r="I27" t="n">
-        <v>70</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>0.5</v>
+        <v>-0.93</v>
       </c>
       <c r="K27" t="n">
-        <v>-1.6</v>
+        <v>0.47</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>8.33</v>
       </c>
       <c r="M27" t="n">
-        <v>-5.76</v>
+        <v>-3.69</v>
       </c>
       <c r="N27" t="n">
         <v>-0.53</v>
@@ -2438,13 +2438,13 @@
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
         <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -2479,22 +2479,22 @@
         <v>43.82</v>
       </c>
       <c r="H28" t="n">
-        <v>5.12</v>
+        <v>3.83</v>
       </c>
       <c r="I28" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J28" t="n">
-        <v>2.42</v>
+        <v>1.12</v>
       </c>
       <c r="K28" t="n">
-        <v>11.74</v>
+        <v>11.08</v>
       </c>
       <c r="L28" t="n">
-        <v>70.83</v>
+        <v>66.67</v>
       </c>
       <c r="M28" t="n">
-        <v>-10.69</v>
+        <v>-11.34</v>
       </c>
       <c r="N28" t="n">
         <v>-3.6</v>
@@ -2553,22 +2553,22 @@
         <v>69.83</v>
       </c>
       <c r="H29" t="n">
-        <v>8.81</v>
+        <v>7.76</v>
       </c>
       <c r="I29" t="n">
         <v>55</v>
       </c>
       <c r="J29" t="n">
-        <v>5.5</v>
+        <v>4.45</v>
       </c>
       <c r="K29" t="n">
-        <v>8.869999999999999</v>
+        <v>-64.61</v>
       </c>
       <c r="L29" t="n">
-        <v>45.83</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>2.52</v>
+        <v>-70.95999999999999</v>
       </c>
       <c r="N29" t="n">
         <v>-4.12</v>
@@ -2636,13 +2636,13 @@
         <v>0.55</v>
       </c>
       <c r="K30" t="n">
-        <v>11.58</v>
+        <v>7.75</v>
       </c>
       <c r="L30" t="n">
-        <v>95.83</v>
+        <v>79.17</v>
       </c>
       <c r="M30" t="n">
-        <v>6.71</v>
+        <v>2.87</v>
       </c>
       <c r="N30" t="n">
         <v>-1.54</v>
@@ -2701,22 +2701,22 @@
         <v>42.84</v>
       </c>
       <c r="H31" t="n">
-        <v>2.53</v>
+        <v>3.65</v>
       </c>
       <c r="I31" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.82</v>
+        <v>0.3</v>
       </c>
       <c r="K31" t="n">
-        <v>7.76</v>
+        <v>6.96</v>
       </c>
       <c r="L31" t="n">
         <v>91.67</v>
       </c>
       <c r="M31" t="n">
-        <v>5.98</v>
+        <v>5.18</v>
       </c>
       <c r="N31" t="n">
         <v>-1.76</v>
@@ -2734,13 +2734,13 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T31" t="n">
         <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2775,22 +2775,22 @@
         <v>62.41</v>
       </c>
       <c r="H32" t="n">
-        <v>9.67</v>
+        <v>6.33</v>
       </c>
       <c r="I32" t="n">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="J32" t="n">
-        <v>3.67</v>
+        <v>0.33</v>
       </c>
       <c r="K32" t="n">
-        <v>4.67</v>
+        <v>5.21</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.78</v>
+        <v>-3.24</v>
       </c>
       <c r="N32" t="n">
         <v>-0.47</v>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3085</v>
+        <v>1.3239</v>
       </c>
       <c r="D2" t="n">
-        <v>78.88</v>
+        <v>77.36</v>
       </c>
       <c r="E2" t="n">
-        <v>79.31999999999999</v>
+        <v>79.04000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>48.01</v>
+        <v>43.77</v>
       </c>
       <c r="G2" t="n">
-        <v>87.02</v>
+        <v>79.67</v>
       </c>
       <c r="H2" t="n">
-        <v>1.71</v>
+        <v>1.59</v>
       </c>
       <c r="I2" t="n">
         <v>40</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.92</v>
+        <v>-1.04</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.73</v>
+        <v>-3.24</v>
       </c>
       <c r="L2" t="n">
         <v>16.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.140000000000001</v>
+        <v>-9.65</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4</v>
+        <v>-1.63</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.24</v>
+        <v>-5.25</v>
       </c>
       <c r="P2" t="n">
-        <v>-15.96</v>
+        <v>-18.42</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.493</v>
+        <v>4.5295</v>
       </c>
       <c r="D3" t="n">
-        <v>23.24</v>
+        <v>22.71</v>
       </c>
       <c r="E3" t="n">
-        <v>56.33</v>
+        <v>53.85</v>
       </c>
       <c r="F3" t="n">
-        <v>37.77</v>
+        <v>35.17</v>
       </c>
       <c r="G3" t="n">
-        <v>51.2</v>
+        <v>45.15</v>
       </c>
       <c r="H3" t="n">
-        <v>4.72</v>
+        <v>4.16</v>
       </c>
       <c r="I3" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="J3" t="n">
-        <v>0.67</v>
+        <v>0.12</v>
       </c>
       <c r="K3" t="n">
-        <v>11.51</v>
+        <v>10.34</v>
       </c>
       <c r="L3" t="n">
         <v>75</v>
       </c>
       <c r="M3" t="n">
-        <v>4.6</v>
+        <v>3.43</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.74</v>
+        <v>-4.49</v>
       </c>
       <c r="O3" t="n">
-        <v>-10.71</v>
+        <v>-12.97</v>
       </c>
       <c r="P3" t="n">
-        <v>-7.59</v>
+        <v>-11.46</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6093</v>
+        <v>0.617</v>
       </c>
       <c r="D4" t="n">
-        <v>28.65</v>
+        <v>28.12</v>
       </c>
       <c r="E4" t="n">
-        <v>70.83</v>
+        <v>69.03</v>
       </c>
       <c r="F4" t="n">
-        <v>18.15</v>
+        <v>17.32</v>
       </c>
       <c r="G4" t="n">
-        <v>33.8</v>
+        <v>30.88</v>
       </c>
       <c r="H4" t="n">
         <v>3.23</v>
@@ -712,22 +712,22 @@
         <v>1.07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.83</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
-        <v>62.5</v>
+        <v>54.17</v>
       </c>
       <c r="M4" t="n">
-        <v>1.8</v>
+        <v>0.37</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.56</v>
+        <v>-3.9</v>
       </c>
       <c r="O4" t="n">
-        <v>-5.11</v>
+        <v>-6.95</v>
       </c>
       <c r="P4" t="n">
-        <v>-18.2</v>
+        <v>-22.93</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.0739</v>
+        <v>5.0562</v>
       </c>
       <c r="D5" t="n">
-        <v>15.16</v>
+        <v>14.64</v>
       </c>
       <c r="E5" t="n">
-        <v>16.82</v>
+        <v>10.71</v>
       </c>
       <c r="F5" t="n">
-        <v>27.04</v>
+        <v>26.51</v>
       </c>
       <c r="G5" t="n">
-        <v>34.19</v>
+        <v>32.43</v>
       </c>
       <c r="H5" t="n">
-        <v>11.02</v>
+        <v>10.68</v>
       </c>
       <c r="I5" t="n">
         <v>95</v>
       </c>
       <c r="J5" t="n">
-        <v>4.58</v>
+        <v>4.24</v>
       </c>
       <c r="K5" t="n">
-        <v>20.06</v>
+        <v>19.36</v>
       </c>
       <c r="L5" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>7.68</v>
+        <v>6.97</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.25</v>
+        <v>-4.62</v>
       </c>
       <c r="O5" t="n">
-        <v>-15.17</v>
+        <v>-17.11</v>
       </c>
       <c r="P5" t="n">
-        <v>-4.85</v>
+        <v>-12</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>18.1951</v>
+        <v>17.356</v>
       </c>
       <c r="D6" t="n">
-        <v>50.68</v>
+        <v>46.74</v>
       </c>
       <c r="E6" t="n">
-        <v>62.19</v>
+        <v>55.55</v>
       </c>
       <c r="F6" t="n">
-        <v>42.75</v>
+        <v>44.79</v>
       </c>
       <c r="G6" t="n">
-        <v>67.91</v>
+        <v>71.37</v>
       </c>
       <c r="H6" t="n">
-        <v>5.04</v>
+        <v>4.93</v>
       </c>
       <c r="I6" t="n">
         <v>80</v>
       </c>
       <c r="J6" t="n">
-        <v>1.71</v>
+        <v>1.6</v>
       </c>
       <c r="K6" t="n">
-        <v>17.48</v>
+        <v>16.64</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>9.66</v>
+        <v>8.82</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-7.57</v>
       </c>
       <c r="O6" t="n">
-        <v>-18.84</v>
+        <v>-26.67</v>
       </c>
       <c r="P6" t="n">
-        <v>4.2</v>
+        <v>-1.1</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.7378</v>
+        <v>3.8206</v>
       </c>
       <c r="D7" t="n">
-        <v>24.13</v>
+        <v>23.9</v>
       </c>
       <c r="E7" t="n">
-        <v>12.65</v>
+        <v>11.25</v>
       </c>
       <c r="F7" t="n">
-        <v>33.39</v>
+        <v>33.77</v>
       </c>
       <c r="G7" t="n">
-        <v>35.51</v>
+        <v>36.23</v>
       </c>
       <c r="H7" t="n">
-        <v>5.46</v>
+        <v>4.98</v>
       </c>
       <c r="I7" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.28</v>
+        <v>-0.76</v>
       </c>
       <c r="K7" t="n">
-        <v>10.12</v>
+        <v>7.76</v>
       </c>
       <c r="L7" t="n">
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="M7" t="n">
-        <v>3.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>1.51</v>
+        <v>-1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>-3.7</v>
+        <v>-6.62</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.77</v>
+        <v>-27.52</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.2815</v>
+        <v>2.309</v>
       </c>
       <c r="D8" t="n">
-        <v>14.62</v>
+        <v>14.34</v>
       </c>
       <c r="E8" t="n">
-        <v>52.7</v>
+        <v>40.45</v>
       </c>
       <c r="F8" t="n">
-        <v>30.43</v>
+        <v>33.51</v>
       </c>
       <c r="G8" t="n">
-        <v>54.86</v>
+        <v>66.41</v>
       </c>
       <c r="H8" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="I8" t="n">
         <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.74</v>
+        <v>-2.95</v>
       </c>
       <c r="K8" t="n">
-        <v>8.57</v>
+        <v>8.08</v>
       </c>
       <c r="L8" t="n">
-        <v>29.17</v>
+        <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.46</v>
+        <v>-4.96</v>
       </c>
       <c r="N8" t="n">
-        <v>0.44</v>
+        <v>-2.32</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.54</v>
+        <v>-3.93</v>
       </c>
       <c r="P8" t="n">
-        <v>-7.49</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6228</v>
+        <v>3.7652</v>
       </c>
       <c r="D9" t="n">
-        <v>21.01</v>
+        <v>21.17</v>
       </c>
       <c r="E9" t="n">
-        <v>26.62</v>
+        <v>30.2</v>
       </c>
       <c r="F9" t="n">
-        <v>31.55</v>
+        <v>31.33</v>
       </c>
       <c r="G9" t="n">
-        <v>62.78</v>
+        <v>61.91</v>
       </c>
       <c r="H9" t="n">
-        <v>6.36</v>
+        <v>5.65</v>
       </c>
       <c r="I9" t="n">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="J9" t="n">
-        <v>1.72</v>
+        <v>1.01</v>
       </c>
       <c r="K9" t="n">
-        <v>6.99</v>
+        <v>7.92</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M9" t="n">
-        <v>-11.04</v>
+        <v>-10.11</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5600000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="O9" t="n">
-        <v>2.96</v>
+        <v>3.26</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.56</v>
+        <v>-17.83</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1109,10 +1109,10 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5336</v>
+        <v>0.5433</v>
       </c>
       <c r="D10" t="n">
-        <v>23.78</v>
+        <v>23.34</v>
       </c>
       <c r="E10" t="n">
-        <v>53.55</v>
+        <v>49.08</v>
       </c>
       <c r="F10" t="n">
-        <v>39.55</v>
+        <v>37.1</v>
       </c>
       <c r="G10" t="n">
-        <v>58.2</v>
+        <v>52.06</v>
       </c>
       <c r="H10" t="n">
-        <v>4.83</v>
+        <v>3.01</v>
       </c>
       <c r="I10" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
-        <v>1.06</v>
+        <v>-0.76</v>
       </c>
       <c r="K10" t="n">
-        <v>5.98</v>
+        <v>4.45</v>
       </c>
       <c r="L10" t="n">
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="M10" t="n">
-        <v>1.67</v>
+        <v>0.15</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.66</v>
+        <v>-3.08</v>
       </c>
       <c r="O10" t="n">
-        <v>-3.56</v>
+        <v>-6.33</v>
       </c>
       <c r="P10" t="n">
-        <v>-10.61</v>
+        <v>-13.17</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1180,13 +1180,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8101</v>
+        <v>0.8124</v>
       </c>
       <c r="D11" t="n">
-        <v>31.24</v>
+        <v>30.26</v>
       </c>
       <c r="E11" t="n">
-        <v>78.94</v>
+        <v>69.41</v>
       </c>
       <c r="F11" t="n">
-        <v>37.24</v>
+        <v>35.74</v>
       </c>
       <c r="G11" t="n">
-        <v>52.91</v>
+        <v>50.58</v>
       </c>
       <c r="H11" t="n">
-        <v>1.89</v>
+        <v>2.68</v>
       </c>
       <c r="I11" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.98</v>
+        <v>-1.19</v>
       </c>
       <c r="K11" t="n">
-        <v>3.49</v>
+        <v>3.62</v>
       </c>
       <c r="L11" t="n">
-        <v>37.5</v>
+        <v>45.83</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.54</v>
+        <v>-0.42</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.43</v>
+        <v>-5.58</v>
       </c>
       <c r="O11" t="n">
-        <v>-6.81</v>
+        <v>-11.04</v>
       </c>
       <c r="P11" t="n">
-        <v>-15.1</v>
+        <v>-18.23</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1280,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.847</v>
+        <v>6.8763</v>
       </c>
       <c r="D12" t="n">
-        <v>31.67</v>
+        <v>30.81</v>
       </c>
       <c r="E12" t="n">
-        <v>57.1</v>
+        <v>50.85</v>
       </c>
       <c r="F12" t="n">
-        <v>40.34</v>
+        <v>38.59</v>
       </c>
       <c r="G12" t="n">
-        <v>80.5</v>
+        <v>77.58</v>
       </c>
       <c r="H12" t="n">
-        <v>4.82</v>
+        <v>4.76</v>
       </c>
       <c r="I12" t="n">
         <v>65</v>
       </c>
       <c r="J12" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="K12" t="n">
-        <v>11.11</v>
+        <v>10.16</v>
       </c>
       <c r="L12" t="n">
-        <v>95.83</v>
+        <v>83.33</v>
       </c>
       <c r="M12" t="n">
-        <v>4.42</v>
+        <v>3.47</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>-3.49</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.27</v>
+        <v>-5.42</v>
       </c>
       <c r="P12" t="n">
-        <v>-15.98</v>
+        <v>-17.25</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.6615</v>
+        <v>2.741</v>
       </c>
       <c r="D13" t="n">
-        <v>21.2</v>
+        <v>21.16</v>
       </c>
       <c r="E13" t="n">
-        <v>54.86</v>
+        <v>54.55</v>
       </c>
       <c r="F13" t="n">
-        <v>27.84</v>
+        <v>26.16</v>
       </c>
       <c r="G13" t="n">
-        <v>46.15</v>
+        <v>39.26</v>
       </c>
       <c r="H13" t="n">
-        <v>5.84</v>
+        <v>5.43</v>
       </c>
       <c r="I13" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J13" t="n">
-        <v>0.43</v>
+        <v>0.02</v>
       </c>
       <c r="K13" t="n">
-        <v>6.6</v>
+        <v>6.11</v>
       </c>
       <c r="L13" t="n">
-        <v>70.83</v>
+        <v>66.67</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.92</v>
+        <v>-2.4</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.99</v>
+        <v>-2.22</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.7</v>
+        <v>-3.08</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.87</v>
+        <v>-4.38</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0066</v>
+        <v>2.1004</v>
       </c>
       <c r="D14" t="n">
-        <v>16.21</v>
+        <v>16.47</v>
       </c>
       <c r="E14" t="n">
-        <v>61.19</v>
+        <v>68.03</v>
       </c>
       <c r="F14" t="n">
-        <v>22.5</v>
+        <v>21.12</v>
       </c>
       <c r="G14" t="n">
-        <v>57.89</v>
+        <v>50.5</v>
       </c>
       <c r="H14" t="n">
-        <v>5.18</v>
+        <v>5.57</v>
       </c>
       <c r="I14" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J14" t="n">
-        <v>0.15</v>
+        <v>0.53</v>
       </c>
       <c r="K14" t="n">
-        <v>8.02</v>
+        <v>7.41</v>
       </c>
       <c r="L14" t="n">
-        <v>75</v>
+        <v>62.5</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.11</v>
+        <v>-1.72</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.9</v>
+        <v>-0.46</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.86</v>
+        <v>-2.44</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.960000000000001</v>
+        <v>-9.43</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9016</v>
+        <v>0.9181</v>
       </c>
       <c r="D15" t="n">
-        <v>12.77</v>
+        <v>12.61</v>
       </c>
       <c r="E15" t="n">
-        <v>31.71</v>
+        <v>30.12</v>
       </c>
       <c r="F15" t="n">
-        <v>37.92</v>
+        <v>33.95</v>
       </c>
       <c r="G15" t="n">
-        <v>62.63</v>
+        <v>53.06</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.15</v>
+        <v>-0.28</v>
       </c>
       <c r="I15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.64</v>
+        <v>-0.77</v>
       </c>
       <c r="K15" t="n">
-        <v>1.1</v>
+        <v>-1.67</v>
       </c>
       <c r="L15" t="n">
-        <v>70.83</v>
+        <v>33.33</v>
       </c>
       <c r="M15" t="n">
-        <v>5.54</v>
+        <v>2.77</v>
       </c>
       <c r="N15" t="n">
-        <v>-3.61</v>
+        <v>-2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>-2.05</v>
+        <v>-6.7</v>
       </c>
       <c r="P15" t="n">
-        <v>-25.65</v>
+        <v>-26.03</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8554</v>
+        <v>0.8863</v>
       </c>
       <c r="D16" t="n">
-        <v>31.49</v>
+        <v>31.6</v>
       </c>
       <c r="E16" t="n">
-        <v>38.66</v>
+        <v>38.98</v>
       </c>
       <c r="F16" t="n">
-        <v>36.05</v>
+        <v>35</v>
       </c>
       <c r="G16" t="n">
-        <v>60.37</v>
+        <v>57.33</v>
       </c>
       <c r="H16" t="n">
-        <v>3.1</v>
+        <v>3.26</v>
       </c>
       <c r="I16" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="J16" t="n">
-        <v>1.25</v>
+        <v>1.41</v>
       </c>
       <c r="K16" t="n">
-        <v>8.960000000000001</v>
+        <v>17.52</v>
       </c>
       <c r="L16" t="n">
-        <v>95.83</v>
+        <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>4.44</v>
+        <v>13</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.16</v>
       </c>
       <c r="O16" t="n">
-        <v>-4.36</v>
+        <v>-5.92</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.63</v>
+        <v>-26.14</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1650,46 +1650,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5149</v>
+        <v>0.5218</v>
       </c>
       <c r="D17" t="n">
-        <v>39.16</v>
+        <v>38.46</v>
       </c>
       <c r="E17" t="n">
-        <v>19.21</v>
+        <v>18.49</v>
       </c>
       <c r="F17" t="n">
-        <v>34.61</v>
+        <v>34.29</v>
       </c>
       <c r="G17" t="n">
-        <v>24.32</v>
+        <v>23.66</v>
       </c>
       <c r="H17" t="n">
-        <v>6.14</v>
+        <v>5.93</v>
       </c>
       <c r="I17" t="n">
         <v>95</v>
       </c>
       <c r="J17" t="n">
-        <v>0.99</v>
+        <v>0.79</v>
       </c>
       <c r="K17" t="n">
-        <v>5.55</v>
+        <v>1.87</v>
       </c>
       <c r="L17" t="n">
-        <v>91.67</v>
+        <v>66.67</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.58</v>
+        <v>-4.27</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.87</v>
+        <v>-3.58</v>
       </c>
       <c r="O17" t="n">
-        <v>-6.28</v>
+        <v>-9.48</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.64</v>
+        <v>-22.25</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1724,19 +1724,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.0302</v>
+        <v>6.4013</v>
       </c>
       <c r="D18" t="n">
-        <v>6.4</v>
+        <v>6.59</v>
       </c>
       <c r="E18" t="n">
-        <v>82.09999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="F18" t="n">
-        <v>14.43</v>
+        <v>14.14</v>
       </c>
       <c r="G18" t="n">
-        <v>86.79000000000001</v>
+        <v>84.87</v>
       </c>
       <c r="H18" t="n">
         <v>8.07</v>
@@ -1748,25 +1748,25 @@
         <v>0.15</v>
       </c>
       <c r="K18" t="n">
-        <v>8.07</v>
+        <v>9.23</v>
       </c>
       <c r="L18" t="n">
-        <v>50</v>
+        <v>58.33</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.25</v>
+        <v>0.91</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.58</v>
+        <v>0.7</v>
       </c>
       <c r="O18" t="n">
-        <v>1</v>
+        <v>4.72</v>
       </c>
       <c r="P18" t="n">
-        <v>5.73</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1775,7 +1775,7 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1419</v>
+        <v>5.2817</v>
       </c>
       <c r="D19" t="n">
-        <v>8.68</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>0.23</v>
+        <v>0.15</v>
       </c>
       <c r="F19" t="n">
-        <v>16.07</v>
+        <v>15.85</v>
       </c>
       <c r="G19" t="n">
-        <v>26.34</v>
+        <v>25.29</v>
       </c>
       <c r="H19" t="n">
-        <v>5.44</v>
+        <v>5.41</v>
       </c>
       <c r="I19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>10.47</v>
+        <v>10.22</v>
       </c>
       <c r="L19" t="n">
         <v>87.5</v>
       </c>
       <c r="M19" t="n">
-        <v>0.68</v>
+        <v>0.43</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.32</v>
+        <v>-0.34</v>
       </c>
       <c r="O19" t="n">
-        <v>-4.43</v>
+        <v>-5</v>
       </c>
       <c r="P19" t="n">
-        <v>-17.86</v>
+        <v>-18.62</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1846,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1872,19 +1872,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1985</v>
+        <v>0.1993</v>
       </c>
       <c r="D20" t="n">
-        <v>70.68000000000001</v>
+        <v>68.78</v>
       </c>
       <c r="E20" t="n">
-        <v>87.27</v>
+        <v>85.90000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>45.96</v>
+        <v>39.39</v>
       </c>
       <c r="G20" t="n">
-        <v>81.51000000000001</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="H20" t="n">
         <v>3.29</v>
@@ -1896,22 +1896,22 @@
         <v>0.03</v>
       </c>
       <c r="K20" t="n">
-        <v>5.99</v>
+        <v>7.59</v>
       </c>
       <c r="L20" t="n">
-        <v>91.67</v>
+        <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>7.44</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-4.12</v>
+        <v>-6.45</v>
       </c>
       <c r="O20" t="n">
-        <v>-11.13</v>
+        <v>-14.51</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.28</v>
+        <v>-3.3</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1946,46 +1946,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8756</v>
+        <v>0.863</v>
       </c>
       <c r="D21" t="n">
-        <v>33.7</v>
+        <v>32.19</v>
       </c>
       <c r="E21" t="n">
-        <v>88.97</v>
+        <v>86.52</v>
       </c>
       <c r="F21" t="n">
-        <v>37.57</v>
+        <v>38.65</v>
       </c>
       <c r="G21" t="n">
-        <v>67.83</v>
+        <v>69.28</v>
       </c>
       <c r="H21" t="n">
-        <v>1.79</v>
+        <v>1.67</v>
       </c>
       <c r="I21" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.46</v>
+        <v>-0.58</v>
       </c>
       <c r="K21" t="n">
-        <v>9.960000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="L21" t="n">
         <v>75</v>
       </c>
       <c r="M21" t="n">
-        <v>5.35</v>
+        <v>4.99</v>
       </c>
       <c r="N21" t="n">
-        <v>-2.21</v>
+        <v>-6.39</v>
       </c>
       <c r="O21" t="n">
-        <v>-14.26</v>
+        <v>-18.38</v>
       </c>
       <c r="P21" t="n">
-        <v>0.07000000000000001</v>
+        <v>-6.91</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2020,55 +2020,55 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3539</v>
+        <v>1.3715</v>
       </c>
       <c r="D22" t="n">
-        <v>13.85</v>
+        <v>13.62</v>
       </c>
       <c r="E22" t="n">
-        <v>91.2</v>
+        <v>89.06</v>
       </c>
       <c r="F22" t="n">
-        <v>24.74</v>
+        <v>24.52</v>
       </c>
       <c r="G22" t="n">
-        <v>30.61</v>
+        <v>29.48</v>
       </c>
       <c r="H22" t="n">
-        <v>3.03</v>
+        <v>2.53</v>
       </c>
       <c r="I22" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J22" t="n">
-        <v>0.15</v>
+        <v>-0.35</v>
       </c>
       <c r="K22" t="n">
-        <v>1.9</v>
+        <v>-0.16</v>
       </c>
       <c r="L22" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.43</v>
+        <v>-2.49</v>
       </c>
       <c r="N22" t="n">
-        <v>-2.5</v>
+        <v>-3.72</v>
       </c>
       <c r="O22" t="n">
-        <v>-6.07</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-13.92</v>
+        <v>-17.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>-1</v>
@@ -2094,46 +2094,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.729</v>
+        <v>7.7207</v>
       </c>
       <c r="D23" t="n">
-        <v>24.53</v>
+        <v>23.73</v>
       </c>
       <c r="E23" t="n">
-        <v>24.38</v>
+        <v>23.88</v>
       </c>
       <c r="F23" t="n">
-        <v>38.93</v>
+        <v>36.57</v>
       </c>
       <c r="G23" t="n">
-        <v>52.91</v>
+        <v>49.42</v>
       </c>
       <c r="H23" t="n">
-        <v>4.38</v>
+        <v>4.01</v>
       </c>
       <c r="I23" t="n">
         <v>55</v>
       </c>
       <c r="J23" t="n">
-        <v>0.48</v>
+        <v>0.11</v>
       </c>
       <c r="K23" t="n">
-        <v>12.15</v>
+        <v>10.66</v>
       </c>
       <c r="L23" t="n">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.73</v>
+        <v>2.24</v>
       </c>
       <c r="N23" t="n">
-        <v>-3.54</v>
+        <v>-5.25</v>
       </c>
       <c r="O23" t="n">
-        <v>-13.08</v>
+        <v>-16.79</v>
       </c>
       <c r="P23" t="n">
-        <v>-27.8</v>
+        <v>-28.28</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2168,46 +2168,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1087</v>
+        <v>6.0095</v>
       </c>
       <c r="D24" t="n">
-        <v>38.11</v>
+        <v>36.29</v>
       </c>
       <c r="E24" t="n">
-        <v>84.26000000000001</v>
+        <v>78.89</v>
       </c>
       <c r="F24" t="n">
-        <v>35.09</v>
+        <v>38.36</v>
       </c>
       <c r="G24" t="n">
-        <v>47.16</v>
+        <v>53.14</v>
       </c>
       <c r="H24" t="n">
-        <v>3.97</v>
+        <v>3.79</v>
       </c>
       <c r="I24" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J24" t="n">
-        <v>0.01</v>
+        <v>-0.17</v>
       </c>
       <c r="K24" t="n">
-        <v>7.98</v>
+        <v>7.73</v>
       </c>
       <c r="L24" t="n">
-        <v>79.17</v>
+        <v>75</v>
       </c>
       <c r="M24" t="n">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>-3.97</v>
       </c>
       <c r="O24" t="n">
-        <v>-11.77</v>
+        <v>-17.61</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.62</v>
+        <v>-11.76</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2216,13 +2216,13 @@
         <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
         <v>-1</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V24" t="inlineStr">
         <is>
@@ -2242,46 +2242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7562</v>
+        <v>2.7083</v>
       </c>
       <c r="D25" t="n">
-        <v>55.43</v>
+        <v>52.78</v>
       </c>
       <c r="E25" t="n">
-        <v>35.65</v>
+        <v>22.19</v>
       </c>
       <c r="F25" t="n">
-        <v>37.79</v>
+        <v>39.9</v>
       </c>
       <c r="G25" t="n">
-        <v>59.36</v>
+        <v>64.7</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3</v>
+        <v>0.47</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.56</v>
+        <v>-1.39</v>
       </c>
       <c r="K25" t="n">
-        <v>5.41</v>
+        <v>4.33</v>
       </c>
       <c r="L25" t="n">
-        <v>75</v>
+        <v>58.33</v>
       </c>
       <c r="M25" t="n">
-        <v>0.66</v>
+        <v>-0.42</v>
       </c>
       <c r="N25" t="n">
-        <v>0.32</v>
+        <v>-5.58</v>
       </c>
       <c r="O25" t="n">
-        <v>-6.81</v>
+        <v>-12.19</v>
       </c>
       <c r="P25" t="n">
-        <v>-11.07</v>
+        <v>-15.38</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.0744</v>
+        <v>5.0245</v>
       </c>
       <c r="D26" t="n">
-        <v>59.83</v>
+        <v>57.38</v>
       </c>
       <c r="E26" t="n">
-        <v>47.61</v>
+        <v>41.76</v>
       </c>
       <c r="F26" t="n">
-        <v>37.65</v>
+        <v>40.74</v>
       </c>
       <c r="G26" t="n">
-        <v>31.55</v>
+        <v>39.02</v>
       </c>
       <c r="H26" t="n">
-        <v>0.51</v>
+        <v>0.3</v>
       </c>
       <c r="I26" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="J26" t="n">
-        <v>0.26</v>
+        <v>0.04</v>
       </c>
       <c r="K26" t="n">
-        <v>5.67</v>
+        <v>4.58</v>
       </c>
       <c r="L26" t="n">
         <v>91.67</v>
       </c>
       <c r="M26" t="n">
-        <v>3.76</v>
+        <v>2.67</v>
       </c>
       <c r="N26" t="n">
-        <v>5.21</v>
+        <v>-1.95</v>
       </c>
       <c r="O26" t="n">
-        <v>-1.6</v>
+        <v>-6.91</v>
       </c>
       <c r="P26" t="n">
-        <v>-25.55</v>
+        <v>-27.32</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2390,46 +2390,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8537</v>
+        <v>1.8842</v>
       </c>
       <c r="D27" t="n">
-        <v>34.36</v>
+        <v>33.86</v>
       </c>
       <c r="E27" t="n">
-        <v>42.82</v>
+        <v>41.45</v>
       </c>
       <c r="F27" t="n">
-        <v>71.43000000000001</v>
+        <v>71.18000000000001</v>
       </c>
       <c r="G27" t="n">
-        <v>85.94</v>
+        <v>85.48999999999999</v>
       </c>
       <c r="H27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="I27" t="n">
+        <v>40</v>
+      </c>
+      <c r="J27" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="K27" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="L27" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="M27" t="n">
         <v>1.29</v>
       </c>
-      <c r="I27" t="n">
-        <v>25</v>
-      </c>
-      <c r="J27" t="n">
-        <v>-0.93</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="L27" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="M27" t="n">
-        <v>-3.69</v>
-      </c>
       <c r="N27" t="n">
-        <v>-0.53</v>
+        <v>-2.68</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.31</v>
+        <v>-2.76</v>
       </c>
       <c r="P27" t="n">
-        <v>-23.46</v>
+        <v>-21.59</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2464,46 +2464,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.126</v>
+        <v>4.965</v>
       </c>
       <c r="D28" t="n">
-        <v>39.97</v>
+        <v>37.53</v>
       </c>
       <c r="E28" t="n">
-        <v>77.78</v>
+        <v>72.5</v>
       </c>
       <c r="F28" t="n">
-        <v>35.53</v>
+        <v>35.65</v>
       </c>
       <c r="G28" t="n">
-        <v>43.82</v>
+        <v>44.22</v>
       </c>
       <c r="H28" t="n">
-        <v>3.83</v>
+        <v>2.2</v>
       </c>
       <c r="I28" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J28" t="n">
-        <v>1.12</v>
+        <v>-0.51</v>
       </c>
       <c r="K28" t="n">
-        <v>11.08</v>
+        <v>10.16</v>
       </c>
       <c r="L28" t="n">
         <v>66.67</v>
       </c>
       <c r="M28" t="n">
-        <v>-11.34</v>
+        <v>-12.26</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.6</v>
+        <v>-9.73</v>
       </c>
       <c r="O28" t="n">
-        <v>-24.77</v>
+        <v>-31.34</v>
       </c>
       <c r="P28" t="n">
-        <v>15.08</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2538,46 +2538,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0454</v>
+        <v>1.0765</v>
       </c>
       <c r="D29" t="n">
-        <v>18.06</v>
+        <v>18.03</v>
       </c>
       <c r="E29" t="n">
-        <v>81.44</v>
+        <v>81.3</v>
       </c>
       <c r="F29" t="n">
-        <v>38.55</v>
+        <v>34.15</v>
       </c>
       <c r="G29" t="n">
-        <v>69.83</v>
+        <v>58.26</v>
       </c>
       <c r="H29" t="n">
-        <v>7.76</v>
+        <v>6.78</v>
       </c>
       <c r="I29" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J29" t="n">
-        <v>4.45</v>
+        <v>3.47</v>
       </c>
       <c r="K29" t="n">
-        <v>-64.61</v>
+        <v>-36.35</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-70.95999999999999</v>
+        <v>-42.7</v>
       </c>
       <c r="N29" t="n">
-        <v>-4.12</v>
+        <v>-3.77</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.41</v>
+        <v>-0.23</v>
       </c>
       <c r="P29" t="n">
-        <v>22.41</v>
+        <v>17.02</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2546</v>
+        <v>1.3101</v>
       </c>
       <c r="D30" t="n">
-        <v>16.35</v>
+        <v>16.55</v>
       </c>
       <c r="E30" t="n">
-        <v>68.52</v>
+        <v>71.81999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>24.66</v>
+        <v>24.35</v>
       </c>
       <c r="G30" t="n">
-        <v>55.43</v>
+        <v>53.96</v>
       </c>
       <c r="H30" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="I30" t="n">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="J30" t="n">
-        <v>0.55</v>
+        <v>1.32</v>
       </c>
       <c r="K30" t="n">
-        <v>7.75</v>
+        <v>10.56</v>
       </c>
       <c r="L30" t="n">
-        <v>79.17</v>
+        <v>95.83</v>
       </c>
       <c r="M30" t="n">
-        <v>2.87</v>
+        <v>5.68</v>
       </c>
       <c r="N30" t="n">
-        <v>-1.54</v>
+        <v>-0.78</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.67</v>
+        <v>1.81</v>
       </c>
       <c r="P30" t="n">
-        <v>19.16</v>
+        <v>17.1</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2686,46 +2686,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.8025</v>
       </c>
       <c r="D31" t="n">
-        <v>23.03</v>
+        <v>22.48</v>
       </c>
       <c r="E31" t="n">
-        <v>65.01000000000001</v>
+        <v>58.75</v>
       </c>
       <c r="F31" t="n">
-        <v>27.26</v>
+        <v>26.38</v>
       </c>
       <c r="G31" t="n">
-        <v>42.84</v>
+        <v>40.28</v>
       </c>
       <c r="H31" t="n">
-        <v>3.65</v>
+        <v>4.61</v>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>75</v>
       </c>
       <c r="J31" t="n">
-        <v>0.3</v>
+        <v>1.26</v>
       </c>
       <c r="K31" t="n">
-        <v>6.96</v>
+        <v>6.37</v>
       </c>
       <c r="L31" t="n">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="M31" t="n">
-        <v>5.18</v>
+        <v>4.58</v>
       </c>
       <c r="N31" t="n">
-        <v>-1.76</v>
+        <v>-4.17</v>
       </c>
       <c r="O31" t="n">
-        <v>-9.26</v>
+        <v>-12.29</v>
       </c>
       <c r="P31" t="n">
-        <v>-12.37</v>
+        <v>-15.72</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2760,46 +2760,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2023</v>
+        <v>0.2049</v>
       </c>
       <c r="D32" t="n">
-        <v>28.1</v>
+        <v>27.59</v>
       </c>
       <c r="E32" t="n">
-        <v>5.73</v>
+        <v>3.76</v>
       </c>
       <c r="F32" t="n">
-        <v>39.65</v>
+        <v>38.05</v>
       </c>
       <c r="G32" t="n">
-        <v>62.41</v>
+        <v>58.61</v>
       </c>
       <c r="H32" t="n">
-        <v>6.33</v>
+        <v>5.95</v>
       </c>
       <c r="I32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J32" t="n">
-        <v>0.33</v>
+        <v>-0.05</v>
       </c>
       <c r="K32" t="n">
-        <v>5.21</v>
+        <v>5.45</v>
       </c>
       <c r="L32" t="n">
         <v>25</v>
       </c>
       <c r="M32" t="n">
-        <v>-3.24</v>
+        <v>-3</v>
       </c>
       <c r="N32" t="n">
-        <v>-0.47</v>
+        <v>-2.79</v>
       </c>
       <c r="O32" t="n">
-        <v>1.95</v>
+        <v>-1.77</v>
       </c>
       <c r="P32" t="n">
-        <v>-28.76</v>
+        <v>-30.74</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2808,13 +2808,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,46 +540,46 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.3239</v>
+        <v>1.2924</v>
       </c>
       <c r="D2" t="n">
-        <v>77.36</v>
+        <v>76.8</v>
       </c>
       <c r="E2" t="n">
-        <v>79.04000000000001</v>
+        <v>78.98</v>
       </c>
       <c r="F2" t="n">
-        <v>43.77</v>
+        <v>42.09</v>
       </c>
       <c r="G2" t="n">
-        <v>79.67</v>
+        <v>76.67</v>
       </c>
       <c r="H2" t="n">
-        <v>1.59</v>
+        <v>1.14</v>
       </c>
       <c r="I2" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.04</v>
+        <v>-1.49</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.24</v>
+        <v>-2.68</v>
       </c>
       <c r="L2" t="n">
         <v>16.67</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.65</v>
+        <v>-9.09</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.63</v>
+        <v>-4.23</v>
       </c>
       <c r="O2" t="n">
-        <v>-5.25</v>
+        <v>-7.9</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.42</v>
+        <v>-18.96</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
@@ -614,19 +614,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.5295</v>
+        <v>4.527</v>
       </c>
       <c r="D3" t="n">
-        <v>22.71</v>
+        <v>23.09</v>
       </c>
       <c r="E3" t="n">
-        <v>53.85</v>
+        <v>55.5</v>
       </c>
       <c r="F3" t="n">
-        <v>35.17</v>
+        <v>33.43</v>
       </c>
       <c r="G3" t="n">
-        <v>45.15</v>
+        <v>41.63</v>
       </c>
       <c r="H3" t="n">
         <v>4.16</v>
@@ -638,22 +638,22 @@
         <v>0.12</v>
       </c>
       <c r="K3" t="n">
-        <v>10.34</v>
+        <v>9.18</v>
       </c>
       <c r="L3" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.43</v>
+        <v>2.27</v>
       </c>
       <c r="N3" t="n">
-        <v>-4.49</v>
+        <v>-2.34</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.97</v>
+        <v>-12.95</v>
       </c>
       <c r="P3" t="n">
-        <v>-11.46</v>
+        <v>-9.17</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -688,46 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.617</v>
+        <v>0.6069</v>
       </c>
       <c r="D4" t="n">
-        <v>28.12</v>
+        <v>28.13</v>
       </c>
       <c r="E4" t="n">
-        <v>69.03</v>
+        <v>69.05</v>
       </c>
       <c r="F4" t="n">
-        <v>17.32</v>
+        <v>16.87</v>
       </c>
       <c r="G4" t="n">
-        <v>30.88</v>
+        <v>28.29</v>
       </c>
       <c r="H4" t="n">
-        <v>3.23</v>
+        <v>2.5</v>
       </c>
       <c r="I4" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J4" t="n">
-        <v>1.07</v>
+        <v>0.34</v>
       </c>
       <c r="K4" t="n">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="L4" t="n">
-        <v>54.17</v>
+        <v>50</v>
       </c>
       <c r="M4" t="n">
-        <v>0.37</v>
+        <v>-0.05</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.9</v>
+        <v>-3.42</v>
       </c>
       <c r="O4" t="n">
-        <v>-6.95</v>
+        <v>-7.88</v>
       </c>
       <c r="P4" t="n">
-        <v>-22.93</v>
+        <v>-24.04</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.0562</v>
+        <v>5.0015</v>
       </c>
       <c r="D5" t="n">
-        <v>14.64</v>
+        <v>14.73</v>
       </c>
       <c r="E5" t="n">
-        <v>10.71</v>
+        <v>11.16</v>
       </c>
       <c r="F5" t="n">
-        <v>26.51</v>
+        <v>26.15</v>
       </c>
       <c r="G5" t="n">
-        <v>32.43</v>
+        <v>31.71</v>
       </c>
       <c r="H5" t="n">
-        <v>10.68</v>
+        <v>9.27</v>
       </c>
       <c r="I5" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="J5" t="n">
-        <v>4.24</v>
+        <v>2.83</v>
       </c>
       <c r="K5" t="n">
-        <v>19.36</v>
+        <v>18.52</v>
       </c>
       <c r="L5" t="n">
         <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>6.97</v>
+        <v>6.13</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.62</v>
+        <v>-3.74</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.11</v>
+        <v>-16.6</v>
       </c>
       <c r="P5" t="n">
-        <v>-12</v>
+        <v>-14.33</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -836,46 +836,46 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.356</v>
+        <v>17.8437</v>
       </c>
       <c r="D6" t="n">
-        <v>46.74</v>
+        <v>48.83</v>
       </c>
       <c r="E6" t="n">
-        <v>55.55</v>
+        <v>59.58</v>
       </c>
       <c r="F6" t="n">
-        <v>44.79</v>
+        <v>42.69</v>
       </c>
       <c r="G6" t="n">
-        <v>71.37</v>
+        <v>67.52</v>
       </c>
       <c r="H6" t="n">
-        <v>4.93</v>
+        <v>4.48</v>
       </c>
       <c r="I6" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6</v>
+        <v>1.15</v>
       </c>
       <c r="K6" t="n">
-        <v>16.64</v>
+        <v>15.99</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>8.82</v>
+        <v>8.17</v>
       </c>
       <c r="N6" t="n">
-        <v>-7.57</v>
+        <v>-4.65</v>
       </c>
       <c r="O6" t="n">
-        <v>-26.67</v>
+        <v>-24.41</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -910,46 +910,46 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.8206</v>
+        <v>3.8552</v>
       </c>
       <c r="D7" t="n">
-        <v>23.9</v>
+        <v>24.52</v>
       </c>
       <c r="E7" t="n">
-        <v>11.25</v>
+        <v>16.32</v>
       </c>
       <c r="F7" t="n">
-        <v>33.77</v>
+        <v>33.95</v>
       </c>
       <c r="G7" t="n">
-        <v>36.23</v>
+        <v>36.59</v>
       </c>
       <c r="H7" t="n">
-        <v>4.98</v>
+        <v>4.9</v>
       </c>
       <c r="I7" t="n">
         <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.76</v>
+        <v>-0.84</v>
       </c>
       <c r="K7" t="n">
-        <v>7.76</v>
+        <v>7.31</v>
       </c>
       <c r="L7" t="n">
         <v>83.33</v>
       </c>
       <c r="M7" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.36</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.22</v>
+        <v>2.63</v>
       </c>
       <c r="O7" t="n">
-        <v>-6.62</v>
+        <v>-5.3</v>
       </c>
       <c r="P7" t="n">
-        <v>-27.52</v>
+        <v>-23.84</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -984,19 +984,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.309</v>
+        <v>2.3081</v>
       </c>
       <c r="D8" t="n">
-        <v>14.34</v>
+        <v>14.58</v>
       </c>
       <c r="E8" t="n">
-        <v>40.45</v>
+        <v>51.19</v>
       </c>
       <c r="F8" t="n">
-        <v>33.51</v>
+        <v>34.28</v>
       </c>
       <c r="G8" t="n">
-        <v>66.41</v>
+        <v>69.61</v>
       </c>
       <c r="H8" t="n">
         <v>2.16</v>
@@ -1005,25 +1005,25 @@
         <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.95</v>
+        <v>-2.94</v>
       </c>
       <c r="K8" t="n">
-        <v>8.08</v>
+        <v>7.57</v>
       </c>
       <c r="L8" t="n">
         <v>25</v>
       </c>
       <c r="M8" t="n">
-        <v>-4.96</v>
+        <v>-5.47</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.32</v>
+        <v>0.95</v>
       </c>
       <c r="O8" t="n">
-        <v>-3.93</v>
+        <v>-0.72</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.789999999999999</v>
+        <v>-5.65</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.7652</v>
+        <v>3.6483</v>
       </c>
       <c r="D9" t="n">
-        <v>21.17</v>
+        <v>20.86</v>
       </c>
       <c r="E9" t="n">
-        <v>30.2</v>
+        <v>22.63</v>
       </c>
       <c r="F9" t="n">
-        <v>31.33</v>
+        <v>32</v>
       </c>
       <c r="G9" t="n">
-        <v>61.91</v>
+        <v>64.73</v>
       </c>
       <c r="H9" t="n">
-        <v>5.65</v>
+        <v>4.87</v>
       </c>
       <c r="I9" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="J9" t="n">
-        <v>1.01</v>
+        <v>0.23</v>
       </c>
       <c r="K9" t="n">
-        <v>7.92</v>
+        <v>8.98</v>
       </c>
       <c r="L9" t="n">
-        <v>4.17</v>
+        <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>-10.11</v>
+        <v>-9.06</v>
       </c>
       <c r="N9" t="n">
-        <v>0.36</v>
+        <v>0.55</v>
       </c>
       <c r="O9" t="n">
-        <v>3.26</v>
+        <v>1.26</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.83</v>
+        <v>-18.19</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5433</v>
+        <v>0.5377</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34</v>
+        <v>23.49</v>
       </c>
       <c r="E10" t="n">
-        <v>49.08</v>
+        <v>51.04</v>
       </c>
       <c r="F10" t="n">
-        <v>37.1</v>
+        <v>35.61</v>
       </c>
       <c r="G10" t="n">
-        <v>52.06</v>
+        <v>48.84</v>
       </c>
       <c r="H10" t="n">
-        <v>3.01</v>
+        <v>3.22</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.76</v>
+        <v>-0.54</v>
       </c>
       <c r="K10" t="n">
-        <v>4.45</v>
+        <v>4.72</v>
       </c>
       <c r="L10" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>0.15</v>
+        <v>0.41</v>
       </c>
       <c r="N10" t="n">
-        <v>-3.08</v>
+        <v>-1.59</v>
       </c>
       <c r="O10" t="n">
-        <v>-6.33</v>
+        <v>-7.04</v>
       </c>
       <c r="P10" t="n">
-        <v>-13.17</v>
+        <v>-11.91</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1206,19 +1206,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8124</v>
+        <v>0.8096</v>
       </c>
       <c r="D11" t="n">
-        <v>30.26</v>
+        <v>30.67</v>
       </c>
       <c r="E11" t="n">
-        <v>69.41</v>
+        <v>73.06</v>
       </c>
       <c r="F11" t="n">
-        <v>35.74</v>
+        <v>34.1</v>
       </c>
       <c r="G11" t="n">
-        <v>50.58</v>
+        <v>46.67</v>
       </c>
       <c r="H11" t="n">
         <v>2.68</v>
@@ -1230,22 +1230,22 @@
         <v>-1.19</v>
       </c>
       <c r="K11" t="n">
-        <v>3.62</v>
+        <v>2.97</v>
       </c>
       <c r="L11" t="n">
-        <v>45.83</v>
+        <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.42</v>
+        <v>-1.06</v>
       </c>
       <c r="N11" t="n">
-        <v>-5.58</v>
+        <v>-3.69</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.04</v>
+        <v>-11.22</v>
       </c>
       <c r="P11" t="n">
-        <v>-18.23</v>
+        <v>-16.71</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1280,46 +1280,46 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8763</v>
+        <v>6.8738</v>
       </c>
       <c r="D12" t="n">
-        <v>30.81</v>
+        <v>31.33</v>
       </c>
       <c r="E12" t="n">
-        <v>50.85</v>
+        <v>54.2</v>
       </c>
       <c r="F12" t="n">
-        <v>38.59</v>
+        <v>37.24</v>
       </c>
       <c r="G12" t="n">
-        <v>77.58</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>4.76</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
         <v>65</v>
       </c>
       <c r="J12" t="n">
-        <v>0.87</v>
+        <v>0.61</v>
       </c>
       <c r="K12" t="n">
-        <v>10.16</v>
+        <v>8.99</v>
       </c>
       <c r="L12" t="n">
-        <v>83.33</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>3.47</v>
+        <v>2.3</v>
       </c>
       <c r="N12" t="n">
-        <v>-3.49</v>
+        <v>-2</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.42</v>
+        <v>-7.39</v>
       </c>
       <c r="P12" t="n">
-        <v>-17.25</v>
+        <v>-14.82</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.741</v>
+        <v>2.7029</v>
       </c>
       <c r="D13" t="n">
-        <v>21.16</v>
+        <v>21.22</v>
       </c>
       <c r="E13" t="n">
-        <v>54.55</v>
+        <v>54.97</v>
       </c>
       <c r="F13" t="n">
-        <v>26.16</v>
+        <v>25.67</v>
       </c>
       <c r="G13" t="n">
-        <v>39.26</v>
+        <v>37.67</v>
       </c>
       <c r="H13" t="n">
-        <v>5.43</v>
+        <v>4.36</v>
       </c>
       <c r="I13" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>0.02</v>
+        <v>-1.05</v>
       </c>
       <c r="K13" t="n">
-        <v>6.11</v>
+        <v>5.45</v>
       </c>
       <c r="L13" t="n">
-        <v>66.67</v>
+        <v>54.17</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4</v>
+        <v>-3.07</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.22</v>
+        <v>-1.6</v>
       </c>
       <c r="O13" t="n">
-        <v>-3.08</v>
+        <v>-2.88</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.38</v>
+        <v>-3.76</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>-1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V13" t="inlineStr">
         <is>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.1004</v>
+        <v>2.0574</v>
       </c>
       <c r="D14" t="n">
-        <v>16.47</v>
+        <v>16.41</v>
       </c>
       <c r="E14" t="n">
-        <v>68.03</v>
+        <v>65.97</v>
       </c>
       <c r="F14" t="n">
-        <v>21.12</v>
+        <v>20.65</v>
       </c>
       <c r="G14" t="n">
-        <v>50.5</v>
+        <v>48.29</v>
       </c>
       <c r="H14" t="n">
-        <v>5.57</v>
+        <v>5.32</v>
       </c>
       <c r="I14" t="n">
         <v>60</v>
       </c>
       <c r="J14" t="n">
-        <v>0.53</v>
+        <v>0.28</v>
       </c>
       <c r="K14" t="n">
-        <v>7.41</v>
+        <v>10.22</v>
       </c>
       <c r="L14" t="n">
-        <v>62.5</v>
+        <v>87.5</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.72</v>
+        <v>1.09</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.46</v>
+        <v>-0.15</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.44</v>
+        <v>-4.08</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.43</v>
+        <v>-9.32</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9181</v>
+        <v>0.9072</v>
       </c>
       <c r="D15" t="n">
-        <v>12.61</v>
+        <v>12.67</v>
       </c>
       <c r="E15" t="n">
-        <v>30.12</v>
+        <v>30.72</v>
       </c>
       <c r="F15" t="n">
-        <v>33.95</v>
+        <v>31.93</v>
       </c>
       <c r="G15" t="n">
-        <v>53.06</v>
+        <v>47.83</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.28</v>
+        <v>-0.36</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.77</v>
+        <v>-0.84</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.67</v>
+        <v>-1.7</v>
       </c>
       <c r="L15" t="n">
         <v>33.33</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>2.74</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.8</v>
+        <v>-2.65</v>
       </c>
       <c r="O15" t="n">
-        <v>-6.7</v>
+        <v>-9.81</v>
       </c>
       <c r="P15" t="n">
-        <v>-26.03</v>
+        <v>-25.45</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8863</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="D16" t="n">
         <v>31.6</v>
       </c>
       <c r="E16" t="n">
-        <v>38.98</v>
+        <v>38.95</v>
       </c>
       <c r="F16" t="n">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="G16" t="n">
-        <v>57.33</v>
+        <v>56.59</v>
       </c>
       <c r="H16" t="n">
-        <v>3.26</v>
+        <v>2.58</v>
       </c>
       <c r="I16" t="n">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>1.41</v>
+        <v>0.73</v>
       </c>
       <c r="K16" t="n">
-        <v>17.52</v>
+        <v>11.79</v>
       </c>
       <c r="L16" t="n">
         <v>100</v>
       </c>
       <c r="M16" t="n">
-        <v>13</v>
+        <v>7.27</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.16</v>
+        <v>0.25</v>
       </c>
       <c r="O16" t="n">
-        <v>-5.92</v>
+        <v>-7.58</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.14</v>
+        <v>-26.03</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1650,46 +1650,46 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5218</v>
+        <v>0.5161</v>
       </c>
       <c r="D17" t="n">
-        <v>38.46</v>
+        <v>38.69</v>
       </c>
       <c r="E17" t="n">
-        <v>18.49</v>
+        <v>18.71</v>
       </c>
       <c r="F17" t="n">
-        <v>34.29</v>
+        <v>33.51</v>
       </c>
       <c r="G17" t="n">
-        <v>23.66</v>
+        <v>21.32</v>
       </c>
       <c r="H17" t="n">
-        <v>5.93</v>
+        <v>4.39</v>
       </c>
       <c r="I17" t="n">
-        <v>95</v>
+        <v>70</v>
       </c>
       <c r="J17" t="n">
-        <v>0.79</v>
+        <v>-0.75</v>
       </c>
       <c r="K17" t="n">
-        <v>1.87</v>
+        <v>2.21</v>
       </c>
       <c r="L17" t="n">
-        <v>66.67</v>
+        <v>70.83</v>
       </c>
       <c r="M17" t="n">
-        <v>-4.27</v>
+        <v>-3.93</v>
       </c>
       <c r="N17" t="n">
-        <v>-3.58</v>
+        <v>-2.54</v>
       </c>
       <c r="O17" t="n">
-        <v>-9.48</v>
+        <v>-10.7</v>
       </c>
       <c r="P17" t="n">
-        <v>-22.25</v>
+        <v>-21.51</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1698,13 +1698,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1724,28 +1724,28 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.4013</v>
+        <v>6.2553</v>
       </c>
       <c r="D18" t="n">
-        <v>6.59</v>
+        <v>6.55</v>
       </c>
       <c r="E18" t="n">
-        <v>90.91</v>
+        <v>89.3</v>
       </c>
       <c r="F18" t="n">
-        <v>14.14</v>
+        <v>14.22</v>
       </c>
       <c r="G18" t="n">
-        <v>84.87</v>
+        <v>85.19</v>
       </c>
       <c r="H18" t="n">
-        <v>8.07</v>
+        <v>8.85</v>
       </c>
       <c r="I18" t="n">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="J18" t="n">
-        <v>0.15</v>
+        <v>0.93</v>
       </c>
       <c r="K18" t="n">
         <v>9.23</v>
@@ -1757,16 +1757,16 @@
         <v>0.91</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>4.72</v>
+        <v>3.58</v>
       </c>
       <c r="P18" t="n">
-        <v>8.609999999999999</v>
+        <v>7.19</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.2817</v>
+        <v>5.1612</v>
       </c>
       <c r="D19" t="n">
-        <v>8.640000000000001</v>
+        <v>8.59</v>
       </c>
       <c r="E19" t="n">
-        <v>0.15</v>
+        <v>0.08</v>
       </c>
       <c r="F19" t="n">
-        <v>15.85</v>
+        <v>15.58</v>
       </c>
       <c r="G19" t="n">
-        <v>25.29</v>
+        <v>23.88</v>
       </c>
       <c r="H19" t="n">
-        <v>5.41</v>
+        <v>5.38</v>
       </c>
       <c r="I19" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="K19" t="n">
-        <v>10.22</v>
+        <v>9.69</v>
       </c>
       <c r="L19" t="n">
-        <v>87.5</v>
+        <v>79.17</v>
       </c>
       <c r="M19" t="n">
-        <v>0.43</v>
+        <v>-0.11</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.34</v>
+        <v>-0.26</v>
       </c>
       <c r="O19" t="n">
-        <v>-5</v>
+        <v>-6.61</v>
       </c>
       <c r="P19" t="n">
-        <v>-18.62</v>
+        <v>-18.15</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1872,46 +1872,46 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1993</v>
+        <v>0.1958</v>
       </c>
       <c r="D20" t="n">
-        <v>68.78</v>
+        <v>68.75</v>
       </c>
       <c r="E20" t="n">
-        <v>85.90000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>39.39</v>
+        <v>36.1</v>
       </c>
       <c r="G20" t="n">
-        <v>68.73999999999999</v>
+        <v>59.92</v>
       </c>
       <c r="H20" t="n">
-        <v>3.29</v>
+        <v>2.92</v>
       </c>
       <c r="I20" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J20" t="n">
-        <v>0.03</v>
+        <v>-0.34</v>
       </c>
       <c r="K20" t="n">
-        <v>7.59</v>
+        <v>7.25</v>
       </c>
       <c r="L20" t="n">
         <v>100</v>
       </c>
       <c r="M20" t="n">
-        <v>9.039999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.45</v>
+        <v>-6.62</v>
       </c>
       <c r="O20" t="n">
-        <v>-14.51</v>
+        <v>-14.45</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.3</v>
+        <v>-2.59</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
@@ -1920,13 +1920,13 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1946,46 +1946,46 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.863</v>
+        <v>0.8575</v>
       </c>
       <c r="D21" t="n">
-        <v>32.19</v>
+        <v>32.53</v>
       </c>
       <c r="E21" t="n">
-        <v>86.52</v>
+        <v>86.84</v>
       </c>
       <c r="F21" t="n">
-        <v>38.65</v>
+        <v>38</v>
       </c>
       <c r="G21" t="n">
-        <v>69.28</v>
+        <v>68.14</v>
       </c>
       <c r="H21" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="I21" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.58</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>9.6</v>
+        <v>8.19</v>
       </c>
       <c r="L21" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M21" t="n">
-        <v>4.99</v>
+        <v>3.58</v>
       </c>
       <c r="N21" t="n">
-        <v>-6.39</v>
+        <v>-5.98</v>
       </c>
       <c r="O21" t="n">
-        <v>-18.38</v>
+        <v>-19.63</v>
       </c>
       <c r="P21" t="n">
-        <v>-6.91</v>
+        <v>-4.83</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2020,46 +2020,46 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3715</v>
+        <v>1.3562</v>
       </c>
       <c r="D22" t="n">
-        <v>13.62</v>
+        <v>13.69</v>
       </c>
       <c r="E22" t="n">
-        <v>89.06</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>24.52</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>29.48</v>
+        <v>27.13</v>
       </c>
       <c r="H22" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="I22" t="n">
         <v>40</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.16</v>
+        <v>0.12</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.49</v>
+        <v>-2.21</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.72</v>
+        <v>-3.19</v>
       </c>
       <c r="O22" t="n">
-        <v>-8.970000000000001</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="P22" t="n">
-        <v>-17.91</v>
+        <v>-17.1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2094,46 +2094,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.7207</v>
+        <v>7.6476</v>
       </c>
       <c r="D23" t="n">
-        <v>23.73</v>
+        <v>23.9</v>
       </c>
       <c r="E23" t="n">
-        <v>23.88</v>
+        <v>23.94</v>
       </c>
       <c r="F23" t="n">
-        <v>36.57</v>
+        <v>34.71</v>
       </c>
       <c r="G23" t="n">
-        <v>49.42</v>
+        <v>44.73</v>
       </c>
       <c r="H23" t="n">
-        <v>4.01</v>
+        <v>3.82</v>
       </c>
       <c r="I23" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J23" t="n">
-        <v>0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="K23" t="n">
-        <v>10.66</v>
+        <v>9.99</v>
       </c>
       <c r="L23" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M23" t="n">
-        <v>2.24</v>
+        <v>1.57</v>
       </c>
       <c r="N23" t="n">
-        <v>-5.25</v>
+        <v>-0.92</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.79</v>
+        <v>-16.06</v>
       </c>
       <c r="P23" t="n">
-        <v>-28.28</v>
+        <v>-27.26</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
         <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V23" t="inlineStr">
         <is>
@@ -2168,46 +2168,46 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.0095</v>
+        <v>6.1253</v>
       </c>
       <c r="D24" t="n">
-        <v>36.29</v>
+        <v>37.61</v>
       </c>
       <c r="E24" t="n">
-        <v>78.89</v>
+        <v>82.45</v>
       </c>
       <c r="F24" t="n">
-        <v>38.36</v>
+        <v>37.96</v>
       </c>
       <c r="G24" t="n">
-        <v>53.14</v>
+        <v>52.87</v>
       </c>
       <c r="H24" t="n">
-        <v>3.79</v>
+        <v>3.64</v>
       </c>
       <c r="I24" t="n">
         <v>45</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.17</v>
+        <v>-0.32</v>
       </c>
       <c r="K24" t="n">
-        <v>7.73</v>
+        <v>6.88</v>
       </c>
       <c r="L24" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M24" t="n">
-        <v>2.39</v>
+        <v>1.54</v>
       </c>
       <c r="N24" t="n">
-        <v>-3.97</v>
+        <v>-0.25</v>
       </c>
       <c r="O24" t="n">
-        <v>-17.61</v>
+        <v>-14.66</v>
       </c>
       <c r="P24" t="n">
-        <v>-11.76</v>
+        <v>-7.75</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2242,46 +2242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7083</v>
+        <v>2.6908</v>
       </c>
       <c r="D25" t="n">
-        <v>52.78</v>
+        <v>53.34</v>
       </c>
       <c r="E25" t="n">
-        <v>22.19</v>
+        <v>23.17</v>
       </c>
       <c r="F25" t="n">
-        <v>39.9</v>
+        <v>39.02</v>
       </c>
       <c r="G25" t="n">
-        <v>64.7</v>
+        <v>62.64</v>
       </c>
       <c r="H25" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.39</v>
+        <v>-1.41</v>
       </c>
       <c r="K25" t="n">
-        <v>4.33</v>
+        <v>5.85</v>
       </c>
       <c r="L25" t="n">
-        <v>58.33</v>
+        <v>83.33</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.42</v>
+        <v>1.1</v>
       </c>
       <c r="N25" t="n">
-        <v>-5.58</v>
+        <v>-4.12</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.19</v>
+        <v>-12.86</v>
       </c>
       <c r="P25" t="n">
-        <v>-15.38</v>
+        <v>-15.22</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>5.0245</v>
+        <v>4.9813</v>
       </c>
       <c r="D26" t="n">
-        <v>57.38</v>
+        <v>57.85</v>
       </c>
       <c r="E26" t="n">
-        <v>41.76</v>
+        <v>42.8</v>
       </c>
       <c r="F26" t="n">
-        <v>40.74</v>
+        <v>40.62</v>
       </c>
       <c r="G26" t="n">
-        <v>39.02</v>
+        <v>38.45</v>
       </c>
       <c r="H26" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I26" t="n">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="K26" t="n">
-        <v>4.58</v>
+        <v>3.73</v>
       </c>
       <c r="L26" t="n">
         <v>91.67</v>
       </c>
       <c r="M26" t="n">
-        <v>2.67</v>
+        <v>1.82</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.95</v>
+        <v>-1.68</v>
       </c>
       <c r="O26" t="n">
-        <v>-6.91</v>
+        <v>-7.32</v>
       </c>
       <c r="P26" t="n">
-        <v>-27.32</v>
+        <v>-26.88</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2364,13 +2364,13 @@
         <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
         <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2390,46 +2390,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8842</v>
+        <v>1.8894</v>
       </c>
       <c r="D27" t="n">
-        <v>33.86</v>
+        <v>34.53</v>
       </c>
       <c r="E27" t="n">
-        <v>41.45</v>
+        <v>43.49</v>
       </c>
       <c r="F27" t="n">
-        <v>71.18000000000001</v>
+        <v>68.48999999999999</v>
       </c>
       <c r="G27" t="n">
-        <v>85.48999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="H27" t="n">
-        <v>1.93</v>
+        <v>1.97</v>
       </c>
       <c r="I27" t="n">
         <v>40</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.29</v>
+        <v>-0.25</v>
       </c>
       <c r="K27" t="n">
-        <v>5.45</v>
+        <v>7.75</v>
       </c>
       <c r="L27" t="n">
-        <v>70.83</v>
+        <v>83.33</v>
       </c>
       <c r="M27" t="n">
-        <v>1.29</v>
+        <v>3.59</v>
       </c>
       <c r="N27" t="n">
-        <v>-2.68</v>
+        <v>-0.71</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.76</v>
+        <v>-2.03</v>
       </c>
       <c r="P27" t="n">
-        <v>-21.59</v>
+        <v>-18.79</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2464,46 +2464,46 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>4.965</v>
+        <v>5.1252</v>
       </c>
       <c r="D28" t="n">
-        <v>37.53</v>
+        <v>39.4</v>
       </c>
       <c r="E28" t="n">
-        <v>72.5</v>
+        <v>77.52</v>
       </c>
       <c r="F28" t="n">
-        <v>35.65</v>
+        <v>33.4</v>
       </c>
       <c r="G28" t="n">
-        <v>44.22</v>
+        <v>36.05</v>
       </c>
       <c r="H28" t="n">
-        <v>2.2</v>
+        <v>3.04</v>
       </c>
       <c r="I28" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.51</v>
+        <v>0.33</v>
       </c>
       <c r="K28" t="n">
-        <v>10.16</v>
+        <v>13.14</v>
       </c>
       <c r="L28" t="n">
-        <v>66.67</v>
+        <v>75</v>
       </c>
       <c r="M28" t="n">
-        <v>-12.26</v>
+        <v>-9.279999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>-9.73</v>
+        <v>-5.77</v>
       </c>
       <c r="O28" t="n">
-        <v>-31.34</v>
+        <v>-28.84</v>
       </c>
       <c r="P28" t="n">
-        <v>9.800000000000001</v>
+        <v>15.77</v>
       </c>
       <c r="Q28" t="n">
         <v>0</v>
@@ -2512,13 +2512,13 @@
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2538,46 +2538,46 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0765</v>
+        <v>1.0617</v>
       </c>
       <c r="D29" t="n">
-        <v>18.03</v>
+        <v>18.08</v>
       </c>
       <c r="E29" t="n">
-        <v>81.3</v>
+        <v>81.48</v>
       </c>
       <c r="F29" t="n">
-        <v>34.15</v>
+        <v>32.64</v>
       </c>
       <c r="G29" t="n">
-        <v>58.26</v>
+        <v>56.32</v>
       </c>
       <c r="H29" t="n">
-        <v>6.78</v>
+        <v>5.46</v>
       </c>
       <c r="I29" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>3.47</v>
+        <v>2.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.35</v>
+        <v>-28.21</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-42.7</v>
+        <v>-34.56</v>
       </c>
       <c r="N29" t="n">
-        <v>-3.77</v>
+        <v>-1.61</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.23</v>
+        <v>-1.87</v>
       </c>
       <c r="P29" t="n">
-        <v>17.02</v>
+        <v>17.52</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2612,46 +2612,46 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.3101</v>
+        <v>1.2931</v>
       </c>
       <c r="D30" t="n">
-        <v>16.55</v>
+        <v>16.61</v>
       </c>
       <c r="E30" t="n">
-        <v>71.81999999999999</v>
+        <v>72.87</v>
       </c>
       <c r="F30" t="n">
-        <v>24.35</v>
+        <v>24.3</v>
       </c>
       <c r="G30" t="n">
-        <v>53.96</v>
+        <v>53.65</v>
       </c>
       <c r="H30" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="I30" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>1.32</v>
+        <v>1.92</v>
       </c>
       <c r="K30" t="n">
-        <v>10.56</v>
+        <v>10.33</v>
       </c>
       <c r="L30" t="n">
         <v>95.83</v>
       </c>
       <c r="M30" t="n">
-        <v>5.68</v>
+        <v>5.45</v>
       </c>
       <c r="N30" t="n">
-        <v>-0.78</v>
+        <v>0.36</v>
       </c>
       <c r="O30" t="n">
-        <v>1.81</v>
+        <v>-0.12</v>
       </c>
       <c r="P30" t="n">
-        <v>17.1</v>
+        <v>18.99</v>
       </c>
       <c r="Q30" t="n">
         <v>0</v>
@@ -2686,46 +2686,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8025</v>
+        <v>0.7996</v>
       </c>
       <c r="D31" t="n">
-        <v>22.48</v>
+        <v>22.77</v>
       </c>
       <c r="E31" t="n">
-        <v>58.75</v>
+        <v>62.63</v>
       </c>
       <c r="F31" t="n">
-        <v>26.38</v>
+        <v>25.41</v>
       </c>
       <c r="G31" t="n">
-        <v>40.28</v>
+        <v>36.63</v>
       </c>
       <c r="H31" t="n">
-        <v>4.61</v>
+        <v>3.54</v>
       </c>
       <c r="I31" t="n">
+        <v>55</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K31" t="n">
+        <v>5.47</v>
+      </c>
+      <c r="L31" t="n">
         <v>75</v>
       </c>
-      <c r="J31" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="K31" t="n">
-        <v>6.37</v>
-      </c>
-      <c r="L31" t="n">
-        <v>87.5</v>
-      </c>
       <c r="M31" t="n">
-        <v>4.58</v>
+        <v>3.69</v>
       </c>
       <c r="N31" t="n">
-        <v>-4.17</v>
+        <v>-2.33</v>
       </c>
       <c r="O31" t="n">
-        <v>-12.29</v>
+        <v>-12.12</v>
       </c>
       <c r="P31" t="n">
-        <v>-15.72</v>
+        <v>-16.02</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2760,46 +2760,46 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2049</v>
+        <v>0.2006</v>
       </c>
       <c r="D32" t="n">
-        <v>27.59</v>
+        <v>27.47</v>
       </c>
       <c r="E32" t="n">
-        <v>3.76</v>
+        <v>3.24</v>
       </c>
       <c r="F32" t="n">
-        <v>38.05</v>
+        <v>37.84</v>
       </c>
       <c r="G32" t="n">
-        <v>58.61</v>
+        <v>57.95</v>
       </c>
       <c r="H32" t="n">
-        <v>5.95</v>
+        <v>6.33</v>
       </c>
       <c r="I32" t="n">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.05</v>
+        <v>0.33</v>
       </c>
       <c r="K32" t="n">
-        <v>5.45</v>
+        <v>6.31</v>
       </c>
       <c r="L32" t="n">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="M32" t="n">
-        <v>-3</v>
+        <v>-2.14</v>
       </c>
       <c r="N32" t="n">
-        <v>-2.79</v>
+        <v>-1.29</v>
       </c>
       <c r="O32" t="n">
-        <v>-1.77</v>
+        <v>-5.01</v>
       </c>
       <c r="P32" t="n">
-        <v>-30.74</v>
+        <v>-29.92</v>
       </c>
       <c r="Q32" t="n">
         <v>1</v>
@@ -2808,13 +2808,13 @@
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,61 +540,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2924</v>
+        <v>1.2152</v>
       </c>
       <c r="D2" t="n">
-        <v>76.8</v>
+        <v>42.69</v>
       </c>
       <c r="E2" t="n">
-        <v>78.98</v>
+        <v>58.43</v>
       </c>
       <c r="F2" t="n">
-        <v>42.09</v>
+        <v>57.74</v>
       </c>
       <c r="G2" t="n">
-        <v>76.67</v>
+        <v>96.41</v>
       </c>
       <c r="H2" t="n">
-        <v>1.14</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.49</v>
+        <v>-2.07</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.68</v>
+        <v>-4.94</v>
       </c>
       <c r="L2" t="n">
-        <v>16.67</v>
+        <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-9.09</v>
+        <v>-11.35</v>
       </c>
       <c r="N2" t="n">
-        <v>-4.23</v>
+        <v>6.46</v>
       </c>
       <c r="O2" t="n">
-        <v>-7.9</v>
+        <v>7.93</v>
       </c>
       <c r="P2" t="n">
-        <v>-18.96</v>
+        <v>-7.22</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.527</v>
+        <v>4.657</v>
       </c>
       <c r="D3" t="n">
-        <v>23.09</v>
+        <v>30.24</v>
       </c>
       <c r="E3" t="n">
-        <v>55.5</v>
+        <v>89.39</v>
       </c>
       <c r="F3" t="n">
-        <v>33.43</v>
+        <v>44.64</v>
       </c>
       <c r="G3" t="n">
-        <v>41.63</v>
+        <v>70.65000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>4.16</v>
+        <v>3.83</v>
       </c>
       <c r="I3" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>0.12</v>
+        <v>-0.21</v>
       </c>
       <c r="K3" t="n">
-        <v>9.18</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>70.83</v>
+        <v>66.67</v>
       </c>
       <c r="M3" t="n">
-        <v>2.27</v>
+        <v>1.4</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.34</v>
+        <v>3.4</v>
       </c>
       <c r="O3" t="n">
-        <v>-12.95</v>
+        <v>8.91</v>
       </c>
       <c r="P3" t="n">
-        <v>-9.17</v>
+        <v>17.02</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -662,10 +662,10 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -688,46 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.6069</v>
+        <v>0.591</v>
       </c>
       <c r="D4" t="n">
-        <v>28.13</v>
+        <v>29.91</v>
       </c>
       <c r="E4" t="n">
-        <v>69.05</v>
+        <v>77.04000000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>16.87</v>
+        <v>20.73</v>
       </c>
       <c r="G4" t="n">
-        <v>28.29</v>
+        <v>41.95</v>
       </c>
       <c r="H4" t="n">
-        <v>2.5</v>
+        <v>0.97</v>
       </c>
       <c r="I4" t="n">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="J4" t="n">
-        <v>0.34</v>
+        <v>-1.2</v>
       </c>
       <c r="K4" t="n">
-        <v>2.98</v>
+        <v>2.14</v>
       </c>
       <c r="L4" t="n">
-        <v>50</v>
+        <v>41.67</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.05</v>
+        <v>-0.89</v>
       </c>
       <c r="N4" t="n">
-        <v>-3.42</v>
+        <v>3.23</v>
       </c>
       <c r="O4" t="n">
-        <v>-7.88</v>
+        <v>1.05</v>
       </c>
       <c r="P4" t="n">
-        <v>-24.04</v>
+        <v>-7.91</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -736,13 +736,13 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
         <v>1</v>
       </c>
-      <c r="T4" t="n">
-        <v>-1</v>
-      </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -762,46 +762,46 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.0015</v>
+        <v>5.6791</v>
       </c>
       <c r="D5" t="n">
-        <v>14.73</v>
+        <v>22.51</v>
       </c>
       <c r="E5" t="n">
-        <v>11.16</v>
+        <v>64.77</v>
       </c>
       <c r="F5" t="n">
-        <v>26.15</v>
+        <v>48.93</v>
       </c>
       <c r="G5" t="n">
-        <v>31.71</v>
+        <v>77.27</v>
       </c>
       <c r="H5" t="n">
-        <v>9.27</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="J5" t="n">
-        <v>2.83</v>
+        <v>2.03</v>
       </c>
       <c r="K5" t="n">
-        <v>18.52</v>
+        <v>18.13</v>
       </c>
       <c r="L5" t="n">
         <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>6.13</v>
+        <v>5.75</v>
       </c>
       <c r="N5" t="n">
-        <v>-3.74</v>
+        <v>1.68</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.6</v>
+        <v>11.35</v>
       </c>
       <c r="P5" t="n">
-        <v>-14.33</v>
+        <v>51.35</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -813,10 +813,10 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="inlineStr">
         <is>
@@ -836,49 +836,49 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>17.8437</v>
+        <v>19.8026</v>
       </c>
       <c r="D6" t="n">
-        <v>48.83</v>
+        <v>80.47</v>
       </c>
       <c r="E6" t="n">
-        <v>59.58</v>
+        <v>95.95999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>42.69</v>
+        <v>55.94</v>
       </c>
       <c r="G6" t="n">
-        <v>67.52</v>
+        <v>82.93000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.48</v>
+        <v>4.19</v>
       </c>
       <c r="I6" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J6" t="n">
-        <v>1.15</v>
+        <v>0.86</v>
       </c>
       <c r="K6" t="n">
-        <v>15.99</v>
+        <v>15.77</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>8.17</v>
+        <v>7.95</v>
       </c>
       <c r="N6" t="n">
-        <v>-4.65</v>
+        <v>0.15</v>
       </c>
       <c r="O6" t="n">
-        <v>-24.41</v>
+        <v>10.24</v>
       </c>
       <c r="P6" t="n">
-        <v>2.88</v>
+        <v>69.34</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.8552</v>
+        <v>3.5901</v>
       </c>
       <c r="D7" t="n">
-        <v>24.52</v>
+        <v>24.97</v>
       </c>
       <c r="E7" t="n">
-        <v>16.32</v>
+        <v>19.79</v>
       </c>
       <c r="F7" t="n">
-        <v>33.95</v>
+        <v>27.86</v>
       </c>
       <c r="G7" t="n">
-        <v>36.59</v>
+        <v>17.3</v>
       </c>
       <c r="H7" t="n">
-        <v>4.9</v>
+        <v>4.32</v>
       </c>
       <c r="I7" t="n">
         <v>55</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.84</v>
+        <v>-1.42</v>
       </c>
       <c r="K7" t="n">
         <v>7.31</v>
@@ -943,13 +943,13 @@
         <v>0.36</v>
       </c>
       <c r="N7" t="n">
-        <v>2.63</v>
+        <v>1.11</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.3</v>
+        <v>0.23</v>
       </c>
       <c r="P7" t="n">
-        <v>-23.84</v>
+        <v>-11.67</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.3081</v>
+        <v>2.0936</v>
       </c>
       <c r="D8" t="n">
-        <v>14.58</v>
+        <v>14.85</v>
       </c>
       <c r="E8" t="n">
-        <v>51.19</v>
+        <v>65</v>
       </c>
       <c r="F8" t="n">
-        <v>34.28</v>
+        <v>28.88</v>
       </c>
       <c r="G8" t="n">
-        <v>69.61</v>
+        <v>48.8</v>
       </c>
       <c r="H8" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="I8" t="n">
         <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.94</v>
+        <v>-2.85</v>
       </c>
       <c r="K8" t="n">
-        <v>7.57</v>
+        <v>12.21</v>
       </c>
       <c r="L8" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>-5.47</v>
+        <v>-0.83</v>
       </c>
       <c r="N8" t="n">
-        <v>0.95</v>
+        <v>0.65</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.72</v>
+        <v>-1.5</v>
       </c>
       <c r="P8" t="n">
-        <v>-5.65</v>
+        <v>-1.36</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.6483</v>
+        <v>3.2137</v>
       </c>
       <c r="D9" t="n">
-        <v>20.86</v>
+        <v>19.98</v>
       </c>
       <c r="E9" t="n">
-        <v>22.63</v>
+        <v>10.61</v>
       </c>
       <c r="F9" t="n">
-        <v>32</v>
+        <v>38.84</v>
       </c>
       <c r="G9" t="n">
-        <v>64.73</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.87</v>
+        <v>4.43</v>
       </c>
       <c r="I9" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J9" t="n">
-        <v>0.23</v>
+        <v>-0.21</v>
       </c>
       <c r="K9" t="n">
-        <v>8.98</v>
+        <v>11.38</v>
       </c>
       <c r="L9" t="n">
         <v>25</v>
       </c>
       <c r="M9" t="n">
-        <v>-9.06</v>
+        <v>-6.66</v>
       </c>
       <c r="N9" t="n">
-        <v>0.55</v>
+        <v>1.14</v>
       </c>
       <c r="O9" t="n">
-        <v>1.26</v>
+        <v>-4.04</v>
       </c>
       <c r="P9" t="n">
-        <v>-18.19</v>
+        <v>-17.26</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1106,13 +1106,13 @@
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.5377</v>
+        <v>0.512</v>
       </c>
       <c r="D10" t="n">
-        <v>23.49</v>
+        <v>24.93</v>
       </c>
       <c r="E10" t="n">
-        <v>51.04</v>
+        <v>67.54000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>35.61</v>
+        <v>41.31</v>
       </c>
       <c r="G10" t="n">
-        <v>48.84</v>
+        <v>62.76</v>
       </c>
       <c r="H10" t="n">
-        <v>3.22</v>
+        <v>3.01</v>
       </c>
       <c r="I10" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.54</v>
+        <v>-0.76</v>
       </c>
       <c r="K10" t="n">
-        <v>4.72</v>
+        <v>2.98</v>
       </c>
       <c r="L10" t="n">
-        <v>75</v>
+        <v>33.33</v>
       </c>
       <c r="M10" t="n">
-        <v>0.41</v>
+        <v>-1.33</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.59</v>
+        <v>2.53</v>
       </c>
       <c r="O10" t="n">
-        <v>-7.04</v>
+        <v>5.71</v>
       </c>
       <c r="P10" t="n">
-        <v>-11.91</v>
+        <v>-3.95</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1183,10 +1183,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.8096</v>
+        <v>0.7734</v>
       </c>
       <c r="D11" t="n">
-        <v>30.67</v>
+        <v>32.45</v>
       </c>
       <c r="E11" t="n">
-        <v>73.06</v>
+        <v>88.92</v>
       </c>
       <c r="F11" t="n">
-        <v>34.1</v>
+        <v>33.55</v>
       </c>
       <c r="G11" t="n">
-        <v>46.67</v>
+        <v>46.73</v>
       </c>
       <c r="H11" t="n">
-        <v>2.68</v>
+        <v>2.57</v>
       </c>
       <c r="I11" t="n">
         <v>35</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.19</v>
+        <v>-1.3</v>
       </c>
       <c r="K11" t="n">
-        <v>2.97</v>
+        <v>3.24</v>
       </c>
       <c r="L11" t="n">
         <v>37.5</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.06</v>
+        <v>-0.79</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.69</v>
+        <v>2.55</v>
       </c>
       <c r="O11" t="n">
-        <v>-11.22</v>
+        <v>5.76</v>
       </c>
       <c r="P11" t="n">
-        <v>-16.71</v>
+        <v>-5.7</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1280,61 +1280,61 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.8738</v>
+        <v>6.3566</v>
       </c>
       <c r="D12" t="n">
-        <v>31.33</v>
+        <v>33.76</v>
       </c>
       <c r="E12" t="n">
-        <v>54.2</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>37.24</v>
+        <v>54.75</v>
       </c>
       <c r="G12" t="n">
-        <v>74.65000000000001</v>
+        <v>96.48999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>3.87</v>
       </c>
       <c r="I12" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>0.61</v>
+        <v>-0.02</v>
       </c>
       <c r="K12" t="n">
-        <v>8.99</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="N12" t="n">
+        <v>-1.43</v>
+      </c>
+      <c r="O12" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-11.45</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U12" t="n">
         <v>-2</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-7.39</v>
-      </c>
-      <c r="P12" t="n">
-        <v>-14.82</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>0</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.7029</v>
+        <v>2.4189</v>
       </c>
       <c r="D13" t="n">
-        <v>21.22</v>
+        <v>20.98</v>
       </c>
       <c r="E13" t="n">
-        <v>54.97</v>
+        <v>54.24</v>
       </c>
       <c r="F13" t="n">
-        <v>25.67</v>
+        <v>28.8</v>
       </c>
       <c r="G13" t="n">
-        <v>37.67</v>
+        <v>48.72</v>
       </c>
       <c r="H13" t="n">
-        <v>4.36</v>
+        <v>4.79</v>
       </c>
       <c r="I13" t="n">
         <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.05</v>
+        <v>-0.62</v>
       </c>
       <c r="K13" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="L13" t="n">
-        <v>54.17</v>
+        <v>58.33</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.07</v>
+        <v>-3.02</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.6</v>
+        <v>1.7</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.88</v>
+        <v>-1.79</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.76</v>
+        <v>4.06</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2.0574</v>
+        <v>1.8702</v>
       </c>
       <c r="D14" t="n">
-        <v>16.41</v>
+        <v>17.06</v>
       </c>
       <c r="E14" t="n">
-        <v>65.97</v>
+        <v>79.81</v>
       </c>
       <c r="F14" t="n">
-        <v>20.65</v>
+        <v>21.02</v>
       </c>
       <c r="G14" t="n">
-        <v>48.29</v>
+        <v>50.64</v>
       </c>
       <c r="H14" t="n">
-        <v>5.32</v>
+        <v>5.38</v>
       </c>
       <c r="I14" t="n">
         <v>60</v>
       </c>
       <c r="J14" t="n">
-        <v>0.28</v>
+        <v>0.34</v>
       </c>
       <c r="K14" t="n">
-        <v>10.22</v>
+        <v>8.91</v>
       </c>
       <c r="L14" t="n">
-        <v>87.5</v>
+        <v>79.17</v>
       </c>
       <c r="M14" t="n">
-        <v>1.09</v>
+        <v>-0.23</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.15</v>
+        <v>1.59</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.08</v>
+        <v>0.42</v>
       </c>
       <c r="P14" t="n">
-        <v>-9.32</v>
+        <v>-5.79</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1479,10 +1479,10 @@
         <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.9072</v>
+        <v>0.8423</v>
       </c>
       <c r="D15" t="n">
-        <v>12.67</v>
+        <v>20.13</v>
       </c>
       <c r="E15" t="n">
-        <v>30.72</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>31.93</v>
+        <v>35.1</v>
       </c>
       <c r="G15" t="n">
-        <v>47.83</v>
+        <v>57.89</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.36</v>
+        <v>-0.32</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.84</v>
+        <v>-0.8</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.7</v>
+        <v>-5.09</v>
       </c>
       <c r="L15" t="n">
-        <v>33.33</v>
+        <v>8.33</v>
       </c>
       <c r="M15" t="n">
-        <v>2.74</v>
+        <v>-0.66</v>
       </c>
       <c r="N15" t="n">
-        <v>-2.65</v>
+        <v>2.59</v>
       </c>
       <c r="O15" t="n">
-        <v>-9.81</v>
+        <v>4.7</v>
       </c>
       <c r="P15" t="n">
-        <v>-25.45</v>
+        <v>-11.88</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8715000000000001</v>
+        <v>0.8192</v>
       </c>
       <c r="D16" t="n">
-        <v>31.6</v>
+        <v>34.96</v>
       </c>
       <c r="E16" t="n">
-        <v>38.95</v>
+        <v>58.75</v>
       </c>
       <c r="F16" t="n">
-        <v>34.75</v>
+        <v>34.91</v>
       </c>
       <c r="G16" t="n">
-        <v>56.59</v>
+        <v>58.61</v>
       </c>
       <c r="H16" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="I16" t="n">
         <v>70</v>
       </c>
       <c r="J16" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="K16" t="n">
-        <v>11.79</v>
+        <v>9.15</v>
       </c>
       <c r="L16" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M16" t="n">
-        <v>7.27</v>
+        <v>4.63</v>
       </c>
       <c r="N16" t="n">
-        <v>0.25</v>
+        <v>3.41</v>
       </c>
       <c r="O16" t="n">
-        <v>-7.58</v>
+        <v>1.06</v>
       </c>
       <c r="P16" t="n">
-        <v>-26.03</v>
+        <v>-17.46</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.5161</v>
+        <v>0.4965</v>
       </c>
       <c r="D17" t="n">
-        <v>38.69</v>
+        <v>40.41</v>
       </c>
       <c r="E17" t="n">
-        <v>18.71</v>
+        <v>21.69</v>
       </c>
       <c r="F17" t="n">
-        <v>33.51</v>
+        <v>36.99</v>
       </c>
       <c r="G17" t="n">
-        <v>21.32</v>
+        <v>28.87</v>
       </c>
       <c r="H17" t="n">
         <v>4.39</v>
@@ -1674,22 +1674,22 @@
         <v>-0.75</v>
       </c>
       <c r="K17" t="n">
-        <v>2.21</v>
+        <v>2.63</v>
       </c>
       <c r="L17" t="n">
         <v>70.83</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.93</v>
+        <v>-3.5</v>
       </c>
       <c r="N17" t="n">
-        <v>-2.54</v>
+        <v>3.32</v>
       </c>
       <c r="O17" t="n">
-        <v>-10.7</v>
+        <v>4.96</v>
       </c>
       <c r="P17" t="n">
-        <v>-21.51</v>
+        <v>-13.84</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1724,46 +1724,46 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6.2553</v>
+        <v>5.1334</v>
       </c>
       <c r="D18" t="n">
-        <v>6.55</v>
+        <v>6.17</v>
       </c>
       <c r="E18" t="n">
-        <v>89.3</v>
+        <v>72.84</v>
       </c>
       <c r="F18" t="n">
-        <v>14.22</v>
+        <v>12.28</v>
       </c>
       <c r="G18" t="n">
-        <v>85.19</v>
+        <v>73.44</v>
       </c>
       <c r="H18" t="n">
-        <v>8.85</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="J18" t="n">
-        <v>0.93</v>
+        <v>0.19</v>
       </c>
       <c r="K18" t="n">
-        <v>9.23</v>
+        <v>9.01</v>
       </c>
       <c r="L18" t="n">
         <v>58.33</v>
       </c>
       <c r="M18" t="n">
-        <v>0.91</v>
+        <v>0.7</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="O18" t="n">
-        <v>3.58</v>
+        <v>-1.38</v>
       </c>
       <c r="P18" t="n">
-        <v>7.19</v>
+        <v>-7.55</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1775,10 +1775,10 @@
         <v>1</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V18" t="inlineStr">
         <is>
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.1612</v>
+        <v>5.011</v>
       </c>
       <c r="D19" t="n">
-        <v>8.59</v>
+        <v>11.58</v>
       </c>
       <c r="E19" t="n">
-        <v>0.08</v>
+        <v>5.3</v>
       </c>
       <c r="F19" t="n">
-        <v>15.58</v>
+        <v>17.92</v>
       </c>
       <c r="G19" t="n">
-        <v>23.88</v>
+        <v>38.2</v>
       </c>
       <c r="H19" t="n">
-        <v>5.38</v>
+        <v>5.48</v>
       </c>
       <c r="I19" t="n">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>9.69</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>79.17</v>
+        <v>70.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.11</v>
+        <v>-0.58</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.26</v>
+        <v>3.94</v>
       </c>
       <c r="O19" t="n">
-        <v>-6.61</v>
+        <v>-0.1</v>
       </c>
       <c r="P19" t="n">
-        <v>-18.15</v>
+        <v>-11.25</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1846,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1872,52 +1872,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.1958</v>
+        <v>0.2021</v>
       </c>
       <c r="D20" t="n">
-        <v>68.75</v>
+        <v>93.7</v>
       </c>
       <c r="E20" t="n">
-        <v>85.76000000000001</v>
+        <v>93.98</v>
       </c>
       <c r="F20" t="n">
-        <v>36.1</v>
+        <v>55.43</v>
       </c>
       <c r="G20" t="n">
-        <v>59.92</v>
+        <v>90.59</v>
       </c>
       <c r="H20" t="n">
-        <v>2.92</v>
+        <v>1.93</v>
       </c>
       <c r="I20" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.34</v>
+        <v>-1.33</v>
       </c>
       <c r="K20" t="n">
-        <v>7.25</v>
+        <v>6.66</v>
       </c>
       <c r="L20" t="n">
-        <v>100</v>
+        <v>95.83</v>
       </c>
       <c r="M20" t="n">
-        <v>8.699999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-6.62</v>
+        <v>-0.7</v>
       </c>
       <c r="O20" t="n">
-        <v>-14.45</v>
+        <v>10.74</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.59</v>
+        <v>34.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-1</v>
+        <v>-3</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1946,49 +1946,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.8575</v>
+        <v>0.883</v>
       </c>
       <c r="D21" t="n">
-        <v>32.53</v>
+        <v>36.03</v>
       </c>
       <c r="E21" t="n">
-        <v>86.84</v>
+        <v>94.14</v>
       </c>
       <c r="F21" t="n">
-        <v>38</v>
+        <v>35.75</v>
       </c>
       <c r="G21" t="n">
-        <v>68.14</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>1.32</v>
+        <v>0.83</v>
       </c>
       <c r="I21" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.42</v>
       </c>
       <c r="K21" t="n">
-        <v>8.19</v>
+        <v>7.34</v>
       </c>
       <c r="L21" t="n">
-        <v>70.83</v>
+        <v>66.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.58</v>
+        <v>2.73</v>
       </c>
       <c r="N21" t="n">
-        <v>-5.98</v>
+        <v>1.97</v>
       </c>
       <c r="O21" t="n">
-        <v>-19.63</v>
+        <v>6.86</v>
       </c>
       <c r="P21" t="n">
-        <v>-4.83</v>
+        <v>21.4</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>-1</v>
@@ -2020,49 +2020,49 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.3562</v>
+        <v>1.2957</v>
       </c>
       <c r="D22" t="n">
-        <v>13.69</v>
+        <v>13.42</v>
       </c>
       <c r="E22" t="n">
-        <v>89.98999999999999</v>
+        <v>90.42</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>29.6</v>
       </c>
       <c r="G22" t="n">
-        <v>27.13</v>
+        <v>47.77</v>
       </c>
       <c r="H22" t="n">
-        <v>2.56</v>
+        <v>1.96</v>
       </c>
       <c r="I22" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.31</v>
+        <v>-0.92</v>
       </c>
       <c r="K22" t="n">
-        <v>0.12</v>
+        <v>1.71</v>
       </c>
       <c r="L22" t="n">
-        <v>4.17</v>
+        <v>37.5</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.21</v>
+        <v>-0.62</v>
       </c>
       <c r="N22" t="n">
-        <v>-3.19</v>
+        <v>1.8</v>
       </c>
       <c r="O22" t="n">
-        <v>-9.300000000000001</v>
+        <v>3.2</v>
       </c>
       <c r="P22" t="n">
-        <v>-17.1</v>
+        <v>-3.59</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>-1</v>
@@ -2094,46 +2094,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>7.6476</v>
+        <v>8.4611</v>
       </c>
       <c r="D23" t="n">
-        <v>23.9</v>
+        <v>31.78</v>
       </c>
       <c r="E23" t="n">
-        <v>23.94</v>
+        <v>49.01</v>
       </c>
       <c r="F23" t="n">
-        <v>34.71</v>
+        <v>39.05</v>
       </c>
       <c r="G23" t="n">
-        <v>44.73</v>
+        <v>52.39</v>
       </c>
       <c r="H23" t="n">
-        <v>3.82</v>
+        <v>3.72</v>
       </c>
       <c r="I23" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.08</v>
+        <v>-0.17</v>
       </c>
       <c r="K23" t="n">
-        <v>9.99</v>
+        <v>9.02</v>
       </c>
       <c r="L23" t="n">
         <v>70.83</v>
       </c>
       <c r="M23" t="n">
-        <v>1.57</v>
+        <v>0.6</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.92</v>
+        <v>-2.87</v>
       </c>
       <c r="O23" t="n">
-        <v>-16.06</v>
+        <v>0.67</v>
       </c>
       <c r="P23" t="n">
-        <v>-27.26</v>
+        <v>19.13</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2168,49 +2168,49 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1253</v>
+        <v>6.1859</v>
       </c>
       <c r="D24" t="n">
-        <v>37.61</v>
+        <v>43.64</v>
       </c>
       <c r="E24" t="n">
-        <v>82.45</v>
+        <v>93.98</v>
       </c>
       <c r="F24" t="n">
-        <v>37.96</v>
+        <v>39.48</v>
       </c>
       <c r="G24" t="n">
-        <v>52.87</v>
+        <v>54.55</v>
       </c>
       <c r="H24" t="n">
-        <v>3.64</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.32</v>
+        <v>-0.41</v>
       </c>
       <c r="K24" t="n">
-        <v>6.88</v>
+        <v>7.77</v>
       </c>
       <c r="L24" t="n">
-        <v>70.83</v>
+        <v>79.17</v>
       </c>
       <c r="M24" t="n">
-        <v>1.54</v>
+        <v>2.43</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.25</v>
+        <v>0.36</v>
       </c>
       <c r="O24" t="n">
-        <v>-14.66</v>
+        <v>8.4</v>
       </c>
       <c r="P24" t="n">
-        <v>-7.75</v>
+        <v>19.08</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2242,46 +2242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6908</v>
+        <v>2.6109</v>
       </c>
       <c r="D25" t="n">
-        <v>53.34</v>
+        <v>59.69</v>
       </c>
       <c r="E25" t="n">
-        <v>23.17</v>
+        <v>50.75</v>
       </c>
       <c r="F25" t="n">
-        <v>39.02</v>
+        <v>31.28</v>
       </c>
       <c r="G25" t="n">
-        <v>62.64</v>
+        <v>44.1</v>
       </c>
       <c r="H25" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.41</v>
+        <v>-1.3</v>
       </c>
       <c r="K25" t="n">
-        <v>5.85</v>
+        <v>4.82</v>
       </c>
       <c r="L25" t="n">
-        <v>83.33</v>
+        <v>70.83</v>
       </c>
       <c r="M25" t="n">
-        <v>1.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>-4.12</v>
+        <v>1.72</v>
       </c>
       <c r="O25" t="n">
-        <v>-12.86</v>
+        <v>3.28</v>
       </c>
       <c r="P25" t="n">
-        <v>-15.22</v>
+        <v>-8.06</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2293,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.9813</v>
+        <v>4.7258</v>
       </c>
       <c r="D26" t="n">
-        <v>57.85</v>
+        <v>67.65000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>42.8</v>
+        <v>63.97</v>
       </c>
       <c r="F26" t="n">
-        <v>40.62</v>
+        <v>39.09</v>
       </c>
       <c r="G26" t="n">
-        <v>38.45</v>
+        <v>33.57</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.15</v>
+        <v>-0.21</v>
       </c>
       <c r="K26" t="n">
-        <v>3.73</v>
+        <v>3.48</v>
       </c>
       <c r="L26" t="n">
-        <v>91.67</v>
+        <v>87.5</v>
       </c>
       <c r="M26" t="n">
-        <v>1.82</v>
+        <v>1.57</v>
       </c>
       <c r="N26" t="n">
-        <v>-1.68</v>
+        <v>1.38</v>
       </c>
       <c r="O26" t="n">
-        <v>-7.32</v>
+        <v>0.41</v>
       </c>
       <c r="P26" t="n">
-        <v>-26.88</v>
+        <v>-13.6</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2390,46 +2390,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.8894</v>
+        <v>1.6308</v>
       </c>
       <c r="D27" t="n">
-        <v>34.53</v>
+        <v>34.73</v>
       </c>
       <c r="E27" t="n">
-        <v>43.49</v>
+        <v>44.73</v>
       </c>
       <c r="F27" t="n">
-        <v>68.48999999999999</v>
+        <v>35.42</v>
       </c>
       <c r="G27" t="n">
-        <v>83.88</v>
+        <v>29.59</v>
       </c>
       <c r="H27" t="n">
-        <v>1.97</v>
+        <v>1.42</v>
       </c>
       <c r="I27" t="n">
         <v>40</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.25</v>
+        <v>-0.8</v>
       </c>
       <c r="K27" t="n">
-        <v>7.75</v>
+        <v>6.59</v>
       </c>
       <c r="L27" t="n">
-        <v>83.33</v>
+        <v>79.17</v>
       </c>
       <c r="M27" t="n">
-        <v>3.59</v>
+        <v>2.43</v>
       </c>
       <c r="N27" t="n">
-        <v>-0.71</v>
+        <v>0.22</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.03</v>
+        <v>-2.94</v>
       </c>
       <c r="P27" t="n">
-        <v>-18.79</v>
+        <v>-14.27</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2464,49 +2464,49 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.1252</v>
+        <v>5.8119</v>
       </c>
       <c r="D28" t="n">
-        <v>39.4</v>
+        <v>57.04</v>
       </c>
       <c r="E28" t="n">
-        <v>77.52</v>
+        <v>93.27</v>
       </c>
       <c r="F28" t="n">
-        <v>33.4</v>
+        <v>49.14</v>
       </c>
       <c r="G28" t="n">
-        <v>36.05</v>
+        <v>70.26000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>3.04</v>
+        <v>2.82</v>
       </c>
       <c r="I28" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J28" t="n">
-        <v>0.33</v>
+        <v>0.11</v>
       </c>
       <c r="K28" t="n">
-        <v>13.14</v>
+        <v>26.45</v>
       </c>
       <c r="L28" t="n">
-        <v>75</v>
+        <v>95.83</v>
       </c>
       <c r="M28" t="n">
-        <v>-9.279999999999999</v>
+        <v>4.02</v>
       </c>
       <c r="N28" t="n">
-        <v>-5.77</v>
+        <v>-3.13</v>
       </c>
       <c r="O28" t="n">
-        <v>-28.84</v>
+        <v>10.13</v>
       </c>
       <c r="P28" t="n">
-        <v>15.77</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2538,49 +2538,49 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.0617</v>
+        <v>0.9446</v>
       </c>
       <c r="D29" t="n">
-        <v>18.08</v>
+        <v>22.77</v>
       </c>
       <c r="E29" t="n">
-        <v>81.48</v>
+        <v>98.59</v>
       </c>
       <c r="F29" t="n">
-        <v>32.64</v>
+        <v>45.46</v>
       </c>
       <c r="G29" t="n">
-        <v>56.32</v>
+        <v>82.79000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>5.46</v>
+        <v>5.26</v>
       </c>
       <c r="I29" t="n">
         <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>2.15</v>
+        <v>1.94</v>
       </c>
       <c r="K29" t="n">
-        <v>-28.21</v>
+        <v>-25.8</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-34.56</v>
+        <v>-32.15</v>
       </c>
       <c r="N29" t="n">
-        <v>-1.61</v>
+        <v>5.13</v>
       </c>
       <c r="O29" t="n">
-        <v>-1.87</v>
+        <v>9.9</v>
       </c>
       <c r="P29" t="n">
-        <v>17.52</v>
+        <v>31.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -2612,49 +2612,49 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.2931</v>
+        <v>1.1858</v>
       </c>
       <c r="D30" t="n">
-        <v>16.61</v>
+        <v>21.36</v>
       </c>
       <c r="E30" t="n">
-        <v>72.87</v>
+        <v>94.01000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>24.3</v>
+        <v>28.39</v>
       </c>
       <c r="G30" t="n">
-        <v>53.65</v>
+        <v>72.31999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>3.95</v>
+        <v>3.56</v>
       </c>
       <c r="I30" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J30" t="n">
-        <v>1.92</v>
+        <v>1.53</v>
       </c>
       <c r="K30" t="n">
-        <v>10.33</v>
+        <v>8.42</v>
       </c>
       <c r="L30" t="n">
-        <v>95.83</v>
+        <v>79.17</v>
       </c>
       <c r="M30" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="N30" t="n">
-        <v>0.36</v>
+        <v>3.23</v>
       </c>
       <c r="O30" t="n">
-        <v>-0.12</v>
+        <v>8.75</v>
       </c>
       <c r="P30" t="n">
-        <v>18.99</v>
+        <v>25.75</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2663,7 +2663,7 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
         <v>0</v>
@@ -2686,46 +2686,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.7996</v>
+        <v>0.8045</v>
       </c>
       <c r="D31" t="n">
-        <v>22.77</v>
+        <v>26.31</v>
       </c>
       <c r="E31" t="n">
-        <v>62.63</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>25.41</v>
+        <v>30.74</v>
       </c>
       <c r="G31" t="n">
-        <v>36.63</v>
+        <v>51.11</v>
       </c>
       <c r="H31" t="n">
-        <v>3.54</v>
+        <v>2.63</v>
       </c>
       <c r="I31" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="J31" t="n">
-        <v>0.19</v>
+        <v>-0.72</v>
       </c>
       <c r="K31" t="n">
-        <v>5.47</v>
+        <v>4.52</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>70.83</v>
       </c>
       <c r="M31" t="n">
-        <v>3.69</v>
+        <v>2.73</v>
       </c>
       <c r="N31" t="n">
-        <v>-2.33</v>
+        <v>1.98</v>
       </c>
       <c r="O31" t="n">
-        <v>-12.12</v>
+        <v>6.79</v>
       </c>
       <c r="P31" t="n">
-        <v>-16.02</v>
+        <v>2.17</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2734,10 +2734,10 @@
         <v>0</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="U31" t="n">
         <v>0</v>
@@ -2760,61 +2760,61 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.2006</v>
+        <v>0.1823</v>
       </c>
       <c r="D32" t="n">
-        <v>27.47</v>
+        <v>30.39</v>
       </c>
       <c r="E32" t="n">
-        <v>3.24</v>
+        <v>16.55</v>
       </c>
       <c r="F32" t="n">
-        <v>37.84</v>
+        <v>38.72</v>
       </c>
       <c r="G32" t="n">
-        <v>57.95</v>
+        <v>61.58</v>
       </c>
       <c r="H32" t="n">
-        <v>6.33</v>
+        <v>5.4</v>
       </c>
       <c r="I32" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J32" t="n">
-        <v>0.33</v>
+        <v>-0.59</v>
       </c>
       <c r="K32" t="n">
-        <v>6.31</v>
+        <v>7.26</v>
       </c>
       <c r="L32" t="n">
-        <v>37.5</v>
+        <v>45.83</v>
       </c>
       <c r="M32" t="n">
-        <v>-2.14</v>
+        <v>-1.19</v>
       </c>
       <c r="N32" t="n">
-        <v>-1.29</v>
+        <v>2.94</v>
       </c>
       <c r="O32" t="n">
-        <v>-5.01</v>
+        <v>-2.54</v>
       </c>
       <c r="P32" t="n">
-        <v>-29.92</v>
+        <v>-27.31</v>
       </c>
       <c r="Q32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32" t="n">
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>

--- a/data/industry_cache/industry_observation.xlsx
+++ b/data/industry_cache/industry_observation.xlsx
@@ -540,61 +540,61 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1.2152</v>
+        <v>1.335</v>
       </c>
       <c r="D2" t="n">
-        <v>42.69</v>
+        <v>75.84</v>
       </c>
       <c r="E2" t="n">
-        <v>58.43</v>
+        <v>78.79000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>57.74</v>
+        <v>40.55</v>
       </c>
       <c r="G2" t="n">
-        <v>96.41</v>
+        <v>73.3</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.31</v>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="J2" t="n">
-        <v>-2.07</v>
+        <v>-2.32</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.94</v>
+        <v>-5.49</v>
       </c>
       <c r="L2" t="n">
         <v>12.5</v>
       </c>
       <c r="M2" t="n">
-        <v>-11.35</v>
+        <v>-11.9</v>
       </c>
       <c r="N2" t="n">
-        <v>6.46</v>
+        <v>-3.89</v>
       </c>
       <c r="O2" t="n">
-        <v>7.93</v>
+        <v>-7.25</v>
       </c>
       <c r="P2" t="n">
-        <v>-7.22</v>
+        <v>-20.13</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -614,46 +614,46 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>4.657</v>
+        <v>4.5361</v>
       </c>
       <c r="D3" t="n">
-        <v>30.24</v>
+        <v>22.12</v>
       </c>
       <c r="E3" t="n">
-        <v>89.39</v>
+        <v>50.42</v>
       </c>
       <c r="F3" t="n">
-        <v>44.64</v>
+        <v>34.04</v>
       </c>
       <c r="G3" t="n">
-        <v>70.65000000000001</v>
+        <v>43.11</v>
       </c>
       <c r="H3" t="n">
-        <v>3.83</v>
+        <v>3.78</v>
       </c>
       <c r="I3" t="n">
         <v>45</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.21</v>
+        <v>-0.25</v>
       </c>
       <c r="K3" t="n">
-        <v>8.300000000000001</v>
+        <v>7.85</v>
       </c>
       <c r="L3" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="M3" t="n">
-        <v>1.4</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>3.4</v>
+        <v>-4.87</v>
       </c>
       <c r="O3" t="n">
-        <v>8.91</v>
+        <v>-16.39</v>
       </c>
       <c r="P3" t="n">
-        <v>17.02</v>
+        <v>-11.85</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
@@ -665,10 +665,10 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -688,46 +688,46 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.591</v>
+        <v>0.6168</v>
       </c>
       <c r="D4" t="n">
-        <v>29.91</v>
+        <v>27.33</v>
       </c>
       <c r="E4" t="n">
-        <v>77.04000000000001</v>
+        <v>67.41</v>
       </c>
       <c r="F4" t="n">
-        <v>20.73</v>
+        <v>16.65</v>
       </c>
       <c r="G4" t="n">
-        <v>41.95</v>
+        <v>27.24</v>
       </c>
       <c r="H4" t="n">
-        <v>0.97</v>
+        <v>-0.36</v>
       </c>
       <c r="I4" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2</v>
+        <v>-2.52</v>
       </c>
       <c r="K4" t="n">
-        <v>2.14</v>
+        <v>0.09</v>
       </c>
       <c r="L4" t="n">
-        <v>41.67</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.89</v>
+        <v>-2.93</v>
       </c>
       <c r="N4" t="n">
-        <v>3.23</v>
+        <v>-4.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.05</v>
+        <v>-9.08</v>
       </c>
       <c r="P4" t="n">
-        <v>-7.91</v>
+        <v>-25.8</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -739,10 +739,10 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V4" t="inlineStr">
         <is>
@@ -762,49 +762,49 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5.6791</v>
+        <v>5.0199</v>
       </c>
       <c r="D5" t="n">
-        <v>22.51</v>
+        <v>14.16</v>
       </c>
       <c r="E5" t="n">
-        <v>64.77</v>
+        <v>7.76</v>
       </c>
       <c r="F5" t="n">
-        <v>48.93</v>
+        <v>27.41</v>
       </c>
       <c r="G5" t="n">
-        <v>77.27</v>
+        <v>34.98</v>
       </c>
       <c r="H5" t="n">
-        <v>8.460000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J5" t="n">
-        <v>2.03</v>
+        <v>1.78</v>
       </c>
       <c r="K5" t="n">
-        <v>18.13</v>
+        <v>17.77</v>
       </c>
       <c r="L5" t="n">
         <v>95.83</v>
       </c>
       <c r="M5" t="n">
-        <v>5.75</v>
+        <v>5.39</v>
       </c>
       <c r="N5" t="n">
-        <v>1.68</v>
+        <v>-6.81</v>
       </c>
       <c r="O5" t="n">
-        <v>11.35</v>
+        <v>-19.51</v>
       </c>
       <c r="P5" t="n">
-        <v>51.35</v>
+        <v>-15.98</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -813,7 +813,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
         <v>1</v>
@@ -836,49 +836,49 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>19.8026</v>
+        <v>16.7477</v>
       </c>
       <c r="D6" t="n">
-        <v>80.47</v>
+        <v>43.75</v>
       </c>
       <c r="E6" t="n">
-        <v>95.95999999999999</v>
+        <v>44.81</v>
       </c>
       <c r="F6" t="n">
-        <v>55.94</v>
+        <v>48.56</v>
       </c>
       <c r="G6" t="n">
-        <v>82.93000000000001</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.19</v>
+        <v>3.87</v>
       </c>
       <c r="I6" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J6" t="n">
-        <v>0.86</v>
+        <v>0.54</v>
       </c>
       <c r="K6" t="n">
-        <v>15.77</v>
+        <v>17.13</v>
       </c>
       <c r="L6" t="n">
         <v>100</v>
       </c>
       <c r="M6" t="n">
-        <v>7.95</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.15</v>
+        <v>-13.82</v>
       </c>
       <c r="O6" t="n">
-        <v>10.24</v>
+        <v>-32.48</v>
       </c>
       <c r="P6" t="n">
-        <v>69.34</v>
+        <v>-5.39</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -887,7 +887,7 @@
         <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
         <v>0</v>
@@ -910,49 +910,49 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3.5901</v>
+        <v>3.8208</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97</v>
+        <v>23.18</v>
       </c>
       <c r="E7" t="n">
-        <v>19.79</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>27.86</v>
+        <v>37.86</v>
       </c>
       <c r="G7" t="n">
-        <v>17.3</v>
+        <v>45.67</v>
       </c>
       <c r="H7" t="n">
-        <v>4.32</v>
+        <v>4.07</v>
       </c>
       <c r="I7" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.42</v>
+        <v>-1.67</v>
       </c>
       <c r="K7" t="n">
-        <v>7.31</v>
+        <v>5.8</v>
       </c>
       <c r="L7" t="n">
-        <v>83.33</v>
+        <v>62.5</v>
       </c>
       <c r="M7" t="n">
-        <v>0.36</v>
+        <v>-1.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.11</v>
+        <v>-3.65</v>
       </c>
       <c r="O7" t="n">
-        <v>0.23</v>
+        <v>-9.890000000000001</v>
       </c>
       <c r="P7" t="n">
-        <v>-11.67</v>
+        <v>-28.19</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -961,10 +961,10 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V7" t="inlineStr">
         <is>
@@ -984,46 +984,46 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2.0936</v>
+        <v>2.4296</v>
       </c>
       <c r="D8" t="n">
-        <v>14.85</v>
+        <v>14.67</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>55.73</v>
       </c>
       <c r="F8" t="n">
-        <v>28.88</v>
+        <v>36.98</v>
       </c>
       <c r="G8" t="n">
-        <v>48.8</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="I8" t="n">
         <v>25</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.85</v>
+        <v>-2.83</v>
       </c>
       <c r="K8" t="n">
-        <v>12.21</v>
+        <v>12.04</v>
       </c>
       <c r="L8" t="n">
         <v>50</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.83</v>
+        <v>-1</v>
       </c>
       <c r="N8" t="n">
-        <v>0.65</v>
+        <v>0.34</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5</v>
+        <v>-1.22</v>
       </c>
       <c r="P8" t="n">
-        <v>-1.36</v>
+        <v>-5.9</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1058,46 +1058,46 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.2137</v>
+        <v>3.9711</v>
       </c>
       <c r="D9" t="n">
-        <v>19.98</v>
+        <v>21.71</v>
       </c>
       <c r="E9" t="n">
-        <v>10.61</v>
+        <v>38.51</v>
       </c>
       <c r="F9" t="n">
-        <v>38.84</v>
+        <v>32.55</v>
       </c>
       <c r="G9" t="n">
-        <v>85.65000000000001</v>
+        <v>66.64</v>
       </c>
       <c r="H9" t="n">
-        <v>4.43</v>
+        <v>4.23</v>
       </c>
       <c r="I9" t="n">
+        <v>45</v>
+      </c>
+      <c r="J9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="L9" t="n">
         <v>50</v>
       </c>
-      <c r="J9" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="K9" t="n">
-        <v>11.38</v>
-      </c>
-      <c r="L9" t="n">
-        <v>25</v>
-      </c>
       <c r="M9" t="n">
-        <v>-6.66</v>
+        <v>-1.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.14</v>
+        <v>3.29</v>
       </c>
       <c r="O9" t="n">
-        <v>-4.04</v>
+        <v>5.17</v>
       </c>
       <c r="P9" t="n">
-        <v>-17.26</v>
+        <v>-16.94</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1109,10 +1109,10 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="V9" t="inlineStr">
         <is>
@@ -1132,46 +1132,46 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.512</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>24.93</v>
+        <v>22.88</v>
       </c>
       <c r="E10" t="n">
-        <v>67.54000000000001</v>
+        <v>44.5</v>
       </c>
       <c r="F10" t="n">
-        <v>41.31</v>
+        <v>35.4</v>
       </c>
       <c r="G10" t="n">
-        <v>62.76</v>
+        <v>48.3</v>
       </c>
       <c r="H10" t="n">
-        <v>3.01</v>
+        <v>3.58</v>
       </c>
       <c r="I10" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.76</v>
+        <v>-0.19</v>
       </c>
       <c r="K10" t="n">
-        <v>2.98</v>
+        <v>3.43</v>
       </c>
       <c r="L10" t="n">
-        <v>33.33</v>
+        <v>41.67</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.33</v>
+        <v>-0.88</v>
       </c>
       <c r="N10" t="n">
-        <v>2.53</v>
+        <v>-3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>5.71</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.95</v>
+        <v>-16.06</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1183,10 +1183,10 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V10" t="inlineStr">
         <is>
@@ -1206,46 +1206,46 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.7734</v>
+        <v>0.8184</v>
       </c>
       <c r="D11" t="n">
-        <v>32.45</v>
+        <v>29.64</v>
       </c>
       <c r="E11" t="n">
-        <v>88.92</v>
+        <v>62.64</v>
       </c>
       <c r="F11" t="n">
-        <v>33.55</v>
+        <v>35.26</v>
       </c>
       <c r="G11" t="n">
-        <v>46.73</v>
+        <v>49.61</v>
       </c>
       <c r="H11" t="n">
-        <v>2.57</v>
+        <v>2.13</v>
       </c>
       <c r="I11" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.3</v>
+        <v>-1.74</v>
       </c>
       <c r="K11" t="n">
-        <v>3.24</v>
+        <v>-4.41</v>
       </c>
       <c r="L11" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.79</v>
+        <v>-8.44</v>
       </c>
       <c r="N11" t="n">
-        <v>2.55</v>
+        <v>-4.98</v>
       </c>
       <c r="O11" t="n">
-        <v>5.76</v>
+        <v>-13.84</v>
       </c>
       <c r="P11" t="n">
-        <v>-5.7</v>
+        <v>-20.53</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1257,10 +1257,10 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V11" t="inlineStr">
         <is>
@@ -1280,52 +1280,52 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.3566</v>
+        <v>7.1276</v>
       </c>
       <c r="D12" t="n">
-        <v>33.76</v>
+        <v>31.05</v>
       </c>
       <c r="E12" t="n">
-        <v>69.98999999999999</v>
+        <v>52.42</v>
       </c>
       <c r="F12" t="n">
-        <v>54.75</v>
+        <v>36.7</v>
       </c>
       <c r="G12" t="n">
-        <v>96.48999999999999</v>
+        <v>72.83</v>
       </c>
       <c r="H12" t="n">
-        <v>3.87</v>
+        <v>3.6</v>
       </c>
       <c r="I12" t="n">
         <v>40</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.02</v>
+        <v>-0.3</v>
       </c>
       <c r="K12" t="n">
-        <v>8.779999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="L12" t="n">
         <v>70.83</v>
       </c>
       <c r="M12" t="n">
-        <v>2.09</v>
+        <v>1.99</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.43</v>
+        <v>-2.17</v>
       </c>
       <c r="O12" t="n">
-        <v>4.22</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>-11.45</v>
+        <v>-15.99</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>
@@ -1334,7 +1334,7 @@
         <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="V12" t="inlineStr">
         <is>
@@ -1354,46 +1354,46 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.4189</v>
+        <v>2.809</v>
       </c>
       <c r="D13" t="n">
-        <v>20.98</v>
+        <v>21.18</v>
       </c>
       <c r="E13" t="n">
-        <v>54.24</v>
+        <v>54.65</v>
       </c>
       <c r="F13" t="n">
-        <v>28.8</v>
+        <v>24.61</v>
       </c>
       <c r="G13" t="n">
-        <v>48.72</v>
+        <v>32.89</v>
       </c>
       <c r="H13" t="n">
-        <v>4.79</v>
+        <v>4.44</v>
       </c>
       <c r="I13" t="n">
         <v>50</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.62</v>
+        <v>-0.97</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>6.59</v>
       </c>
       <c r="L13" t="n">
-        <v>58.33</v>
+        <v>70.83</v>
       </c>
       <c r="M13" t="n">
-        <v>-3.02</v>
+        <v>-1.93</v>
       </c>
       <c r="N13" t="n">
-        <v>1.7</v>
+        <v>-0.58</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.79</v>
+        <v>-2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>4.06</v>
+        <v>-5.26</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -1428,46 +1428,46 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1.8702</v>
+        <v>2.177</v>
       </c>
       <c r="D14" t="n">
-        <v>17.06</v>
+        <v>16.6</v>
       </c>
       <c r="E14" t="n">
-        <v>79.81</v>
+        <v>71.56</v>
       </c>
       <c r="F14" t="n">
-        <v>21.02</v>
+        <v>20.3</v>
       </c>
       <c r="G14" t="n">
-        <v>50.64</v>
+        <v>46.67</v>
       </c>
       <c r="H14" t="n">
-        <v>5.38</v>
+        <v>5.02</v>
       </c>
       <c r="I14" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="J14" t="n">
-        <v>0.34</v>
+        <v>-0.02</v>
       </c>
       <c r="K14" t="n">
-        <v>8.91</v>
+        <v>7.03</v>
       </c>
       <c r="L14" t="n">
-        <v>79.17</v>
+        <v>62.5</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.23</v>
+        <v>-2.11</v>
       </c>
       <c r="N14" t="n">
-        <v>1.59</v>
+        <v>2.44</v>
       </c>
       <c r="O14" t="n">
-        <v>0.42</v>
+        <v>-1.1</v>
       </c>
       <c r="P14" t="n">
-        <v>-5.79</v>
+        <v>-9.4</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1476,13 +1476,13 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="V14" t="inlineStr">
         <is>
@@ -1502,46 +1502,46 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.8423</v>
+        <v>0.9109</v>
       </c>
       <c r="D15" t="n">
-        <v>20.13</v>
+        <v>12.16</v>
       </c>
       <c r="E15" t="n">
-        <v>66.90000000000001</v>
+        <v>26.06</v>
       </c>
       <c r="F15" t="n">
-        <v>35.1</v>
+        <v>30.45</v>
       </c>
       <c r="G15" t="n">
-        <v>57.89</v>
+        <v>42.41</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.32</v>
+        <v>-0.67</v>
       </c>
       <c r="I15" t="n">
         <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.8</v>
+        <v>-1.15</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.09</v>
+        <v>-5.75</v>
       </c>
       <c r="L15" t="n">
         <v>8.33</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.66</v>
+        <v>-1.31</v>
       </c>
       <c r="N15" t="n">
-        <v>2.59</v>
+        <v>-4.81</v>
       </c>
       <c r="O15" t="n">
-        <v>4.7</v>
+        <v>-14.04</v>
       </c>
       <c r="P15" t="n">
-        <v>-11.88</v>
+        <v>-28.37</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V15" t="inlineStr">
         <is>
@@ -1576,46 +1576,46 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.8192</v>
+        <v>0.886</v>
       </c>
       <c r="D16" t="n">
-        <v>34.96</v>
+        <v>30.71</v>
       </c>
       <c r="E16" t="n">
-        <v>58.75</v>
+        <v>36.51</v>
       </c>
       <c r="F16" t="n">
-        <v>34.91</v>
+        <v>36.14</v>
       </c>
       <c r="G16" t="n">
-        <v>58.61</v>
+        <v>60.6</v>
       </c>
       <c r="H16" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="I16" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="J16" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="K16" t="n">
-        <v>9.15</v>
+        <v>7.86</v>
       </c>
       <c r="L16" t="n">
-        <v>95.83</v>
+        <v>87.5</v>
       </c>
       <c r="M16" t="n">
-        <v>4.63</v>
+        <v>3.34</v>
       </c>
       <c r="N16" t="n">
-        <v>3.41</v>
+        <v>-2.61</v>
       </c>
       <c r="O16" t="n">
-        <v>1.06</v>
+        <v>-7.99</v>
       </c>
       <c r="P16" t="n">
-        <v>-17.46</v>
+        <v>-29.63</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
@@ -1627,10 +1627,10 @@
         <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U16" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V16" t="inlineStr">
         <is>
@@ -1650,19 +1650,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.4965</v>
+        <v>0.5232</v>
       </c>
       <c r="D17" t="n">
-        <v>40.41</v>
+        <v>37.49</v>
       </c>
       <c r="E17" t="n">
-        <v>21.69</v>
+        <v>17.76</v>
       </c>
       <c r="F17" t="n">
-        <v>36.99</v>
+        <v>34.77</v>
       </c>
       <c r="G17" t="n">
-        <v>28.87</v>
+        <v>25</v>
       </c>
       <c r="H17" t="n">
         <v>4.39</v>
@@ -1674,22 +1674,22 @@
         <v>-0.75</v>
       </c>
       <c r="K17" t="n">
-        <v>2.63</v>
+        <v>2.59</v>
       </c>
       <c r="L17" t="n">
         <v>70.83</v>
       </c>
       <c r="M17" t="n">
-        <v>-3.5</v>
+        <v>-3.54</v>
       </c>
       <c r="N17" t="n">
-        <v>3.32</v>
+        <v>-4.24</v>
       </c>
       <c r="O17" t="n">
-        <v>4.96</v>
+        <v>-13.45</v>
       </c>
       <c r="P17" t="n">
-        <v>-13.84</v>
+        <v>-24.69</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1701,10 +1701,10 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U17" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V17" t="inlineStr">
         <is>
@@ -1724,58 +1724,58 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>5.1334</v>
+        <v>6.7068</v>
       </c>
       <c r="D18" t="n">
-        <v>6.17</v>
+        <v>6.72</v>
       </c>
       <c r="E18" t="n">
-        <v>72.84</v>
+        <v>93.62</v>
       </c>
       <c r="F18" t="n">
-        <v>12.28</v>
+        <v>14.45</v>
       </c>
       <c r="G18" t="n">
-        <v>73.44</v>
+        <v>86.84</v>
       </c>
       <c r="H18" t="n">
-        <v>8.109999999999999</v>
+        <v>7.56</v>
       </c>
       <c r="I18" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="J18" t="n">
-        <v>0.19</v>
+        <v>-0.36</v>
       </c>
       <c r="K18" t="n">
-        <v>9.01</v>
+        <v>8</v>
       </c>
       <c r="L18" t="n">
-        <v>58.33</v>
+        <v>50</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7</v>
+        <v>-0.32</v>
       </c>
       <c r="N18" t="n">
-        <v>0.02</v>
+        <v>4.97</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.38</v>
+        <v>6.78</v>
       </c>
       <c r="P18" t="n">
-        <v>-7.55</v>
+        <v>6.59</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
         <v>1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>-1</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1798,46 +1798,46 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>5.011</v>
+        <v>5.3919</v>
       </c>
       <c r="D19" t="n">
-        <v>11.58</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92</v>
+        <v>15.89</v>
       </c>
       <c r="G19" t="n">
-        <v>38.2</v>
+        <v>25.54</v>
       </c>
       <c r="H19" t="n">
-        <v>5.48</v>
+        <v>5.41</v>
       </c>
       <c r="I19" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="J19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>9.220000000000001</v>
+        <v>8.92</v>
       </c>
       <c r="L19" t="n">
         <v>70.83</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.58</v>
+        <v>-0.87</v>
       </c>
       <c r="N19" t="n">
-        <v>3.94</v>
+        <v>-2.68</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1</v>
+        <v>-7.82</v>
       </c>
       <c r="P19" t="n">
-        <v>-11.25</v>
+        <v>-20.99</v>
       </c>
       <c r="Q19" t="n">
         <v>1</v>
@@ -1846,13 +1846,13 @@
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
         <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V19" t="inlineStr">
         <is>
@@ -1872,52 +1872,52 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.2021</v>
+        <v>0.1934</v>
       </c>
       <c r="D20" t="n">
-        <v>93.7</v>
+        <v>64.89</v>
       </c>
       <c r="E20" t="n">
-        <v>93.98</v>
+        <v>82.78</v>
       </c>
       <c r="F20" t="n">
-        <v>55.43</v>
+        <v>34.65</v>
       </c>
       <c r="G20" t="n">
-        <v>90.59</v>
+        <v>57.28</v>
       </c>
       <c r="H20" t="n">
-        <v>1.93</v>
+        <v>2.55</v>
       </c>
       <c r="I20" t="n">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.33</v>
+        <v>-0.71</v>
       </c>
       <c r="K20" t="n">
-        <v>6.66</v>
+        <v>5.79</v>
       </c>
       <c r="L20" t="n">
-        <v>95.83</v>
+        <v>91.67</v>
       </c>
       <c r="M20" t="n">
-        <v>8.109999999999999</v>
+        <v>7.24</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.7</v>
+        <v>-8.18</v>
       </c>
       <c r="O20" t="n">
-        <v>10.74</v>
+        <v>-19.33</v>
       </c>
       <c r="P20" t="n">
-        <v>34.83</v>
+        <v>-8.470000000000001</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -1926,7 +1926,7 @@
         <v>-1</v>
       </c>
       <c r="U20" t="n">
-        <v>-3</v>
+        <v>-1</v>
       </c>
       <c r="V20" t="inlineStr">
         <is>
@@ -1946,49 +1946,49 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.883</v>
+        <v>0.8474</v>
       </c>
       <c r="D21" t="n">
-        <v>36.03</v>
+        <v>30.77</v>
       </c>
       <c r="E21" t="n">
-        <v>94.14</v>
+        <v>85.47</v>
       </c>
       <c r="F21" t="n">
-        <v>35.75</v>
+        <v>40.39</v>
       </c>
       <c r="G21" t="n">
-        <v>66.34999999999999</v>
+        <v>71.75</v>
       </c>
       <c r="H21" t="n">
-        <v>0.83</v>
+        <v>0.97</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.42</v>
+        <v>-1.29</v>
       </c>
       <c r="K21" t="n">
-        <v>7.34</v>
+        <v>6.87</v>
       </c>
       <c r="L21" t="n">
         <v>66.67</v>
       </c>
       <c r="M21" t="n">
-        <v>2.73</v>
+        <v>2.26</v>
       </c>
       <c r="N21" t="n">
-        <v>1.97</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>6.86</v>
+        <v>-23.08</v>
       </c>
       <c r="P21" t="n">
-        <v>21.4</v>
+        <v>-10.97</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -1997,7 +1997,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U21" t="n">
         <v>-1</v>
@@ -2020,49 +2020,49 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2957</v>
+        <v>1.3743</v>
       </c>
       <c r="D22" t="n">
-        <v>13.42</v>
+        <v>13.27</v>
       </c>
       <c r="E22" t="n">
-        <v>90.42</v>
+        <v>86.86</v>
       </c>
       <c r="F22" t="n">
-        <v>29.6</v>
+        <v>24.34</v>
       </c>
       <c r="G22" t="n">
-        <v>47.77</v>
+        <v>28.87</v>
       </c>
       <c r="H22" t="n">
-        <v>1.96</v>
+        <v>2.24</v>
       </c>
       <c r="I22" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.92</v>
+        <v>-0.64</v>
       </c>
       <c r="K22" t="n">
-        <v>1.71</v>
+        <v>2.09</v>
       </c>
       <c r="L22" t="n">
-        <v>37.5</v>
+        <v>41.67</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.62</v>
+        <v>-0.24</v>
       </c>
       <c r="N22" t="n">
-        <v>1.8</v>
+        <v>-4.36</v>
       </c>
       <c r="O22" t="n">
-        <v>3.2</v>
+        <v>-11.46</v>
       </c>
       <c r="P22" t="n">
-        <v>-3.59</v>
+        <v>-20.38</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
         <v>-1</v>
@@ -2094,46 +2094,46 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.4611</v>
+        <v>7.7074</v>
       </c>
       <c r="D23" t="n">
-        <v>31.78</v>
+        <v>23.06</v>
       </c>
       <c r="E23" t="n">
-        <v>49.01</v>
+        <v>22.91</v>
       </c>
       <c r="F23" t="n">
-        <v>39.05</v>
+        <v>35.4</v>
       </c>
       <c r="G23" t="n">
-        <v>52.39</v>
+        <v>46.44</v>
       </c>
       <c r="H23" t="n">
-        <v>3.72</v>
+        <v>3.59</v>
       </c>
       <c r="I23" t="n">
         <v>40</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="K23" t="n">
-        <v>9.02</v>
+        <v>8.01</v>
       </c>
       <c r="L23" t="n">
-        <v>70.83</v>
+        <v>45.83</v>
       </c>
       <c r="M23" t="n">
-        <v>0.6</v>
+        <v>-0.41</v>
       </c>
       <c r="N23" t="n">
-        <v>-2.87</v>
+        <v>-5.92</v>
       </c>
       <c r="O23" t="n">
-        <v>0.67</v>
+        <v>-18.69</v>
       </c>
       <c r="P23" t="n">
-        <v>19.13</v>
+        <v>-30.04</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2168,49 +2168,49 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>6.1859</v>
+        <v>5.9573</v>
       </c>
       <c r="D24" t="n">
-        <v>43.64</v>
+        <v>34.95</v>
       </c>
       <c r="E24" t="n">
-        <v>93.98</v>
+        <v>75.79000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>39.48</v>
+        <v>43.78</v>
       </c>
       <c r="G24" t="n">
-        <v>54.55</v>
+        <v>62.93</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>3.37</v>
       </c>
       <c r="I24" t="n">
         <v>40</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.41</v>
+        <v>-0.59</v>
       </c>
       <c r="K24" t="n">
-        <v>7.77</v>
+        <v>6.83</v>
       </c>
       <c r="L24" t="n">
-        <v>79.17</v>
+        <v>70.83</v>
       </c>
       <c r="M24" t="n">
-        <v>2.43</v>
+        <v>1.49</v>
       </c>
       <c r="N24" t="n">
-        <v>0.36</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>8.4</v>
+        <v>-20.28</v>
       </c>
       <c r="P24" t="n">
-        <v>19.08</v>
+        <v>-14.2</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U24" t="n">
         <v>-1</v>
@@ -2242,46 +2242,46 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.6109</v>
+        <v>2.6979</v>
       </c>
       <c r="D25" t="n">
-        <v>59.69</v>
+        <v>51.1</v>
       </c>
       <c r="E25" t="n">
-        <v>50.75</v>
+        <v>17.68</v>
       </c>
       <c r="F25" t="n">
-        <v>31.28</v>
+        <v>41.85</v>
       </c>
       <c r="G25" t="n">
-        <v>44.1</v>
+        <v>70.05</v>
       </c>
       <c r="H25" t="n">
-        <v>0.55</v>
+        <v>0.47</v>
       </c>
       <c r="I25" t="n">
         <v>10</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.3</v>
+        <v>-1.39</v>
       </c>
       <c r="K25" t="n">
-        <v>4.82</v>
+        <v>5.21</v>
       </c>
       <c r="L25" t="n">
-        <v>70.83</v>
+        <v>75</v>
       </c>
       <c r="M25" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.46</v>
       </c>
       <c r="N25" t="n">
-        <v>1.72</v>
+        <v>-7.77</v>
       </c>
       <c r="O25" t="n">
-        <v>3.28</v>
+        <v>-14.62</v>
       </c>
       <c r="P25" t="n">
-        <v>-8.06</v>
+        <v>-17.85</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2293,10 +2293,10 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V25" t="inlineStr">
         <is>
@@ -2316,46 +2316,46 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>4.7258</v>
+        <v>4.8078</v>
       </c>
       <c r="D26" t="n">
-        <v>67.65000000000001</v>
+        <v>53.37</v>
       </c>
       <c r="E26" t="n">
-        <v>63.97</v>
+        <v>30.13</v>
       </c>
       <c r="F26" t="n">
-        <v>39.09</v>
+        <v>45.93</v>
       </c>
       <c r="G26" t="n">
-        <v>33.57</v>
+        <v>50.85</v>
       </c>
       <c r="H26" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="I26" t="n">
         <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.21</v>
+        <v>-0.35</v>
       </c>
       <c r="K26" t="n">
-        <v>3.48</v>
+        <v>2.94</v>
       </c>
       <c r="L26" t="n">
-        <v>87.5</v>
+        <v>79.17</v>
       </c>
       <c r="M26" t="n">
-        <v>1.57</v>
+        <v>1.04</v>
       </c>
       <c r="N26" t="n">
-        <v>1.38</v>
+        <v>-10.85</v>
       </c>
       <c r="O26" t="n">
-        <v>0.41</v>
+        <v>-14.47</v>
       </c>
       <c r="P26" t="n">
-        <v>-13.6</v>
+        <v>-31.51</v>
       </c>
       <c r="Q26" t="n">
         <v>0</v>
@@ -2367,10 +2367,10 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="V26" t="inlineStr">
         <is>
@@ -2390,46 +2390,46 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.6308</v>
+        <v>1.8384</v>
       </c>
       <c r="D27" t="n">
-        <v>34.73</v>
+        <v>32.12</v>
       </c>
       <c r="E27" t="n">
-        <v>44.73</v>
+        <v>37.82</v>
       </c>
       <c r="F27" t="n">
-        <v>35.42</v>
+        <v>69</v>
       </c>
       <c r="G27" t="n">
-        <v>29.59</v>
+        <v>84.13</v>
       </c>
       <c r="H27" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="I27" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.8</v>
+        <v>-0.91</v>
       </c>
       <c r="K27" t="n">
-        <v>6.59</v>
+        <v>6.06</v>
       </c>
       <c r="L27" t="n">
         <v>79.17</v>
       </c>
       <c r="M27" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="N27" t="n">
-        <v>0.22</v>
+        <v>-6.55</v>
       </c>
       <c r="O27" t="n">
-        <v>-2.94</v>
+        <v>-8.140000000000001</v>
       </c>
       <c r="P27" t="n">
-        <v>-14.27</v>
+        <v>-23.69</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2464,49 +2464,49 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5.8119</v>
+        <v>4.6394</v>
       </c>
       <c r="D28" t="n">
-        <v>57.04</v>
+        <v>34.1</v>
       </c>
       <c r="E28" t="n">
-        <v>93.27</v>
+        <v>58.19</v>
       </c>
       <c r="F28" t="n">
-        <v>49.14</v>
+        <v>39.06</v>
       </c>
       <c r="G28" t="n">
-        <v>70.26000000000001</v>
+        <v>53.72</v>
       </c>
       <c r="H28" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="I28" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="J28" t="n">
-        <v>0.11</v>
+        <v>0.3</v>
       </c>
       <c r="K28" t="n">
-        <v>26.45</v>
+        <v>26</v>
       </c>
       <c r="L28" t="n">
         <v>95.83</v>
       </c>
       <c r="M28" t="n">
-        <v>4.02</v>
+        <v>3.58</v>
       </c>
       <c r="N28" t="n">
-        <v>-3.13</v>
+        <v>-14.77</v>
       </c>
       <c r="O28" t="n">
-        <v>10.13</v>
+        <v>-37.47</v>
       </c>
       <c r="P28" t="n">
-        <v>85.06999999999999</v>
+        <v>3.87</v>
       </c>
       <c r="Q28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
@@ -2518,7 +2518,7 @@
         <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -2538,49 +2538,49 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.9446</v>
+        <v>1.1819</v>
       </c>
       <c r="D29" t="n">
-        <v>22.77</v>
+        <v>18.56</v>
       </c>
       <c r="E29" t="n">
-        <v>98.59</v>
+        <v>84.41</v>
       </c>
       <c r="F29" t="n">
-        <v>45.46</v>
+        <v>28.74</v>
       </c>
       <c r="G29" t="n">
-        <v>82.79000000000001</v>
+        <v>48.15</v>
       </c>
       <c r="H29" t="n">
-        <v>5.26</v>
+        <v>5.46</v>
       </c>
       <c r="I29" t="n">
         <v>35</v>
       </c>
       <c r="J29" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-25.8</v>
+        <v>-23.84</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-32.15</v>
+        <v>-30.19</v>
       </c>
       <c r="N29" t="n">
-        <v>5.13</v>
+        <v>2.97</v>
       </c>
       <c r="O29" t="n">
-        <v>9.9</v>
+        <v>1.45</v>
       </c>
       <c r="P29" t="n">
-        <v>31.81</v>
+        <v>17.78</v>
       </c>
       <c r="Q29" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>0</v>
@@ -2589,10 +2589,10 @@
         <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -2612,49 +2612,49 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.1858</v>
+        <v>1.3779</v>
       </c>
       <c r="D30" t="n">
-        <v>21.36</v>
+        <v>16.92</v>
       </c>
       <c r="E30" t="n">
-        <v>94.01000000000001</v>
+        <v>76.92</v>
       </c>
       <c r="F30" t="n">
-        <v>28.39</v>
+        <v>24.31</v>
       </c>
       <c r="G30" t="n">
-        <v>72.31999999999999</v>
+        <v>53.73</v>
       </c>
       <c r="H30" t="n">
-        <v>3.56</v>
+        <v>4.05</v>
       </c>
       <c r="I30" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="J30" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="K30" t="n">
-        <v>8.42</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>79.17</v>
+        <v>83.33</v>
       </c>
       <c r="M30" t="n">
-        <v>3.55</v>
+        <v>4.5</v>
       </c>
       <c r="N30" t="n">
-        <v>3.23</v>
+        <v>3.5</v>
       </c>
       <c r="O30" t="n">
-        <v>8.75</v>
+        <v>2.82</v>
       </c>
       <c r="P30" t="n">
-        <v>25.75</v>
+        <v>20.96</v>
       </c>
       <c r="Q30" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -2663,10 +2663,10 @@
         <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -2686,46 +2686,46 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>0.8045</v>
+        <v>0.8013</v>
       </c>
       <c r="D31" t="n">
-        <v>26.31</v>
+        <v>21.81</v>
       </c>
       <c r="E31" t="n">
-        <v>80.90000000000001</v>
+        <v>44.97</v>
       </c>
       <c r="F31" t="n">
-        <v>30.74</v>
+        <v>26.55</v>
       </c>
       <c r="G31" t="n">
-        <v>51.11</v>
+        <v>40.94</v>
       </c>
       <c r="H31" t="n">
-        <v>2.63</v>
+        <v>2.61</v>
       </c>
       <c r="I31" t="n">
         <v>40</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.72</v>
+        <v>-0.74</v>
       </c>
       <c r="K31" t="n">
-        <v>4.52</v>
+        <v>4.38</v>
       </c>
       <c r="L31" t="n">
         <v>70.83</v>
       </c>
       <c r="M31" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="N31" t="n">
-        <v>1.98</v>
+        <v>-5.2</v>
       </c>
       <c r="O31" t="n">
-        <v>6.79</v>
+        <v>-15.23</v>
       </c>
       <c r="P31" t="n">
-        <v>2.17</v>
+        <v>-19.53</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -2737,10 +2737,10 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -2760,49 +2760,49 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.1823</v>
+        <v>0.2001</v>
       </c>
       <c r="D32" t="n">
-        <v>30.39</v>
+        <v>26.19</v>
       </c>
       <c r="E32" t="n">
-        <v>16.55</v>
+        <v>2.13</v>
       </c>
       <c r="F32" t="n">
-        <v>38.72</v>
+        <v>40.73</v>
       </c>
       <c r="G32" t="n">
-        <v>61.58</v>
+        <v>66.34999999999999</v>
       </c>
       <c r="H32" t="n">
-        <v>5.4</v>
+        <v>5.07</v>
       </c>
       <c r="I32" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.59</v>
+        <v>-0.93</v>
       </c>
       <c r="K32" t="n">
-        <v>7.26</v>
+        <v>7.18</v>
       </c>
       <c r="L32" t="n">
-        <v>45.83</v>
+        <v>41.67</v>
       </c>
       <c r="M32" t="n">
-        <v>-1.19</v>
+        <v>-1.27</v>
       </c>
       <c r="N32" t="n">
-        <v>2.94</v>
+        <v>-6.81</v>
       </c>
       <c r="O32" t="n">
-        <v>-2.54</v>
+        <v>-8.609999999999999</v>
       </c>
       <c r="P32" t="n">
-        <v>-27.31</v>
+        <v>-34.4</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -2814,7 +2814,7 @@
         <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
